--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:08 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:10 UTC</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.11644554138184</v>
+        <v>27.11644744873047</v>
       </c>
       <c r="C3" t="n">
         <v>5.481500148773193</v>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.11644554138184</v>
+        <v>27.11644744873047</v>
       </c>
       <c r="C6" t="n">
         <v>5.406099796295166</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.20759582519531</v>
+        <v>27.20759773254395</v>
       </c>
       <c r="C8" t="n">
         <v>5.38670015335083</v>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.51749801635742</v>
+        <v>27.51749610900879</v>
       </c>
       <c r="C9" t="n">
         <v>5.399400234222412</v>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.34431838989258</v>
+        <v>27.34431648254395</v>
       </c>
       <c r="C11" t="n">
         <v>5.388299942016602</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:08 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:10 UTC</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27.33520317077637</v>
+        <v>27.33520126342773</v>
       </c>
       <c r="C12" t="n">
         <v>5.373300075531006</v>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27.24405288696289</v>
+        <v>27.24405479431152</v>
       </c>
       <c r="C14" t="n">
         <v>5.357800006866455</v>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.11644554138184</v>
+        <v>27.11644744873047</v>
       </c>
       <c r="C15" t="n">
         <v>5.381999969482422</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27.43546485900879</v>
+        <v>27.43546676635742</v>
       </c>
       <c r="C16" t="n">
         <v>5.374599933624268</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28.11907196044922</v>
+        <v>28.11907386779785</v>
       </c>
       <c r="C18" t="n">
         <v>5.395899772644043</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29.49540328979492</v>
+        <v>29.49540519714355</v>
       </c>
       <c r="C21" t="n">
         <v>5.330900192260742</v>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30.26104545593262</v>
+        <v>30.26104354858398</v>
       </c>
       <c r="C22" t="n">
         <v>5.289700031280518</v>
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29.6138973236084</v>
+        <v>29.61389541625977</v>
       </c>
       <c r="C24" t="n">
         <v>5.291299819946289</v>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.80530738830566</v>
+        <v>29.8053035736084</v>
       </c>
       <c r="C25" t="n">
         <v>5.296500205993652</v>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>30.06963348388672</v>
+        <v>30.06963539123535</v>
       </c>
       <c r="C27" t="n">
         <v>5.329500198364258</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.68681335449219</v>
+        <v>29.68681144714355</v>
       </c>
       <c r="C29" t="n">
         <v>5.332300186157227</v>
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29.65946769714355</v>
+        <v>29.65947151184082</v>
       </c>
       <c r="C30" t="n">
         <v>5.402100086212158</v>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.37690925598145</v>
+        <v>29.37691116333008</v>
       </c>
       <c r="C32" t="n">
         <v>5.37939977645874</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.53186225891113</v>
+        <v>29.53186416625977</v>
       </c>
       <c r="C33" t="n">
         <v>5.33080005645752</v>
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28.97586441040039</v>
+        <v>28.97586250305176</v>
       </c>
       <c r="C34" t="n">
         <v>5.355400085449219</v>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.23107528686523</v>
+        <v>29.2310733795166</v>
       </c>
       <c r="C36" t="n">
         <v>5.355800151824951</v>
@@ -6663,7 +6663,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29.4498291015625</v>
+        <v>29.44983100891113</v>
       </c>
       <c r="C37" t="n">
         <v>5.326300144195557</v>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.59304237365723</v>
+        <v>28.59304046630859</v>
       </c>
       <c r="C39" t="n">
         <v>5.309299945831299</v>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.85737037658691</v>
+        <v>28.85736846923828</v>
       </c>
       <c r="C40" t="n">
         <v>5.43809986114502</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.62950134277344</v>
+        <v>28.6294994354248</v>
       </c>
       <c r="C43" t="n">
         <v>5.469799995422363</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28.01880836486816</v>
+        <v>28.0188102722168</v>
       </c>
       <c r="C46" t="n">
         <v>5.413400173187256</v>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28.32871055603027</v>
+        <v>28.32871246337891</v>
       </c>
       <c r="C47" t="n">
         <v>5.507500171661377</v>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28.16464614868164</v>
+        <v>28.16464424133301</v>
       </c>
       <c r="C48" t="n">
         <v>5.518499851226807</v>
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.3469409942627</v>
+        <v>28.34694290161133</v>
       </c>
       <c r="C50" t="n">
         <v>5.53980016708374</v>
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28.4993839263916</v>
+        <v>28.49938201904297</v>
       </c>
       <c r="C51" t="n">
         <v>5.590000152587891</v>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>28.59340858459473</v>
+        <v>28.59341049194336</v>
       </c>
       <c r="C52" t="n">
         <v>5.519499778747559</v>
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.89429473876953</v>
+        <v>28.8942928314209</v>
       </c>
       <c r="C53" t="n">
         <v>5.542500019073486</v>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28.48998260498047</v>
+        <v>28.48998069763184</v>
       </c>
       <c r="C60" t="n">
         <v>5.386600017547607</v>
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28.5463981628418</v>
+        <v>28.54640007019043</v>
       </c>
       <c r="C61" t="n">
         <v>5.370299816131592</v>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>30.07902717590332</v>
+        <v>30.07902526855469</v>
       </c>
       <c r="C63" t="n">
         <v>5.371300220489502</v>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>30.24827194213867</v>
+        <v>30.2482738494873</v>
       </c>
       <c r="C66" t="n">
         <v>5.367700099945068</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>30.36110687255859</v>
+        <v>30.36110496520996</v>
       </c>
       <c r="C67" t="n">
         <v>5.36870002746582</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>31.43300437927246</v>
+        <v>31.43300819396973</v>
       </c>
       <c r="C68" t="n">
         <v>5.374300003051758</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>31.57404708862305</v>
+        <v>31.57404899597168</v>
       </c>
       <c r="C69" t="n">
         <v>5.31879997253418</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>34.78974533081055</v>
+        <v>34.78974914550781</v>
       </c>
       <c r="C79" t="n">
         <v>5.23799991607666</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.09062957763672</v>
+        <v>35.09063339233398</v>
       </c>
       <c r="C81" t="n">
         <v>5.21589994430542</v>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.11883544921875</v>
+        <v>35.11883926391602</v>
       </c>
       <c r="C82" t="n">
         <v>5.19159984588623</v>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>34.89317321777344</v>
+        <v>34.8931770324707</v>
       </c>
       <c r="C84" t="n">
         <v>5.198699951171875</v>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>34.68631362915039</v>
+        <v>34.68631744384766</v>
       </c>
       <c r="C85" t="n">
         <v>5.213900089263916</v>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>34.96839141845703</v>
+        <v>34.9683952331543</v>
       </c>
       <c r="C86" t="n">
         <v>5.220499992370605</v>
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>36.98056030273438</v>
+        <v>36.98056411743164</v>
       </c>
       <c r="C93" t="n">
         <v>5.136600017547607</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>38.67303848266602</v>
+        <v>38.67303466796875</v>
       </c>
       <c r="C94" t="n">
         <v>5.129600048065186</v>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>38.5037841796875</v>
+        <v>38.50378799438477</v>
       </c>
       <c r="C95" t="n">
         <v>5.170300006866455</v>
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>38.25931930541992</v>
+        <v>38.25931549072266</v>
       </c>
       <c r="C97" t="n">
         <v>5.230100154876709</v>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>42.12380218505859</v>
+        <v>42.12379837036133</v>
       </c>
       <c r="C101" t="n">
         <v>5.162399768829346</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>42.00156784057617</v>
+        <v>42.00156402587891</v>
       </c>
       <c r="C103" t="n">
         <v>5.243899822235107</v>
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>43.12047958374023</v>
+        <v>43.1204833984375</v>
       </c>
       <c r="C104" t="n">
         <v>5.329100131988525</v>
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>44.1923828125</v>
+        <v>44.19237899780273</v>
       </c>
       <c r="C106" t="n">
         <v>5.19290018081665</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>43.98552322387695</v>
+        <v>43.98551940917969</v>
       </c>
       <c r="C107" t="n">
         <v>5.262100219726562</v>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>42.94182968139648</v>
+        <v>42.94182586669922</v>
       </c>
       <c r="C108" t="n">
         <v>5.219900131225586</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>43.28032684326172</v>
+        <v>43.28032302856445</v>
       </c>
       <c r="C109" t="n">
         <v>5.31190013885498</v>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>45.15144729614258</v>
+        <v>45.15145111083984</v>
       </c>
       <c r="C112" t="n">
         <v>5.236800193786621</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>46.45841598510742</v>
+        <v>46.45841217041016</v>
       </c>
       <c r="C113" t="n">
         <v>5.235099792480469</v>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>46.0164909362793</v>
+        <v>46.01648712158203</v>
       </c>
       <c r="C118" t="n">
         <v>5.157899856567383</v>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>45.61217880249023</v>
+        <v>45.61217498779297</v>
       </c>
       <c r="C119" t="n">
         <v>5.138299942016602</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>46.10111618041992</v>
+        <v>46.10111236572266</v>
       </c>
       <c r="C122" t="n">
         <v>5.095799922943115</v>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>46.80630874633789</v>
+        <v>46.80631256103516</v>
       </c>
       <c r="C123" t="n">
         <v>5.005000114440918</v>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>45.01980972290039</v>
+        <v>45.01981353759766</v>
       </c>
       <c r="C124" t="n">
         <v>4.994400024414062</v>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>45.67800140380859</v>
+        <v>45.67799758911133</v>
       </c>
       <c r="C126" t="n">
         <v>4.992400169372559</v>
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>46.68469619750977</v>
+        <v>46.6846923828125</v>
       </c>
       <c r="C134" t="n">
         <v>4.99429988861084</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>46.79911804199219</v>
+        <v>46.79912185668945</v>
       </c>
       <c r="C135" t="n">
         <v>5.017499923706055</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>47.04703903198242</v>
+        <v>47.04703521728516</v>
       </c>
       <c r="C136" t="n">
         <v>4.951929092407227</v>
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>46.39863967895508</v>
+        <v>46.39863586425781</v>
       </c>
       <c r="C137" t="n">
         <v>4.984799861907959</v>
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>43.55712509155273</v>
+        <v>43.55712890625</v>
       </c>
       <c r="C142" t="n">
         <v>4.906400203704834</v>
@@ -8931,7 +8931,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>43.35688400268555</v>
+        <v>43.35688781738281</v>
       </c>
       <c r="C145" t="n">
         <v>5.00409984588623</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>42.52731704711914</v>
+        <v>42.52731323242188</v>
       </c>
       <c r="C148" t="n">
         <v>5.058199882507324</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>42.86105346679688</v>
+        <v>42.86104965209961</v>
       </c>
       <c r="C149" t="n">
         <v>5.01170015335083</v>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>42.41289138793945</v>
+        <v>42.41289520263672</v>
       </c>
       <c r="C150" t="n">
         <v>5.017099857330322</v>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:08 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:10 UTC</t>
         </is>
       </c>
     </row>

--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:10 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:12 UTC</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.8976936340332</v>
+        <v>26.89769172668457</v>
       </c>
       <c r="C7" t="n">
         <v>5.36870002746582</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.20759773254395</v>
+        <v>27.20759582519531</v>
       </c>
       <c r="C8" t="n">
         <v>5.38670015335083</v>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.51749610900879</v>
+        <v>27.51749801635742</v>
       </c>
       <c r="C9" t="n">
         <v>5.399400234222412</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30.45730995234394</v>
+        <v>30.45733205672228</v>
       </c>
     </row>
     <row r="10">
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.1984806060791</v>
+        <v>27.19847869873047</v>
       </c>
       <c r="C10" t="n">
         <v>5.382900238037109</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:10 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:12 UTC</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28.26490783691406</v>
+        <v>28.2649097442627</v>
       </c>
       <c r="C19" t="n">
         <v>5.35860013961792</v>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30.26104354858398</v>
+        <v>30.26104545593262</v>
       </c>
       <c r="C22" t="n">
         <v>5.289700031280518</v>
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29.48628616333008</v>
+        <v>29.48628807067871</v>
       </c>
       <c r="C23" t="n">
         <v>5.270699977874756</v>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.8053035736084</v>
+        <v>29.80530548095703</v>
       </c>
       <c r="C25" t="n">
         <v>5.296500205993652</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.96936988830566</v>
+        <v>29.9693717956543</v>
       </c>
       <c r="C26" t="n">
         <v>5.295599937438965</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.68681144714355</v>
+        <v>29.68681335449219</v>
       </c>
       <c r="C29" t="n">
         <v>5.332300186157227</v>
@@ -6516,7 +6516,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29.65947151184082</v>
+        <v>29.65946960449219</v>
       </c>
       <c r="C30" t="n">
         <v>5.402100086212158</v>
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29.03055000305176</v>
+        <v>29.03055191040039</v>
       </c>
       <c r="C35" t="n">
         <v>5.335400104522705</v>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.03966522216797</v>
+        <v>29.03966331481934</v>
       </c>
       <c r="C41" t="n">
         <v>5.429999828338623</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28.79356575012207</v>
+        <v>28.79356384277344</v>
       </c>
       <c r="C44" t="n">
         <v>5.405499935150146</v>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.89382743835449</v>
+        <v>28.89382934570312</v>
       </c>
       <c r="C45" t="n">
         <v>5.418200016021729</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28.0188102722168</v>
+        <v>28.01880836486816</v>
       </c>
       <c r="C46" t="n">
         <v>5.413400173187256</v>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28.32871246337891</v>
+        <v>28.32871055603027</v>
       </c>
       <c r="C47" t="n">
         <v>5.507500171661377</v>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28.16464424133301</v>
+        <v>28.16464614868164</v>
       </c>
       <c r="C48" t="n">
         <v>5.518499851226807</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28.26490783691406</v>
+        <v>28.2649097442627</v>
       </c>
       <c r="C49" t="n">
         <v>5.521299839019775</v>
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.34694290161133</v>
+        <v>28.3469409942627</v>
       </c>
       <c r="C50" t="n">
         <v>5.53980016708374</v>
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28.49938201904297</v>
+        <v>28.4993839263916</v>
       </c>
       <c r="C51" t="n">
         <v>5.590000152587891</v>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>28.59341049194336</v>
+        <v>28.59341239929199</v>
       </c>
       <c r="C52" t="n">
         <v>5.519499778747559</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>27.86940765380859</v>
+        <v>27.86940574645996</v>
       </c>
       <c r="C57" t="n">
         <v>5.40749979019165</v>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28.48998069763184</v>
+        <v>28.48998260498047</v>
       </c>
       <c r="C60" t="n">
         <v>5.386600017547607</v>
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28.54640007019043</v>
+        <v>28.54639625549316</v>
       </c>
       <c r="C61" t="n">
         <v>5.370299816131592</v>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>29.2798023223877</v>
+        <v>29.27980041503906</v>
       </c>
       <c r="C62" t="n">
         <v>5.373700141906738</v>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>30.07902526855469</v>
+        <v>30.07902717590332</v>
       </c>
       <c r="C63" t="n">
         <v>5.371300220489502</v>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>30.12604141235352</v>
+        <v>30.12603950500488</v>
       </c>
       <c r="C65" t="n">
         <v>5.367899894714355</v>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>30.2482738494873</v>
+        <v>30.24827194213867</v>
       </c>
       <c r="C66" t="n">
         <v>5.367700099945068</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>30.36110496520996</v>
+        <v>30.36110687255859</v>
       </c>
       <c r="C67" t="n">
         <v>5.36870002746582</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>31.43300819396973</v>
+        <v>31.43300628662109</v>
       </c>
       <c r="C68" t="n">
         <v>5.374300003051758</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>31.57404899597168</v>
+        <v>31.57404708862305</v>
       </c>
       <c r="C69" t="n">
         <v>5.31879997253418</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>32.94683456420898</v>
+        <v>32.94683074951172</v>
       </c>
       <c r="C70" t="n">
         <v>5.283699989318848</v>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>33.97171783447266</v>
+        <v>33.97172164916992</v>
       </c>
       <c r="C72" t="n">
         <v>5.279099941253662</v>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>35.44792938232422</v>
+        <v>35.44793319702148</v>
       </c>
       <c r="C74" t="n">
         <v>5.197100162506104</v>
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>35.01541137695312</v>
+        <v>35.01540756225586</v>
       </c>
       <c r="C76" t="n">
         <v>5.255000114440918</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>35.27868270874023</v>
+        <v>35.2786865234375</v>
       </c>
       <c r="C78" t="n">
         <v>5.237500190734863</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.09063339233398</v>
+        <v>35.09062957763672</v>
       </c>
       <c r="C81" t="n">
         <v>5.21589994430542</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>35.80523300170898</v>
+        <v>35.80522918701172</v>
       </c>
       <c r="C83" t="n">
         <v>5.196199893951416</v>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>34.8931770324707</v>
+        <v>34.89317321777344</v>
       </c>
       <c r="C84" t="n">
         <v>5.198699951171875</v>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35.70180130004883</v>
+        <v>35.70180511474609</v>
       </c>
       <c r="C88" t="n">
         <v>5.208799839019775</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>37.20622253417969</v>
+        <v>37.20622634887695</v>
       </c>
       <c r="C90" t="n">
         <v>5.170899868011475</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37.20622253417969</v>
+        <v>37.20622634887695</v>
       </c>
       <c r="C91" t="n">
         <v>5.151999950408936</v>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>37.24383544921875</v>
+        <v>37.24383926391602</v>
       </c>
       <c r="C92" t="n">
         <v>5.124199867248535</v>
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>36.98056411743164</v>
+        <v>36.98056030273438</v>
       </c>
       <c r="C93" t="n">
         <v>5.136600017547607</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>38.08066940307617</v>
+        <v>38.08066558837891</v>
       </c>
       <c r="C96" t="n">
         <v>5.277299880981445</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>40.58177185058594</v>
+        <v>40.58176803588867</v>
       </c>
       <c r="C99" t="n">
         <v>5.243500232696533</v>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>42.12379837036133</v>
+        <v>42.12380218505859</v>
       </c>
       <c r="C101" t="n">
         <v>5.162399768829346</v>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>42.31185531616211</v>
+        <v>42.31185150146484</v>
       </c>
       <c r="C102" t="n">
         <v>5.151400089263916</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>42.00156402587891</v>
+        <v>42.00156784057617</v>
       </c>
       <c r="C103" t="n">
         <v>5.243899822235107</v>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>42.94182586669922</v>
+        <v>42.94182968139648</v>
       </c>
       <c r="C108" t="n">
         <v>5.219900131225586</v>
@@ -8196,7 +8196,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>44.44625473022461</v>
+        <v>44.44625091552734</v>
       </c>
       <c r="C110" t="n">
         <v>5.232900142669678</v>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>44.66250991821289</v>
+        <v>44.66251373291016</v>
       </c>
       <c r="C111" t="n">
         <v>5.232600212097168</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>46.45841217041016</v>
+        <v>46.45841598510742</v>
       </c>
       <c r="C113" t="n">
         <v>5.235099792480469</v>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>46.702880859375</v>
+        <v>46.70288467407227</v>
       </c>
       <c r="C114" t="n">
         <v>5.23799991607666</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>45.76261901855469</v>
+        <v>45.76262283325195</v>
       </c>
       <c r="C115" t="n">
         <v>5.263999938964844</v>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>46.01648712158203</v>
+        <v>46.0164909362793</v>
       </c>
       <c r="C118" t="n">
         <v>5.157899856567383</v>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>45.61217498779297</v>
+        <v>45.61217880249023</v>
       </c>
       <c r="C119" t="n">
         <v>5.138299942016602</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>43.82567977905273</v>
+        <v>43.82567596435547</v>
       </c>
       <c r="C120" t="n">
         <v>5.150599956512451</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>46.10111236572266</v>
+        <v>46.10111618041992</v>
       </c>
       <c r="C122" t="n">
         <v>5.095799922943115</v>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>46.80631256103516</v>
+        <v>46.80630874633789</v>
       </c>
       <c r="C123" t="n">
         <v>5.005000114440918</v>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>44.08895111083984</v>
+        <v>44.08895492553711</v>
       </c>
       <c r="C125" t="n">
         <v>4.984799861907959</v>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>44.21118545532227</v>
+        <v>44.21118927001953</v>
       </c>
       <c r="C128" t="n">
         <v>5.00629997253418</v>
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>44.82235336303711</v>
+        <v>44.82235717773438</v>
       </c>
       <c r="C129" t="n">
         <v>5.007999897003174</v>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:10 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:12 UTC</t>
         </is>
       </c>
     </row>

--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:12 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:14 UTC</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5867,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.36254692077637</v>
+        <v>27.36254501342773</v>
       </c>
       <c r="C2" t="n">
         <v>5.464099884033203</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.84300422668457</v>
+        <v>26.84300231933594</v>
       </c>
       <c r="C4" t="n">
         <v>5.449299812316895</v>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.09821701049805</v>
+        <v>27.09821891784668</v>
       </c>
       <c r="C5" t="n">
         <v>5.440814971923828</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>26.89769172668457</v>
+        <v>26.8976936340332</v>
       </c>
       <c r="C7" t="n">
         <v>5.36870002746582</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30.45733205672228</v>
+        <v>30.45734581100089</v>
       </c>
     </row>
     <row r="10">
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.19847869873047</v>
+        <v>27.1984806060791</v>
       </c>
       <c r="C10" t="n">
         <v>5.382900238037109</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:12 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:14 UTC</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27.33520126342773</v>
+        <v>27.3351993560791</v>
       </c>
       <c r="C12" t="n">
         <v>5.373300075531006</v>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.36254692077637</v>
+        <v>27.36254501342773</v>
       </c>
       <c r="C13" t="n">
         <v>5.357399940490723</v>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27.24405479431152</v>
+        <v>27.24405288696289</v>
       </c>
       <c r="C14" t="n">
         <v>5.357800006866455</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27.43546676635742</v>
+        <v>27.43546485900879</v>
       </c>
       <c r="C16" t="n">
         <v>5.374599933624268</v>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28.2649097442627</v>
+        <v>28.26490783691406</v>
       </c>
       <c r="C19" t="n">
         <v>5.35860013961792</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29.49540519714355</v>
+        <v>29.49540328979492</v>
       </c>
       <c r="C21" t="n">
         <v>5.330900192260742</v>
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29.48628807067871</v>
+        <v>29.48628616333008</v>
       </c>
       <c r="C23" t="n">
         <v>5.270699977874756</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.9693717956543</v>
+        <v>29.96936988830566</v>
       </c>
       <c r="C26" t="n">
         <v>5.295599937438965</v>
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29.91468238830566</v>
+        <v>29.9146842956543</v>
       </c>
       <c r="C28" t="n">
         <v>5.321499824523926</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.53186416625977</v>
+        <v>29.53186225891113</v>
       </c>
       <c r="C33" t="n">
         <v>5.33080005645752</v>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.2310733795166</v>
+        <v>29.23107528686523</v>
       </c>
       <c r="C36" t="n">
         <v>5.355800151824951</v>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.03966331481934</v>
+        <v>29.03966522216797</v>
       </c>
       <c r="C41" t="n">
         <v>5.429999828338623</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29.11258316040039</v>
+        <v>29.11258125305176</v>
       </c>
       <c r="C42" t="n">
         <v>5.43149995803833</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.6294994354248</v>
+        <v>28.62950134277344</v>
       </c>
       <c r="C43" t="n">
         <v>5.469799995422363</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28.01880836486816</v>
+        <v>28.0188102722168</v>
       </c>
       <c r="C46" t="n">
         <v>5.413400173187256</v>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28.32871055603027</v>
+        <v>28.32871246337891</v>
       </c>
       <c r="C47" t="n">
         <v>5.507500171661377</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28.2649097442627</v>
+        <v>28.26490783691406</v>
       </c>
       <c r="C49" t="n">
         <v>5.521299839019775</v>
@@ -6978,7 +6978,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>28.59341239929199</v>
+        <v>28.59341049194336</v>
       </c>
       <c r="C52" t="n">
         <v>5.519499778747559</v>
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.8942928314209</v>
+        <v>28.89429473876953</v>
       </c>
       <c r="C53" t="n">
         <v>5.542500019073486</v>
@@ -7188,7 +7188,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>29.27980041503906</v>
+        <v>29.2798023223877</v>
       </c>
       <c r="C62" t="n">
         <v>5.373700141906738</v>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>30.24827194213867</v>
+        <v>30.24827003479004</v>
       </c>
       <c r="C66" t="n">
         <v>5.367700099945068</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>31.43300628662109</v>
+        <v>31.43300437927246</v>
       </c>
       <c r="C68" t="n">
         <v>5.374300003051758</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>32.94683074951172</v>
+        <v>32.94683456420898</v>
       </c>
       <c r="C70" t="n">
         <v>5.283699989318848</v>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>33.97172164916992</v>
+        <v>33.97171783447266</v>
       </c>
       <c r="C72" t="n">
         <v>5.279099941253662</v>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>35.44793319702148</v>
+        <v>35.44792938232422</v>
       </c>
       <c r="C74" t="n">
         <v>5.197100162506104</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>34.78974914550781</v>
+        <v>34.78974533081055</v>
       </c>
       <c r="C79" t="n">
         <v>5.23799991607666</v>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.11883926391602</v>
+        <v>35.11883544921875</v>
       </c>
       <c r="C82" t="n">
         <v>5.19159984588623</v>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>34.68631744384766</v>
+        <v>34.68631362915039</v>
       </c>
       <c r="C85" t="n">
         <v>5.213900089263916</v>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>35.55136108398438</v>
+        <v>35.55135726928711</v>
       </c>
       <c r="C87" t="n">
         <v>5.234399795532227</v>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>35.70180511474609</v>
+        <v>35.70180130004883</v>
       </c>
       <c r="C88" t="n">
         <v>5.208799839019775</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>37.20622634887695</v>
+        <v>37.20622253417969</v>
       </c>
       <c r="C90" t="n">
         <v>5.170899868011475</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37.20622634887695</v>
+        <v>37.20622253417969</v>
       </c>
       <c r="C91" t="n">
         <v>5.151999950408936</v>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>37.24383926391602</v>
+        <v>37.24383544921875</v>
       </c>
       <c r="C92" t="n">
         <v>5.124199867248535</v>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>38.50378799438477</v>
+        <v>38.5037841796875</v>
       </c>
       <c r="C95" t="n">
         <v>5.170300006866455</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>38.08066558837891</v>
+        <v>38.08066940307617</v>
       </c>
       <c r="C96" t="n">
         <v>5.277299880981445</v>
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>43.1204833984375</v>
+        <v>43.12047958374023</v>
       </c>
       <c r="C104" t="n">
         <v>5.329100131988525</v>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>43.60941696166992</v>
+        <v>43.60942077636719</v>
       </c>
       <c r="C105" t="n">
         <v>5.233399868011475</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>43.28032302856445</v>
+        <v>43.28032684326172</v>
       </c>
       <c r="C109" t="n">
         <v>5.31190013885498</v>
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>44.66251373291016</v>
+        <v>44.66250991821289</v>
       </c>
       <c r="C111" t="n">
         <v>5.232600212097168</v>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>46.70288467407227</v>
+        <v>46.702880859375</v>
       </c>
       <c r="C114" t="n">
         <v>5.23799991607666</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>45.76262283325195</v>
+        <v>45.76261901855469</v>
       </c>
       <c r="C115" t="n">
         <v>5.263999938964844</v>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>45.61217880249023</v>
+        <v>45.61217498779297</v>
       </c>
       <c r="C119" t="n">
         <v>5.138299942016602</v>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>45.01981353759766</v>
+        <v>45.01980972290039</v>
       </c>
       <c r="C124" t="n">
         <v>4.994400024414062</v>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>44.08895492553711</v>
+        <v>44.08895111083984</v>
       </c>
       <c r="C125" t="n">
         <v>4.984799861907959</v>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>45.67799758911133</v>
+        <v>45.67800140380859</v>
       </c>
       <c r="C126" t="n">
         <v>4.992400169372559</v>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>44.21118927001953</v>
+        <v>44.21118545532227</v>
       </c>
       <c r="C128" t="n">
         <v>5.00629997253418</v>
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>46.6846923828125</v>
+        <v>46.68469619750977</v>
       </c>
       <c r="C134" t="n">
         <v>4.99429988861084</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>46.79912185668945</v>
+        <v>46.79911804199219</v>
       </c>
       <c r="C135" t="n">
         <v>5.017499923706055</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>47.04703521728516</v>
+        <v>47.04703903198242</v>
       </c>
       <c r="C136" t="n">
         <v>4.951929092407227</v>
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>46.39863586425781</v>
+        <v>46.39863967895508</v>
       </c>
       <c r="C137" t="n">
         <v>4.984799861907959</v>
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>43.55712890625</v>
+        <v>43.55712509155273</v>
       </c>
       <c r="C142" t="n">
         <v>4.906400203704834</v>
@@ -8931,7 +8931,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>43.35688781738281</v>
+        <v>43.35688400268555</v>
       </c>
       <c r="C145" t="n">
         <v>5.00409984588623</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>42.52731323242188</v>
+        <v>42.52731704711914</v>
       </c>
       <c r="C148" t="n">
         <v>5.058199882507324</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>42.86104965209961</v>
+        <v>42.86105346679688</v>
       </c>
       <c r="C149" t="n">
         <v>5.01170015335083</v>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>42.41289520263672</v>
+        <v>42.41289138793945</v>
       </c>
       <c r="C150" t="n">
         <v>5.017099857330322</v>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:12 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:14 UTC</t>
         </is>
       </c>
     </row>

--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:14 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:21 UTC</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.11644744873047</v>
+        <v>27.11644554138184</v>
       </c>
       <c r="C3" t="n">
         <v>5.481500148773193</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.84300231933594</v>
+        <v>26.84300422668457</v>
       </c>
       <c r="C4" t="n">
         <v>5.449299812316895</v>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.09821891784668</v>
+        <v>27.09821701049805</v>
       </c>
       <c r="C5" t="n">
         <v>5.440814971923828</v>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.11644744873047</v>
+        <v>27.11644554138184</v>
       </c>
       <c r="C6" t="n">
         <v>5.406099796295166</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30.45734581100089</v>
+        <v>30.45733205672228</v>
       </c>
     </row>
     <row r="10">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:14 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:21 UTC</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27.3351993560791</v>
+        <v>27.33520126342773</v>
       </c>
       <c r="C12" t="n">
         <v>5.373300075531006</v>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27.24405288696289</v>
+        <v>27.24405097961426</v>
       </c>
       <c r="C14" t="n">
         <v>5.357800006866455</v>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.11644744873047</v>
+        <v>27.11644554138184</v>
       </c>
       <c r="C15" t="n">
         <v>5.381999969482422</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28.11907386779785</v>
+        <v>28.11907196044922</v>
       </c>
       <c r="C18" t="n">
         <v>5.395899772644043</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29.49540328979492</v>
+        <v>29.49540519714355</v>
       </c>
       <c r="C21" t="n">
         <v>5.330900192260742</v>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30.26104545593262</v>
+        <v>30.26104354858398</v>
       </c>
       <c r="C22" t="n">
         <v>5.289700031280518</v>
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29.48628616333008</v>
+        <v>29.48628807067871</v>
       </c>
       <c r="C23" t="n">
         <v>5.270699977874756</v>
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29.61389541625977</v>
+        <v>29.6138973236084</v>
       </c>
       <c r="C24" t="n">
         <v>5.291299819946289</v>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.80530548095703</v>
+        <v>29.8053035736084</v>
       </c>
       <c r="C25" t="n">
         <v>5.296500205993652</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.96936988830566</v>
+        <v>29.96937370300293</v>
       </c>
       <c r="C26" t="n">
         <v>5.295599937438965</v>
@@ -6453,7 +6453,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>30.06963539123535</v>
+        <v>30.06963348388672</v>
       </c>
       <c r="C27" t="n">
         <v>5.329500198364258</v>
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29.9146842956543</v>
+        <v>29.91468238830566</v>
       </c>
       <c r="C28" t="n">
         <v>5.321499824523926</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.68681335449219</v>
+        <v>29.68680953979492</v>
       </c>
       <c r="C29" t="n">
         <v>5.332300186157227</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.53186225891113</v>
+        <v>29.53186416625977</v>
       </c>
       <c r="C33" t="n">
         <v>5.33080005645752</v>
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29.03055191040039</v>
+        <v>29.03055000305176</v>
       </c>
       <c r="C35" t="n">
         <v>5.335400104522705</v>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.23107528686523</v>
+        <v>29.2310733795166</v>
       </c>
       <c r="C36" t="n">
         <v>5.355800151824951</v>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29.64123916625977</v>
+        <v>29.6412410736084</v>
       </c>
       <c r="C38" t="n">
         <v>5.306099891662598</v>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.59304046630859</v>
+        <v>28.59304237365723</v>
       </c>
       <c r="C39" t="n">
         <v>5.309299945831299</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29.11258125305176</v>
+        <v>29.11258316040039</v>
       </c>
       <c r="C42" t="n">
         <v>5.43149995803833</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.62950134277344</v>
+        <v>28.6294994354248</v>
       </c>
       <c r="C43" t="n">
         <v>5.469799995422363</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28.79356384277344</v>
+        <v>28.79356575012207</v>
       </c>
       <c r="C44" t="n">
         <v>5.405499935150146</v>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.89382934570312</v>
+        <v>28.89382743835449</v>
       </c>
       <c r="C45" t="n">
         <v>5.418200016021729</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28.0188102722168</v>
+        <v>28.01880836486816</v>
       </c>
       <c r="C46" t="n">
         <v>5.413400173187256</v>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28.32871246337891</v>
+        <v>28.32871437072754</v>
       </c>
       <c r="C47" t="n">
         <v>5.507500171661377</v>
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.3469409942627</v>
+        <v>28.34694290161133</v>
       </c>
       <c r="C50" t="n">
         <v>5.53980016708374</v>
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28.4993839263916</v>
+        <v>28.49938201904297</v>
       </c>
       <c r="C51" t="n">
         <v>5.590000152587891</v>
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.89429473876953</v>
+        <v>28.8942928314209</v>
       </c>
       <c r="C53" t="n">
         <v>5.542500019073486</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>27.86940574645996</v>
+        <v>27.86940765380859</v>
       </c>
       <c r="C57" t="n">
         <v>5.40749979019165</v>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28.48998260498047</v>
+        <v>28.48998069763184</v>
       </c>
       <c r="C60" t="n">
         <v>5.386600017547607</v>
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28.54639625549316</v>
+        <v>28.54640007019043</v>
       </c>
       <c r="C61" t="n">
         <v>5.370299816131592</v>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>30.07902717590332</v>
+        <v>30.07902526855469</v>
       </c>
       <c r="C63" t="n">
         <v>5.371300220489502</v>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>30.12603950500488</v>
+        <v>30.12604141235352</v>
       </c>
       <c r="C65" t="n">
         <v>5.367899894714355</v>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>30.24827003479004</v>
+        <v>30.2482738494873</v>
       </c>
       <c r="C66" t="n">
         <v>5.367700099945068</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>30.36110687255859</v>
+        <v>30.36110496520996</v>
       </c>
       <c r="C67" t="n">
         <v>5.36870002746582</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>31.43300437927246</v>
+        <v>31.43300819396973</v>
       </c>
       <c r="C68" t="n">
         <v>5.374300003051758</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>31.57404708862305</v>
+        <v>31.57404899597168</v>
       </c>
       <c r="C69" t="n">
         <v>5.31879997253418</v>
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>35.01540756225586</v>
+        <v>35.01541137695312</v>
       </c>
       <c r="C76" t="n">
         <v>5.255000114440918</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>35.2786865234375</v>
+        <v>35.27868270874023</v>
       </c>
       <c r="C78" t="n">
         <v>5.237500190734863</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>34.78974533081055</v>
+        <v>34.78974914550781</v>
       </c>
       <c r="C79" t="n">
         <v>5.23799991607666</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.09062957763672</v>
+        <v>35.09063339233398</v>
       </c>
       <c r="C81" t="n">
         <v>5.21589994430542</v>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.11883544921875</v>
+        <v>35.11883926391602</v>
       </c>
       <c r="C82" t="n">
         <v>5.19159984588623</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>35.80522918701172</v>
+        <v>35.80523300170898</v>
       </c>
       <c r="C83" t="n">
         <v>5.196199893951416</v>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>34.89317321777344</v>
+        <v>34.8931770324707</v>
       </c>
       <c r="C84" t="n">
         <v>5.198699951171875</v>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>34.68631362915039</v>
+        <v>34.68631744384766</v>
       </c>
       <c r="C85" t="n">
         <v>5.213900089263916</v>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>35.55135726928711</v>
+        <v>35.55136108398438</v>
       </c>
       <c r="C87" t="n">
         <v>5.234399795532227</v>
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>36.98056030273438</v>
+        <v>36.98056411743164</v>
       </c>
       <c r="C93" t="n">
         <v>5.136600017547607</v>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>38.5037841796875</v>
+        <v>38.50378799438477</v>
       </c>
       <c r="C95" t="n">
         <v>5.170300006866455</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>40.58176803588867</v>
+        <v>40.58177185058594</v>
       </c>
       <c r="C99" t="n">
         <v>5.243500232696533</v>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>42.12380218505859</v>
+        <v>42.12379837036133</v>
       </c>
       <c r="C101" t="n">
         <v>5.162399768829346</v>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>42.31185150146484</v>
+        <v>42.31185531616211</v>
       </c>
       <c r="C102" t="n">
         <v>5.151400089263916</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>42.00156784057617</v>
+        <v>42.00156402587891</v>
       </c>
       <c r="C103" t="n">
         <v>5.243899822235107</v>
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>43.12047958374023</v>
+        <v>43.1204833984375</v>
       </c>
       <c r="C104" t="n">
         <v>5.329100131988525</v>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>43.60942077636719</v>
+        <v>43.60941696166992</v>
       </c>
       <c r="C105" t="n">
         <v>5.233399868011475</v>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>42.94182968139648</v>
+        <v>42.94182586669922</v>
       </c>
       <c r="C108" t="n">
         <v>5.219900131225586</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>43.28032684326172</v>
+        <v>43.28032302856445</v>
       </c>
       <c r="C109" t="n">
         <v>5.31190013885498</v>
@@ -8196,7 +8196,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>44.44625091552734</v>
+        <v>44.44625473022461</v>
       </c>
       <c r="C110" t="n">
         <v>5.232900142669678</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>46.45841598510742</v>
+        <v>46.45841217041016</v>
       </c>
       <c r="C113" t="n">
         <v>5.235099792480469</v>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>46.0164909362793</v>
+        <v>46.01648712158203</v>
       </c>
       <c r="C118" t="n">
         <v>5.157899856567383</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>43.82567596435547</v>
+        <v>43.82567977905273</v>
       </c>
       <c r="C120" t="n">
         <v>5.150599956512451</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>46.10111618041992</v>
+        <v>46.10111236572266</v>
       </c>
       <c r="C122" t="n">
         <v>5.095799922943115</v>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>46.80630874633789</v>
+        <v>46.80631256103516</v>
       </c>
       <c r="C123" t="n">
         <v>5.005000114440918</v>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>45.01980972290039</v>
+        <v>45.01981353759766</v>
       </c>
       <c r="C124" t="n">
         <v>4.994400024414062</v>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>45.67800140380859</v>
+        <v>45.67799758911133</v>
       </c>
       <c r="C126" t="n">
         <v>4.992400169372559</v>
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>44.82235717773438</v>
+        <v>44.82235336303711</v>
       </c>
       <c r="C129" t="n">
         <v>5.007999897003174</v>
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>46.68469619750977</v>
+        <v>46.6846923828125</v>
       </c>
       <c r="C134" t="n">
         <v>4.99429988861084</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>46.79911804199219</v>
+        <v>46.79912185668945</v>
       </c>
       <c r="C135" t="n">
         <v>5.017499923706055</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>47.04703903198242</v>
+        <v>47.04703521728516</v>
       </c>
       <c r="C136" t="n">
         <v>4.951929092407227</v>
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>46.39863967895508</v>
+        <v>46.39863586425781</v>
       </c>
       <c r="C137" t="n">
         <v>4.984799861907959</v>
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>43.55712509155273</v>
+        <v>43.55712890625</v>
       </c>
       <c r="C142" t="n">
         <v>4.906400203704834</v>
@@ -8931,7 +8931,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>43.35688400268555</v>
+        <v>43.35688781738281</v>
       </c>
       <c r="C145" t="n">
         <v>5.00409984588623</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>42.52731704711914</v>
+        <v>42.52731323242188</v>
       </c>
       <c r="C148" t="n">
         <v>5.058199882507324</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>42.86105346679688</v>
+        <v>42.86104965209961</v>
       </c>
       <c r="C149" t="n">
         <v>5.01170015335083</v>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>42.41289138793945</v>
+        <v>42.41289520263672</v>
       </c>
       <c r="C150" t="n">
         <v>5.017099857330322</v>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:14 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:21 UTC</t>
         </is>
       </c>
     </row>

--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:21 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:56 UTC</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30.45733205672228</v>
+        <v>30.45734581100089</v>
       </c>
     </row>
     <row r="10">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:21 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:56 UTC</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27.33520126342773</v>
+        <v>27.3351993560791</v>
       </c>
       <c r="C12" t="n">
         <v>5.373300075531006</v>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27.24405097961426</v>
+        <v>27.24405288696289</v>
       </c>
       <c r="C14" t="n">
         <v>5.357800006866455</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27.43546485900879</v>
+        <v>27.43546295166016</v>
       </c>
       <c r="C16" t="n">
         <v>5.374599933624268</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28.11907196044922</v>
+        <v>28.11907386779785</v>
       </c>
       <c r="C18" t="n">
         <v>5.395899772644043</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29.49540519714355</v>
+        <v>29.49540328979492</v>
       </c>
       <c r="C21" t="n">
         <v>5.330900192260742</v>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>30.26104354858398</v>
+        <v>30.26104545593262</v>
       </c>
       <c r="C22" t="n">
         <v>5.289700031280518</v>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.8053035736084</v>
+        <v>29.80530548095703</v>
       </c>
       <c r="C25" t="n">
         <v>5.296500205993652</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.96937370300293</v>
+        <v>29.9693717956543</v>
       </c>
       <c r="C26" t="n">
         <v>5.295599937438965</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.68680953979492</v>
+        <v>29.68681335449219</v>
       </c>
       <c r="C29" t="n">
         <v>5.332300186157227</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29.42248344421387</v>
+        <v>29.42248153686523</v>
       </c>
       <c r="C31" t="n">
         <v>5.386799812316895</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.53186416625977</v>
+        <v>29.53186225891113</v>
       </c>
       <c r="C33" t="n">
         <v>5.33080005645752</v>
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29.03055000305176</v>
+        <v>29.03055191040039</v>
       </c>
       <c r="C35" t="n">
         <v>5.335400104522705</v>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29.6412410736084</v>
+        <v>29.64123916625977</v>
       </c>
       <c r="C38" t="n">
         <v>5.306099891662598</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29.11258316040039</v>
+        <v>29.11258125305176</v>
       </c>
       <c r="C42" t="n">
         <v>5.43149995803833</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.6294994354248</v>
+        <v>28.62950134277344</v>
       </c>
       <c r="C43" t="n">
         <v>5.469799995422363</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28.01880836486816</v>
+        <v>28.0188102722168</v>
       </c>
       <c r="C46" t="n">
         <v>5.413400173187256</v>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28.32871437072754</v>
+        <v>28.32871246337891</v>
       </c>
       <c r="C47" t="n">
         <v>5.507500171661377</v>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28.16464614868164</v>
+        <v>28.16464424133301</v>
       </c>
       <c r="C48" t="n">
         <v>5.518499851226807</v>
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.34694290161133</v>
+        <v>28.3469409942627</v>
       </c>
       <c r="C50" t="n">
         <v>5.53980016708374</v>
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28.49938201904297</v>
+        <v>28.4993839263916</v>
       </c>
       <c r="C51" t="n">
         <v>5.590000152587891</v>
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.8942928314209</v>
+        <v>28.89429473876953</v>
       </c>
       <c r="C53" t="n">
         <v>5.542500019073486</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>27.86940765380859</v>
+        <v>27.86940574645996</v>
       </c>
       <c r="C57" t="n">
         <v>5.40749979019165</v>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28.48998069763184</v>
+        <v>28.48998260498047</v>
       </c>
       <c r="C60" t="n">
         <v>5.386600017547607</v>
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28.54640007019043</v>
+        <v>28.54639625549316</v>
       </c>
       <c r="C61" t="n">
         <v>5.370299816131592</v>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>30.07902526855469</v>
+        <v>30.07902717590332</v>
       </c>
       <c r="C63" t="n">
         <v>5.371300220489502</v>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>30.12604141235352</v>
+        <v>30.12603950500488</v>
       </c>
       <c r="C65" t="n">
         <v>5.367899894714355</v>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>30.2482738494873</v>
+        <v>30.24827003479004</v>
       </c>
       <c r="C66" t="n">
         <v>5.367700099945068</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>30.36110496520996</v>
+        <v>30.36110687255859</v>
       </c>
       <c r="C67" t="n">
         <v>5.36870002746582</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>31.43300819396973</v>
+        <v>31.43300437927246</v>
       </c>
       <c r="C68" t="n">
         <v>5.374300003051758</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>31.57404899597168</v>
+        <v>31.57404708862305</v>
       </c>
       <c r="C69" t="n">
         <v>5.31879997253418</v>
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>35.01541137695312</v>
+        <v>35.01540756225586</v>
       </c>
       <c r="C76" t="n">
         <v>5.255000114440918</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>35.27868270874023</v>
+        <v>35.2786865234375</v>
       </c>
       <c r="C78" t="n">
         <v>5.237500190734863</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>34.78974914550781</v>
+        <v>34.78974533081055</v>
       </c>
       <c r="C79" t="n">
         <v>5.23799991607666</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.09063339233398</v>
+        <v>35.09062957763672</v>
       </c>
       <c r="C81" t="n">
         <v>5.21589994430542</v>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.11883926391602</v>
+        <v>35.11883544921875</v>
       </c>
       <c r="C82" t="n">
         <v>5.19159984588623</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>35.80523300170898</v>
+        <v>35.80522918701172</v>
       </c>
       <c r="C83" t="n">
         <v>5.196199893951416</v>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>34.8931770324707</v>
+        <v>34.89317321777344</v>
       </c>
       <c r="C84" t="n">
         <v>5.198699951171875</v>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>34.68631744384766</v>
+        <v>34.68631362915039</v>
       </c>
       <c r="C85" t="n">
         <v>5.213900089263916</v>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>35.55136108398438</v>
+        <v>35.55135726928711</v>
       </c>
       <c r="C87" t="n">
         <v>5.234399795532227</v>
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>36.98056411743164</v>
+        <v>36.98056030273438</v>
       </c>
       <c r="C93" t="n">
         <v>5.136600017547607</v>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>38.50378799438477</v>
+        <v>38.5037841796875</v>
       </c>
       <c r="C95" t="n">
         <v>5.170300006866455</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>40.58177185058594</v>
+        <v>40.58176803588867</v>
       </c>
       <c r="C99" t="n">
         <v>5.243500232696533</v>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>42.12379837036133</v>
+        <v>42.12380218505859</v>
       </c>
       <c r="C101" t="n">
         <v>5.162399768829346</v>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>42.31185531616211</v>
+        <v>42.31185150146484</v>
       </c>
       <c r="C102" t="n">
         <v>5.151400089263916</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>42.00156402587891</v>
+        <v>42.00156784057617</v>
       </c>
       <c r="C103" t="n">
         <v>5.243899822235107</v>
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>43.1204833984375</v>
+        <v>43.12047958374023</v>
       </c>
       <c r="C104" t="n">
         <v>5.329100131988525</v>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>43.60941696166992</v>
+        <v>43.60942077636719</v>
       </c>
       <c r="C105" t="n">
         <v>5.233399868011475</v>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>42.94182586669922</v>
+        <v>42.94182968139648</v>
       </c>
       <c r="C108" t="n">
         <v>5.219900131225586</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>43.28032302856445</v>
+        <v>43.28032684326172</v>
       </c>
       <c r="C109" t="n">
         <v>5.31190013885498</v>
@@ -8196,7 +8196,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>44.44625473022461</v>
+        <v>44.44625091552734</v>
       </c>
       <c r="C110" t="n">
         <v>5.232900142669678</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>46.45841217041016</v>
+        <v>46.45841598510742</v>
       </c>
       <c r="C113" t="n">
         <v>5.235099792480469</v>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>46.01648712158203</v>
+        <v>46.0164909362793</v>
       </c>
       <c r="C118" t="n">
         <v>5.157899856567383</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>43.82567977905273</v>
+        <v>43.82567596435547</v>
       </c>
       <c r="C120" t="n">
         <v>5.150599956512451</v>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>46.10111236572266</v>
+        <v>46.10111618041992</v>
       </c>
       <c r="C122" t="n">
         <v>5.095799922943115</v>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>46.80631256103516</v>
+        <v>46.80630874633789</v>
       </c>
       <c r="C123" t="n">
         <v>5.005000114440918</v>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>45.01981353759766</v>
+        <v>45.01980972290039</v>
       </c>
       <c r="C124" t="n">
         <v>4.994400024414062</v>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>45.67799758911133</v>
+        <v>45.67800140380859</v>
       </c>
       <c r="C126" t="n">
         <v>4.992400169372559</v>
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>44.82235336303711</v>
+        <v>44.82235717773438</v>
       </c>
       <c r="C129" t="n">
         <v>5.007999897003174</v>
@@ -8700,7 +8700,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>46.6846923828125</v>
+        <v>46.68469619750977</v>
       </c>
       <c r="C134" t="n">
         <v>4.99429988861084</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>46.79912185668945</v>
+        <v>46.79911804199219</v>
       </c>
       <c r="C135" t="n">
         <v>5.017499923706055</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>47.04703521728516</v>
+        <v>47.04703903198242</v>
       </c>
       <c r="C136" t="n">
         <v>4.951929092407227</v>
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>46.39863586425781</v>
+        <v>46.39863967895508</v>
       </c>
       <c r="C137" t="n">
         <v>4.984799861907959</v>
@@ -8868,7 +8868,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>43.55712890625</v>
+        <v>43.55712509155273</v>
       </c>
       <c r="C142" t="n">
         <v>4.906400203704834</v>
@@ -8931,7 +8931,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>43.35688781738281</v>
+        <v>43.35688400268555</v>
       </c>
       <c r="C145" t="n">
         <v>5.00409984588623</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>42.52731323242188</v>
+        <v>42.52731704711914</v>
       </c>
       <c r="C148" t="n">
         <v>5.058199882507324</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>42.86104965209961</v>
+        <v>42.86105346679688</v>
       </c>
       <c r="C149" t="n">
         <v>5.01170015335083</v>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>42.41289520263672</v>
+        <v>42.41289138793945</v>
       </c>
       <c r="C150" t="n">
         <v>5.017099857330322</v>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:21 UTC</t>
+          <t>Snapshot as of 2026-10-14 19:56 UTC</t>
         </is>
       </c>
     </row>

--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -471,11 +471,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>218.0899963378906</v>
+        <v>238.6000061035156</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -490,18 +490,18 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D252/D57-1)*100</f>
+        <f>(D252/D56-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>238.6000061035156</v>
+        <v>234.5599975585938</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -527,11 +527,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>234.5599975585938</v>
+        <v>233.0800018310547</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -557,11 +557,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>233.0800018310547</v>
+        <v>240.5599975585938</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -587,11 +587,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>240.5599975585938</v>
+        <v>238.0299987792969</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -608,11 +608,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>238.0299987792969</v>
+        <v>230.2299957275391</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -637,11 +637,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>230.2299957275391</v>
+        <v>234.9900054931641</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -666,11 +666,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>234.9900054931641</v>
+        <v>252.9199981689453</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -695,11 +695,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>252.9199981689453</v>
+        <v>259.6700134277344</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -716,11 +716,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>259.6700134277344</v>
+        <v>258.010009765625</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -735,18 +735,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:56 UTC</t>
+          <t>Snapshot as of 2026-10-14 20:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>258.010009765625</v>
+        <v>264.3299865722656</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -763,11 +763,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>264.3299865722656</v>
+        <v>254.8399963378906</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -784,11 +784,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>254.8399963378906</v>
+        <v>256.1199951171875</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -805,11 +805,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>256.1199951171875</v>
+        <v>259.6499938964844</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -826,11 +826,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>259.6499938964844</v>
+        <v>250.0500030517578</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -847,11 +847,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>250.0500030517578</v>
+        <v>256.3299865722656</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -868,11 +868,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>256.3299865722656</v>
+        <v>237.6999969482422</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -889,11 +889,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>237.6999969482422</v>
+        <v>233.5399932861328</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -910,11 +910,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>233.5399932861328</v>
+        <v>243.9799957275391</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -931,11 +931,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>243.9799957275391</v>
+        <v>237.5200042724609</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -952,11 +952,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>237.5200042724609</v>
+        <v>258.8900146484375</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -973,11 +973,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>258.8900146484375</v>
+        <v>247.9600067138672</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -994,11 +994,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>247.9600067138672</v>
+        <v>246.8099975585938</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1015,11 +1015,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>246.8099975585938</v>
+        <v>240.5200042724609</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1036,11 +1036,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>240.5200042724609</v>
+        <v>230.2899932861328</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1057,11 +1057,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>230.2899932861328</v>
+        <v>223.5500030517578</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1078,11 +1078,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>223.5500030517578</v>
+        <v>206.0200042724609</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>206.0200042724609</v>
+        <v>203.7799987792969</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1120,11 +1120,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>203.7799987792969</v>
+        <v>215.0500030517578</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1141,11 +1141,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>215.0500030517578</v>
+        <v>206.1300048828125</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1162,11 +1162,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>206.1300048828125</v>
+        <v>214.2400054931641</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -1183,11 +1183,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>214.2400054931641</v>
+        <v>217.5299987792969</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1204,11 +1204,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>217.5299987792969</v>
+        <v>219.7599945068359</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -1225,11 +1225,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>219.7599945068359</v>
+        <v>215.2400054931641</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1246,11 +1246,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>215.2400054931641</v>
+        <v>217.6000061035156</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1267,11 +1267,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>217.6000061035156</v>
+        <v>215.9799957275391</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1288,11 +1288,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>215.9799957275391</v>
+        <v>217.9700012207031</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -1309,11 +1309,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>217.9700012207031</v>
+        <v>221.1100006103516</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -1330,11 +1330,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>221.1100006103516</v>
+        <v>221.6199951171875</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1351,11 +1351,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>221.6199951171875</v>
+        <v>221.4199981689453</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1372,11 +1372,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>221.4199981689453</v>
+        <v>221.4299926757812</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1393,11 +1393,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>221.4299926757812</v>
+        <v>210.7799987792969</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1414,11 +1414,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>210.7799987792969</v>
+        <v>207.5800018310547</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -1435,11 +1435,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>207.5800018310547</v>
+        <v>209.1699981689453</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1456,11 +1456,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>209.1699981689453</v>
+        <v>198.1100006103516</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1477,11 +1477,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>198.1100006103516</v>
+        <v>201.0599975585938</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1498,11 +1498,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>201.0599975585938</v>
+        <v>213.4299926757812</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -1519,11 +1519,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>213.4299926757812</v>
+        <v>214.9499969482422</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -1540,11 +1540,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>214.9499969482422</v>
+        <v>214.8999938964844</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -1561,11 +1561,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>214.8999938964844</v>
+        <v>215.0399932861328</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -1582,11 +1582,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>215.0399932861328</v>
+        <v>214.9900054931641</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -1603,11 +1603,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>214.9900054931641</v>
+        <v>215.6100006103516</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -1624,11 +1624,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>215.6100006103516</v>
+        <v>215.3399963378906</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -1645,11 +1645,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>215.3399963378906</v>
+        <v>214.1600036621094</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -1666,11 +1666,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>214.1600036621094</v>
+        <v>223.4700012207031</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -1687,11 +1687,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>223.4700012207031</v>
+        <v>221.0800018310547</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -1708,11 +1708,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>221.0800018310547</v>
+        <v>214.3500061035156</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -1729,11 +1729,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>214.3500061035156</v>
+        <v>210.0200042724609</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -1750,11 +1750,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>210.0200042724609</v>
+        <v>204.6799926757812</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -1771,11 +1771,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>204.6799926757812</v>
+        <v>203.1699981689453</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -1792,11 +1792,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>203.1699981689453</v>
+        <v>207.6900024414062</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -1813,11 +1813,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>207.6900024414062</v>
+        <v>220.9700012207031</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -1834,11 +1834,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>220.9700012207031</v>
+        <v>223.6000061035156</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -1855,11 +1855,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>223.6000061035156</v>
+        <v>227.9199981689453</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -1876,11 +1876,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>227.9199981689453</v>
+        <v>231.8300018310547</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -1897,11 +1897,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>231.8300018310547</v>
+        <v>231.9199981689453</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -1918,11 +1918,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>231.9199981689453</v>
+        <v>249.8000030517578</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -1939,11 +1939,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>249.8000030517578</v>
+        <v>253.7299957275391</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -1960,11 +1960,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>253.7299957275391</v>
+        <v>259.6799926757812</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -1981,11 +1981,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>259.6799926757812</v>
+        <v>251.3099975585938</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -2002,11 +2002,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>251.3099975585938</v>
+        <v>252.0299987792969</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
@@ -2023,11 +2023,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>252.0299987792969</v>
+        <v>252.7400054931641</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
@@ -2044,11 +2044,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>252.7400054931641</v>
+        <v>252.1799926757812</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
@@ -2065,11 +2065,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>252.1799926757812</v>
+        <v>236.7299957275391</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -2086,11 +2086,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>236.7299957275391</v>
+        <v>246.2700042724609</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
@@ -2107,11 +2107,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>246.2700042724609</v>
+        <v>242.1100006103516</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -2128,11 +2128,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>242.1100006103516</v>
+        <v>200.1900024414062</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -2149,11 +2149,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>200.1900024414062</v>
+        <v>192.5</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -2170,11 +2170,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>192.5</v>
+        <v>208.4400024414062</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -2191,11 +2191,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>208.4400024414062</v>
+        <v>216</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -2212,11 +2212,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>216</v>
+        <v>213.5700073242188</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -2233,11 +2233,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>213.5700073242188</v>
+        <v>213.5800018310547</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -2254,11 +2254,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>213.5800018310547</v>
+        <v>205.9400024414062</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
@@ -2275,11 +2275,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>205.9400024414062</v>
+        <v>207.3200073242188</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -2296,11 +2296,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>207.3200073242188</v>
+        <v>203.0800018310547</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -2317,11 +2317,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>203.0800018310547</v>
+        <v>200.1199951171875</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
@@ -2338,11 +2338,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>200.1199951171875</v>
+        <v>203.3699951171875</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -2359,11 +2359,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>203.3699951171875</v>
+        <v>200.1499938964844</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
@@ -2380,11 +2380,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>200.1499938964844</v>
+        <v>196.6000061035156</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -2401,11 +2401,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>196.6000061035156</v>
+        <v>213.8399963378906</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -2422,11 +2422,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>213.8399963378906</v>
+        <v>210.8600006103516</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -2443,11 +2443,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>210.8600006103516</v>
+        <v>203.6799926757812</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -2464,11 +2464,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>203.6799926757812</v>
+        <v>200.2100067138672</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -2485,11 +2485,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>200.2100067138672</v>
+        <v>198.6199951171875</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
@@ -2506,11 +2506,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>198.6199951171875</v>
+        <v>190.9499969482422</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -2527,11 +2527,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>190.9499969482422</v>
+        <v>202.0700073242188</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -2548,11 +2548,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>202.0700073242188</v>
+        <v>199.4499969482422</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
@@ -2569,11 +2569,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>199.4499969482422</v>
+        <v>192.4299926757812</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
@@ -2590,11 +2590,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>192.4299926757812</v>
+        <v>202.6799926757812</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -2611,11 +2611,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>202.6799926757812</v>
+        <v>203.2299957275391</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -2632,11 +2632,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>203.2299957275391</v>
+        <v>204.8300018310547</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
@@ -2653,11 +2653,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>204.8300018310547</v>
+        <v>197.7400054931641</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -2674,11 +2674,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>197.7400054931641</v>
+        <v>193.3899993896484</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
@@ -2695,11 +2695,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>193.3899993896484</v>
+        <v>196.5800018310547</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
@@ -2716,11 +2716,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>196.5800018310547</v>
+        <v>196.3099975585938</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
@@ -2737,11 +2737,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>196.3099975585938</v>
+        <v>199.4600067138672</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -2758,11 +2758,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>199.4600067138672</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
@@ -2779,11 +2779,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>205.2700042724609</v>
+        <v>201.3300018310547</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
@@ -2800,11 +2800,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>201.3300018310547</v>
+        <v>202.6799926757812</v>
       </c>
       <c r="C110" t="n">
         <v>1</v>
@@ -2821,11 +2821,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>202.6799926757812</v>
+        <v>205.3699951171875</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
@@ -2842,11 +2842,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>205.3699951171875</v>
+        <v>220.2700042724609</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
@@ -2863,11 +2863,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>220.2700042724609</v>
+        <v>203.7700042724609</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
@@ -2884,11 +2884,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>203.7700042724609</v>
+        <v>201.9900054931641</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -2905,11 +2905,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>201.9900054931641</v>
+        <v>196.0399932861328</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -2926,11 +2926,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>196.0399932861328</v>
+        <v>203.4299926757812</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
@@ -2947,11 +2947,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>203.4299926757812</v>
+        <v>210.2100067138672</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
@@ -2968,11 +2968,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>210.2100067138672</v>
+        <v>217.5</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
@@ -2989,11 +2989,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>217.5</v>
+        <v>220.1799926757812</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -3010,11 +3010,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>220.1799926757812</v>
+        <v>221.5299987792969</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -3031,11 +3031,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>221.5299987792969</v>
+        <v>231.8200073242188</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
@@ -3052,11 +3052,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>231.8200073242188</v>
+        <v>236.6399993896484</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
@@ -3073,11 +3073,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>236.6399993896484</v>
+        <v>245.0399932861328</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -3094,11 +3094,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>245.0399932861328</v>
+        <v>246.8300018310547</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -3115,11 +3115,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>246.8300018310547</v>
+        <v>255.0700073242188</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -3136,11 +3136,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>255.0700073242188</v>
+        <v>258.1199951171875</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -3157,11 +3157,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>258.1199951171875</v>
+        <v>278.260009765625</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -3178,11 +3178,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>278.260009765625</v>
+        <v>278.3900146484375</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
@@ -3199,11 +3199,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>278.3900146484375</v>
+        <v>274.9500122070312</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -3220,11 +3220,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>274.9500122070312</v>
+        <v>284.489990234375</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -3241,11 +3241,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>284.489990234375</v>
+        <v>303.4599914550781</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -3262,11 +3262,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>303.4599914550781</v>
+        <v>305.3299865722656</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
@@ -3283,11 +3283,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>305.3299865722656</v>
+        <v>347.8099975585938</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -3304,11 +3304,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>347.8099975585938</v>
+        <v>334.6300048828125</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
@@ -3325,11 +3325,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>334.6300048828125</v>
+        <v>323.2099914550781</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
@@ -3346,11 +3346,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>323.2099914550781</v>
+        <v>337.1099853515625</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -3367,11 +3367,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>337.1099853515625</v>
+        <v>354.489990234375</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
@@ -3388,11 +3388,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>354.489990234375</v>
+        <v>360.5400085449219</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
@@ -3409,11 +3409,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>360.5400085449219</v>
+        <v>341.5400085449219</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
@@ -3430,11 +3430,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>341.5400085449219</v>
+        <v>355.260009765625</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -3451,11 +3451,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>355.260009765625</v>
+        <v>421.3900146484375</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
@@ -3472,11 +3472,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>421.3900146484375</v>
+        <v>408.4599914550781</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
@@ -3493,11 +3493,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>408.4599914550781</v>
+        <v>455.1900024414062</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -3514,11 +3514,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>455.1900024414062</v>
+        <v>458.7900085449219</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
@@ -3535,11 +3535,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>458.7900085449219</v>
+        <v>448.2900085449219</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
@@ -3556,11 +3556,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>448.2900085449219</v>
+        <v>445.5</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
@@ -3577,11 +3577,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>445.5</v>
+        <v>449.7000122070312</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
@@ -3598,11 +3598,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>449.7000122070312</v>
+        <v>424.1000061035156</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
@@ -3619,11 +3619,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>424.1000061035156</v>
+        <v>420.989990234375</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
@@ -3640,11 +3640,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>420.989990234375</v>
+        <v>414.0499877929688</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -3661,11 +3661,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>414.0499877929688</v>
+        <v>447.5799865722656</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -3682,11 +3682,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>447.5799865722656</v>
+        <v>449.5899963378906</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -3703,11 +3703,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>449.5899963378906</v>
+        <v>467.510009765625</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
@@ -3724,11 +3724,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>467.510009765625</v>
+        <v>503.8900146484375</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
@@ -3745,11 +3745,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>503.8900146484375</v>
+        <v>495.5400085449219</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
@@ -3766,11 +3766,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>495.5400085449219</v>
+        <v>518.0900268554688</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
@@ -3787,11 +3787,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>518.0900268554688</v>
+        <v>516.0999755859375</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -3808,11 +3808,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>516.0999755859375</v>
+        <v>510.1300048828125</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -3829,11 +3829,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>510.1300048828125</v>
+        <v>521.5399780273438</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
@@ -3850,11 +3850,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>521.5399780273438</v>
+        <v>542.52001953125</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
@@ -3871,11 +3871,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>542.52001953125</v>
+        <v>523.2000122070312</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -3892,11 +3892,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>523.2000122070312</v>
+        <v>466.3800048828125</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -3913,11 +3913,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>466.3800048828125</v>
+        <v>490.3299865722656</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -3934,11 +3934,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>490.3299865722656</v>
+        <v>475.510009765625</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
@@ -3955,11 +3955,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>475.510009765625</v>
+        <v>452.3999938964844</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -3976,11 +3976,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>452.3999938964844</v>
+        <v>488.4500122070312</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
@@ -3997,11 +3997,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>488.4500122070312</v>
+        <v>511.5700073242188</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
@@ -4018,11 +4018,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>511.5700073242188</v>
+        <v>547.260009765625</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
@@ -4039,11 +4039,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>547.260009765625</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
@@ -4060,11 +4060,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>507.2900085449219</v>
+        <v>512.47998046875</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
@@ -4081,11 +4081,11 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>512.47998046875</v>
+        <v>537.3699951171875</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -4102,11 +4102,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>537.3699951171875</v>
+        <v>551.6300048828125</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
@@ -4123,11 +4123,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>551.6300048828125</v>
+        <v>519.8499755859375</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
@@ -4144,11 +4144,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>519.8499755859375</v>
+        <v>519.739990234375</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
@@ -4165,11 +4165,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>519.739990234375</v>
+        <v>532.5700073242188</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
@@ -4186,11 +4186,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>532.5700073242188</v>
+        <v>521.5800170898438</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
@@ -4207,11 +4207,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>521.5800170898438</v>
+        <v>539.489990234375</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
@@ -4228,11 +4228,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>539.489990234375</v>
+        <v>580.9099731445312</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
@@ -4249,11 +4249,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>580.9099731445312</v>
+        <v>540.8800048828125</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
@@ -4270,11 +4270,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>540.8800048828125</v>
+        <v>517.8200073242188</v>
       </c>
       <c r="C180" t="n">
         <v>1</v>
@@ -4291,11 +4291,11 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>517.8200073242188</v>
+        <v>552.0499877929688</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
@@ -4312,11 +4312,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>552.0499877929688</v>
+        <v>516.1099853515625</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -4333,11 +4333,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>516.1099853515625</v>
+        <v>517.4099731445312</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
@@ -4354,11 +4354,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>517.4099731445312</v>
+        <v>546.719970703125</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
@@ -4375,11 +4375,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>546.719970703125</v>
+        <v>557.8900146484375</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -4396,11 +4396,11 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>557.8900146484375</v>
+        <v>534.3900146484375</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
@@ -4417,11 +4417,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>534.3900146484375</v>
+        <v>548.1300048828125</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
@@ -4438,11 +4438,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>548.1300048828125</v>
+        <v>529.1400146484375</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -4459,11 +4459,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>529.1400146484375</v>
+        <v>500.9400024414062</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
@@ -4480,11 +4480,11 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>500.9400024414062</v>
+        <v>495.760009765625</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -4501,11 +4501,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>495.760009765625</v>
+        <v>503.5700073242188</v>
       </c>
       <c r="C191" t="n">
         <v>1</v>
@@ -4522,11 +4522,11 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>503.5700073242188</v>
+        <v>544.4299926757812</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
@@ -4543,11 +4543,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>544.4299926757812</v>
+        <v>552.3300170898438</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
@@ -4564,11 +4564,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>552.3300170898438</v>
+        <v>539.6900024414062</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -4585,11 +4585,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>539.6900024414062</v>
+        <v>521.9500122070312</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
@@ -4606,11 +4606,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>521.9500122070312</v>
+        <v>494.9500122070312</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
@@ -4627,11 +4627,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>494.9500122070312</v>
+        <v>454.6199951171875</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -4648,11 +4648,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>454.6199951171875</v>
+        <v>429.5599975585938</v>
       </c>
       <c r="C198" t="n">
         <v>1</v>
@@ -4669,11 +4669,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>429.5599975585938</v>
+        <v>485.3900146484375</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
@@ -4690,11 +4690,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>485.3900146484375</v>
+        <v>476.1499938964844</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
@@ -4711,11 +4711,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>476.1499938964844</v>
+        <v>484.6400146484375</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
@@ -4732,11 +4732,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>484.6400146484375</v>
+        <v>518.5800170898438</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
@@ -4753,11 +4753,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>518.5800170898438</v>
+        <v>482.0499877929688</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
@@ -4774,11 +4774,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>482.0499877929688</v>
+        <v>489.2799987792969</v>
       </c>
       <c r="C204" t="n">
         <v>1</v>
@@ -4795,11 +4795,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>489.2799987792969</v>
+        <v>483.3599853515625</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
@@ -4816,11 +4816,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>483.3599853515625</v>
+        <v>469.5599975585938</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
@@ -4837,11 +4837,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>469.5599975585938</v>
+        <v>474.3200073242188</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
@@ -4858,11 +4858,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>474.3200073242188</v>
+        <v>482.9299926757812</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
@@ -4879,11 +4879,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>482.9299926757812</v>
+        <v>483.010009765625</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
@@ -4900,11 +4900,11 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>483.010009765625</v>
+        <v>514.3900146484375</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
@@ -4921,11 +4921,11 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>514.3900146484375</v>
+        <v>506</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
@@ -4942,11 +4942,11 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>506</v>
+        <v>484.3900146484375</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
@@ -4963,11 +4963,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>484.3900146484375</v>
+        <v>466.4200134277344</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
@@ -4984,11 +4984,11 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>466.4200134277344</v>
+        <v>469.4599914550781</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
@@ -5005,11 +5005,11 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>469.4599914550781</v>
+        <v>473.25</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
@@ -5026,11 +5026,11 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>473.25</v>
+        <v>456.75</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
@@ -5047,11 +5047,11 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>456.75</v>
+        <v>479.1799926757812</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
@@ -5068,11 +5068,11 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>479.1799926757812</v>
+        <v>480.9299926757812</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
@@ -5089,11 +5089,11 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>480.9299926757812</v>
+        <v>476.6700134277344</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
@@ -5110,11 +5110,11 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>476.6700134277344</v>
+        <v>465.5799865722656</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
@@ -5131,11 +5131,11 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>465.5799865722656</v>
+        <v>470.7200012207031</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
@@ -5152,11 +5152,11 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>470.7200012207031</v>
+        <v>459.6099853515625</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
@@ -5173,11 +5173,11 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>459.6099853515625</v>
+        <v>457.0599975585938</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
@@ -5194,11 +5194,11 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>457.0599975585938</v>
+        <v>456.1600036621094</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
@@ -5215,11 +5215,11 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>456.1600036621094</v>
+        <v>477.5700073242188</v>
       </c>
       <c r="C225" t="n">
         <v>1</v>
@@ -5236,11 +5236,11 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>477.5700073242188</v>
+        <v>505.739990234375</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
@@ -5257,11 +5257,11 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>505.739990234375</v>
+        <v>521.0999755859375</v>
       </c>
       <c r="C227" t="n">
         <v>1</v>
@@ -5278,11 +5278,11 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>521.0999755859375</v>
+        <v>503.6000061035156</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
@@ -5299,11 +5299,11 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>503.6000061035156</v>
+        <v>516.1300048828125</v>
       </c>
       <c r="C229" t="n">
         <v>1</v>
@@ -5320,11 +5320,11 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>516.1300048828125</v>
+        <v>493.4100036621094</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
@@ -5341,11 +5341,11 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>493.4100036621094</v>
+        <v>504.2000122070312</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
@@ -5362,11 +5362,11 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>504.2000122070312</v>
+        <v>512.5</v>
       </c>
       <c r="C232" t="n">
         <v>1</v>
@@ -5383,11 +5383,11 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>512.5</v>
+        <v>545.0900268554688</v>
       </c>
       <c r="C233" t="n">
         <v>1</v>
@@ -5404,11 +5404,11 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>545.0900268554688</v>
+        <v>559.8200073242188</v>
       </c>
       <c r="C234" t="n">
         <v>1</v>
@@ -5425,11 +5425,11 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>559.8200073242188</v>
+        <v>615.52001953125</v>
       </c>
       <c r="C235" t="n">
         <v>1</v>
@@ -5446,11 +5446,11 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>615.52001953125</v>
+        <v>623.77001953125</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
@@ -5467,11 +5467,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>623.77001953125</v>
+        <v>614.6099853515625</v>
       </c>
       <c r="C237" t="n">
         <v>1</v>
@@ -5488,11 +5488,11 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>614.6099853515625</v>
+        <v>629.260009765625</v>
       </c>
       <c r="C238" t="n">
         <v>1</v>
@@ -5509,11 +5509,11 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>629.260009765625</v>
+        <v>630.6300048828125</v>
       </c>
       <c r="C239" t="n">
         <v>1</v>
@@ -5530,11 +5530,11 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>630.6300048828125</v>
+        <v>607.8699951171875</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
@@ -5551,11 +5551,11 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>607.8699951171875</v>
+        <v>607.5700073242188</v>
       </c>
       <c r="C241" t="n">
         <v>1</v>
@@ -5572,11 +5572,11 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>607.5700073242188</v>
+        <v>611.760009765625</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
@@ -5593,11 +5593,11 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>611.760009765625</v>
+        <v>615.72998046875</v>
       </c>
       <c r="C243" t="n">
         <v>1</v>
@@ -5614,11 +5614,11 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>615.72998046875</v>
+        <v>633.9099731445312</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
@@ -5635,11 +5635,11 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>633.9099731445312</v>
+        <v>631.75</v>
       </c>
       <c r="C245" t="n">
         <v>1</v>
@@ -5656,11 +5656,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>631.75</v>
+        <v>649.4199829101562</v>
       </c>
       <c r="C246" t="n">
         <v>1</v>
@@ -5677,11 +5677,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>649.4199829101562</v>
+        <v>645.8599853515625</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
@@ -5698,11 +5698,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>645.8599853515625</v>
+        <v>620.6799926757812</v>
       </c>
       <c r="C248" t="n">
         <v>1</v>
@@ -5719,11 +5719,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>620.6799926757812</v>
+        <v>608.0999755859375</v>
       </c>
       <c r="C249" t="n">
         <v>1</v>
@@ -5740,11 +5740,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>608.0999755859375</v>
+        <v>594.239990234375</v>
       </c>
       <c r="C250" t="n">
         <v>1</v>
@@ -5761,11 +5761,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>594.239990234375</v>
+        <v>605.530029296875</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>
@@ -5782,11 +5782,11 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>605.530029296875</v>
+        <v>570.72998046875</v>
       </c>
       <c r="C252" t="n">
         <v>1</v>
@@ -5811,7 +5811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D249/D55-1)*100</f>
+        <f>(D250/D55-1)*100</f>
         <v/>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.11644554138184</v>
+        <v>27.11644744873047</v>
       </c>
       <c r="C3" t="n">
         <v>5.481500148773193</v>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="H3">
-        <f>(D249/D2-1)*100</f>
+        <f>(D250/D2-1)*100</f>
         <v/>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="H4">
-        <f>(COUNT(D2:D249)-1)/((DATEVALUE(A249)-DATEVALUE(A2))/365.25)</f>
+        <f>(COUNT(D2:D250)-1)/((DATEVALUE(A250)-DATEVALUE(A2))/365.25)</f>
         <v/>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="H5">
-        <f>STDEV.S(E3:E249)*SQRT(H4)*100</f>
+        <f>STDEV.S(E3:E250)*SQRT(H4)*100</f>
         <v/>
       </c>
     </row>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.11644554138184</v>
+        <v>27.11644744873047</v>
       </c>
       <c r="C6" t="n">
         <v>5.406099796295166</v>
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.20759582519531</v>
+        <v>27.20759391784668</v>
       </c>
       <c r="C8" t="n">
         <v>5.38670015335083</v>
@@ -6112,7 +6112,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.34431648254395</v>
+        <v>27.34431457519531</v>
       </c>
       <c r="C11" t="n">
         <v>5.388299942016602</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:56 UTC</t>
+          <t>Snapshot as of 2026-10-14 20:00 UTC</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27.3351993560791</v>
+        <v>27.33520126342773</v>
       </c>
       <c r="C12" t="n">
         <v>5.373300075531006</v>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27.24405288696289</v>
+        <v>27.24405097961426</v>
       </c>
       <c r="C14" t="n">
         <v>5.357800006866455</v>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>27.11644554138184</v>
+        <v>27.11644744873047</v>
       </c>
       <c r="C15" t="n">
         <v>5.381999969482422</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>27.43546295166016</v>
+        <v>27.43546485900879</v>
       </c>
       <c r="C16" t="n">
         <v>5.374599933624268</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28.11907386779785</v>
+        <v>28.11907196044922</v>
       </c>
       <c r="C18" t="n">
         <v>5.395899772644043</v>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28.26490783691406</v>
+        <v>28.2649097442627</v>
       </c>
       <c r="C19" t="n">
         <v>5.35860013961792</v>
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29.33133697509766</v>
+        <v>29.33133506774902</v>
       </c>
       <c r="C20" t="n">
         <v>5.349500179290771</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29.49540328979492</v>
+        <v>29.49540519714355</v>
       </c>
       <c r="C21" t="n">
         <v>5.330900192260742</v>
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29.48628807067871</v>
+        <v>29.48628616333008</v>
       </c>
       <c r="C23" t="n">
         <v>5.270699977874756</v>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.80530548095703</v>
+        <v>29.8053035736084</v>
       </c>
       <c r="C25" t="n">
         <v>5.296500205993652</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.68681335449219</v>
+        <v>29.68681144714355</v>
       </c>
       <c r="C29" t="n">
         <v>5.332300186157227</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29.42248153686523</v>
+        <v>29.42248344421387</v>
       </c>
       <c r="C31" t="n">
         <v>5.386799812316895</v>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.37691116333008</v>
+        <v>29.37691307067871</v>
       </c>
       <c r="C32" t="n">
         <v>5.37939977645874</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.53186225891113</v>
+        <v>29.53186416625977</v>
       </c>
       <c r="C33" t="n">
         <v>5.33080005645752</v>
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29.03055191040039</v>
+        <v>29.03055000305176</v>
       </c>
       <c r="C35" t="n">
         <v>5.335400104522705</v>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.2310733795166</v>
+        <v>29.23107147216797</v>
       </c>
       <c r="C36" t="n">
         <v>5.355800151824951</v>
@@ -6663,7 +6663,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29.44983100891113</v>
+        <v>29.4498291015625</v>
       </c>
       <c r="C37" t="n">
         <v>5.326300144195557</v>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29.64123916625977</v>
+        <v>29.6412410736084</v>
       </c>
       <c r="C38" t="n">
         <v>5.306099891662598</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29.11258125305176</v>
+        <v>29.11258316040039</v>
       </c>
       <c r="C42" t="n">
         <v>5.43149995803833</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.62950134277344</v>
+        <v>28.6294994354248</v>
       </c>
       <c r="C43" t="n">
         <v>5.469799995422363</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28.0188102722168</v>
+        <v>28.01880836486816</v>
       </c>
       <c r="C46" t="n">
         <v>5.413400173187256</v>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28.32871246337891</v>
+        <v>28.32871437072754</v>
       </c>
       <c r="C47" t="n">
         <v>5.507500171661377</v>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28.16464424133301</v>
+        <v>28.16464614868164</v>
       </c>
       <c r="C48" t="n">
         <v>5.518499851226807</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28.26490783691406</v>
+        <v>28.2649097442627</v>
       </c>
       <c r="C49" t="n">
         <v>5.521299839019775</v>
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.3469409942627</v>
+        <v>28.34694290161133</v>
       </c>
       <c r="C50" t="n">
         <v>5.53980016708374</v>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>28.97891807556152</v>
+        <v>28.97891998291016</v>
       </c>
       <c r="C54" t="n">
         <v>5.569099903106689</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28.87548828125</v>
+        <v>28.87549018859863</v>
       </c>
       <c r="C55" t="n">
         <v>5.517000198364258</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>27.86940574645996</v>
+        <v>27.86940765380859</v>
       </c>
       <c r="C57" t="n">
         <v>5.40749979019165</v>
@@ -7146,7 +7146,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28.48998260498047</v>
+        <v>28.48998069763184</v>
       </c>
       <c r="C60" t="n">
         <v>5.386600017547607</v>
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28.54639625549316</v>
+        <v>28.5463981628418</v>
       </c>
       <c r="C61" t="n">
         <v>5.370299816131592</v>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>30.12603950500488</v>
+        <v>30.12604141235352</v>
       </c>
       <c r="C65" t="n">
         <v>5.367899894714355</v>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>30.24827003479004</v>
+        <v>30.24827194213867</v>
       </c>
       <c r="C66" t="n">
         <v>5.367700099945068</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>31.43300437927246</v>
+        <v>31.43300819396973</v>
       </c>
       <c r="C68" t="n">
         <v>5.374300003051758</v>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>35.44792938232422</v>
+        <v>35.44793319702148</v>
       </c>
       <c r="C74" t="n">
         <v>5.197100162506104</v>
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>35.01540756225586</v>
+        <v>35.01541137695312</v>
       </c>
       <c r="C76" t="n">
         <v>5.255000114440918</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>35.2786865234375</v>
+        <v>35.27868270874023</v>
       </c>
       <c r="C78" t="n">
         <v>5.237500190734863</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.09062957763672</v>
+        <v>35.09063339233398</v>
       </c>
       <c r="C81" t="n">
         <v>5.21589994430542</v>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.11883544921875</v>
+        <v>35.11883926391602</v>
       </c>
       <c r="C82" t="n">
         <v>5.19159984588623</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>35.80522918701172</v>
+        <v>35.80523300170898</v>
       </c>
       <c r="C83" t="n">
         <v>5.196199893951416</v>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>34.68631362915039</v>
+        <v>34.68631744384766</v>
       </c>
       <c r="C85" t="n">
         <v>5.213900089263916</v>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>35.55135726928711</v>
+        <v>35.55136108398438</v>
       </c>
       <c r="C87" t="n">
         <v>5.234399795532227</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>37.20622253417969</v>
+        <v>37.20622634887695</v>
       </c>
       <c r="C90" t="n">
         <v>5.170899868011475</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37.20622253417969</v>
+        <v>37.20622634887695</v>
       </c>
       <c r="C91" t="n">
         <v>5.151999950408936</v>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>38.5037841796875</v>
+        <v>38.50378799438477</v>
       </c>
       <c r="C95" t="n">
         <v>5.170300006866455</v>
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>38.25931549072266</v>
+        <v>38.25931930541992</v>
       </c>
       <c r="C97" t="n">
         <v>5.230100154876709</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>40.58176803588867</v>
+        <v>40.58177185058594</v>
       </c>
       <c r="C99" t="n">
         <v>5.243500232696533</v>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>42.31185150146484</v>
+        <v>42.31185913085938</v>
       </c>
       <c r="C102" t="n">
         <v>5.151400089263916</v>
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>43.12047958374023</v>
+        <v>43.1204833984375</v>
       </c>
       <c r="C104" t="n">
         <v>5.329100131988525</v>
@@ -8091,7 +8091,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>43.60942077636719</v>
+        <v>43.60941696166992</v>
       </c>
       <c r="C105" t="n">
         <v>5.233399868011475</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>43.98551940917969</v>
+        <v>43.98552322387695</v>
       </c>
       <c r="C107" t="n">
         <v>5.262100219726562</v>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>42.94182968139648</v>
+        <v>42.94182586669922</v>
       </c>
       <c r="C108" t="n">
         <v>5.219900131225586</v>
@@ -8196,7 +8196,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>44.44625091552734</v>
+        <v>44.44625473022461</v>
       </c>
       <c r="C110" t="n">
         <v>5.232900142669678</v>
@@ -8238,7 +8238,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>45.15145111083984</v>
+        <v>45.15144729614258</v>
       </c>
       <c r="C112" t="n">
         <v>5.236800193786621</v>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>45.61217498779297</v>
+        <v>45.61217880249023</v>
       </c>
       <c r="C119" t="n">
         <v>5.138299942016602</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>43.82567596435547</v>
+        <v>43.82567977905273</v>
       </c>
       <c r="C120" t="n">
         <v>5.150599956512451</v>
@@ -8490,7 +8490,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>45.01980972290039</v>
+        <v>45.01981353759766</v>
       </c>
       <c r="C124" t="n">
         <v>4.994400024414062</v>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>44.08895111083984</v>
+        <v>44.08895492553711</v>
       </c>
       <c r="C125" t="n">
         <v>4.984799861907959</v>
@@ -8532,7 +8532,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>45.67800140380859</v>
+        <v>45.67799758911133</v>
       </c>
       <c r="C126" t="n">
         <v>4.992400169372559</v>
@@ -8574,7 +8574,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>44.21118545532227</v>
+        <v>44.21118927001953</v>
       </c>
       <c r="C128" t="n">
         <v>5.00629997253418</v>
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>44.82235717773438</v>
+        <v>44.82235336303711</v>
       </c>
       <c r="C129" t="n">
         <v>5.007999897003174</v>
@@ -11126,6 +11126,27 @@
       </c>
       <c r="E249">
         <f>LN(D249/D248)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>57.90000152587891</v>
+      </c>
+      <c r="C250" t="n">
+        <v>5.025800228118896</v>
+      </c>
+      <c r="D250">
+        <f>B250/C250</f>
+        <v/>
+      </c>
+      <c r="E250">
+        <f>LN(D250/D249)</f>
         <v/>
       </c>
     </row>
@@ -11192,11 +11213,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>380.7900085449219</v>
+        <v>387.3900146484375</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -11211,18 +11232,18 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D252/D57-1)*100</f>
+        <f>(D252/D56-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>387.3900146484375</v>
+        <v>396.4500122070312</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -11248,11 +11269,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>396.4500122070312</v>
+        <v>388.989990234375</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -11278,11 +11299,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>388.989990234375</v>
+        <v>403.1499938964844</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -11308,11 +11329,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>403.1499938964844</v>
+        <v>377.239990234375</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -11329,11 +11350,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>377.239990234375</v>
+        <v>377.2799987792969</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -11358,11 +11379,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>377.2799987792969</v>
+        <v>378.7900085449219</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -11387,11 +11408,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>378.7900085449219</v>
+        <v>377.5199890136719</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -11416,11 +11437,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>377.5199890136719</v>
+        <v>367.010009765625</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -11437,11 +11458,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>367.010009765625</v>
+        <v>364.3800048828125</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -11456,18 +11477,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 19:56 UTC</t>
+          <t>Snapshot as of 2026-10-14 20:00 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>364.3800048828125</v>
+        <v>363</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -11484,11 +11505,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>363</v>
+        <v>370.1300048828125</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -11505,11 +11526,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>370.1300048828125</v>
+        <v>368.1199951171875</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -11526,11 +11547,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>368.1199951171875</v>
+        <v>368.7799987792969</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -11547,11 +11568,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>368.7799987792969</v>
+        <v>362.3200073242188</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -11568,11 +11589,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>362.3200073242188</v>
+        <v>366.510009765625</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -11589,11 +11610,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>366.510009765625</v>
+        <v>366.0700073242188</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -11610,11 +11631,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>366.0700073242188</v>
+        <v>368.3099975585938</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -11631,11 +11652,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>368.3099975585938</v>
+        <v>378.3800048828125</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -11652,11 +11673,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>378.3800048828125</v>
+        <v>379.8699951171875</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -11673,11 +11694,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>379.8699951171875</v>
+        <v>385.989990234375</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -11694,11 +11715,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>385.989990234375</v>
+        <v>382.8699951171875</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -11715,11 +11736,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>382.8699951171875</v>
+        <v>375.9599914550781</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -11736,11 +11757,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>375.9599914550781</v>
+        <v>371.6499938964844</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -11757,11 +11778,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>371.6499938964844</v>
+        <v>374.3500061035156</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -11778,11 +11799,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>374.3500061035156</v>
+        <v>374.9599914550781</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -11799,11 +11820,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>374.9599914550781</v>
+        <v>374.8500061035156</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -11820,11 +11841,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>374.8500061035156</v>
+        <v>374.2699890136719</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -11841,11 +11862,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>374.2699890136719</v>
+        <v>380.2000122070312</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -11862,11 +11883,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>380.2000122070312</v>
+        <v>380.0799865722656</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -11883,11 +11904,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>380.0799865722656</v>
+        <v>383.1199951171875</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -11904,11 +11925,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>383.1199951171875</v>
+        <v>387.8800048828125</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -11925,11 +11946,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>387.8800048828125</v>
+        <v>389.75</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -11946,11 +11967,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>389.75</v>
+        <v>387.239990234375</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -11967,11 +11988,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>387.239990234375</v>
+        <v>386.8800048828125</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -11988,11 +12009,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>386.8800048828125</v>
+        <v>387.1300048828125</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -12009,11 +12030,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>387.1300048828125</v>
+        <v>386.4400024414062</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -12030,11 +12051,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>386.4400024414062</v>
+        <v>385.4200134277344</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -12051,11 +12072,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>385.4200134277344</v>
+        <v>387.3999938964844</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -12072,11 +12093,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>387.3999938964844</v>
+        <v>389.0499877929688</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -12093,11 +12114,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>389.0499877929688</v>
+        <v>393.239990234375</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -12114,11 +12135,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>393.239990234375</v>
+        <v>395.4400024414062</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -12135,11 +12156,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>395.4400024414062</v>
+        <v>395.7999877929688</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -12156,11 +12177,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>395.7999877929688</v>
+        <v>395.8900146484375</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -12177,11 +12198,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>395.8900146484375</v>
+        <v>399.2900085449219</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -12198,11 +12219,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>399.2900085449219</v>
+        <v>398.5700073242188</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -12219,11 +12240,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>398.5700073242188</v>
+        <v>399.0199890136719</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -12240,11 +12261,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>399.0199890136719</v>
+        <v>408.2300109863281</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -12261,11 +12282,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>408.2300109863281</v>
+        <v>413.6400146484375</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -12282,11 +12303,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>413.6400146484375</v>
+        <v>411.9299926757812</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -12303,11 +12324,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>411.9299926757812</v>
+        <v>416.739990234375</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -12324,11 +12345,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>416.739990234375</v>
+        <v>398.6000061035156</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -12345,11 +12366,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>398.6000061035156</v>
+        <v>398.8900146484375</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -12366,11 +12387,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>398.8900146484375</v>
+        <v>396.3099975585938</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -12387,11 +12408,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>396.3099975585938</v>
+        <v>398.2799987792969</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -12408,11 +12429,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>398.2799987792969</v>
+        <v>408.760009765625</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -12429,11 +12450,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>408.760009765625</v>
+        <v>413.1799926757812</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -12450,11 +12471,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>413.1799926757812</v>
+        <v>409.2300109863281</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -12471,11 +12492,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>409.2300109863281</v>
+        <v>411.489990234375</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -12492,11 +12513,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>411.489990234375</v>
+        <v>414.4700012207031</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -12513,11 +12534,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>414.4700012207031</v>
+        <v>422.2300109863281</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -12534,11 +12555,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>422.2300109863281</v>
+        <v>421.6300048828125</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -12555,11 +12576,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>421.6300048828125</v>
+        <v>425.9400024414062</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -12576,11 +12597,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>425.9400024414062</v>
+        <v>423.3299865722656</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -12597,11 +12618,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>423.3299865722656</v>
+        <v>421.2900085449219</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -12618,11 +12639,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>421.2900085449219</v>
+        <v>437.2300109863281</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -12639,11 +12660,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>437.2300109863281</v>
+        <v>443.6000061035156</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -12660,11 +12681,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>443.6000061035156</v>
+        <v>451.7900085449219</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -12681,11 +12702,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>451.7900085449219</v>
+        <v>458</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -12702,11 +12723,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>458</v>
+        <v>464.7000122070312</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -12723,11 +12744,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>464.7000122070312</v>
+        <v>476.1000061035156</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
@@ -12744,11 +12765,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>476.1000061035156</v>
+        <v>494.5599975585938</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
@@ -12765,11 +12786,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>494.5599975585938</v>
+        <v>495.8999938964844</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
@@ -12786,11 +12807,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>495.8999938964844</v>
+        <v>444.9500122070312</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -12807,11 +12828,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>444.9500122070312</v>
+        <v>427.1300048828125</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
@@ -12828,11 +12849,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>427.1300048828125</v>
+        <v>454.2900085449219</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -12849,11 +12870,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>454.2900085449219</v>
+        <v>453.9700012207031</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -12870,11 +12891,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>453.9700012207031</v>
+        <v>441.8800048828125</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -12891,11 +12912,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>441.8800048828125</v>
+        <v>455.4599914550781</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -12912,11 +12933,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>455.4599914550781</v>
+        <v>467.0299987792969</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -12933,11 +12954,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>467.0299987792969</v>
+        <v>462.3999938964844</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -12954,11 +12975,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>462.3999938964844</v>
+        <v>467.6300048828125</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -12975,11 +12996,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>467.6300048828125</v>
+        <v>451.3900146484375</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
@@ -12996,11 +13017,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>451.3900146484375</v>
+        <v>462.6199951171875</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -13017,11 +13038,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>462.6199951171875</v>
+        <v>448.2000122070312</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -13038,11 +13059,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>448.2000122070312</v>
+        <v>458.2799987792969</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
@@ -13059,11 +13080,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>458.2799987792969</v>
+        <v>459.5599975585938</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -13080,11 +13101,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>459.5599975585938</v>
+        <v>468.6199951171875</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
@@ -13101,11 +13122,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>468.6199951171875</v>
+        <v>481.2799987792969</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -13122,11 +13143,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>481.2799987792969</v>
+        <v>474.6099853515625</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -13143,11 +13164,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>474.6099853515625</v>
+        <v>473.4200134277344</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -13164,11 +13185,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>473.4200134277344</v>
+        <v>477.4800109863281</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -13185,11 +13206,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>477.4800109863281</v>
+        <v>483.75</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -13206,11 +13227,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>483.75</v>
+        <v>490</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
@@ -13227,11 +13248,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>490</v>
+        <v>468.1400146484375</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -13248,11 +13269,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>468.1400146484375</v>
+        <v>471.7999877929688</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -13269,11 +13290,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>471.7999877929688</v>
+        <v>466.1300048828125</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
@@ -13290,11 +13311,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>466.1300048828125</v>
+        <v>473.510009765625</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
@@ -13311,11 +13332,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>473.510009765625</v>
+        <v>472.5299987792969</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -13332,11 +13353,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>472.5299987792969</v>
+        <v>477.8599853515625</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -13353,11 +13374,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>477.8599853515625</v>
+        <v>476.239990234375</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
@@ -13374,11 +13395,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>476.239990234375</v>
+        <v>466.8800048828125</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -13395,11 +13416,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>466.8800048828125</v>
+        <v>460.8399963378906</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
@@ -13416,11 +13437,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>460.8399963378906</v>
+        <v>460.4299926757812</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
@@ -13437,11 +13458,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>460.4299926757812</v>
+        <v>459.2699890136719</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
@@ -13458,11 +13479,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>459.2699890136719</v>
+        <v>444.739990234375</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -13479,11 +13500,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>444.739990234375</v>
+        <v>426.4100036621094</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
@@ -13500,11 +13521,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>426.4100036621094</v>
+        <v>413.3800048828125</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
@@ -13521,11 +13542,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>413.3800048828125</v>
+        <v>404.0400085449219</v>
       </c>
       <c r="C110" t="n">
         <v>1</v>
@@ -13542,11 +13563,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>404.0400085449219</v>
+        <v>404.1300048828125</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
@@ -13563,11 +13584,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>404.1300048828125</v>
+        <v>416.2900085449219</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
@@ -13584,11 +13605,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>416.2900085449219</v>
+        <v>400.6400146484375</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
@@ -13605,11 +13626,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>400.6400146484375</v>
+        <v>414.7000122070312</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -13626,11 +13647,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>414.7000122070312</v>
+        <v>414.5799865722656</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -13647,11 +13668,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>414.5799865722656</v>
+        <v>430.2900085449219</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
@@ -13668,11 +13689,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>430.2900085449219</v>
+        <v>437.8200073242188</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
@@ -13689,11 +13710,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>437.8200073242188</v>
+        <v>429.4100036621094</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
@@ -13710,11 +13731,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>429.4100036621094</v>
+        <v>427.6499938964844</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -13731,11 +13752,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>427.6499938964844</v>
+        <v>431.8099975585938</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -13752,11 +13773,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>431.8099975585938</v>
+        <v>434.5299987792969</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
@@ -13773,11 +13794,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>434.5299987792969</v>
+        <v>437.9100036621094</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
@@ -13794,11 +13815,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>437.9100036621094</v>
+        <v>437.1300048828125</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -13815,11 +13836,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>437.1300048828125</v>
+        <v>435.3599853515625</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -13836,11 +13857,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>435.3599853515625</v>
+        <v>445.0899963378906</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -13857,11 +13878,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>445.0899963378906</v>
+        <v>440.4599914550781</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -13878,11 +13899,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>440.4599914550781</v>
+        <v>440.0799865722656</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -13899,11 +13920,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>440.0799865722656</v>
+        <v>445.9299926757812</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
@@ -13920,11 +13941,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>445.9299926757812</v>
+        <v>442.0899963378906</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -13941,11 +13962,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>442.0899963378906</v>
+        <v>429.5700073242188</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -13962,11 +13983,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>429.5700073242188</v>
+        <v>435.260009765625</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -13983,11 +14004,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>435.260009765625</v>
+        <v>431.0400085449219</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
@@ -14004,11 +14025,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>431.0400085449219</v>
+        <v>433.25</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -14025,11 +14046,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>433.25</v>
+        <v>429.8900146484375</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
@@ -14046,11 +14067,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>429.8900146484375</v>
+        <v>421.9100036621094</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
@@ -14067,11 +14088,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>421.9100036621094</v>
+        <v>417.4100036621094</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -14088,11 +14109,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>417.4100036621094</v>
+        <v>423.6600036621094</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
@@ -14109,11 +14130,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>423.6600036621094</v>
+        <v>423.1799926757812</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
@@ -14130,11 +14151,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>423.1799926757812</v>
+        <v>414.7099914550781</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
@@ -14151,11 +14172,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>414.7099914550781</v>
+        <v>418.2699890136719</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -14172,11 +14193,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>418.2699890136719</v>
+        <v>430.9599914550781</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
@@ -14193,11 +14214,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>430.9599914550781</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
@@ -14214,11 +14235,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>431.6799926757812</v>
+        <v>433.7699890136719</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -14235,11 +14256,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>433.7699890136719</v>
+        <v>434.6499938964844</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
@@ -14256,11 +14277,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>434.6499938964844</v>
+        <v>432.9299926757812</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
@@ -14277,11 +14298,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>432.9299926757812</v>
+        <v>430.5</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
@@ -14298,11 +14319,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>430.5</v>
+        <v>427.2099914550781</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
@@ -14319,11 +14340,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>427.2099914550781</v>
+        <v>417.2900085449219</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
@@ -14340,11 +14361,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>417.2900085449219</v>
+        <v>418.4299926757812</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
@@ -14361,11 +14382,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>418.4299926757812</v>
+        <v>411.5</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -14382,11 +14403,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>411.5</v>
+        <v>417.3999938964844</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -14403,11 +14424,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>417.3999938964844</v>
+        <v>416.989990234375</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -14424,11 +14445,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>416.989990234375</v>
+        <v>413.8200073242188</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
@@ -14445,11 +14466,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>413.8200073242188</v>
+        <v>414</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
@@ -14466,11 +14487,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>414</v>
+        <v>408.489990234375</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
@@ -14487,11 +14508,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>408.489990234375</v>
+        <v>412.7699890136719</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
@@ -14508,11 +14529,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>412.7699890136719</v>
+        <v>417.1199951171875</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -14529,11 +14550,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>417.1199951171875</v>
+        <v>411.260009765625</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -14550,11 +14571,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>411.260009765625</v>
+        <v>411.9500122070312</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
@@ -14571,11 +14592,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>411.9500122070312</v>
+        <v>407.8699951171875</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
@@ -14592,11 +14613,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>407.8699951171875</v>
+        <v>411.2699890136719</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -14613,11 +14634,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>411.2699890136719</v>
+        <v>396.239990234375</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -14634,11 +14655,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>396.239990234375</v>
+        <v>397.2699890136719</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -14655,11 +14676,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>397.2699890136719</v>
+        <v>390.7799987792969</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
@@ -14676,11 +14697,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>390.7799987792969</v>
+        <v>374.5799865722656</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -14697,11 +14718,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>374.5799865722656</v>
+        <v>386.3200073242188</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
@@ -14718,11 +14739,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>386.3200073242188</v>
+        <v>386.5400085449219</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
@@ -14739,11 +14760,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>386.5400085449219</v>
+        <v>396.5499877929688</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
@@ -14760,11 +14781,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>396.5499877929688</v>
+        <v>397.6300048828125</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
@@ -14781,11 +14802,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>397.6300048828125</v>
+        <v>388.6000061035156</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
@@ -14802,11 +14823,11 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>388.6000061035156</v>
+        <v>387.1199951171875</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -14823,11 +14844,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>387.1199951171875</v>
+        <v>384.5899963378906</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
@@ -14844,11 +14865,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>384.5899963378906</v>
+        <v>377.3200073242188</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
@@ -14865,11 +14886,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>377.3200073242188</v>
+        <v>365.9200134277344</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
@@ -14886,11 +14907,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>365.9200134277344</v>
+        <v>369.4599914550781</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
@@ -14907,11 +14928,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>369.4599914550781</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
@@ -14928,11 +14949,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>373.6300048828125</v>
+        <v>368.5799865722656</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
@@ -14949,11 +14970,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>368.5799865722656</v>
+        <v>368.3800048828125</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
@@ -14970,11 +14991,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>368.3800048828125</v>
+        <v>370.6000061035156</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
@@ -14991,11 +15012,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>370.6000061035156</v>
+        <v>378.1300048828125</v>
       </c>
       <c r="C180" t="n">
         <v>1</v>
@@ -15012,11 +15033,11 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>378.1300048828125</v>
+        <v>382.1300048828125</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
@@ -15033,11 +15054,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>382.1300048828125</v>
+        <v>377.489990234375</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -15054,11 +15075,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>377.489990234375</v>
+        <v>374.4500122070312</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
@@ -15075,11 +15096,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>374.4500122070312</v>
+        <v>378.1799926757812</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
@@ -15096,11 +15117,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>378.1799926757812</v>
+        <v>377.010009765625</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -15117,11 +15138,11 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>377.010009765625</v>
+        <v>367.1300048828125</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
@@ -15138,11 +15159,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>367.1300048828125</v>
+        <v>372.1499938964844</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
@@ -15159,11 +15180,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>372.1499938964844</v>
+        <v>372.3500061035156</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -15180,11 +15201,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>372.3500061035156</v>
+        <v>364.9599914550781</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
@@ -15201,11 +15222,11 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>364.9599914550781</v>
+        <v>368.4100036621094</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -15222,11 +15243,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>368.4100036621094</v>
+        <v>367.6000061035156</v>
       </c>
       <c r="C191" t="n">
         <v>1</v>
@@ -15243,11 +15264,11 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>367.6000061035156</v>
+        <v>374.8099975585938</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
@@ -15264,11 +15285,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>374.8099975585938</v>
+        <v>379.1199951171875</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
@@ -15285,11 +15306,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>379.1199951171875</v>
+        <v>371.5199890136719</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -15306,11 +15327,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>371.5199890136719</v>
+        <v>371.8999938964844</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
@@ -15327,11 +15348,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>371.8999938964844</v>
+        <v>374.6300048828125</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
@@ -15348,11 +15369,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>374.6300048828125</v>
+        <v>369.3699951171875</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -15369,11 +15390,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>369.3699951171875</v>
+        <v>371.0799865722656</v>
       </c>
       <c r="C198" t="n">
         <v>1</v>
@@ -15390,11 +15411,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>371.0799865722656</v>
+        <v>377.1600036621094</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
@@ -15411,11 +15432,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>377.1600036621094</v>
+        <v>371.5400085449219</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
@@ -15432,11 +15453,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>371.5400085449219</v>
+        <v>371.7099914550781</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
@@ -15453,11 +15474,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>371.7099914550781</v>
+        <v>374.1600036621094</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
@@ -15474,11 +15495,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>374.1600036621094</v>
+        <v>389.6400146484375</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
@@ -15495,11 +15516,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>389.6400146484375</v>
+        <v>389.6700134277344</v>
       </c>
       <c r="C204" t="n">
         <v>1</v>
@@ -15516,11 +15537,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>389.6700134277344</v>
+        <v>398.4700012207031</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
@@ -15537,11 +15558,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>398.4700012207031</v>
+        <v>402.5400085449219</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
@@ -15558,11 +15579,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>402.5400085449219</v>
+        <v>400.9599914550781</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
@@ -15579,11 +15600,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>400.9599914550781</v>
+        <v>404.9200134277344</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
@@ -15600,11 +15621,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>404.9200134277344</v>
+        <v>398.9599914550781</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
@@ -15621,11 +15642,11 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>398.9599914550781</v>
+        <v>401.4800109863281</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
@@ -15642,11 +15663,11 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>401.4800109863281</v>
+        <v>405.489990234375</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
@@ -15663,11 +15684,11 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>405.489990234375</v>
+        <v>398.5499877929688</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
@@ -15684,11 +15705,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>398.5499877929688</v>
+        <v>413.8399963378906</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
@@ -15705,11 +15726,11 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>413.8399963378906</v>
+        <v>415.260009765625</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
@@ -15726,11 +15747,11 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>415.260009765625</v>
+        <v>423.3599853515625</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
@@ -15747,11 +15768,11 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>423.3599853515625</v>
+        <v>426.6900024414062</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
@@ -15768,11 +15789,11 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>426.6900024414062</v>
+        <v>428.0700073242188</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
@@ -15789,11 +15810,11 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>428.0700073242188</v>
+        <v>421.3200073242188</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
@@ -15810,11 +15831,11 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>421.3200073242188</v>
+        <v>422.6000061035156</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
@@ -15831,11 +15852,11 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>422.6000061035156</v>
+        <v>408.8900146484375</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
@@ -15852,11 +15873,11 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>408.8900146484375</v>
+        <v>408.4200134277344</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
@@ -15873,11 +15894,11 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>408.4200134277344</v>
+        <v>396.75</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
@@ -15894,11 +15915,11 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>396.75</v>
+        <v>402.7799987792969</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
@@ -15915,11 +15936,11 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>402.7799987792969</v>
+        <v>410.2200012207031</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
@@ -15936,11 +15957,11 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>410.2200012207031</v>
+        <v>406.7699890136719</v>
       </c>
       <c r="C225" t="n">
         <v>1</v>
@@ -15957,11 +15978,11 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>406.7699890136719</v>
+        <v>399.7200012207031</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
@@ -15978,11 +15999,11 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>399.7200012207031</v>
+        <v>403.3500061035156</v>
       </c>
       <c r="C227" t="n">
         <v>1</v>
@@ -15999,11 +16020,11 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>403.3500061035156</v>
+        <v>396.3599853515625</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
@@ -16020,11 +16041,11 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>396.3599853515625</v>
+        <v>398.7699890136719</v>
       </c>
       <c r="C229" t="n">
         <v>1</v>
@@ -16041,11 +16062,11 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>398.7699890136719</v>
+        <v>392.8399963378906</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
@@ -16062,11 +16083,11 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>392.8399963378906</v>
+        <v>394.1499938964844</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
@@ -16083,11 +16104,11 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>394.1499938964844</v>
+        <v>391.739990234375</v>
       </c>
       <c r="C232" t="n">
         <v>1</v>
@@ -16104,11 +16125,11 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>391.739990234375</v>
+        <v>398.3599853515625</v>
       </c>
       <c r="C233" t="n">
         <v>1</v>
@@ -16125,11 +16146,11 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>398.3599853515625</v>
+        <v>401.1700134277344</v>
       </c>
       <c r="C234" t="n">
         <v>1</v>
@@ -16146,11 +16167,11 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>401.1700134277344</v>
+        <v>398.3800048828125</v>
       </c>
       <c r="C235" t="n">
         <v>1</v>
@@ -16167,11 +16188,11 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>398.3800048828125</v>
+        <v>400.0700073242188</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
@@ -16188,11 +16209,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>400.0700073242188</v>
+        <v>392.8800048828125</v>
       </c>
       <c r="C237" t="n">
         <v>1</v>
@@ -16209,11 +16230,11 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>392.8800048828125</v>
+        <v>391.6900024414062</v>
       </c>
       <c r="C238" t="n">
         <v>1</v>
@@ -16230,11 +16251,11 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>391.6900024414062</v>
+        <v>393.4100036621094</v>
       </c>
       <c r="C239" t="n">
         <v>1</v>
@@ -16251,11 +16272,11 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>393.4100036621094</v>
+        <v>377.9100036621094</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
@@ -16272,11 +16293,11 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>377.9100036621094</v>
+        <v>382.8900146484375</v>
       </c>
       <c r="C241" t="n">
         <v>1</v>
@@ -16293,11 +16314,11 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>382.8900146484375</v>
+        <v>380.8399963378906</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
@@ -16314,11 +16335,11 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>380.8399963378906</v>
+        <v>382.760009765625</v>
       </c>
       <c r="C243" t="n">
         <v>1</v>
@@ -16335,11 +16356,11 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>382.760009765625</v>
+        <v>380.1400146484375</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
@@ -16356,11 +16377,11 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>380.1400146484375</v>
+        <v>379.5499877929688</v>
       </c>
       <c r="C245" t="n">
         <v>1</v>
@@ -16377,11 +16398,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>379.5499877929688</v>
+        <v>382.2699890136719</v>
       </c>
       <c r="C246" t="n">
         <v>1</v>
@@ -16398,11 +16419,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>382.2699890136719</v>
+        <v>375.8800048828125</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
@@ -16419,11 +16440,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>375.8800048828125</v>
+        <v>378.6199951171875</v>
       </c>
       <c r="C248" t="n">
         <v>1</v>
@@ -16440,11 +16461,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>378.6199951171875</v>
+        <v>384.5799865722656</v>
       </c>
       <c r="C249" t="n">
         <v>1</v>
@@ -16461,11 +16482,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>384.5799865722656</v>
+        <v>382.1499938964844</v>
       </c>
       <c r="C250" t="n">
         <v>1</v>
@@ -16482,11 +16503,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>382.1499938964844</v>
+        <v>381.6700134277344</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>
@@ -16503,11 +16524,11 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>381.6700134277344</v>
+        <v>375.9349975585938</v>
       </c>
       <c r="C252" t="n">
         <v>1</v>

--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D252/D56-1)*100</f>
+        <f>(D251/D56-1)*100</f>
         <v/>
       </c>
     </row>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="H3">
-        <f>(D252/D2-1)*100</f>
+        <f>(D251/D2-1)*100</f>
         <v/>
       </c>
     </row>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="H4">
-        <f>(COUNT(D2:D252)-1)/((DATEVALUE(A252)-DATEVALUE(A2))/365.25)</f>
+        <f>(COUNT(D2:D251)-1)/((DATEVALUE(A251)-DATEVALUE(A2))/365.25)</f>
         <v/>
       </c>
     </row>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="H5">
-        <f>STDEV.S(E3:E252)*SQRT(H4)*100</f>
+        <f>STDEV.S(E3:E251)*SQRT(H4)*100</f>
         <v/>
       </c>
     </row>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>170.9670201816798</v>
+        <v>155.4347339687654</v>
       </c>
     </row>
     <row r="8">
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>177.6514283094135</v>
+        <v>139.2372170997485</v>
       </c>
     </row>
     <row r="9">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>67.3646158343856</v>
+        <v>67.1049283050386</v>
       </c>
     </row>
     <row r="10">
@@ -735,7 +735,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 20:00 UTC</t>
+          <t>Snapshot as of 2026-10-15 00:32 UTC</t>
         </is>
       </c>
     </row>
@@ -5776,27 +5776,6 @@
       </c>
       <c r="E251">
         <f>LN(D251/D250)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>570.72998046875</v>
-      </c>
-      <c r="C252" t="n">
-        <v>1</v>
-      </c>
-      <c r="D252">
-        <f>B252/C252</f>
-        <v/>
-      </c>
-      <c r="E252">
-        <f>LN(D252/D251)</f>
         <v/>
       </c>
     </row>
@@ -5870,7 +5849,7 @@
         <v>27.36254501342773</v>
       </c>
       <c r="C2" t="n">
-        <v>5.464099884033203</v>
+        <v>5.481500148773193</v>
       </c>
       <c r="D2">
         <f>B2/C2</f>
@@ -5923,7 +5902,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.84300422668457</v>
+        <v>26.84300231933594</v>
       </c>
       <c r="C4" t="n">
         <v>5.449299812316895</v>
@@ -5953,7 +5932,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.09821701049805</v>
+        <v>27.09821891784668</v>
       </c>
       <c r="C5" t="n">
         <v>5.440814971923828</v>
@@ -6023,7 +6002,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>117.8907417131136</v>
+        <v>120.9119169876084</v>
       </c>
     </row>
     <row r="8">
@@ -6033,7 +6012,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.20759391784668</v>
+        <v>27.20759582519531</v>
       </c>
       <c r="C8" t="n">
         <v>5.38670015335083</v>
@@ -6052,7 +6031,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>127.7341554127893</v>
+        <v>131.6270720105725</v>
       </c>
     </row>
     <row r="9">
@@ -6081,7 +6060,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30.45734581100089</v>
+        <v>30.41854661511665</v>
       </c>
     </row>
     <row r="10">
@@ -6112,7 +6091,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.34431457519531</v>
+        <v>27.34431648254395</v>
       </c>
       <c r="C11" t="n">
         <v>5.388299942016602</v>
@@ -6127,7 +6106,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 20:00 UTC</t>
+          <t>Snapshot as of 2026-10-15 00:32 UTC</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6117,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27.33520126342773</v>
+        <v>27.3351993560791</v>
       </c>
       <c r="C12" t="n">
         <v>5.373300075531006</v>
@@ -6180,7 +6159,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>27.24405097961426</v>
+        <v>27.24405288696289</v>
       </c>
       <c r="C14" t="n">
         <v>5.357800006866455</v>
@@ -6264,7 +6243,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28.11907196044922</v>
+        <v>28.11907386779785</v>
       </c>
       <c r="C18" t="n">
         <v>5.395899772644043</v>
@@ -6285,7 +6264,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28.2649097442627</v>
+        <v>28.26490783691406</v>
       </c>
       <c r="C19" t="n">
         <v>5.35860013961792</v>
@@ -6306,7 +6285,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29.33133506774902</v>
+        <v>29.33133697509766</v>
       </c>
       <c r="C20" t="n">
         <v>5.349500179290771</v>
@@ -6327,7 +6306,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29.49540519714355</v>
+        <v>29.49540328979492</v>
       </c>
       <c r="C21" t="n">
         <v>5.330900192260742</v>
@@ -6390,7 +6369,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29.6138973236084</v>
+        <v>29.61389541625977</v>
       </c>
       <c r="C24" t="n">
         <v>5.291299819946289</v>
@@ -6411,7 +6390,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.8053035736084</v>
+        <v>29.80530548095703</v>
       </c>
       <c r="C25" t="n">
         <v>5.296500205993652</v>
@@ -6432,7 +6411,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.9693717956543</v>
+        <v>29.96936988830566</v>
       </c>
       <c r="C26" t="n">
         <v>5.295599937438965</v>
@@ -6453,7 +6432,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>30.06963348388672</v>
+        <v>30.06963539123535</v>
       </c>
       <c r="C27" t="n">
         <v>5.329500198364258</v>
@@ -6474,7 +6453,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29.91468238830566</v>
+        <v>29.9146842956543</v>
       </c>
       <c r="C28" t="n">
         <v>5.321499824523926</v>
@@ -6495,7 +6474,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.68681144714355</v>
+        <v>29.68681335449219</v>
       </c>
       <c r="C29" t="n">
         <v>5.332300186157227</v>
@@ -6558,7 +6537,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.37691307067871</v>
+        <v>29.37691116333008</v>
       </c>
       <c r="C32" t="n">
         <v>5.37939977645874</v>
@@ -6579,7 +6558,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.53186416625977</v>
+        <v>29.53186225891113</v>
       </c>
       <c r="C33" t="n">
         <v>5.33080005645752</v>
@@ -6621,7 +6600,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29.03055000305176</v>
+        <v>29.03055191040039</v>
       </c>
       <c r="C35" t="n">
         <v>5.335400104522705</v>
@@ -6642,7 +6621,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29.23107147216797</v>
+        <v>29.23107528686523</v>
       </c>
       <c r="C36" t="n">
         <v>5.355800151824951</v>
@@ -6663,7 +6642,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29.4498291015625</v>
+        <v>29.44983100891113</v>
       </c>
       <c r="C37" t="n">
         <v>5.326300144195557</v>
@@ -6684,7 +6663,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29.6412410736084</v>
+        <v>29.64123916625977</v>
       </c>
       <c r="C38" t="n">
         <v>5.306099891662598</v>
@@ -6705,7 +6684,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.59304237365723</v>
+        <v>28.59304046630859</v>
       </c>
       <c r="C39" t="n">
         <v>5.309299945831299</v>
@@ -6768,7 +6747,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29.11258316040039</v>
+        <v>29.11258125305176</v>
       </c>
       <c r="C42" t="n">
         <v>5.43149995803833</v>
@@ -6789,7 +6768,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.6294994354248</v>
+        <v>28.62950134277344</v>
       </c>
       <c r="C43" t="n">
         <v>5.469799995422363</v>
@@ -6810,7 +6789,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28.79356575012207</v>
+        <v>28.79356384277344</v>
       </c>
       <c r="C44" t="n">
         <v>5.405499935150146</v>
@@ -6831,7 +6810,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.89382743835449</v>
+        <v>28.89382934570312</v>
       </c>
       <c r="C45" t="n">
         <v>5.418200016021729</v>
@@ -6852,7 +6831,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28.01880836486816</v>
+        <v>28.0188102722168</v>
       </c>
       <c r="C46" t="n">
         <v>5.413400173187256</v>
@@ -6873,7 +6852,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>28.32871437072754</v>
+        <v>28.32871246337891</v>
       </c>
       <c r="C47" t="n">
         <v>5.507500171661377</v>
@@ -6915,7 +6894,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28.2649097442627</v>
+        <v>28.26490783691406</v>
       </c>
       <c r="C49" t="n">
         <v>5.521299839019775</v>
@@ -6936,7 +6915,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.34694290161133</v>
+        <v>28.3469409942627</v>
       </c>
       <c r="C50" t="n">
         <v>5.53980016708374</v>
@@ -7020,7 +6999,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>28.97891998291016</v>
+        <v>28.97891807556152</v>
       </c>
       <c r="C54" t="n">
         <v>5.569099903106689</v>
@@ -7041,7 +7020,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28.87549018859863</v>
+        <v>28.87548828125</v>
       </c>
       <c r="C55" t="n">
         <v>5.517000198364258</v>
@@ -7083,7 +7062,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>27.86940765380859</v>
+        <v>27.86940574645996</v>
       </c>
       <c r="C57" t="n">
         <v>5.40749979019165</v>
@@ -7146,7 +7125,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28.48998069763184</v>
+        <v>28.48998260498047</v>
       </c>
       <c r="C60" t="n">
         <v>5.386600017547607</v>
@@ -7167,7 +7146,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28.5463981628418</v>
+        <v>28.54639625549316</v>
       </c>
       <c r="C61" t="n">
         <v>5.370299816131592</v>
@@ -7251,7 +7230,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>30.12604141235352</v>
+        <v>30.12603950500488</v>
       </c>
       <c r="C65" t="n">
         <v>5.367899894714355</v>
@@ -7272,7 +7251,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>30.24827194213867</v>
+        <v>30.24827003479004</v>
       </c>
       <c r="C66" t="n">
         <v>5.367700099945068</v>
@@ -7314,7 +7293,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>31.43300819396973</v>
+        <v>31.43300437927246</v>
       </c>
       <c r="C68" t="n">
         <v>5.374300003051758</v>
@@ -7440,7 +7419,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>35.44793319702148</v>
+        <v>35.44792938232422</v>
       </c>
       <c r="C74" t="n">
         <v>5.197100162506104</v>
@@ -7482,7 +7461,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>35.01541137695312</v>
+        <v>35.01540756225586</v>
       </c>
       <c r="C76" t="n">
         <v>5.255000114440918</v>
@@ -7524,7 +7503,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>35.27868270874023</v>
+        <v>35.2786865234375</v>
       </c>
       <c r="C78" t="n">
         <v>5.237500190734863</v>
@@ -7587,7 +7566,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.09063339233398</v>
+        <v>35.09062957763672</v>
       </c>
       <c r="C81" t="n">
         <v>5.21589994430542</v>
@@ -7608,7 +7587,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.11883926391602</v>
+        <v>35.11883544921875</v>
       </c>
       <c r="C82" t="n">
         <v>5.19159984588623</v>
@@ -7629,7 +7608,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>35.80523300170898</v>
+        <v>35.80522918701172</v>
       </c>
       <c r="C83" t="n">
         <v>5.196199893951416</v>
@@ -7671,7 +7650,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>34.68631744384766</v>
+        <v>34.68631362915039</v>
       </c>
       <c r="C85" t="n">
         <v>5.213900089263916</v>
@@ -7713,7 +7692,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>35.55136108398438</v>
+        <v>35.55135726928711</v>
       </c>
       <c r="C87" t="n">
         <v>5.234399795532227</v>
@@ -7776,7 +7755,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>37.20622634887695</v>
+        <v>37.20622253417969</v>
       </c>
       <c r="C90" t="n">
         <v>5.170899868011475</v>
@@ -7797,7 +7776,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37.20622634887695</v>
+        <v>37.20622253417969</v>
       </c>
       <c r="C91" t="n">
         <v>5.151999950408936</v>
@@ -7881,7 +7860,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>38.50378799438477</v>
+        <v>38.5037841796875</v>
       </c>
       <c r="C95" t="n">
         <v>5.170300006866455</v>
@@ -7923,7 +7902,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>38.25931930541992</v>
+        <v>38.25931549072266</v>
       </c>
       <c r="C97" t="n">
         <v>5.230100154876709</v>
@@ -7965,7 +7944,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>40.58177185058594</v>
+        <v>40.58176803588867</v>
       </c>
       <c r="C99" t="n">
         <v>5.243500232696533</v>
@@ -8028,7 +8007,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>42.31185913085938</v>
+        <v>42.31185150146484</v>
       </c>
       <c r="C102" t="n">
         <v>5.151400089263916</v>
@@ -8070,7 +8049,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>43.1204833984375</v>
+        <v>43.12047958374023</v>
       </c>
       <c r="C104" t="n">
         <v>5.329100131988525</v>
@@ -8091,7 +8070,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>43.60941696166992</v>
+        <v>43.60942077636719</v>
       </c>
       <c r="C105" t="n">
         <v>5.233399868011475</v>
@@ -8133,7 +8112,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>43.98552322387695</v>
+        <v>43.98551940917969</v>
       </c>
       <c r="C107" t="n">
         <v>5.262100219726562</v>
@@ -8154,7 +8133,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>42.94182586669922</v>
+        <v>42.94182968139648</v>
       </c>
       <c r="C108" t="n">
         <v>5.219900131225586</v>
@@ -8196,7 +8175,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>44.44625473022461</v>
+        <v>44.44625091552734</v>
       </c>
       <c r="C110" t="n">
         <v>5.232900142669678</v>
@@ -8238,7 +8217,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>45.15144729614258</v>
+        <v>45.15145111083984</v>
       </c>
       <c r="C112" t="n">
         <v>5.236800193786621</v>
@@ -8385,7 +8364,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>45.61217880249023</v>
+        <v>45.61217498779297</v>
       </c>
       <c r="C119" t="n">
         <v>5.138299942016602</v>
@@ -8406,7 +8385,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>43.82567977905273</v>
+        <v>43.82567596435547</v>
       </c>
       <c r="C120" t="n">
         <v>5.150599956512451</v>
@@ -8490,7 +8469,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>45.01981353759766</v>
+        <v>45.01980972290039</v>
       </c>
       <c r="C124" t="n">
         <v>4.994400024414062</v>
@@ -8511,7 +8490,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>44.08895492553711</v>
+        <v>44.08895111083984</v>
       </c>
       <c r="C125" t="n">
         <v>4.984799861907959</v>
@@ -8532,7 +8511,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>45.67799758911133</v>
+        <v>45.67800140380859</v>
       </c>
       <c r="C126" t="n">
         <v>4.992400169372559</v>
@@ -8574,7 +8553,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>44.21118927001953</v>
+        <v>44.21118545532227</v>
       </c>
       <c r="C128" t="n">
         <v>5.00629997253418</v>
@@ -8595,7 +8574,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>44.82235336303711</v>
+        <v>44.82235717773438</v>
       </c>
       <c r="C129" t="n">
         <v>5.007999897003174</v>
@@ -11136,7 +11115,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>57.90000152587891</v>
+        <v>58.11000061035156</v>
       </c>
       <c r="C250" t="n">
         <v>5.025800228118896</v>
@@ -11161,7 +11140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11232,7 +11211,7 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D252/D56-1)*100</f>
+        <f>(D251/D56-1)*100</f>
         <v/>
       </c>
     </row>
@@ -11262,7 +11241,7 @@
         </is>
       </c>
       <c r="H3">
-        <f>(D252/D2-1)*100</f>
+        <f>(D251/D2-1)*100</f>
         <v/>
       </c>
     </row>
@@ -11292,7 +11271,7 @@
         </is>
       </c>
       <c r="H4">
-        <f>(COUNT(D2:D252)-1)/((DATEVALUE(A252)-DATEVALUE(A2))/365.25)</f>
+        <f>(COUNT(D2:D251)-1)/((DATEVALUE(A251)-DATEVALUE(A2))/365.25)</f>
         <v/>
       </c>
     </row>
@@ -11322,7 +11301,7 @@
         </is>
       </c>
       <c r="H5">
-        <f>STDEV.S(E3:E252)*SQRT(H4)*100</f>
+        <f>STDEV.S(E3:E251)*SQRT(H4)*100</f>
         <v/>
       </c>
     </row>
@@ -11373,7 +11352,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-4.170432861303595</v>
+        <v>-5.596565230491104</v>
       </c>
     </row>
     <row r="8">
@@ -11402,7 +11381,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.2310985057380696</v>
+        <v>-2.942770851080301</v>
       </c>
     </row>
     <row r="9">
@@ -11431,7 +11410,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>29.67800037722592</v>
+        <v>29.66543425274842</v>
       </c>
     </row>
     <row r="10">
@@ -11477,7 +11456,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-14 20:00 UTC</t>
+          <t>Snapshot as of 2026-10-15 00:32 UTC</t>
         </is>
       </c>
     </row>
@@ -16518,27 +16497,6 @@
       </c>
       <c r="E251">
         <f>LN(D251/D250)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="B252" t="n">
-        <v>375.9349975585938</v>
-      </c>
-      <c r="C252" t="n">
-        <v>1</v>
-      </c>
-      <c r="D252">
-        <f>B252/C252</f>
-        <v/>
-      </c>
-      <c r="E252">
-        <f>LN(D252/D251)</f>
         <v/>
       </c>
     </row>

--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -471,11 +471,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>240.5599975585938</v>
+        <v>238.0299987792969</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -490,18 +490,18 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D251/D53-1)*100</f>
+        <f>(D251/D52-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>238.0299987792969</v>
+        <v>230.2299957275391</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -527,11 +527,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>230.2299957275391</v>
+        <v>234.9900054931641</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -557,11 +557,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>234.9900054931641</v>
+        <v>252.9199981689453</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -587,11 +587,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>252.9199981689453</v>
+        <v>259.6700134277344</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -608,11 +608,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>259.6700134277344</v>
+        <v>258.010009765625</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -631,17 +631,17 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>140.7705732313062</v>
+        <v>139.2893900747304</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>258.010009765625</v>
+        <v>264.3299865722656</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -660,17 +660,17 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>123.6656135683405</v>
+        <v>124.6523547452002</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>264.3299865722656</v>
+        <v>254.8399963378906</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -689,17 +689,17 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>67.36156698957399</v>
+        <v>67.35392917849576</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>254.8399963378906</v>
+        <v>256.1199951171875</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -716,11 +716,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>256.1199951171875</v>
+        <v>259.6499938964844</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -735,18 +735,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-20 01:06 UTC</t>
+          <t>Snapshot as of 2026-10-21 00:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>259.6499938964844</v>
+        <v>250.0500030517578</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -763,11 +763,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>250.0500030517578</v>
+        <v>256.3299865722656</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -784,11 +784,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>256.3299865722656</v>
+        <v>237.6999969482422</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -805,11 +805,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>237.6999969482422</v>
+        <v>233.5399932861328</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -826,11 +826,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>233.5399932861328</v>
+        <v>243.9799957275391</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -847,11 +847,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>243.9799957275391</v>
+        <v>237.5200042724609</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -868,11 +868,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>237.5200042724609</v>
+        <v>258.8900146484375</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -889,11 +889,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>258.8900146484375</v>
+        <v>247.9600067138672</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -910,11 +910,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>247.9600067138672</v>
+        <v>246.8099975585938</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -931,11 +931,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>246.8099975585938</v>
+        <v>240.5200042724609</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -952,11 +952,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>240.5200042724609</v>
+        <v>230.2899932861328</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -973,11 +973,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>230.2899932861328</v>
+        <v>223.5500030517578</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -994,11 +994,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>223.5500030517578</v>
+        <v>206.0200042724609</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1015,11 +1015,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>206.0200042724609</v>
+        <v>203.7799987792969</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1036,11 +1036,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>203.7799987792969</v>
+        <v>215.0500030517578</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1057,11 +1057,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>215.0500030517578</v>
+        <v>206.1300048828125</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1078,11 +1078,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>206.1300048828125</v>
+        <v>214.2400054931641</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>214.2400054931641</v>
+        <v>217.5299987792969</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1120,11 +1120,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>217.5299987792969</v>
+        <v>219.7599945068359</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1141,11 +1141,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>219.7599945068359</v>
+        <v>215.2400054931641</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1162,11 +1162,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>215.2400054931641</v>
+        <v>217.6000061035156</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -1183,11 +1183,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>217.6000061035156</v>
+        <v>215.9799957275391</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1204,11 +1204,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>215.9799957275391</v>
+        <v>217.9700012207031</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -1225,11 +1225,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>217.9700012207031</v>
+        <v>221.1100006103516</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1246,11 +1246,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>221.1100006103516</v>
+        <v>221.6199951171875</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1267,11 +1267,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>221.6199951171875</v>
+        <v>221.4199981689453</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1288,11 +1288,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>221.4199981689453</v>
+        <v>221.4299926757812</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -1309,11 +1309,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>221.4299926757812</v>
+        <v>210.7799987792969</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -1330,11 +1330,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>210.7799987792969</v>
+        <v>207.5800018310547</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1351,11 +1351,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>207.5800018310547</v>
+        <v>209.1699981689453</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1372,11 +1372,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>209.1699981689453</v>
+        <v>198.1100006103516</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1393,11 +1393,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>198.1100006103516</v>
+        <v>201.0599975585938</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1414,11 +1414,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>201.0599975585938</v>
+        <v>213.4299926757812</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -1435,11 +1435,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>213.4299926757812</v>
+        <v>214.9499969482422</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1456,11 +1456,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>214.9499969482422</v>
+        <v>214.8999938964844</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1477,11 +1477,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>214.8999938964844</v>
+        <v>215.0399932861328</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1498,11 +1498,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>215.0399932861328</v>
+        <v>214.9900054931641</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -1519,11 +1519,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>214.9900054931641</v>
+        <v>215.6100006103516</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -1540,11 +1540,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>215.6100006103516</v>
+        <v>215.3399963378906</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -1561,11 +1561,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>215.3399963378906</v>
+        <v>214.1600036621094</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -1582,11 +1582,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>214.1600036621094</v>
+        <v>223.4700012207031</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -1603,11 +1603,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>223.4700012207031</v>
+        <v>221.0800018310547</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -1624,11 +1624,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>221.0800018310547</v>
+        <v>214.3500061035156</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -1645,11 +1645,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>214.3500061035156</v>
+        <v>210.0200042724609</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -1666,11 +1666,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>210.0200042724609</v>
+        <v>204.6799926757812</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -1687,11 +1687,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>204.6799926757812</v>
+        <v>203.1699981689453</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -1708,11 +1708,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>203.1699981689453</v>
+        <v>207.6900024414062</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -1729,11 +1729,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>207.6900024414062</v>
+        <v>220.9700012207031</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -1750,11 +1750,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>220.9700012207031</v>
+        <v>223.6000061035156</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -1771,11 +1771,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>223.6000061035156</v>
+        <v>227.9199981689453</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -1792,11 +1792,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>227.9199981689453</v>
+        <v>231.8300018310547</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -1813,11 +1813,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>231.8300018310547</v>
+        <v>231.9199981689453</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -1834,11 +1834,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>231.9199981689453</v>
+        <v>249.8000030517578</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -1855,11 +1855,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>249.8000030517578</v>
+        <v>253.7299957275391</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -1876,11 +1876,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>253.7299957275391</v>
+        <v>259.6799926757812</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -1897,11 +1897,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>259.6799926757812</v>
+        <v>251.3099975585938</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -1918,11 +1918,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>251.3099975585938</v>
+        <v>252.0299987792969</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -1939,11 +1939,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>252.0299987792969</v>
+        <v>252.7400054931641</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -1960,11 +1960,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>252.7400054931641</v>
+        <v>252.1799926757812</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -1981,11 +1981,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>252.1799926757812</v>
+        <v>236.7299957275391</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -2002,11 +2002,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>236.7299957275391</v>
+        <v>246.2700042724609</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
@@ -2023,11 +2023,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>246.2700042724609</v>
+        <v>242.1100006103516</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
@@ -2044,11 +2044,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>242.1100006103516</v>
+        <v>200.1900024414062</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
@@ -2065,11 +2065,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>200.1900024414062</v>
+        <v>192.5</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -2086,11 +2086,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>192.5</v>
+        <v>208.4400024414062</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
@@ -2107,11 +2107,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>208.4400024414062</v>
+        <v>216</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -2128,11 +2128,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>216</v>
+        <v>213.5700073242188</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -2149,11 +2149,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>213.5700073242188</v>
+        <v>213.5800018310547</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -2170,11 +2170,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>213.5800018310547</v>
+        <v>205.9400024414062</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -2191,11 +2191,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>205.9400024414062</v>
+        <v>207.3200073242188</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -2212,11 +2212,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>207.3200073242188</v>
+        <v>203.0800018310547</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -2233,11 +2233,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>203.0800018310547</v>
+        <v>200.1199951171875</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -2254,11 +2254,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>200.1199951171875</v>
+        <v>203.3699951171875</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
@@ -2275,11 +2275,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>203.3699951171875</v>
+        <v>200.1499938964844</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -2296,11 +2296,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>200.1499938964844</v>
+        <v>196.6000061035156</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -2317,11 +2317,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>196.6000061035156</v>
+        <v>213.8399963378906</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
@@ -2338,11 +2338,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>213.8399963378906</v>
+        <v>210.8600006103516</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -2359,11 +2359,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>210.8600006103516</v>
+        <v>203.6799926757812</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
@@ -2380,11 +2380,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>203.6799926757812</v>
+        <v>200.2100067138672</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -2401,11 +2401,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>200.2100067138672</v>
+        <v>198.6199951171875</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -2422,11 +2422,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>198.6199951171875</v>
+        <v>190.9499969482422</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -2443,11 +2443,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>190.9499969482422</v>
+        <v>202.0700073242188</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -2464,11 +2464,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>202.0700073242188</v>
+        <v>199.4499969482422</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -2485,11 +2485,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>199.4499969482422</v>
+        <v>192.4299926757812</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
@@ -2506,11 +2506,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>192.4299926757812</v>
+        <v>202.6799926757812</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -2527,11 +2527,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>202.6799926757812</v>
+        <v>203.2299957275391</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -2548,11 +2548,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>203.2299957275391</v>
+        <v>204.8300018310547</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
@@ -2569,11 +2569,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>204.8300018310547</v>
+        <v>197.7400054931641</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
@@ -2590,11 +2590,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>197.7400054931641</v>
+        <v>193.3899993896484</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -2611,11 +2611,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>193.3899993896484</v>
+        <v>196.5800018310547</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -2632,11 +2632,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>196.5800018310547</v>
+        <v>196.3099975585938</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
@@ -2653,11 +2653,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>196.3099975585938</v>
+        <v>199.4600067138672</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -2674,11 +2674,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>199.4600067138672</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
@@ -2695,11 +2695,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>205.2700042724609</v>
+        <v>201.3300018310547</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
@@ -2716,11 +2716,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>201.3300018310547</v>
+        <v>202.6799926757812</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
@@ -2737,11 +2737,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>202.6799926757812</v>
+        <v>205.3699951171875</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -2758,11 +2758,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>205.3699951171875</v>
+        <v>220.2700042724609</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
@@ -2779,11 +2779,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>220.2700042724609</v>
+        <v>203.7700042724609</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
@@ -2800,11 +2800,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>203.7700042724609</v>
+        <v>201.9900054931641</v>
       </c>
       <c r="C110" t="n">
         <v>1</v>
@@ -2821,11 +2821,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>201.9900054931641</v>
+        <v>196.0399932861328</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
@@ -2842,11 +2842,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>196.0399932861328</v>
+        <v>203.4299926757812</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
@@ -2863,11 +2863,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>203.4299926757812</v>
+        <v>210.2100067138672</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
@@ -2884,11 +2884,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>210.2100067138672</v>
+        <v>217.5</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -2905,11 +2905,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>217.5</v>
+        <v>220.1799926757812</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -2926,11 +2926,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>220.1799926757812</v>
+        <v>221.5299987792969</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
@@ -2947,11 +2947,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>221.5299987792969</v>
+        <v>231.8200073242188</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
@@ -2968,11 +2968,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>231.8200073242188</v>
+        <v>236.6399993896484</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
@@ -2989,11 +2989,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>236.6399993896484</v>
+        <v>245.0399932861328</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -3010,11 +3010,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>245.0399932861328</v>
+        <v>246.8300018310547</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -3031,11 +3031,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>246.8300018310547</v>
+        <v>255.0700073242188</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
@@ -3052,11 +3052,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>255.0700073242188</v>
+        <v>258.1199951171875</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
@@ -3073,11 +3073,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>258.1199951171875</v>
+        <v>278.260009765625</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -3094,11 +3094,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>278.260009765625</v>
+        <v>278.3900146484375</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -3115,11 +3115,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>278.3900146484375</v>
+        <v>274.9500122070312</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -3136,11 +3136,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>274.9500122070312</v>
+        <v>284.489990234375</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -3157,11 +3157,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>284.489990234375</v>
+        <v>303.4599914550781</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -3178,11 +3178,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>303.4599914550781</v>
+        <v>305.3299865722656</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
@@ -3199,11 +3199,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>305.3299865722656</v>
+        <v>347.8099975585938</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -3220,11 +3220,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>347.8099975585938</v>
+        <v>334.6300048828125</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -3241,11 +3241,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>334.6300048828125</v>
+        <v>323.2099914550781</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -3262,11 +3262,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>323.2099914550781</v>
+        <v>337.1099853515625</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
@@ -3283,11 +3283,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>337.1099853515625</v>
+        <v>354.489990234375</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -3304,11 +3304,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>354.489990234375</v>
+        <v>360.5400085449219</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
@@ -3325,11 +3325,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>360.5400085449219</v>
+        <v>341.5400085449219</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
@@ -3346,11 +3346,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>341.5400085449219</v>
+        <v>355.260009765625</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -3367,11 +3367,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>355.260009765625</v>
+        <v>421.3900146484375</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
@@ -3388,11 +3388,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>421.3900146484375</v>
+        <v>408.4599914550781</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
@@ -3409,11 +3409,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>408.4599914550781</v>
+        <v>455.1900024414062</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
@@ -3430,11 +3430,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>455.1900024414062</v>
+        <v>458.7900085449219</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -3451,11 +3451,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>458.7900085449219</v>
+        <v>448.2900085449219</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
@@ -3472,11 +3472,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>448.2900085449219</v>
+        <v>445.5</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
@@ -3493,11 +3493,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>445.5</v>
+        <v>449.7000122070312</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -3514,11 +3514,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>449.7000122070312</v>
+        <v>424.1000061035156</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
@@ -3535,11 +3535,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>424.1000061035156</v>
+        <v>420.989990234375</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
@@ -3556,11 +3556,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>420.989990234375</v>
+        <v>414.0499877929688</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
@@ -3577,11 +3577,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>414.0499877929688</v>
+        <v>447.5799865722656</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
@@ -3598,11 +3598,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>447.5799865722656</v>
+        <v>449.5899963378906</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
@@ -3619,11 +3619,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>449.5899963378906</v>
+        <v>467.510009765625</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
@@ -3640,11 +3640,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>467.510009765625</v>
+        <v>503.8900146484375</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -3661,11 +3661,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>503.8900146484375</v>
+        <v>495.5400085449219</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -3682,11 +3682,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>495.5400085449219</v>
+        <v>518.0900268554688</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -3703,11 +3703,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>518.0900268554688</v>
+        <v>516.0999755859375</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
@@ -3724,11 +3724,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>516.0999755859375</v>
+        <v>510.1300048828125</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
@@ -3745,11 +3745,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>510.1300048828125</v>
+        <v>521.5399780273438</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
@@ -3766,11 +3766,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>521.5399780273438</v>
+        <v>542.52001953125</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
@@ -3787,11 +3787,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>542.52001953125</v>
+        <v>523.2000122070312</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -3808,11 +3808,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>523.2000122070312</v>
+        <v>466.3800048828125</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -3829,11 +3829,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>466.3800048828125</v>
+        <v>490.3299865722656</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
@@ -3850,11 +3850,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>490.3299865722656</v>
+        <v>475.510009765625</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
@@ -3871,11 +3871,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>475.510009765625</v>
+        <v>452.3999938964844</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -3892,11 +3892,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>452.3999938964844</v>
+        <v>488.4500122070312</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -3913,11 +3913,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>488.4500122070312</v>
+        <v>511.5700073242188</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -3934,11 +3934,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>511.5700073242188</v>
+        <v>547.260009765625</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
@@ -3955,11 +3955,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>547.260009765625</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -3976,11 +3976,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>507.2900085449219</v>
+        <v>512.47998046875</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
@@ -3997,11 +3997,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>512.47998046875</v>
+        <v>537.3699951171875</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
@@ -4018,11 +4018,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>537.3699951171875</v>
+        <v>551.6300048828125</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
@@ -4039,11 +4039,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>551.6300048828125</v>
+        <v>519.8499755859375</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
@@ -4060,11 +4060,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>519.8499755859375</v>
+        <v>519.739990234375</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
@@ -4081,11 +4081,11 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>519.739990234375</v>
+        <v>532.5700073242188</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -4102,11 +4102,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>532.5700073242188</v>
+        <v>521.5800170898438</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
@@ -4123,11 +4123,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>521.5800170898438</v>
+        <v>539.489990234375</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
@@ -4144,11 +4144,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>539.489990234375</v>
+        <v>580.9099731445312</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
@@ -4165,11 +4165,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>580.9099731445312</v>
+        <v>540.8800048828125</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
@@ -4186,11 +4186,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>540.8800048828125</v>
+        <v>517.8200073242188</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
@@ -4207,11 +4207,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>517.8200073242188</v>
+        <v>552.0499877929688</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
@@ -4228,11 +4228,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>552.0499877929688</v>
+        <v>516.1099853515625</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
@@ -4249,11 +4249,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>516.1099853515625</v>
+        <v>517.4099731445312</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
@@ -4270,11 +4270,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>517.4099731445312</v>
+        <v>546.719970703125</v>
       </c>
       <c r="C180" t="n">
         <v>1</v>
@@ -4291,11 +4291,11 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>546.719970703125</v>
+        <v>557.8900146484375</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
@@ -4312,11 +4312,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>557.8900146484375</v>
+        <v>534.3900146484375</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -4333,11 +4333,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>534.3900146484375</v>
+        <v>548.1300048828125</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
@@ -4354,11 +4354,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>548.1300048828125</v>
+        <v>529.1400146484375</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
@@ -4375,11 +4375,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>529.1400146484375</v>
+        <v>500.9400024414062</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -4396,11 +4396,11 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>500.9400024414062</v>
+        <v>495.760009765625</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
@@ -4417,11 +4417,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>495.760009765625</v>
+        <v>503.5700073242188</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
@@ -4438,11 +4438,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>503.5700073242188</v>
+        <v>544.4299926757812</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -4459,11 +4459,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>544.4299926757812</v>
+        <v>552.3300170898438</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
@@ -4480,11 +4480,11 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>552.3300170898438</v>
+        <v>539.6900024414062</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -4501,11 +4501,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>539.6900024414062</v>
+        <v>521.9500122070312</v>
       </c>
       <c r="C191" t="n">
         <v>1</v>
@@ -4522,11 +4522,11 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>521.9500122070312</v>
+        <v>494.9500122070312</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
@@ -4543,11 +4543,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>494.9500122070312</v>
+        <v>454.6199951171875</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
@@ -4564,11 +4564,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>454.6199951171875</v>
+        <v>429.5599975585938</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -4585,11 +4585,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>429.5599975585938</v>
+        <v>485.3900146484375</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
@@ -4606,11 +4606,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>485.3900146484375</v>
+        <v>476.1499938964844</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
@@ -4627,11 +4627,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>476.1499938964844</v>
+        <v>484.6400146484375</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -4648,11 +4648,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>484.6400146484375</v>
+        <v>518.5800170898438</v>
       </c>
       <c r="C198" t="n">
         <v>1</v>
@@ -4669,11 +4669,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>518.5800170898438</v>
+        <v>482.0499877929688</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
@@ -4690,11 +4690,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>482.0499877929688</v>
+        <v>489.2799987792969</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
@@ -4711,11 +4711,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>489.2799987792969</v>
+        <v>483.3599853515625</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
@@ -4732,11 +4732,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>483.3599853515625</v>
+        <v>469.5599975585938</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
@@ -4753,11 +4753,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>469.5599975585938</v>
+        <v>474.3200073242188</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
@@ -4774,11 +4774,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>474.3200073242188</v>
+        <v>482.9299926757812</v>
       </c>
       <c r="C204" t="n">
         <v>1</v>
@@ -4795,11 +4795,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>482.9299926757812</v>
+        <v>483.010009765625</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
@@ -4816,11 +4816,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>483.010009765625</v>
+        <v>514.3900146484375</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
@@ -4837,11 +4837,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>514.3900146484375</v>
+        <v>506</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
@@ -4858,11 +4858,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>506</v>
+        <v>484.3900146484375</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
@@ -4879,11 +4879,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>484.3900146484375</v>
+        <v>466.4200134277344</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
@@ -4900,11 +4900,11 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>466.4200134277344</v>
+        <v>469.4599914550781</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
@@ -4921,11 +4921,11 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>469.4599914550781</v>
+        <v>473.25</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
@@ -4942,11 +4942,11 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>473.25</v>
+        <v>456.75</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
@@ -4963,11 +4963,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>456.75</v>
+        <v>479.1799926757812</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
@@ -4984,11 +4984,11 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>479.1799926757812</v>
+        <v>480.9299926757812</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
@@ -5005,11 +5005,11 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>480.9299926757812</v>
+        <v>476.6700134277344</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
@@ -5026,11 +5026,11 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>476.6700134277344</v>
+        <v>465.5799865722656</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
@@ -5047,11 +5047,11 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>465.5799865722656</v>
+        <v>470.7200012207031</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
@@ -5068,11 +5068,11 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>470.7200012207031</v>
+        <v>459.6099853515625</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
@@ -5089,11 +5089,11 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>459.6099853515625</v>
+        <v>457.0599975585938</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
@@ -5110,11 +5110,11 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>457.0599975585938</v>
+        <v>456.1600036621094</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
@@ -5131,11 +5131,11 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>456.1600036621094</v>
+        <v>477.5700073242188</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
@@ -5152,11 +5152,11 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>477.5700073242188</v>
+        <v>505.739990234375</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
@@ -5173,11 +5173,11 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>505.739990234375</v>
+        <v>521.0999755859375</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
@@ -5194,11 +5194,11 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>521.0999755859375</v>
+        <v>503.6000061035156</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
@@ -5215,11 +5215,11 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>503.6000061035156</v>
+        <v>516.1300048828125</v>
       </c>
       <c r="C225" t="n">
         <v>1</v>
@@ -5236,11 +5236,11 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>516.1300048828125</v>
+        <v>493.4100036621094</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
@@ -5257,11 +5257,11 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>493.4100036621094</v>
+        <v>504.2000122070312</v>
       </c>
       <c r="C227" t="n">
         <v>1</v>
@@ -5278,11 +5278,11 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>504.2000122070312</v>
+        <v>512.5</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
@@ -5299,11 +5299,11 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>512.5</v>
+        <v>545.0900268554688</v>
       </c>
       <c r="C229" t="n">
         <v>1</v>
@@ -5320,11 +5320,11 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>545.0900268554688</v>
+        <v>559.8200073242188</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
@@ -5341,11 +5341,11 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>559.8200073242188</v>
+        <v>615.52001953125</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
@@ -5362,11 +5362,11 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>615.52001953125</v>
+        <v>623.77001953125</v>
       </c>
       <c r="C232" t="n">
         <v>1</v>
@@ -5383,11 +5383,11 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>623.77001953125</v>
+        <v>614.6099853515625</v>
       </c>
       <c r="C233" t="n">
         <v>1</v>
@@ -5404,11 +5404,11 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>614.6099853515625</v>
+        <v>629.260009765625</v>
       </c>
       <c r="C234" t="n">
         <v>1</v>
@@ -5425,11 +5425,11 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>629.260009765625</v>
+        <v>630.6300048828125</v>
       </c>
       <c r="C235" t="n">
         <v>1</v>
@@ -5446,11 +5446,11 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>630.6300048828125</v>
+        <v>607.8699951171875</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
@@ -5467,11 +5467,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>607.8699951171875</v>
+        <v>607.5700073242188</v>
       </c>
       <c r="C237" t="n">
         <v>1</v>
@@ -5488,11 +5488,11 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>607.5700073242188</v>
+        <v>611.760009765625</v>
       </c>
       <c r="C238" t="n">
         <v>1</v>
@@ -5509,11 +5509,11 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>611.760009765625</v>
+        <v>615.72998046875</v>
       </c>
       <c r="C239" t="n">
         <v>1</v>
@@ -5530,11 +5530,11 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>615.72998046875</v>
+        <v>633.9099731445312</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
@@ -5551,11 +5551,11 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>633.9099731445312</v>
+        <v>631.75</v>
       </c>
       <c r="C241" t="n">
         <v>1</v>
@@ -5572,11 +5572,11 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>631.75</v>
+        <v>649.4199829101562</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
@@ -5593,11 +5593,11 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>649.4199829101562</v>
+        <v>645.8599853515625</v>
       </c>
       <c r="C243" t="n">
         <v>1</v>
@@ -5614,11 +5614,11 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>645.8599853515625</v>
+        <v>620.6799926757812</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
@@ -5635,11 +5635,11 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>620.6799926757812</v>
+        <v>608.0999755859375</v>
       </c>
       <c r="C245" t="n">
         <v>1</v>
@@ -5656,11 +5656,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>608.0999755859375</v>
+        <v>594.239990234375</v>
       </c>
       <c r="C246" t="n">
         <v>1</v>
@@ -5677,11 +5677,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>594.239990234375</v>
+        <v>605.530029296875</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
@@ -5698,11 +5698,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>605.530029296875</v>
+        <v>570.8200073242188</v>
       </c>
       <c r="C248" t="n">
         <v>1</v>
@@ -5719,11 +5719,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>570.8200073242188</v>
+        <v>562.22998046875</v>
       </c>
       <c r="C249" t="n">
         <v>1</v>
@@ -5740,11 +5740,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>562.22998046875</v>
+        <v>528.75</v>
       </c>
       <c r="C250" t="n">
         <v>1</v>
@@ -5761,11 +5761,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>528.75</v>
+        <v>538.0499877929688</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>
@@ -5790,7 +5790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5846,10 +5846,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.11644744873047</v>
+        <v>27.11644554138184</v>
       </c>
       <c r="C2" t="n">
-        <v>5.406099796295166</v>
+        <v>5.36870002746582</v>
       </c>
       <c r="D2">
         <f>B2/C2</f>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D249/D51-1)*100</f>
+        <f>(D250/D51-1)*100</f>
         <v/>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="H3">
-        <f>(D249/D2-1)*100</f>
+        <f>(D250/D2-1)*100</f>
         <v/>
       </c>
     </row>
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.20759773254395</v>
+        <v>27.20759582519531</v>
       </c>
       <c r="C4" t="n">
         <v>5.38670015335083</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="H4">
-        <f>(COUNT(D2:D249)-1)/((DATEVALUE(A249)-DATEVALUE(A2))/365.25)</f>
+        <f>(COUNT(D2:D250)-1)/((DATEVALUE(A250)-DATEVALUE(A2))/365.25)</f>
         <v/>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="H5">
-        <f>STDEV.S(E3:E249)*SQRT(H4)*100</f>
+        <f>STDEV.S(E3:E250)*SQRT(H4)*100</f>
         <v/>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.1984806060791</v>
+        <v>27.19847869873047</v>
       </c>
       <c r="C6" t="n">
         <v>5.382900238037109</v>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.34431838989258</v>
+        <v>27.34431648254395</v>
       </c>
       <c r="C7" t="n">
         <v>5.388299942016602</v>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>118.8693556325766</v>
+        <v>120.8000255435194</v>
       </c>
     </row>
     <row r="8">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>128.3828728290006</v>
+        <v>128.8035472641337</v>
       </c>
     </row>
     <row r="9">
@@ -6041,7 +6041,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.36254692077637</v>
+        <v>27.36254501342773</v>
       </c>
       <c r="C9" t="n">
         <v>5.357399940490723</v>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>30.68251883645005</v>
+        <v>30.66322759964586</v>
       </c>
     </row>
     <row r="10">
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.11644744873047</v>
+        <v>27.11644554138184</v>
       </c>
       <c r="C11" t="n">
         <v>5.381999969482422</v>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-20 01:06 UTC</t>
+          <t>Snapshot as of 2026-10-21 00:38 UTC</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27.57218360900879</v>
+        <v>27.57218551635742</v>
       </c>
       <c r="C13" t="n">
         <v>5.354899883270264</v>
@@ -6159,7 +6159,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28.11907386779785</v>
+        <v>28.11907196044922</v>
       </c>
       <c r="C14" t="n">
         <v>5.395899772644043</v>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28.26490783691406</v>
+        <v>28.2649097442627</v>
       </c>
       <c r="C15" t="n">
         <v>5.35860013961792</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29.48628616333008</v>
+        <v>29.48628807067871</v>
       </c>
       <c r="C19" t="n">
         <v>5.270699977874756</v>
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29.80530738830566</v>
+        <v>29.80530548095703</v>
       </c>
       <c r="C21" t="n">
         <v>5.296500205993652</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.96936988830566</v>
+        <v>29.9693717956543</v>
       </c>
       <c r="C22" t="n">
         <v>5.295599937438965</v>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30.06963539123535</v>
+        <v>30.06963348388672</v>
       </c>
       <c r="C23" t="n">
         <v>5.329500198364258</v>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.65946769714355</v>
+        <v>29.65946960449219</v>
       </c>
       <c r="C26" t="n">
         <v>5.402100086212158</v>
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.53186225891113</v>
+        <v>29.53186416625977</v>
       </c>
       <c r="C29" t="n">
         <v>5.33080005645752</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.23107528686523</v>
+        <v>29.2310733795166</v>
       </c>
       <c r="C32" t="n">
         <v>5.355800151824951</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29.6412410736084</v>
+        <v>29.64123916625977</v>
       </c>
       <c r="C34" t="n">
         <v>5.306099891662598</v>
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28.59304046630859</v>
+        <v>28.59304237365723</v>
       </c>
       <c r="C35" t="n">
         <v>5.309299945831299</v>
@@ -6663,7 +6663,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29.11258316040039</v>
+        <v>29.11258125305176</v>
       </c>
       <c r="C38" t="n">
         <v>5.43149995803833</v>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.79356575012207</v>
+        <v>28.7935676574707</v>
       </c>
       <c r="C40" t="n">
         <v>5.405499935150146</v>
@@ -6747,7 +6747,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>28.01880836486816</v>
+        <v>28.0188102722168</v>
       </c>
       <c r="C42" t="n">
         <v>5.413400173187256</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.32871055603027</v>
+        <v>28.32871246337891</v>
       </c>
       <c r="C43" t="n">
         <v>5.507500171661377</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.26490783691406</v>
+        <v>28.2649097442627</v>
       </c>
       <c r="C45" t="n">
         <v>5.521299839019775</v>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28.3469409942627</v>
+        <v>28.34694290161133</v>
       </c>
       <c r="C46" t="n">
         <v>5.53980016708374</v>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28.59341049194336</v>
+        <v>28.59341239929199</v>
       </c>
       <c r="C48" t="n">
         <v>5.519499778747559</v>
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28.89429473876953</v>
+        <v>28.8942928314209</v>
       </c>
       <c r="C49" t="n">
         <v>5.542500019073486</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29.2798023223877</v>
+        <v>29.27980041503906</v>
       </c>
       <c r="C58" t="n">
         <v>5.373700141906738</v>
@@ -7167,7 +7167,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>30.24827003479004</v>
+        <v>30.24827194213867</v>
       </c>
       <c r="C62" t="n">
         <v>5.367700099945068</v>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>31.43300437927246</v>
+        <v>31.43300628662109</v>
       </c>
       <c r="C64" t="n">
         <v>5.374300003051758</v>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>32.94683456420898</v>
+        <v>32.94683074951172</v>
       </c>
       <c r="C66" t="n">
         <v>5.283699989318848</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>33.97171783447266</v>
+        <v>33.97172164916992</v>
       </c>
       <c r="C68" t="n">
         <v>5.279099941253662</v>
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>35.44792938232422</v>
+        <v>35.44793319702148</v>
       </c>
       <c r="C70" t="n">
         <v>5.197100162506104</v>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>34.78974533081055</v>
+        <v>34.78974914550781</v>
       </c>
       <c r="C75" t="n">
         <v>5.23799991607666</v>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>35.11883544921875</v>
+        <v>35.11883926391602</v>
       </c>
       <c r="C78" t="n">
         <v>5.19159984588623</v>
@@ -7566,7 +7566,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>34.68631362915039</v>
+        <v>34.68631744384766</v>
       </c>
       <c r="C81" t="n">
         <v>5.213900089263916</v>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>35.55135726928711</v>
+        <v>35.55136108398438</v>
       </c>
       <c r="C83" t="n">
         <v>5.234399795532227</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>35.70180130004883</v>
+        <v>35.70180511474609</v>
       </c>
       <c r="C84" t="n">
         <v>5.208799839019775</v>
@@ -7671,7 +7671,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>37.20622253417969</v>
+        <v>37.20622634887695</v>
       </c>
       <c r="C86" t="n">
         <v>5.170899868011475</v>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>37.20622253417969</v>
+        <v>37.20622634887695</v>
       </c>
       <c r="C87" t="n">
         <v>5.151999950408936</v>
@@ -7713,7 +7713,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>37.24383544921875</v>
+        <v>37.24383926391602</v>
       </c>
       <c r="C88" t="n">
         <v>5.124199867248535</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>38.5037841796875</v>
+        <v>38.50378799438477</v>
       </c>
       <c r="C91" t="n">
         <v>5.170300006866455</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>38.08066940307617</v>
+        <v>38.08066558837891</v>
       </c>
       <c r="C92" t="n">
         <v>5.277299880981445</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>43.12047958374023</v>
+        <v>43.1204833984375</v>
       </c>
       <c r="C100" t="n">
         <v>5.329100131988525</v>
@@ -7986,7 +7986,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>43.60942077636719</v>
+        <v>43.60941696166992</v>
       </c>
       <c r="C101" t="n">
         <v>5.233399868011475</v>
@@ -8070,7 +8070,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>43.28032684326172</v>
+        <v>43.28032302856445</v>
       </c>
       <c r="C105" t="n">
         <v>5.31190013885498</v>
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>44.66250991821289</v>
+        <v>44.66251373291016</v>
       </c>
       <c r="C107" t="n">
         <v>5.232600212097168</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>46.702880859375</v>
+        <v>46.70288467407227</v>
       </c>
       <c r="C110" t="n">
         <v>5.23799991607666</v>
@@ -8196,7 +8196,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>45.76261901855469</v>
+        <v>45.76262283325195</v>
       </c>
       <c r="C111" t="n">
         <v>5.263999938964844</v>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>45.61217498779297</v>
+        <v>45.61217880249023</v>
       </c>
       <c r="C115" t="n">
         <v>5.138299942016602</v>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>45.01980972290039</v>
+        <v>45.01981353759766</v>
       </c>
       <c r="C120" t="n">
         <v>4.994400024414062</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>44.08895111083984</v>
+        <v>44.08895492553711</v>
       </c>
       <c r="C121" t="n">
         <v>4.984799861907959</v>
@@ -8427,7 +8427,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>45.67800140380859</v>
+        <v>45.67799758911133</v>
       </c>
       <c r="C122" t="n">
         <v>4.992400169372559</v>
@@ -8469,7 +8469,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>44.21118545532227</v>
+        <v>44.21118927001953</v>
       </c>
       <c r="C124" t="n">
         <v>5.00629997253418</v>
@@ -8595,7 +8595,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>46.68469619750977</v>
+        <v>46.6846923828125</v>
       </c>
       <c r="C130" t="n">
         <v>4.99429988861084</v>
@@ -8616,7 +8616,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>46.79911804199219</v>
+        <v>46.79912185668945</v>
       </c>
       <c r="C131" t="n">
         <v>5.017499923706055</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>47.04703903198242</v>
+        <v>47.04703521728516</v>
       </c>
       <c r="C132" t="n">
         <v>4.951929092407227</v>
@@ -8658,7 +8658,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>46.39863967895508</v>
+        <v>46.39863586425781</v>
       </c>
       <c r="C133" t="n">
         <v>4.984799861907959</v>
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>43.55712509155273</v>
+        <v>43.55712890625</v>
       </c>
       <c r="C138" t="n">
         <v>4.906400203704834</v>
@@ -8826,7 +8826,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>43.35688400268555</v>
+        <v>43.35688781738281</v>
       </c>
       <c r="C141" t="n">
         <v>5.00409984588623</v>
@@ -8889,7 +8889,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>42.52731704711914</v>
+        <v>42.52731323242188</v>
       </c>
       <c r="C144" t="n">
         <v>5.058199882507324</v>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>42.86105346679688</v>
+        <v>42.86104965209961</v>
       </c>
       <c r="C145" t="n">
         <v>5.01170015335083</v>
@@ -8931,7 +8931,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>42.41289138793945</v>
+        <v>42.41289520263672</v>
       </c>
       <c r="C146" t="n">
         <v>5.017099857330322</v>
@@ -11105,6 +11105,27 @@
       </c>
       <c r="E249">
         <f>LN(D249/D248)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>58.20999908447266</v>
+      </c>
+      <c r="C250" t="n">
+        <v>5.037000179290771</v>
+      </c>
+      <c r="D250">
+        <f>B250/C250</f>
+        <v/>
+      </c>
+      <c r="E250">
+        <f>LN(D250/D249)</f>
         <v/>
       </c>
     </row>
@@ -11171,11 +11192,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>403.1499938964844</v>
+        <v>377.239990234375</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -11190,18 +11211,18 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D251/D53-1)*100</f>
+        <f>(D251/D52-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>377.239990234375</v>
+        <v>377.2799987792969</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -11227,11 +11248,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>377.2799987792969</v>
+        <v>378.7900085449219</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -11257,11 +11278,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>378.7900085449219</v>
+        <v>377.5199890136719</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -11287,11 +11308,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>377.5199890136719</v>
+        <v>367.010009765625</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -11308,11 +11329,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>367.010009765625</v>
+        <v>364.3800048828125</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -11331,17 +11352,17 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-4.667570553379527</v>
+        <v>-5.179773024003214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>364.3800048828125</v>
+        <v>363</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -11360,17 +11381,17 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-5.819174004712881</v>
+        <v>0.1086841268158117</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>363</v>
+        <v>370.1300048828125</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -11389,17 +11410,17 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>29.35300391553927</v>
+        <v>28.59337467576674</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>370.1300048828125</v>
+        <v>368.1199951171875</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -11416,11 +11437,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>368.1199951171875</v>
+        <v>368.7799987792969</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -11435,18 +11456,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-20 01:06 UTC</t>
+          <t>Snapshot as of 2026-10-21 00:38 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>368.7799987792969</v>
+        <v>362.3200073242188</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -11463,11 +11484,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>362.3200073242188</v>
+        <v>366.510009765625</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -11484,11 +11505,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>366.510009765625</v>
+        <v>366.0700073242188</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -11505,11 +11526,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>366.0700073242188</v>
+        <v>368.3099975585938</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -11526,11 +11547,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>368.3099975585938</v>
+        <v>378.3800048828125</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -11547,11 +11568,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>378.3800048828125</v>
+        <v>379.8699951171875</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -11568,11 +11589,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>379.8699951171875</v>
+        <v>385.989990234375</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -11589,11 +11610,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>385.989990234375</v>
+        <v>382.8699951171875</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -11610,11 +11631,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.8699951171875</v>
+        <v>375.9599914550781</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -11631,11 +11652,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>375.9599914550781</v>
+        <v>371.6499938964844</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -11652,11 +11673,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>371.6499938964844</v>
+        <v>374.3500061035156</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -11673,11 +11694,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>374.3500061035156</v>
+        <v>374.9599914550781</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -11694,11 +11715,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>374.9599914550781</v>
+        <v>374.8500061035156</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -11715,11 +11736,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>374.8500061035156</v>
+        <v>374.2699890136719</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -11736,11 +11757,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>374.2699890136719</v>
+        <v>380.2000122070312</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -11757,11 +11778,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>380.2000122070312</v>
+        <v>380.0799865722656</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -11778,11 +11799,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>380.0799865722656</v>
+        <v>383.1199951171875</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -11799,11 +11820,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>383.1199951171875</v>
+        <v>387.8800048828125</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -11820,11 +11841,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>387.8800048828125</v>
+        <v>389.75</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -11841,11 +11862,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>389.75</v>
+        <v>387.239990234375</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -11862,11 +11883,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>387.239990234375</v>
+        <v>386.8800048828125</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -11883,11 +11904,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>386.8800048828125</v>
+        <v>387.1300048828125</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -11904,11 +11925,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>387.1300048828125</v>
+        <v>386.4400024414062</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -11925,11 +11946,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>386.4400024414062</v>
+        <v>385.4200134277344</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -11946,11 +11967,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>385.4200134277344</v>
+        <v>387.3999938964844</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -11967,11 +11988,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>387.3999938964844</v>
+        <v>389.0499877929688</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -11988,11 +12009,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>389.0499877929688</v>
+        <v>393.239990234375</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -12009,11 +12030,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>393.239990234375</v>
+        <v>395.4400024414062</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -12030,11 +12051,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>395.4400024414062</v>
+        <v>395.7999877929688</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -12051,11 +12072,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>395.7999877929688</v>
+        <v>395.8900146484375</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -12072,11 +12093,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>395.8900146484375</v>
+        <v>399.2900085449219</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -12093,11 +12114,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>399.2900085449219</v>
+        <v>398.5700073242188</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -12114,11 +12135,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>398.5700073242188</v>
+        <v>399.0199890136719</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -12135,11 +12156,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>399.0199890136719</v>
+        <v>408.2300109863281</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -12156,11 +12177,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>408.2300109863281</v>
+        <v>413.6400146484375</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -12177,11 +12198,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>413.6400146484375</v>
+        <v>411.9299926757812</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -12198,11 +12219,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>411.9299926757812</v>
+        <v>416.739990234375</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -12219,11 +12240,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>416.739990234375</v>
+        <v>398.6000061035156</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -12240,11 +12261,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>398.6000061035156</v>
+        <v>398.8900146484375</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -12261,11 +12282,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>398.8900146484375</v>
+        <v>396.3099975585938</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -12282,11 +12303,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>396.3099975585938</v>
+        <v>398.2799987792969</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -12303,11 +12324,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>398.2799987792969</v>
+        <v>408.760009765625</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -12324,11 +12345,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>408.760009765625</v>
+        <v>413.1799926757812</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -12345,11 +12366,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>413.1799926757812</v>
+        <v>409.2300109863281</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -12366,11 +12387,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>409.2300109863281</v>
+        <v>411.489990234375</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -12387,11 +12408,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>411.489990234375</v>
+        <v>414.4700012207031</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -12408,11 +12429,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>414.4700012207031</v>
+        <v>422.2300109863281</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -12429,11 +12450,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>422.2300109863281</v>
+        <v>421.6300048828125</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -12450,11 +12471,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>421.6300048828125</v>
+        <v>425.9400024414062</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -12471,11 +12492,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>425.9400024414062</v>
+        <v>423.3299865722656</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -12492,11 +12513,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>423.3299865722656</v>
+        <v>421.2900085449219</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -12513,11 +12534,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>421.2900085449219</v>
+        <v>437.2300109863281</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -12534,11 +12555,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>437.2300109863281</v>
+        <v>443.6000061035156</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -12555,11 +12576,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>443.6000061035156</v>
+        <v>451.7900085449219</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -12576,11 +12597,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>451.7900085449219</v>
+        <v>458</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -12597,11 +12618,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>458</v>
+        <v>464.7000122070312</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -12618,11 +12639,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>464.7000122070312</v>
+        <v>476.1000061035156</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -12639,11 +12660,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>476.1000061035156</v>
+        <v>494.5599975585938</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -12660,11 +12681,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>494.5599975585938</v>
+        <v>495.8999938964844</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -12681,11 +12702,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>495.8999938964844</v>
+        <v>444.9500122070312</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -12702,11 +12723,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>444.9500122070312</v>
+        <v>427.1300048828125</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
@@ -12723,11 +12744,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>427.1300048828125</v>
+        <v>454.2900085449219</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
@@ -12744,11 +12765,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>454.2900085449219</v>
+        <v>453.9700012207031</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
@@ -12765,11 +12786,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>453.9700012207031</v>
+        <v>441.8800048828125</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -12786,11 +12807,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>441.8800048828125</v>
+        <v>455.4599914550781</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
@@ -12807,11 +12828,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>455.4599914550781</v>
+        <v>467.0299987792969</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -12828,11 +12849,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>467.0299987792969</v>
+        <v>462.3999938964844</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -12849,11 +12870,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>462.3999938964844</v>
+        <v>467.6300048828125</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -12870,11 +12891,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>467.6300048828125</v>
+        <v>451.3900146484375</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -12891,11 +12912,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>451.3900146484375</v>
+        <v>462.6199951171875</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -12912,11 +12933,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>462.6199951171875</v>
+        <v>448.2000122070312</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -12933,11 +12954,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>448.2000122070312</v>
+        <v>458.2799987792969</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -12954,11 +12975,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>458.2799987792969</v>
+        <v>459.5599975585938</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
@@ -12975,11 +12996,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>459.5599975585938</v>
+        <v>468.6199951171875</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -12996,11 +13017,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>468.6199951171875</v>
+        <v>481.2799987792969</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -13017,11 +13038,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>481.2799987792969</v>
+        <v>474.6099853515625</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
@@ -13038,11 +13059,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>474.6099853515625</v>
+        <v>473.4200134277344</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -13059,11 +13080,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>473.4200134277344</v>
+        <v>477.4800109863281</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
@@ -13080,11 +13101,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>477.4800109863281</v>
+        <v>483.75</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -13101,11 +13122,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>483.75</v>
+        <v>490</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -13122,11 +13143,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>490</v>
+        <v>468.1400146484375</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -13143,11 +13164,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>468.1400146484375</v>
+        <v>471.7999877929688</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -13164,11 +13185,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>471.7999877929688</v>
+        <v>466.1300048828125</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -13185,11 +13206,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>466.1300048828125</v>
+        <v>473.510009765625</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
@@ -13206,11 +13227,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>473.510009765625</v>
+        <v>472.5299987792969</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -13227,11 +13248,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>472.5299987792969</v>
+        <v>477.8599853515625</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -13248,11 +13269,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>477.8599853515625</v>
+        <v>476.239990234375</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
@@ -13269,11 +13290,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>476.239990234375</v>
+        <v>466.8800048828125</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
@@ -13290,11 +13311,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>466.8800048828125</v>
+        <v>460.8399963378906</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -13311,11 +13332,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>460.8399963378906</v>
+        <v>460.4299926757812</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -13332,11 +13353,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>460.4299926757812</v>
+        <v>459.2699890136719</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
@@ -13353,11 +13374,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>459.2699890136719</v>
+        <v>444.739990234375</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -13374,11 +13395,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>444.739990234375</v>
+        <v>426.4100036621094</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
@@ -13395,11 +13416,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>426.4100036621094</v>
+        <v>413.3800048828125</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
@@ -13416,11 +13437,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>413.3800048828125</v>
+        <v>404.0400085449219</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
@@ -13437,11 +13458,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>404.0400085449219</v>
+        <v>404.1300048828125</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -13458,11 +13479,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>404.1300048828125</v>
+        <v>416.2900085449219</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
@@ -13479,11 +13500,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>416.2900085449219</v>
+        <v>400.6400146484375</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
@@ -13500,11 +13521,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>400.6400146484375</v>
+        <v>414.7000122070312</v>
       </c>
       <c r="C110" t="n">
         <v>1</v>
@@ -13521,11 +13542,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>414.7000122070312</v>
+        <v>414.5799865722656</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
@@ -13542,11 +13563,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>414.5799865722656</v>
+        <v>430.2900085449219</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
@@ -13563,11 +13584,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>430.2900085449219</v>
+        <v>437.8200073242188</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
@@ -13584,11 +13605,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>437.8200073242188</v>
+        <v>429.4100036621094</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -13605,11 +13626,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>429.4100036621094</v>
+        <v>427.6499938964844</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -13626,11 +13647,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>427.6499938964844</v>
+        <v>431.8099975585938</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
@@ -13647,11 +13668,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>431.8099975585938</v>
+        <v>434.5299987792969</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
@@ -13668,11 +13689,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>434.5299987792969</v>
+        <v>437.9100036621094</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
@@ -13689,11 +13710,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>437.9100036621094</v>
+        <v>437.1300048828125</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -13710,11 +13731,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>437.1300048828125</v>
+        <v>435.3599853515625</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -13731,11 +13752,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>435.3599853515625</v>
+        <v>445.0899963378906</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
@@ -13752,11 +13773,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>445.0899963378906</v>
+        <v>440.4599914550781</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
@@ -13773,11 +13794,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>440.4599914550781</v>
+        <v>440.0799865722656</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -13794,11 +13815,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>440.0799865722656</v>
+        <v>445.9299926757812</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -13815,11 +13836,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>445.9299926757812</v>
+        <v>442.0899963378906</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -13836,11 +13857,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>442.0899963378906</v>
+        <v>429.5700073242188</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -13857,11 +13878,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>429.5700073242188</v>
+        <v>435.260009765625</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -13878,11 +13899,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>435.260009765625</v>
+        <v>431.0400085449219</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
@@ -13899,11 +13920,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>431.0400085449219</v>
+        <v>433.25</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -13920,11 +13941,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>433.25</v>
+        <v>429.8900146484375</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -13941,11 +13962,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>429.8900146484375</v>
+        <v>421.9100036621094</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -13962,11 +13983,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>421.9100036621094</v>
+        <v>417.4100036621094</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
@@ -13983,11 +14004,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>417.4100036621094</v>
+        <v>423.6600036621094</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -14004,11 +14025,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>423.6600036621094</v>
+        <v>423.1799926757812</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
@@ -14025,11 +14046,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>423.1799926757812</v>
+        <v>414.7099914550781</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
@@ -14046,11 +14067,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>414.7099914550781</v>
+        <v>418.2699890136719</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -14067,11 +14088,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>418.2699890136719</v>
+        <v>430.9599914550781</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
@@ -14088,11 +14109,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>430.9599914550781</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
@@ -14109,11 +14130,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>431.6799926757812</v>
+        <v>433.7699890136719</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
@@ -14130,11 +14151,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>433.7699890136719</v>
+        <v>434.6499938964844</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -14151,11 +14172,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>434.6499938964844</v>
+        <v>432.9299926757812</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
@@ -14172,11 +14193,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>432.9299926757812</v>
+        <v>430.5</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
@@ -14193,11 +14214,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>430.5</v>
+        <v>427.2099914550781</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -14214,11 +14235,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>427.2099914550781</v>
+        <v>417.2900085449219</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
@@ -14235,11 +14256,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>417.2900085449219</v>
+        <v>418.4299926757812</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
@@ -14256,11 +14277,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>418.4299926757812</v>
+        <v>411.5</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
@@ -14277,11 +14298,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>411.5</v>
+        <v>417.3999938964844</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
@@ -14298,11 +14319,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>417.3999938964844</v>
+        <v>416.989990234375</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
@@ -14319,11 +14340,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>416.989990234375</v>
+        <v>413.8200073242188</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
@@ -14340,11 +14361,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>413.8200073242188</v>
+        <v>414</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -14361,11 +14382,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>414</v>
+        <v>408.489990234375</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -14382,11 +14403,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>408.489990234375</v>
+        <v>412.7699890136719</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -14403,11 +14424,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>412.7699890136719</v>
+        <v>417.1199951171875</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
@@ -14424,11 +14445,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>417.1199951171875</v>
+        <v>411.260009765625</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
@@ -14445,11 +14466,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>411.260009765625</v>
+        <v>411.9500122070312</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
@@ -14466,11 +14487,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>411.9500122070312</v>
+        <v>407.8699951171875</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
@@ -14487,11 +14508,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>407.8699951171875</v>
+        <v>411.2699890136719</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -14508,11 +14529,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>411.2699890136719</v>
+        <v>396.239990234375</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -14529,11 +14550,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>396.239990234375</v>
+        <v>397.2699890136719</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
@@ -14550,11 +14571,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>397.2699890136719</v>
+        <v>390.7799987792969</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
@@ -14571,11 +14592,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>390.7799987792969</v>
+        <v>374.5799865722656</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -14592,11 +14613,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>374.5799865722656</v>
+        <v>386.3200073242188</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -14613,11 +14634,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>386.3200073242188</v>
+        <v>386.5400085449219</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -14634,11 +14655,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>386.5400085449219</v>
+        <v>396.5499877929688</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
@@ -14655,11 +14676,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>396.5499877929688</v>
+        <v>397.6300048828125</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -14676,11 +14697,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>397.6300048828125</v>
+        <v>388.6000061035156</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
@@ -14697,11 +14718,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>388.6000061035156</v>
+        <v>387.1199951171875</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
@@ -14718,11 +14739,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>387.1199951171875</v>
+        <v>384.5899963378906</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
@@ -14739,11 +14760,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>384.5899963378906</v>
+        <v>377.3200073242188</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
@@ -14760,11 +14781,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>377.3200073242188</v>
+        <v>365.9200134277344</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
@@ -14781,11 +14802,11 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>365.9200134277344</v>
+        <v>369.4599914550781</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -14802,11 +14823,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>369.4599914550781</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
@@ -14823,11 +14844,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>373.6300048828125</v>
+        <v>368.5799865722656</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
@@ -14844,11 +14865,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>368.5799865722656</v>
+        <v>368.3800048828125</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
@@ -14865,11 +14886,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>368.3800048828125</v>
+        <v>370.6000061035156</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
@@ -14886,11 +14907,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>370.6000061035156</v>
+        <v>378.1300048828125</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
@@ -14907,11 +14928,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>378.1300048828125</v>
+        <v>382.1300048828125</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
@@ -14928,11 +14949,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>382.1300048828125</v>
+        <v>377.489990234375</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
@@ -14949,11 +14970,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>377.489990234375</v>
+        <v>374.4500122070312</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
@@ -14970,11 +14991,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>374.4500122070312</v>
+        <v>378.1799926757812</v>
       </c>
       <c r="C180" t="n">
         <v>1</v>
@@ -14991,11 +15012,11 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>378.1799926757812</v>
+        <v>377.010009765625</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
@@ -15012,11 +15033,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>377.010009765625</v>
+        <v>367.1300048828125</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -15033,11 +15054,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>367.1300048828125</v>
+        <v>372.1499938964844</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
@@ -15054,11 +15075,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>372.1499938964844</v>
+        <v>372.3500061035156</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
@@ -15075,11 +15096,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>372.3500061035156</v>
+        <v>364.9599914550781</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -15096,11 +15117,11 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>364.9599914550781</v>
+        <v>368.4100036621094</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
@@ -15117,11 +15138,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>368.4100036621094</v>
+        <v>367.6000061035156</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
@@ -15138,11 +15159,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>367.6000061035156</v>
+        <v>374.8099975585938</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -15159,11 +15180,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>374.8099975585938</v>
+        <v>379.1199951171875</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
@@ -15180,11 +15201,11 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>379.1199951171875</v>
+        <v>371.5199890136719</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -15201,11 +15222,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>371.5199890136719</v>
+        <v>371.8999938964844</v>
       </c>
       <c r="C191" t="n">
         <v>1</v>
@@ -15222,11 +15243,11 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>371.8999938964844</v>
+        <v>374.6300048828125</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
@@ -15243,11 +15264,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>374.6300048828125</v>
+        <v>369.3699951171875</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
@@ -15264,11 +15285,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>369.3699951171875</v>
+        <v>371.0799865722656</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -15285,11 +15306,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>371.0799865722656</v>
+        <v>377.1600036621094</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
@@ -15306,11 +15327,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>377.1600036621094</v>
+        <v>371.5400085449219</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
@@ -15327,11 +15348,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>371.5400085449219</v>
+        <v>371.7099914550781</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -15348,11 +15369,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>371.7099914550781</v>
+        <v>374.1600036621094</v>
       </c>
       <c r="C198" t="n">
         <v>1</v>
@@ -15369,11 +15390,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>374.1600036621094</v>
+        <v>389.6400146484375</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
@@ -15390,11 +15411,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>389.6400146484375</v>
+        <v>389.6700134277344</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
@@ -15411,11 +15432,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>389.6700134277344</v>
+        <v>398.4700012207031</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
@@ -15432,11 +15453,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>398.4700012207031</v>
+        <v>402.5400085449219</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
@@ -15453,11 +15474,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>402.5400085449219</v>
+        <v>400.9599914550781</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
@@ -15474,11 +15495,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>400.9599914550781</v>
+        <v>404.9200134277344</v>
       </c>
       <c r="C204" t="n">
         <v>1</v>
@@ -15495,11 +15516,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>404.9200134277344</v>
+        <v>398.9599914550781</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
@@ -15516,11 +15537,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>398.9599914550781</v>
+        <v>401.4800109863281</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
@@ -15537,11 +15558,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>401.4800109863281</v>
+        <v>405.489990234375</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
@@ -15558,11 +15579,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>405.489990234375</v>
+        <v>398.5499877929688</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
@@ -15579,11 +15600,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>398.5499877929688</v>
+        <v>413.8399963378906</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
@@ -15600,11 +15621,11 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>413.8399963378906</v>
+        <v>415.260009765625</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
@@ -15621,11 +15642,11 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>415.260009765625</v>
+        <v>423.3599853515625</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
@@ -15642,11 +15663,11 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>423.3599853515625</v>
+        <v>426.6900024414062</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
@@ -15663,11 +15684,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>426.6900024414062</v>
+        <v>428.0700073242188</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
@@ -15684,11 +15705,11 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>428.0700073242188</v>
+        <v>421.3200073242188</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
@@ -15705,11 +15726,11 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>421.3200073242188</v>
+        <v>422.6000061035156</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
@@ -15726,11 +15747,11 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>422.6000061035156</v>
+        <v>408.8900146484375</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
@@ -15747,11 +15768,11 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>408.8900146484375</v>
+        <v>408.4200134277344</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
@@ -15768,11 +15789,11 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>408.4200134277344</v>
+        <v>396.75</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
@@ -15789,11 +15810,11 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>396.75</v>
+        <v>402.7799987792969</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
@@ -15810,11 +15831,11 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>402.7799987792969</v>
+        <v>410.2200012207031</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
@@ -15831,11 +15852,11 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>410.2200012207031</v>
+        <v>406.7699890136719</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
@@ -15852,11 +15873,11 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>406.7699890136719</v>
+        <v>399.7200012207031</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
@@ -15873,11 +15894,11 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>399.7200012207031</v>
+        <v>403.3500061035156</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
@@ -15894,11 +15915,11 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>403.3500061035156</v>
+        <v>396.3599853515625</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
@@ -15915,11 +15936,11 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>396.3599853515625</v>
+        <v>398.7699890136719</v>
       </c>
       <c r="C225" t="n">
         <v>1</v>
@@ -15936,11 +15957,11 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>398.7699890136719</v>
+        <v>392.8399963378906</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
@@ -15957,11 +15978,11 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>392.8399963378906</v>
+        <v>394.1499938964844</v>
       </c>
       <c r="C227" t="n">
         <v>1</v>
@@ -15978,11 +15999,11 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>394.1499938964844</v>
+        <v>391.739990234375</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
@@ -15999,11 +16020,11 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>391.739990234375</v>
+        <v>398.3599853515625</v>
       </c>
       <c r="C229" t="n">
         <v>1</v>
@@ -16020,11 +16041,11 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>398.3599853515625</v>
+        <v>401.1700134277344</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
@@ -16041,11 +16062,11 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>401.1700134277344</v>
+        <v>398.3800048828125</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
@@ -16062,11 +16083,11 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>398.3800048828125</v>
+        <v>400.0700073242188</v>
       </c>
       <c r="C232" t="n">
         <v>1</v>
@@ -16083,11 +16104,11 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>400.0700073242188</v>
+        <v>392.8800048828125</v>
       </c>
       <c r="C233" t="n">
         <v>1</v>
@@ -16104,11 +16125,11 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>392.8800048828125</v>
+        <v>391.6900024414062</v>
       </c>
       <c r="C234" t="n">
         <v>1</v>
@@ -16125,11 +16146,11 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>391.6900024414062</v>
+        <v>393.4100036621094</v>
       </c>
       <c r="C235" t="n">
         <v>1</v>
@@ -16146,11 +16167,11 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>393.4100036621094</v>
+        <v>377.9100036621094</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
@@ -16167,11 +16188,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>377.9100036621094</v>
+        <v>382.8900146484375</v>
       </c>
       <c r="C237" t="n">
         <v>1</v>
@@ -16188,11 +16209,11 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>382.8900146484375</v>
+        <v>380.8399963378906</v>
       </c>
       <c r="C238" t="n">
         <v>1</v>
@@ -16209,11 +16230,11 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>380.8399963378906</v>
+        <v>382.760009765625</v>
       </c>
       <c r="C239" t="n">
         <v>1</v>
@@ -16230,11 +16251,11 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>382.760009765625</v>
+        <v>380.1400146484375</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
@@ -16251,11 +16272,11 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>380.1400146484375</v>
+        <v>379.5499877929688</v>
       </c>
       <c r="C241" t="n">
         <v>1</v>
@@ -16272,11 +16293,11 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>379.5499877929688</v>
+        <v>382.2699890136719</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
@@ -16293,11 +16314,11 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>382.2699890136719</v>
+        <v>375.8800048828125</v>
       </c>
       <c r="C243" t="n">
         <v>1</v>
@@ -16314,11 +16335,11 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>375.8800048828125</v>
+        <v>378.6199951171875</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
@@ -16335,11 +16356,11 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>378.6199951171875</v>
+        <v>384.5799865722656</v>
       </c>
       <c r="C245" t="n">
         <v>1</v>
@@ -16356,11 +16377,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>384.5799865722656</v>
+        <v>382.1499938964844</v>
       </c>
       <c r="C246" t="n">
         <v>1</v>
@@ -16377,11 +16398,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>382.1499938964844</v>
+        <v>381.6700134277344</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
@@ -16398,11 +16419,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>381.6700134277344</v>
+        <v>375.989990234375</v>
       </c>
       <c r="C248" t="n">
         <v>1</v>
@@ -16419,11 +16440,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>375.989990234375</v>
+        <v>382.7099914550781</v>
       </c>
       <c r="C249" t="n">
         <v>1</v>
@@ -16440,11 +16461,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>382.7099914550781</v>
+        <v>382.010009765625</v>
       </c>
       <c r="C250" t="n">
         <v>1</v>
@@ -16461,11 +16482,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>382.010009765625</v>
+        <v>379.6900024414062</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>

--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -471,11 +471,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>259.6700134277344</v>
+        <v>258.010009765625</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -490,18 +490,18 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D251/D48-1)*100</f>
+        <f>(D251/D47-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>258.010009765625</v>
+        <v>264.3299865722656</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -527,11 +527,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>264.3299865722656</v>
+        <v>254.8399963378906</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -557,11 +557,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>254.8399963378906</v>
+        <v>256.1199951171875</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -587,11 +587,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>256.1199951171875</v>
+        <v>259.6499938964844</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -608,11 +608,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>259.6499938964844</v>
+        <v>250.0500030517578</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -631,17 +631,17 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>137.7410838143822</v>
+        <v>150.7092674631942</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>250.0500030517578</v>
+        <v>256.3299865722656</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -660,17 +660,17 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>104.5981437978973</v>
+        <v>117.1466222239448</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>256.3299865722656</v>
+        <v>237.6999969482422</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -689,17 +689,17 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>67.52126269382606</v>
+        <v>67.70190881102532</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>237.6999969482422</v>
+        <v>233.5399932861328</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -716,11 +716,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>233.5399932861328</v>
+        <v>243.9799957275391</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -735,18 +735,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-27 01:29 UTC</t>
+          <t>Snapshot as of 2026-10-28 01:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>243.9799957275391</v>
+        <v>237.5200042724609</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -763,11 +763,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>237.5200042724609</v>
+        <v>258.8900146484375</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -784,11 +784,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>258.8900146484375</v>
+        <v>247.9600067138672</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -805,11 +805,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>247.9600067138672</v>
+        <v>246.8099975585938</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -826,11 +826,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>246.8099975585938</v>
+        <v>240.5200042724609</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -847,11 +847,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>240.5200042724609</v>
+        <v>230.2899932861328</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -868,11 +868,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>230.2899932861328</v>
+        <v>223.5500030517578</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -889,11 +889,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>223.5500030517578</v>
+        <v>206.0200042724609</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -910,11 +910,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>206.0200042724609</v>
+        <v>203.7799987792969</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -931,11 +931,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>203.7799987792969</v>
+        <v>215.0500030517578</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -952,11 +952,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>215.0500030517578</v>
+        <v>206.1300048828125</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -973,11 +973,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>206.1300048828125</v>
+        <v>214.2400054931641</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -994,11 +994,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>214.2400054931641</v>
+        <v>217.5299987792969</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1015,11 +1015,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>217.5299987792969</v>
+        <v>219.7599945068359</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1036,11 +1036,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>219.7599945068359</v>
+        <v>215.2400054931641</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1057,11 +1057,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>215.2400054931641</v>
+        <v>217.6000061035156</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1078,11 +1078,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>217.6000061035156</v>
+        <v>215.9799957275391</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>215.9799957275391</v>
+        <v>217.9700012207031</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1120,11 +1120,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>217.9700012207031</v>
+        <v>221.1100006103516</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1141,11 +1141,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>221.1100006103516</v>
+        <v>221.6199951171875</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1162,11 +1162,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>221.6199951171875</v>
+        <v>221.4199981689453</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -1183,11 +1183,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>221.4199981689453</v>
+        <v>221.4299926757812</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1204,11 +1204,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>221.4299926757812</v>
+        <v>210.7799987792969</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -1225,11 +1225,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>210.7799987792969</v>
+        <v>207.5800018310547</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1246,11 +1246,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>207.5800018310547</v>
+        <v>209.1699981689453</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1267,11 +1267,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>209.1699981689453</v>
+        <v>198.1100006103516</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1288,11 +1288,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>198.1100006103516</v>
+        <v>201.0599975585938</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -1309,11 +1309,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>201.0599975585938</v>
+        <v>213.4299926757812</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -1330,11 +1330,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>213.4299926757812</v>
+        <v>214.9499969482422</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1351,11 +1351,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>214.9499969482422</v>
+        <v>214.8999938964844</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1372,11 +1372,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>214.8999938964844</v>
+        <v>215.0399932861328</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1393,11 +1393,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>215.0399932861328</v>
+        <v>214.9900054931641</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1414,11 +1414,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>214.9900054931641</v>
+        <v>215.6100006103516</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -1435,11 +1435,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>215.6100006103516</v>
+        <v>215.3399963378906</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1456,11 +1456,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>215.3399963378906</v>
+        <v>214.1600036621094</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1477,11 +1477,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>214.1600036621094</v>
+        <v>223.4700012207031</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1498,11 +1498,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>223.4700012207031</v>
+        <v>221.0800018310547</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -1519,11 +1519,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>221.0800018310547</v>
+        <v>214.3500061035156</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -1540,11 +1540,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>214.3500061035156</v>
+        <v>210.0200042724609</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -1561,11 +1561,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>210.0200042724609</v>
+        <v>204.6799926757812</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -1582,11 +1582,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>204.6799926757812</v>
+        <v>203.1699981689453</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -1603,11 +1603,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>203.1699981689453</v>
+        <v>207.6900024414062</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -1624,11 +1624,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>207.6900024414062</v>
+        <v>220.9700012207031</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -1645,11 +1645,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>220.9700012207031</v>
+        <v>223.6000061035156</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -1666,11 +1666,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>223.6000061035156</v>
+        <v>227.9199981689453</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -1687,11 +1687,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>227.9199981689453</v>
+        <v>231.8300018310547</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -1708,11 +1708,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>231.8300018310547</v>
+        <v>231.9199981689453</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -1729,11 +1729,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>231.9199981689453</v>
+        <v>249.8000030517578</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -1750,11 +1750,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>249.8000030517578</v>
+        <v>253.7299957275391</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -1771,11 +1771,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>253.7299957275391</v>
+        <v>259.6799926757812</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -1792,11 +1792,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>259.6799926757812</v>
+        <v>251.3099975585938</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -1813,11 +1813,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>251.3099975585938</v>
+        <v>252.0299987792969</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -1834,11 +1834,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>252.0299987792969</v>
+        <v>252.7400054931641</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -1855,11 +1855,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>252.7400054931641</v>
+        <v>252.1799926757812</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -1876,11 +1876,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>252.1799926757812</v>
+        <v>236.7299957275391</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -1897,11 +1897,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>236.7299957275391</v>
+        <v>246.2700042724609</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -1918,11 +1918,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>246.2700042724609</v>
+        <v>242.1100006103516</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -1939,11 +1939,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>242.1100006103516</v>
+        <v>200.1900024414062</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -1960,11 +1960,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>200.1900024414062</v>
+        <v>192.5</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -1981,11 +1981,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>192.5</v>
+        <v>208.4400024414062</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -2002,11 +2002,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>208.4400024414062</v>
+        <v>216</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
@@ -2023,11 +2023,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>216</v>
+        <v>213.5700073242188</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
@@ -2044,11 +2044,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>213.5700073242188</v>
+        <v>213.5800018310547</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
@@ -2065,11 +2065,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>213.5800018310547</v>
+        <v>205.9400024414062</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -2086,11 +2086,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>205.9400024414062</v>
+        <v>207.3200073242188</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
@@ -2107,11 +2107,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>207.3200073242188</v>
+        <v>203.0800018310547</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -2128,11 +2128,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>203.0800018310547</v>
+        <v>200.1199951171875</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -2149,11 +2149,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>200.1199951171875</v>
+        <v>203.3699951171875</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -2170,11 +2170,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>203.3699951171875</v>
+        <v>200.1499938964844</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -2191,11 +2191,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>200.1499938964844</v>
+        <v>196.6000061035156</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -2212,11 +2212,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>196.6000061035156</v>
+        <v>213.8399963378906</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -2233,11 +2233,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>213.8399963378906</v>
+        <v>210.8600006103516</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -2254,11 +2254,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>210.8600006103516</v>
+        <v>203.6799926757812</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
@@ -2275,11 +2275,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>203.6799926757812</v>
+        <v>200.2100067138672</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -2296,11 +2296,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>200.2100067138672</v>
+        <v>198.6199951171875</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -2317,11 +2317,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>198.6199951171875</v>
+        <v>190.9499969482422</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
@@ -2338,11 +2338,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>190.9499969482422</v>
+        <v>202.0700073242188</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -2359,11 +2359,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>202.0700073242188</v>
+        <v>199.4499969482422</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
@@ -2380,11 +2380,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>199.4499969482422</v>
+        <v>192.4299926757812</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -2401,11 +2401,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>192.4299926757812</v>
+        <v>202.6799926757812</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -2422,11 +2422,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>202.6799926757812</v>
+        <v>203.2299957275391</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -2443,11 +2443,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>203.2299957275391</v>
+        <v>204.8300018310547</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -2464,11 +2464,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>204.8300018310547</v>
+        <v>197.7400054931641</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -2485,11 +2485,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>197.7400054931641</v>
+        <v>193.3899993896484</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
@@ -2506,11 +2506,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>193.3899993896484</v>
+        <v>196.5800018310547</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -2527,11 +2527,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>196.5800018310547</v>
+        <v>196.3099975585938</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -2548,11 +2548,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>196.3099975585938</v>
+        <v>199.4600067138672</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
@@ -2569,11 +2569,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>199.4600067138672</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
@@ -2590,11 +2590,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>205.2700042724609</v>
+        <v>201.3300018310547</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -2611,11 +2611,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>201.3300018310547</v>
+        <v>202.6799926757812</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -2632,11 +2632,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>202.6799926757812</v>
+        <v>205.3699951171875</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
@@ -2653,11 +2653,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>205.3699951171875</v>
+        <v>220.2700042724609</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -2674,11 +2674,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>220.2700042724609</v>
+        <v>203.7700042724609</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
@@ -2695,11 +2695,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>203.7700042724609</v>
+        <v>201.9900054931641</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
@@ -2716,11 +2716,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>201.9900054931641</v>
+        <v>196.0399932861328</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
@@ -2737,11 +2737,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>196.0399932861328</v>
+        <v>203.4299926757812</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -2758,11 +2758,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>203.4299926757812</v>
+        <v>210.2100067138672</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
@@ -2779,11 +2779,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>210.2100067138672</v>
+        <v>217.5</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
@@ -2800,11 +2800,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>217.5</v>
+        <v>220.1799926757812</v>
       </c>
       <c r="C110" t="n">
         <v>1</v>
@@ -2821,11 +2821,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>220.1799926757812</v>
+        <v>221.5299987792969</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
@@ -2842,11 +2842,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>221.5299987792969</v>
+        <v>231.8200073242188</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
@@ -2863,11 +2863,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>231.8200073242188</v>
+        <v>236.6399993896484</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
@@ -2884,11 +2884,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>236.6399993896484</v>
+        <v>245.0399932861328</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -2905,11 +2905,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>245.0399932861328</v>
+        <v>246.8300018310547</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -2926,11 +2926,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>246.8300018310547</v>
+        <v>255.0700073242188</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
@@ -2947,11 +2947,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>255.0700073242188</v>
+        <v>258.1199951171875</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
@@ -2968,11 +2968,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>258.1199951171875</v>
+        <v>278.260009765625</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
@@ -2989,11 +2989,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>278.260009765625</v>
+        <v>278.3900146484375</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -3010,11 +3010,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>278.3900146484375</v>
+        <v>274.9500122070312</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -3031,11 +3031,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>274.9500122070312</v>
+        <v>284.489990234375</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
@@ -3052,11 +3052,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>284.489990234375</v>
+        <v>303.4599914550781</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
@@ -3073,11 +3073,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>303.4599914550781</v>
+        <v>305.3299865722656</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -3094,11 +3094,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>305.3299865722656</v>
+        <v>347.8099975585938</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -3115,11 +3115,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>347.8099975585938</v>
+        <v>334.6300048828125</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -3136,11 +3136,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>334.6300048828125</v>
+        <v>323.2099914550781</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -3157,11 +3157,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>323.2099914550781</v>
+        <v>337.1099853515625</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -3178,11 +3178,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>337.1099853515625</v>
+        <v>354.489990234375</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
@@ -3199,11 +3199,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>354.489990234375</v>
+        <v>360.5400085449219</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -3220,11 +3220,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>360.5400085449219</v>
+        <v>341.5400085449219</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -3241,11 +3241,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>341.5400085449219</v>
+        <v>355.260009765625</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -3262,11 +3262,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>355.260009765625</v>
+        <v>421.3900146484375</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
@@ -3283,11 +3283,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>421.3900146484375</v>
+        <v>408.4599914550781</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -3304,11 +3304,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>408.4599914550781</v>
+        <v>455.1900024414062</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
@@ -3325,11 +3325,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>455.1900024414062</v>
+        <v>458.7900085449219</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
@@ -3346,11 +3346,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>458.7900085449219</v>
+        <v>448.2900085449219</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -3367,11 +3367,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>448.2900085449219</v>
+        <v>445.5</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
@@ -3388,11 +3388,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>445.5</v>
+        <v>449.7000122070312</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
@@ -3409,11 +3409,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>449.7000122070312</v>
+        <v>424.1000061035156</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
@@ -3430,11 +3430,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>424.1000061035156</v>
+        <v>420.989990234375</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -3451,11 +3451,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>420.989990234375</v>
+        <v>414.0499877929688</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
@@ -3472,11 +3472,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>414.0499877929688</v>
+        <v>447.5799865722656</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
@@ -3493,11 +3493,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>447.5799865722656</v>
+        <v>449.5899963378906</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -3514,11 +3514,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>449.5899963378906</v>
+        <v>467.510009765625</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
@@ -3535,11 +3535,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>467.510009765625</v>
+        <v>503.8900146484375</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
@@ -3556,11 +3556,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>503.8900146484375</v>
+        <v>495.5400085449219</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
@@ -3577,11 +3577,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>495.5400085449219</v>
+        <v>518.0900268554688</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
@@ -3598,11 +3598,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>518.0900268554688</v>
+        <v>516.0999755859375</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
@@ -3619,11 +3619,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>516.0999755859375</v>
+        <v>510.1300048828125</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
@@ -3640,11 +3640,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>510.1300048828125</v>
+        <v>521.5399780273438</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -3661,11 +3661,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>521.5399780273438</v>
+        <v>542.52001953125</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -3682,11 +3682,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>542.52001953125</v>
+        <v>523.2000122070312</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -3703,11 +3703,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>523.2000122070312</v>
+        <v>466.3800048828125</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
@@ -3724,11 +3724,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>466.3800048828125</v>
+        <v>490.3299865722656</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
@@ -3745,11 +3745,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>490.3299865722656</v>
+        <v>475.510009765625</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
@@ -3766,11 +3766,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>475.510009765625</v>
+        <v>452.3999938964844</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
@@ -3787,11 +3787,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>452.3999938964844</v>
+        <v>488.4500122070312</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -3808,11 +3808,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>488.4500122070312</v>
+        <v>511.5700073242188</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -3829,11 +3829,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>511.5700073242188</v>
+        <v>547.260009765625</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
@@ -3850,11 +3850,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>547.260009765625</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
@@ -3871,11 +3871,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>507.2900085449219</v>
+        <v>512.47998046875</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -3892,11 +3892,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>512.47998046875</v>
+        <v>537.3699951171875</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -3913,11 +3913,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>537.3699951171875</v>
+        <v>551.6300048828125</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -3934,11 +3934,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>551.6300048828125</v>
+        <v>519.8499755859375</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
@@ -3955,11 +3955,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>519.8499755859375</v>
+        <v>519.739990234375</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -3976,11 +3976,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>519.739990234375</v>
+        <v>532.5700073242188</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
@@ -3997,11 +3997,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>532.5700073242188</v>
+        <v>521.5800170898438</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
@@ -4018,11 +4018,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>521.5800170898438</v>
+        <v>539.489990234375</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
@@ -4039,11 +4039,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>539.489990234375</v>
+        <v>580.9099731445312</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
@@ -4060,11 +4060,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>580.9099731445312</v>
+        <v>540.8800048828125</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
@@ -4081,11 +4081,11 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>540.8800048828125</v>
+        <v>517.8200073242188</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -4102,11 +4102,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>517.8200073242188</v>
+        <v>552.0499877929688</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
@@ -4123,11 +4123,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>552.0499877929688</v>
+        <v>516.1099853515625</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
@@ -4144,11 +4144,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>516.1099853515625</v>
+        <v>517.4099731445312</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
@@ -4165,11 +4165,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>517.4099731445312</v>
+        <v>546.719970703125</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
@@ -4186,11 +4186,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>546.719970703125</v>
+        <v>557.8900146484375</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
@@ -4207,11 +4207,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>557.8900146484375</v>
+        <v>534.3900146484375</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
@@ -4228,11 +4228,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>534.3900146484375</v>
+        <v>548.1300048828125</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
@@ -4249,11 +4249,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>548.1300048828125</v>
+        <v>529.1400146484375</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
@@ -4270,11 +4270,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>529.1400146484375</v>
+        <v>500.9400024414062</v>
       </c>
       <c r="C180" t="n">
         <v>1</v>
@@ -4291,11 +4291,11 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>500.9400024414062</v>
+        <v>495.760009765625</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
@@ -4312,11 +4312,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>495.760009765625</v>
+        <v>503.5700073242188</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -4333,11 +4333,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>503.5700073242188</v>
+        <v>544.4299926757812</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
@@ -4354,11 +4354,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>544.4299926757812</v>
+        <v>552.3300170898438</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
@@ -4375,11 +4375,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>552.3300170898438</v>
+        <v>539.6900024414062</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -4396,11 +4396,11 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>539.6900024414062</v>
+        <v>521.9500122070312</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
@@ -4417,11 +4417,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>521.9500122070312</v>
+        <v>494.9500122070312</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
@@ -4438,11 +4438,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>494.9500122070312</v>
+        <v>454.6199951171875</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -4459,11 +4459,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>454.6199951171875</v>
+        <v>429.5599975585938</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
@@ -4480,11 +4480,11 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>429.5599975585938</v>
+        <v>485.3900146484375</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -4501,11 +4501,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>485.3900146484375</v>
+        <v>476.1499938964844</v>
       </c>
       <c r="C191" t="n">
         <v>1</v>
@@ -4522,11 +4522,11 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>476.1499938964844</v>
+        <v>484.6400146484375</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
@@ -4543,11 +4543,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>484.6400146484375</v>
+        <v>518.5800170898438</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
@@ -4564,11 +4564,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>518.5800170898438</v>
+        <v>482.0499877929688</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -4585,11 +4585,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>482.0499877929688</v>
+        <v>489.2799987792969</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
@@ -4606,11 +4606,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>489.2799987792969</v>
+        <v>483.3599853515625</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
@@ -4627,11 +4627,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>483.3599853515625</v>
+        <v>469.5599975585938</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -4648,11 +4648,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>469.5599975585938</v>
+        <v>474.3200073242188</v>
       </c>
       <c r="C198" t="n">
         <v>1</v>
@@ -4669,11 +4669,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>474.3200073242188</v>
+        <v>482.9299926757812</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
@@ -4690,11 +4690,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>482.9299926757812</v>
+        <v>483.010009765625</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
@@ -4711,11 +4711,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>483.010009765625</v>
+        <v>514.3900146484375</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
@@ -4732,11 +4732,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>514.3900146484375</v>
+        <v>506</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
@@ -4753,11 +4753,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>506</v>
+        <v>484.3900146484375</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
@@ -4774,11 +4774,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>484.3900146484375</v>
+        <v>466.4200134277344</v>
       </c>
       <c r="C204" t="n">
         <v>1</v>
@@ -4795,11 +4795,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>466.4200134277344</v>
+        <v>469.4599914550781</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
@@ -4816,11 +4816,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>469.4599914550781</v>
+        <v>473.25</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
@@ -4837,11 +4837,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>473.25</v>
+        <v>456.75</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
@@ -4858,11 +4858,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>456.75</v>
+        <v>479.1799926757812</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
@@ -4879,11 +4879,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>479.1799926757812</v>
+        <v>480.9299926757812</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
@@ -4900,11 +4900,11 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>480.9299926757812</v>
+        <v>476.6700134277344</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
@@ -4921,11 +4921,11 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>476.6700134277344</v>
+        <v>465.5799865722656</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
@@ -4942,11 +4942,11 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>465.5799865722656</v>
+        <v>470.7200012207031</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
@@ -4963,11 +4963,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>470.7200012207031</v>
+        <v>459.6099853515625</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
@@ -4984,11 +4984,11 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>459.6099853515625</v>
+        <v>457.0599975585938</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
@@ -5005,11 +5005,11 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>457.0599975585938</v>
+        <v>456.1600036621094</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
@@ -5026,11 +5026,11 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>456.1600036621094</v>
+        <v>477.5700073242188</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
@@ -5047,11 +5047,11 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>477.5700073242188</v>
+        <v>505.739990234375</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
@@ -5068,11 +5068,11 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>505.739990234375</v>
+        <v>521.0999755859375</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
@@ -5089,11 +5089,11 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>521.0999755859375</v>
+        <v>503.6000061035156</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
@@ -5110,11 +5110,11 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>503.6000061035156</v>
+        <v>516.1300048828125</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
@@ -5131,11 +5131,11 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>516.1300048828125</v>
+        <v>493.4100036621094</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
@@ -5152,11 +5152,11 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>493.4100036621094</v>
+        <v>504.2000122070312</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
@@ -5173,11 +5173,11 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>504.2000122070312</v>
+        <v>512.5</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
@@ -5194,11 +5194,11 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>512.5</v>
+        <v>545.0900268554688</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
@@ -5215,11 +5215,11 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>545.0900268554688</v>
+        <v>559.8200073242188</v>
       </c>
       <c r="C225" t="n">
         <v>1</v>
@@ -5236,11 +5236,11 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>559.8200073242188</v>
+        <v>615.52001953125</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
@@ -5257,11 +5257,11 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>615.52001953125</v>
+        <v>623.77001953125</v>
       </c>
       <c r="C227" t="n">
         <v>1</v>
@@ -5278,11 +5278,11 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>623.77001953125</v>
+        <v>614.6099853515625</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
@@ -5299,11 +5299,11 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>614.6099853515625</v>
+        <v>629.260009765625</v>
       </c>
       <c r="C229" t="n">
         <v>1</v>
@@ -5320,11 +5320,11 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>629.260009765625</v>
+        <v>630.6300048828125</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
@@ -5341,11 +5341,11 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>630.6300048828125</v>
+        <v>607.8699951171875</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
@@ -5362,11 +5362,11 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>607.8699951171875</v>
+        <v>607.5700073242188</v>
       </c>
       <c r="C232" t="n">
         <v>1</v>
@@ -5383,11 +5383,11 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>607.5700073242188</v>
+        <v>611.760009765625</v>
       </c>
       <c r="C233" t="n">
         <v>1</v>
@@ -5404,11 +5404,11 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>611.760009765625</v>
+        <v>615.72998046875</v>
       </c>
       <c r="C234" t="n">
         <v>1</v>
@@ -5425,11 +5425,11 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>615.72998046875</v>
+        <v>633.9099731445312</v>
       </c>
       <c r="C235" t="n">
         <v>1</v>
@@ -5446,11 +5446,11 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>633.9099731445312</v>
+        <v>631.75</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
@@ -5467,11 +5467,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>631.75</v>
+        <v>649.4199829101562</v>
       </c>
       <c r="C237" t="n">
         <v>1</v>
@@ -5488,11 +5488,11 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>649.4199829101562</v>
+        <v>645.8599853515625</v>
       </c>
       <c r="C238" t="n">
         <v>1</v>
@@ -5509,11 +5509,11 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>645.8599853515625</v>
+        <v>620.6799926757812</v>
       </c>
       <c r="C239" t="n">
         <v>1</v>
@@ -5530,11 +5530,11 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>620.6799926757812</v>
+        <v>608.0999755859375</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
@@ -5551,11 +5551,11 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>608.0999755859375</v>
+        <v>594.239990234375</v>
       </c>
       <c r="C241" t="n">
         <v>1</v>
@@ -5572,11 +5572,11 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>594.239990234375</v>
+        <v>605.530029296875</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
@@ -5593,11 +5593,11 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>605.530029296875</v>
+        <v>570.8200073242188</v>
       </c>
       <c r="C243" t="n">
         <v>1</v>
@@ -5614,11 +5614,11 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>570.8200073242188</v>
+        <v>562.22998046875</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
@@ -5635,11 +5635,11 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>562.22998046875</v>
+        <v>528.75</v>
       </c>
       <c r="C245" t="n">
         <v>1</v>
@@ -5656,11 +5656,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>528.75</v>
+        <v>538.0499877929688</v>
       </c>
       <c r="C246" t="n">
         <v>1</v>
@@ -5677,11 +5677,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>538.0499877929688</v>
+        <v>534.739990234375</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
@@ -5698,11 +5698,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>534.739990234375</v>
+        <v>552.719970703125</v>
       </c>
       <c r="C248" t="n">
         <v>1</v>
@@ -5719,11 +5719,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>552.719970703125</v>
+        <v>507.9299926757812</v>
       </c>
       <c r="C249" t="n">
         <v>1</v>
@@ -5740,11 +5740,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>507.9299926757812</v>
+        <v>516.7899780273438</v>
       </c>
       <c r="C250" t="n">
         <v>1</v>
@@ -5761,11 +5761,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>516.7899780273438</v>
+        <v>531.280029296875</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>
@@ -5790,7 +5790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5849,7 +5849,7 @@
         <v>27.34431648254395</v>
       </c>
       <c r="C2" t="n">
-        <v>5.388299942016602</v>
+        <v>5.373300075531006</v>
       </c>
       <c r="D2">
         <f>B2/C2</f>
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D249/D46-1)*100</f>
+        <f>(D250/D46-1)*100</f>
         <v/>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="H3">
-        <f>(D249/D2-1)*100</f>
+        <f>(D250/D2-1)*100</f>
         <v/>
       </c>
     </row>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="H4">
-        <f>(COUNT(D2:D249)-1)/((DATEVALUE(A249)-DATEVALUE(A2))/365.25)</f>
+        <f>(COUNT(D2:D250)-1)/((DATEVALUE(A250)-DATEVALUE(A2))/365.25)</f>
         <v/>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
         </is>
       </c>
       <c r="H5">
-        <f>STDEV.S(E3:E249)*SQRT(H4)*100</f>
+        <f>STDEV.S(E3:E250)*SQRT(H4)*100</f>
         <v/>
       </c>
     </row>
@@ -5962,7 +5962,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.11644554138184</v>
+        <v>27.11644744873047</v>
       </c>
       <c r="C6" t="n">
         <v>5.381999969482422</v>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.43546676635742</v>
+        <v>27.43546485900879</v>
       </c>
       <c r="C7" t="n">
         <v>5.374599933624268</v>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>107.5400274844234</v>
+        <v>87.73300208923806</v>
       </c>
     </row>
     <row r="8">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>114.0490755369194</v>
+        <v>93.08184172888882</v>
       </c>
     </row>
     <row r="9">
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>32.84296257894807</v>
+        <v>34.39090818440647</v>
       </c>
     </row>
     <row r="10">
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28.26490783691406</v>
+        <v>28.2649097442627</v>
       </c>
       <c r="C10" t="n">
         <v>5.35860013961792</v>
@@ -6106,7 +6106,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-27 01:29 UTC</t>
+          <t>Snapshot as of 2026-10-28 01:21 UTC</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.26104354858398</v>
+        <v>30.26104545593262</v>
       </c>
       <c r="C13" t="n">
         <v>5.289700031280518</v>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.61389541625977</v>
+        <v>29.6138973236084</v>
       </c>
       <c r="C15" t="n">
         <v>5.291299819946289</v>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29.8053035736084</v>
+        <v>29.80530548095703</v>
       </c>
       <c r="C16" t="n">
         <v>5.296500205993652</v>
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29.65946960449219</v>
+        <v>29.65946769714355</v>
       </c>
       <c r="C21" t="n">
         <v>5.402100086212158</v>
@@ -6390,7 +6390,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28.97586441040039</v>
+        <v>28.97586250305176</v>
       </c>
       <c r="C25" t="n">
         <v>5.355400085449219</v>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.16464424133301</v>
+        <v>28.16464614868164</v>
       </c>
       <c r="C39" t="n">
         <v>5.518499851226807</v>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.26490783691406</v>
+        <v>28.2649097442627</v>
       </c>
       <c r="C40" t="n">
         <v>5.521299839019775</v>
@@ -11105,6 +11105,27 @@
       </c>
       <c r="E249">
         <f>LN(D249/D248)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>52.79000091552734</v>
+      </c>
+      <c r="C250" t="n">
+        <v>5.372600078582764</v>
+      </c>
+      <c r="D250">
+        <f>B250/C250</f>
+        <v/>
+      </c>
+      <c r="E250">
+        <f>LN(D250/D249)</f>
         <v/>
       </c>
     </row>
@@ -11171,11 +11192,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>367.010009765625</v>
+        <v>364.3800048828125</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -11190,18 +11211,18 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D251/D48-1)*100</f>
+        <f>(D251/D47-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>364.3800048828125</v>
+        <v>363</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -11227,11 +11248,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>363</v>
+        <v>370.1300048828125</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -11257,11 +11278,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>370.1300048828125</v>
+        <v>368.1199951171875</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -11287,11 +11308,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>368.1199951171875</v>
+        <v>368.7799987792969</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -11308,11 +11329,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>368.7799987792969</v>
+        <v>362.3200073242188</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -11331,17 +11352,17 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-7.647885909410461</v>
+        <v>-6.528070704027318</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>362.3200073242188</v>
+        <v>366.510009765625</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -11360,17 +11381,17 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.2207024331762084</v>
+        <v>2.168066304407481</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>366.510009765625</v>
+        <v>366.0700073242188</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -11389,17 +11410,17 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>28.58428506716411</v>
+        <v>28.60044428620008</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>366.0700073242188</v>
+        <v>368.3099975585938</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -11416,11 +11437,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>368.3099975585938</v>
+        <v>378.3800048828125</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -11435,18 +11456,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-27 01:29 UTC</t>
+          <t>Snapshot as of 2026-10-28 01:21 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>378.3800048828125</v>
+        <v>379.8699951171875</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -11463,11 +11484,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>379.8699951171875</v>
+        <v>385.989990234375</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -11484,11 +11505,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>385.989990234375</v>
+        <v>382.8699951171875</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -11505,11 +11526,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>382.8699951171875</v>
+        <v>375.9599914550781</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -11526,11 +11547,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>375.9599914550781</v>
+        <v>371.6499938964844</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -11547,11 +11568,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>371.6499938964844</v>
+        <v>374.3500061035156</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -11568,11 +11589,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>374.3500061035156</v>
+        <v>374.9599914550781</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -11589,11 +11610,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>374.9599914550781</v>
+        <v>374.8500061035156</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -11610,11 +11631,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>374.8500061035156</v>
+        <v>374.2699890136719</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -11631,11 +11652,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>374.2699890136719</v>
+        <v>380.2000122070312</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -11652,11 +11673,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>380.2000122070312</v>
+        <v>380.0799865722656</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -11673,11 +11694,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>380.0799865722656</v>
+        <v>383.1199951171875</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -11694,11 +11715,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>383.1199951171875</v>
+        <v>387.8800048828125</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -11715,11 +11736,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>387.8800048828125</v>
+        <v>389.75</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -11736,11 +11757,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>389.75</v>
+        <v>387.239990234375</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -11757,11 +11778,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>387.239990234375</v>
+        <v>386.8800048828125</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -11778,11 +11799,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>386.8800048828125</v>
+        <v>387.1300048828125</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -11799,11 +11820,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>387.1300048828125</v>
+        <v>386.4400024414062</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -11820,11 +11841,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>386.4400024414062</v>
+        <v>385.4200134277344</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -11841,11 +11862,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>385.4200134277344</v>
+        <v>387.3999938964844</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -11862,11 +11883,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>387.3999938964844</v>
+        <v>389.0499877929688</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -11883,11 +11904,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>389.0499877929688</v>
+        <v>393.239990234375</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -11904,11 +11925,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>393.239990234375</v>
+        <v>395.4400024414062</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -11925,11 +11946,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>395.4400024414062</v>
+        <v>395.7999877929688</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -11946,11 +11967,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>395.7999877929688</v>
+        <v>395.8900146484375</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -11967,11 +11988,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>395.8900146484375</v>
+        <v>399.2900085449219</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -11988,11 +12009,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>399.2900085449219</v>
+        <v>398.5700073242188</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -12009,11 +12030,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>398.5700073242188</v>
+        <v>399.0199890136719</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -12030,11 +12051,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>399.0199890136719</v>
+        <v>408.2300109863281</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -12051,11 +12072,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>408.2300109863281</v>
+        <v>413.6400146484375</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -12072,11 +12093,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>413.6400146484375</v>
+        <v>411.9299926757812</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -12093,11 +12114,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>411.9299926757812</v>
+        <v>416.739990234375</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -12114,11 +12135,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>416.739990234375</v>
+        <v>398.6000061035156</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -12135,11 +12156,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>398.6000061035156</v>
+        <v>398.8900146484375</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -12156,11 +12177,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>398.8900146484375</v>
+        <v>396.3099975585938</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -12177,11 +12198,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>396.3099975585938</v>
+        <v>398.2799987792969</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -12198,11 +12219,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>398.2799987792969</v>
+        <v>408.760009765625</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -12219,11 +12240,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>408.760009765625</v>
+        <v>413.1799926757812</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -12240,11 +12261,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>413.1799926757812</v>
+        <v>409.2300109863281</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -12261,11 +12282,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>409.2300109863281</v>
+        <v>411.489990234375</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -12282,11 +12303,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>411.489990234375</v>
+        <v>414.4700012207031</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -12303,11 +12324,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>414.4700012207031</v>
+        <v>422.2300109863281</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -12324,11 +12345,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>422.2300109863281</v>
+        <v>421.6300048828125</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -12345,11 +12366,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>421.6300048828125</v>
+        <v>425.9400024414062</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -12366,11 +12387,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>425.9400024414062</v>
+        <v>423.3299865722656</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -12387,11 +12408,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>423.3299865722656</v>
+        <v>421.2900085449219</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -12408,11 +12429,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>421.2900085449219</v>
+        <v>437.2300109863281</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -12429,11 +12450,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>437.2300109863281</v>
+        <v>443.6000061035156</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -12450,11 +12471,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>443.6000061035156</v>
+        <v>451.7900085449219</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -12471,11 +12492,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>451.7900085449219</v>
+        <v>458</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -12492,11 +12513,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>458</v>
+        <v>464.7000122070312</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -12513,11 +12534,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>464.7000122070312</v>
+        <v>476.1000061035156</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -12534,11 +12555,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>476.1000061035156</v>
+        <v>494.5599975585938</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -12555,11 +12576,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>494.5599975585938</v>
+        <v>495.8999938964844</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -12576,11 +12597,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>495.8999938964844</v>
+        <v>444.9500122070312</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -12597,11 +12618,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>444.9500122070312</v>
+        <v>427.1300048828125</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -12618,11 +12639,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>427.1300048828125</v>
+        <v>454.2900085449219</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -12639,11 +12660,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>454.2900085449219</v>
+        <v>453.9700012207031</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -12660,11 +12681,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>453.9700012207031</v>
+        <v>441.8800048828125</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -12681,11 +12702,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>441.8800048828125</v>
+        <v>455.4599914550781</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -12702,11 +12723,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>455.4599914550781</v>
+        <v>467.0299987792969</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
@@ -12723,11 +12744,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>467.0299987792969</v>
+        <v>462.3999938964844</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
@@ -12744,11 +12765,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>462.3999938964844</v>
+        <v>467.6300048828125</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
@@ -12765,11 +12786,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>467.6300048828125</v>
+        <v>451.3900146484375</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -12786,11 +12807,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>451.3900146484375</v>
+        <v>462.6199951171875</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
@@ -12807,11 +12828,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>462.6199951171875</v>
+        <v>448.2000122070312</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -12828,11 +12849,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>448.2000122070312</v>
+        <v>458.2799987792969</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -12849,11 +12870,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>458.2799987792969</v>
+        <v>459.5599975585938</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -12870,11 +12891,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>459.5599975585938</v>
+        <v>468.6199951171875</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -12891,11 +12912,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>468.6199951171875</v>
+        <v>481.2799987792969</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -12912,11 +12933,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>481.2799987792969</v>
+        <v>474.6099853515625</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -12933,11 +12954,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>474.6099853515625</v>
+        <v>473.4200134277344</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -12954,11 +12975,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>473.4200134277344</v>
+        <v>477.4800109863281</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
@@ -12975,11 +12996,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>477.4800109863281</v>
+        <v>483.75</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -12996,11 +13017,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>483.75</v>
+        <v>490</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -13017,11 +13038,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>490</v>
+        <v>468.1400146484375</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
@@ -13038,11 +13059,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>468.1400146484375</v>
+        <v>471.7999877929688</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -13059,11 +13080,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>471.7999877929688</v>
+        <v>466.1300048828125</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
@@ -13080,11 +13101,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>466.1300048828125</v>
+        <v>473.510009765625</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -13101,11 +13122,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>473.510009765625</v>
+        <v>472.5299987792969</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -13122,11 +13143,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>472.5299987792969</v>
+        <v>477.8599853515625</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -13143,11 +13164,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>477.8599853515625</v>
+        <v>476.239990234375</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -13164,11 +13185,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>476.239990234375</v>
+        <v>466.8800048828125</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -13185,11 +13206,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>466.8800048828125</v>
+        <v>460.8399963378906</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
@@ -13206,11 +13227,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>460.8399963378906</v>
+        <v>460.4299926757812</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -13227,11 +13248,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>460.4299926757812</v>
+        <v>459.2699890136719</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -13248,11 +13269,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>459.2699890136719</v>
+        <v>444.739990234375</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
@@ -13269,11 +13290,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>444.739990234375</v>
+        <v>426.4100036621094</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
@@ -13290,11 +13311,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>426.4100036621094</v>
+        <v>413.3800048828125</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -13311,11 +13332,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>413.3800048828125</v>
+        <v>404.0400085449219</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -13332,11 +13353,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>404.0400085449219</v>
+        <v>404.1300048828125</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
@@ -13353,11 +13374,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>404.1300048828125</v>
+        <v>416.2900085449219</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -13374,11 +13395,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>416.2900085449219</v>
+        <v>400.6400146484375</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
@@ -13395,11 +13416,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>400.6400146484375</v>
+        <v>414.7000122070312</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
@@ -13416,11 +13437,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>414.7000122070312</v>
+        <v>414.5799865722656</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
@@ -13437,11 +13458,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>414.5799865722656</v>
+        <v>430.2900085449219</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -13458,11 +13479,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>430.2900085449219</v>
+        <v>437.8200073242188</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
@@ -13479,11 +13500,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>437.8200073242188</v>
+        <v>429.4100036621094</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
@@ -13500,11 +13521,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>429.4100036621094</v>
+        <v>427.6499938964844</v>
       </c>
       <c r="C110" t="n">
         <v>1</v>
@@ -13521,11 +13542,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>427.6499938964844</v>
+        <v>431.8099975585938</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
@@ -13542,11 +13563,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>431.8099975585938</v>
+        <v>434.5299987792969</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
@@ -13563,11 +13584,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>434.5299987792969</v>
+        <v>437.9100036621094</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
@@ -13584,11 +13605,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>437.9100036621094</v>
+        <v>437.1300048828125</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -13605,11 +13626,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>437.1300048828125</v>
+        <v>435.3599853515625</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -13626,11 +13647,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>435.3599853515625</v>
+        <v>445.0899963378906</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
@@ -13647,11 +13668,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>445.0899963378906</v>
+        <v>440.4599914550781</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
@@ -13668,11 +13689,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>440.4599914550781</v>
+        <v>440.0799865722656</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
@@ -13689,11 +13710,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>440.0799865722656</v>
+        <v>445.9299926757812</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -13710,11 +13731,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>445.9299926757812</v>
+        <v>442.0899963378906</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -13731,11 +13752,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>442.0899963378906</v>
+        <v>429.5700073242188</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
@@ -13752,11 +13773,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>429.5700073242188</v>
+        <v>435.260009765625</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
@@ -13773,11 +13794,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>435.260009765625</v>
+        <v>431.0400085449219</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -13794,11 +13815,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>431.0400085449219</v>
+        <v>433.25</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -13815,11 +13836,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>433.25</v>
+        <v>429.8900146484375</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -13836,11 +13857,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>429.8900146484375</v>
+        <v>421.9100036621094</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -13857,11 +13878,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>421.9100036621094</v>
+        <v>417.4100036621094</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -13878,11 +13899,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>417.4100036621094</v>
+        <v>423.6600036621094</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
@@ -13899,11 +13920,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>423.6600036621094</v>
+        <v>423.1799926757812</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -13920,11 +13941,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>423.1799926757812</v>
+        <v>414.7099914550781</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -13941,11 +13962,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>414.7099914550781</v>
+        <v>418.2699890136719</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -13962,11 +13983,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>418.2699890136719</v>
+        <v>430.9599914550781</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
@@ -13983,11 +14004,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>430.9599914550781</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -14004,11 +14025,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>431.6799926757812</v>
+        <v>433.7699890136719</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
@@ -14025,11 +14046,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>433.7699890136719</v>
+        <v>434.6499938964844</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
@@ -14046,11 +14067,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>434.6499938964844</v>
+        <v>432.9299926757812</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -14067,11 +14088,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>432.9299926757812</v>
+        <v>430.5</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
@@ -14088,11 +14109,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>430.5</v>
+        <v>427.2099914550781</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
@@ -14109,11 +14130,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>427.2099914550781</v>
+        <v>417.2900085449219</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
@@ -14130,11 +14151,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>417.2900085449219</v>
+        <v>418.4299926757812</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -14151,11 +14172,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>418.4299926757812</v>
+        <v>411.5</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
@@ -14172,11 +14193,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>411.5</v>
+        <v>417.3999938964844</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
@@ -14193,11 +14214,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>417.3999938964844</v>
+        <v>416.989990234375</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -14214,11 +14235,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>416.989990234375</v>
+        <v>413.8200073242188</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
@@ -14235,11 +14256,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>413.8200073242188</v>
+        <v>414</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
@@ -14256,11 +14277,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>414</v>
+        <v>408.489990234375</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
@@ -14277,11 +14298,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>408.489990234375</v>
+        <v>412.7699890136719</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
@@ -14298,11 +14319,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>412.7699890136719</v>
+        <v>417.1199951171875</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
@@ -14319,11 +14340,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>417.1199951171875</v>
+        <v>411.260009765625</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
@@ -14340,11 +14361,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>411.260009765625</v>
+        <v>411.9500122070312</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -14361,11 +14382,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>411.9500122070312</v>
+        <v>407.8699951171875</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -14382,11 +14403,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>407.8699951171875</v>
+        <v>411.2699890136719</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -14403,11 +14424,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>411.2699890136719</v>
+        <v>396.239990234375</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
@@ -14424,11 +14445,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>396.239990234375</v>
+        <v>397.2699890136719</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
@@ -14445,11 +14466,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>397.2699890136719</v>
+        <v>390.7799987792969</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
@@ -14466,11 +14487,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>390.7799987792969</v>
+        <v>374.5799865722656</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
@@ -14487,11 +14508,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>374.5799865722656</v>
+        <v>386.3200073242188</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -14508,11 +14529,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>386.3200073242188</v>
+        <v>386.5400085449219</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -14529,11 +14550,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>386.5400085449219</v>
+        <v>396.5499877929688</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
@@ -14550,11 +14571,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>396.5499877929688</v>
+        <v>397.6300048828125</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
@@ -14571,11 +14592,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>397.6300048828125</v>
+        <v>388.6000061035156</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -14592,11 +14613,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>388.6000061035156</v>
+        <v>387.1199951171875</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -14613,11 +14634,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>387.1199951171875</v>
+        <v>384.5899963378906</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -14634,11 +14655,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>384.5899963378906</v>
+        <v>377.3200073242188</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
@@ -14655,11 +14676,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>377.3200073242188</v>
+        <v>365.9200134277344</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -14676,11 +14697,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>365.9200134277344</v>
+        <v>369.4599914550781</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
@@ -14697,11 +14718,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>369.4599914550781</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
@@ -14718,11 +14739,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>373.6300048828125</v>
+        <v>368.5799865722656</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
@@ -14739,11 +14760,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>368.5799865722656</v>
+        <v>368.3800048828125</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
@@ -14760,11 +14781,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>368.3800048828125</v>
+        <v>370.6000061035156</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
@@ -14781,11 +14802,11 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>370.6000061035156</v>
+        <v>378.1300048828125</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -14802,11 +14823,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>378.1300048828125</v>
+        <v>382.1300048828125</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
@@ -14823,11 +14844,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>382.1300048828125</v>
+        <v>377.489990234375</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
@@ -14844,11 +14865,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>377.489990234375</v>
+        <v>374.4500122070312</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
@@ -14865,11 +14886,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>374.4500122070312</v>
+        <v>378.1799926757812</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
@@ -14886,11 +14907,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>378.1799926757812</v>
+        <v>377.010009765625</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
@@ -14907,11 +14928,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>377.010009765625</v>
+        <v>367.1300048828125</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
@@ -14928,11 +14949,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>367.1300048828125</v>
+        <v>372.1499938964844</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
@@ -14949,11 +14970,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>372.1499938964844</v>
+        <v>372.3500061035156</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
@@ -14970,11 +14991,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>372.3500061035156</v>
+        <v>364.9599914550781</v>
       </c>
       <c r="C180" t="n">
         <v>1</v>
@@ -14991,11 +15012,11 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>364.9599914550781</v>
+        <v>368.4100036621094</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
@@ -15012,11 +15033,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>368.4100036621094</v>
+        <v>367.6000061035156</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -15033,11 +15054,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>367.6000061035156</v>
+        <v>374.8099975585938</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
@@ -15054,11 +15075,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>374.8099975585938</v>
+        <v>379.1199951171875</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
@@ -15075,11 +15096,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>379.1199951171875</v>
+        <v>371.5199890136719</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -15096,11 +15117,11 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>371.5199890136719</v>
+        <v>371.8999938964844</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
@@ -15117,11 +15138,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>371.8999938964844</v>
+        <v>374.6300048828125</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
@@ -15138,11 +15159,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>374.6300048828125</v>
+        <v>369.3699951171875</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -15159,11 +15180,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>369.3699951171875</v>
+        <v>371.0799865722656</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
@@ -15180,11 +15201,11 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>371.0799865722656</v>
+        <v>377.1600036621094</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -15201,11 +15222,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>377.1600036621094</v>
+        <v>371.5400085449219</v>
       </c>
       <c r="C191" t="n">
         <v>1</v>
@@ -15222,11 +15243,11 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>371.5400085449219</v>
+        <v>371.7099914550781</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
@@ -15243,11 +15264,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>371.7099914550781</v>
+        <v>374.1600036621094</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
@@ -15264,11 +15285,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>374.1600036621094</v>
+        <v>389.6400146484375</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -15285,11 +15306,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>389.6400146484375</v>
+        <v>389.6700134277344</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
@@ -15306,11 +15327,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>389.6700134277344</v>
+        <v>398.4700012207031</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
@@ -15327,11 +15348,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>398.4700012207031</v>
+        <v>402.5400085449219</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -15348,11 +15369,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>402.5400085449219</v>
+        <v>400.9599914550781</v>
       </c>
       <c r="C198" t="n">
         <v>1</v>
@@ -15369,11 +15390,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>400.9599914550781</v>
+        <v>404.9200134277344</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
@@ -15390,11 +15411,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>404.9200134277344</v>
+        <v>398.9599914550781</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
@@ -15411,11 +15432,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>398.9599914550781</v>
+        <v>401.4800109863281</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
@@ -15432,11 +15453,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>401.4800109863281</v>
+        <v>405.489990234375</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
@@ -15453,11 +15474,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>405.489990234375</v>
+        <v>398.5499877929688</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
@@ -15474,11 +15495,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>398.5499877929688</v>
+        <v>413.8399963378906</v>
       </c>
       <c r="C204" t="n">
         <v>1</v>
@@ -15495,11 +15516,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>413.8399963378906</v>
+        <v>415.260009765625</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
@@ -15516,11 +15537,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>415.260009765625</v>
+        <v>423.3599853515625</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
@@ -15537,11 +15558,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>423.3599853515625</v>
+        <v>426.6900024414062</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
@@ -15558,11 +15579,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>426.6900024414062</v>
+        <v>428.0700073242188</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
@@ -15579,11 +15600,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>428.0700073242188</v>
+        <v>421.3200073242188</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
@@ -15600,11 +15621,11 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>421.3200073242188</v>
+        <v>422.6000061035156</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
@@ -15621,11 +15642,11 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>422.6000061035156</v>
+        <v>408.8900146484375</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
@@ -15642,11 +15663,11 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>408.8900146484375</v>
+        <v>408.4200134277344</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
@@ -15663,11 +15684,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>408.4200134277344</v>
+        <v>396.75</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
@@ -15684,11 +15705,11 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>396.75</v>
+        <v>402.7799987792969</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
@@ -15705,11 +15726,11 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>402.7799987792969</v>
+        <v>410.2200012207031</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
@@ -15726,11 +15747,11 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>410.2200012207031</v>
+        <v>406.7699890136719</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
@@ -15747,11 +15768,11 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>406.7699890136719</v>
+        <v>399.7200012207031</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
@@ -15768,11 +15789,11 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>399.7200012207031</v>
+        <v>403.3500061035156</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
@@ -15789,11 +15810,11 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>403.3500061035156</v>
+        <v>396.3599853515625</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
@@ -15810,11 +15831,11 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>396.3599853515625</v>
+        <v>398.7699890136719</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
@@ -15831,11 +15852,11 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>398.7699890136719</v>
+        <v>392.8399963378906</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
@@ -15852,11 +15873,11 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>392.8399963378906</v>
+        <v>394.1499938964844</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
@@ -15873,11 +15894,11 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>394.1499938964844</v>
+        <v>391.739990234375</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
@@ -15894,11 +15915,11 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>391.739990234375</v>
+        <v>398.3599853515625</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
@@ -15915,11 +15936,11 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>398.3599853515625</v>
+        <v>401.1700134277344</v>
       </c>
       <c r="C225" t="n">
         <v>1</v>
@@ -15936,11 +15957,11 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>401.1700134277344</v>
+        <v>398.3800048828125</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
@@ -15957,11 +15978,11 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>398.3800048828125</v>
+        <v>400.0700073242188</v>
       </c>
       <c r="C227" t="n">
         <v>1</v>
@@ -15978,11 +15999,11 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>400.0700073242188</v>
+        <v>392.8800048828125</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
@@ -15999,11 +16020,11 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>392.8800048828125</v>
+        <v>391.6900024414062</v>
       </c>
       <c r="C229" t="n">
         <v>1</v>
@@ -16020,11 +16041,11 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>391.6900024414062</v>
+        <v>393.4100036621094</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
@@ -16041,11 +16062,11 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>393.4100036621094</v>
+        <v>377.9100036621094</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
@@ -16062,11 +16083,11 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>377.9100036621094</v>
+        <v>382.8900146484375</v>
       </c>
       <c r="C232" t="n">
         <v>1</v>
@@ -16083,11 +16104,11 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>382.8900146484375</v>
+        <v>380.8399963378906</v>
       </c>
       <c r="C233" t="n">
         <v>1</v>
@@ -16104,11 +16125,11 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>380.8399963378906</v>
+        <v>382.760009765625</v>
       </c>
       <c r="C234" t="n">
         <v>1</v>
@@ -16125,11 +16146,11 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>382.760009765625</v>
+        <v>380.1400146484375</v>
       </c>
       <c r="C235" t="n">
         <v>1</v>
@@ -16146,11 +16167,11 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>380.1400146484375</v>
+        <v>379.5499877929688</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
@@ -16167,11 +16188,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>379.5499877929688</v>
+        <v>382.2699890136719</v>
       </c>
       <c r="C237" t="n">
         <v>1</v>
@@ -16188,11 +16209,11 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>382.2699890136719</v>
+        <v>375.8800048828125</v>
       </c>
       <c r="C238" t="n">
         <v>1</v>
@@ -16209,11 +16230,11 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>375.8800048828125</v>
+        <v>378.6199951171875</v>
       </c>
       <c r="C239" t="n">
         <v>1</v>
@@ -16230,11 +16251,11 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>378.6199951171875</v>
+        <v>384.5799865722656</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
@@ -16251,11 +16272,11 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>384.5799865722656</v>
+        <v>382.1499938964844</v>
       </c>
       <c r="C241" t="n">
         <v>1</v>
@@ -16272,11 +16293,11 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>382.1499938964844</v>
+        <v>381.6700134277344</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
@@ -16293,11 +16314,11 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>381.6700134277344</v>
+        <v>375.989990234375</v>
       </c>
       <c r="C243" t="n">
         <v>1</v>
@@ -16314,11 +16335,11 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>375.989990234375</v>
+        <v>382.7099914550781</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
@@ -16335,11 +16356,11 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>382.7099914550781</v>
+        <v>382.010009765625</v>
       </c>
       <c r="C245" t="n">
         <v>1</v>
@@ -16356,11 +16377,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>382.010009765625</v>
+        <v>379.6900024414062</v>
       </c>
       <c r="C246" t="n">
         <v>1</v>
@@ -16377,11 +16398,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>379.6900024414062</v>
+        <v>377.6499938964844</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
@@ -16398,11 +16419,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>377.6499938964844</v>
+        <v>378.9500122070312</v>
       </c>
       <c r="C248" t="n">
         <v>1</v>
@@ -16419,11 +16440,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>378.9500122070312</v>
+        <v>369</v>
       </c>
       <c r="C249" t="n">
         <v>1</v>
@@ -16440,11 +16461,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>369</v>
+        <v>366.6099853515625</v>
       </c>
       <c r="C250" t="n">
         <v>1</v>
@@ -16461,11 +16482,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>366.6099853515625</v>
+        <v>367.8200073242188</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>

--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="AMD" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="GLD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PETR4_SA" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="GLD" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,7 +735,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-28 23:18 UTC</t>
+          <t>Snapshot as of 2026-10-29 01:48 UTC</t>
         </is>
       </c>
     </row>
@@ -5805,6 +5806,5356 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H250"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>local close (total return)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>USD per local</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>USD close</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>log return</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>measure</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Excel</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>27.33520317077637</v>
+      </c>
+      <c r="C2" t="n">
+        <v>5.357399940490723</v>
+      </c>
+      <c r="D2">
+        <f>B2/C2</f>
+        <v/>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>YTD %</t>
+        </is>
+      </c>
+      <c r="H2">
+        <f>(D250/D45-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>27.36254692077637</v>
+      </c>
+      <c r="C3" t="n">
+        <v>5.357399940490723</v>
+      </c>
+      <c r="D3">
+        <f>B3/C3</f>
+        <v/>
+      </c>
+      <c r="E3">
+        <f>LN(D3/D2)</f>
+        <v/>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1-year %</t>
+        </is>
+      </c>
+      <c r="H3">
+        <f>(D250/D2-1)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>27.24405288696289</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5.357800006866455</v>
+      </c>
+      <c r="D4">
+        <f>B4/C4</f>
+        <v/>
+      </c>
+      <c r="E4">
+        <f>LN(D4/D3)</f>
+        <v/>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>observations per year</t>
+        </is>
+      </c>
+      <c r="H4">
+        <f>(COUNT(D2:D250)-1)/((DATEVALUE(A250)-DATEVALUE(A2))/365.25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>27.11644554138184</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5.381999969482422</v>
+      </c>
+      <c r="D5">
+        <f>B5/C5</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>LN(D5/D4)</f>
+        <v/>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>volatility %</t>
+        </is>
+      </c>
+      <c r="H5">
+        <f>STDEV.S(E3:E250)*SQRT(H4)*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>27.43546676635742</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.374599933624268</v>
+      </c>
+      <c r="D6">
+        <f>B6/C6</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>LN(D6/D5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>27.57218551635742</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.354899883270264</v>
+      </c>
+      <c r="D7">
+        <f>B7/C7</f>
+        <v/>
+      </c>
+      <c r="E7">
+        <f>LN(D7/D6)</f>
+        <v/>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>pipeline YTD %</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>87.51557884207661</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>28.11907196044922</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5.395899772644043</v>
+      </c>
+      <c r="D8">
+        <f>B8/C8</f>
+        <v/>
+      </c>
+      <c r="E8">
+        <f>LN(D8/D7)</f>
+        <v/>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>pipeline 1-year %</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>92.35155499432163</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>28.26490783691406</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.35860013961792</v>
+      </c>
+      <c r="D9">
+        <f>B9/C9</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>LN(D9/D8)</f>
+        <v/>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>pipeline volatility %</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>34.39185795373886</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>29.33133697509766</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5.349500179290771</v>
+      </c>
+      <c r="D10">
+        <f>B10/C10</f>
+        <v/>
+      </c>
+      <c r="E10">
+        <f>LN(D10/D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>29.49540519714355</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5.330900192260742</v>
+      </c>
+      <c r="D11">
+        <f>B11/C11</f>
+        <v/>
+      </c>
+      <c r="E11">
+        <f>LN(D11/D10)</f>
+        <v/>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Snapshot as of 2026-10-29 01:48 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>30.26104354858398</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.289700031280518</v>
+      </c>
+      <c r="D12">
+        <f>B12/C12</f>
+        <v/>
+      </c>
+      <c r="E12">
+        <f>LN(D12/D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>29.48628425598145</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5.270699977874756</v>
+      </c>
+      <c r="D13">
+        <f>B13/C13</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>LN(D13/D12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>29.61389541625977</v>
+      </c>
+      <c r="C14" t="n">
+        <v>5.291299819946289</v>
+      </c>
+      <c r="D14">
+        <f>B14/C14</f>
+        <v/>
+      </c>
+      <c r="E14">
+        <f>LN(D14/D13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>29.8053035736084</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5.296500205993652</v>
+      </c>
+      <c r="D15">
+        <f>B15/C15</f>
+        <v/>
+      </c>
+      <c r="E15">
+        <f>LN(D15/D14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>29.9693717956543</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5.295599937438965</v>
+      </c>
+      <c r="D16">
+        <f>B16/C16</f>
+        <v/>
+      </c>
+      <c r="E16">
+        <f>LN(D16/D15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>30.06963539123535</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5.329500198364258</v>
+      </c>
+      <c r="D17">
+        <f>B17/C17</f>
+        <v/>
+      </c>
+      <c r="E17">
+        <f>LN(D17/D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>29.9146842956543</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5.321499824523926</v>
+      </c>
+      <c r="D18">
+        <f>B18/C18</f>
+        <v/>
+      </c>
+      <c r="E18">
+        <f>LN(D18/D17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>29.68681144714355</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.332300186157227</v>
+      </c>
+      <c r="D19">
+        <f>B19/C19</f>
+        <v/>
+      </c>
+      <c r="E19">
+        <f>LN(D19/D18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>29.65946960449219</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5.402100086212158</v>
+      </c>
+      <c r="D20">
+        <f>B20/C20</f>
+        <v/>
+      </c>
+      <c r="E20">
+        <f>LN(D20/D19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>29.42248344421387</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.386799812316895</v>
+      </c>
+      <c r="D21">
+        <f>B21/C21</f>
+        <v/>
+      </c>
+      <c r="E21">
+        <f>LN(D21/D20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>29.37690925598145</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.37939977645874</v>
+      </c>
+      <c r="D22">
+        <f>B22/C22</f>
+        <v/>
+      </c>
+      <c r="E22">
+        <f>LN(D22/D21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>29.53186416625977</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5.33080005645752</v>
+      </c>
+      <c r="D23">
+        <f>B23/C23</f>
+        <v/>
+      </c>
+      <c r="E23">
+        <f>LN(D23/D22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>28.97586441040039</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5.355400085449219</v>
+      </c>
+      <c r="D24">
+        <f>B24/C24</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>LN(D24/D23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>29.03055000305176</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5.335400104522705</v>
+      </c>
+      <c r="D25">
+        <f>B25/C25</f>
+        <v/>
+      </c>
+      <c r="E25">
+        <f>LN(D25/D24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>29.2310733795166</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5.355800151824951</v>
+      </c>
+      <c r="D26">
+        <f>B26/C26</f>
+        <v/>
+      </c>
+      <c r="E26">
+        <f>LN(D26/D25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>29.4498291015625</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5.326300144195557</v>
+      </c>
+      <c r="D27">
+        <f>B27/C27</f>
+        <v/>
+      </c>
+      <c r="E27">
+        <f>LN(D27/D26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>29.64123916625977</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5.306099891662598</v>
+      </c>
+      <c r="D28">
+        <f>B28/C28</f>
+        <v/>
+      </c>
+      <c r="E28">
+        <f>LN(D28/D27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>28.59304237365723</v>
+      </c>
+      <c r="C29" t="n">
+        <v>5.309299945831299</v>
+      </c>
+      <c r="D29">
+        <f>B29/C29</f>
+        <v/>
+      </c>
+      <c r="E29">
+        <f>LN(D29/D28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>28.85736846923828</v>
+      </c>
+      <c r="C30" t="n">
+        <v>5.43809986114502</v>
+      </c>
+      <c r="D30">
+        <f>B30/C30</f>
+        <v/>
+      </c>
+      <c r="E30">
+        <f>LN(D30/D29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>29.03966522216797</v>
+      </c>
+      <c r="C31" t="n">
+        <v>5.429999828338623</v>
+      </c>
+      <c r="D31">
+        <f>B31/C31</f>
+        <v/>
+      </c>
+      <c r="E31">
+        <f>LN(D31/D30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>29.11258316040039</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5.43149995803833</v>
+      </c>
+      <c r="D32">
+        <f>B32/C32</f>
+        <v/>
+      </c>
+      <c r="E32">
+        <f>LN(D32/D31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>28.6294994354248</v>
+      </c>
+      <c r="C33" t="n">
+        <v>5.469799995422363</v>
+      </c>
+      <c r="D33">
+        <f>B33/C33</f>
+        <v/>
+      </c>
+      <c r="E33">
+        <f>LN(D33/D32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>28.79356575012207</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5.405499935150146</v>
+      </c>
+      <c r="D34">
+        <f>B34/C34</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>LN(D34/D33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>28.89382934570312</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5.418200016021729</v>
+      </c>
+      <c r="D35">
+        <f>B35/C35</f>
+        <v/>
+      </c>
+      <c r="E35">
+        <f>LN(D35/D34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>28.0188102722168</v>
+      </c>
+      <c r="C36" t="n">
+        <v>5.413400173187256</v>
+      </c>
+      <c r="D36">
+        <f>B36/C36</f>
+        <v/>
+      </c>
+      <c r="E36">
+        <f>LN(D36/D35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>28.32871055603027</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5.507500171661377</v>
+      </c>
+      <c r="D37">
+        <f>B37/C37</f>
+        <v/>
+      </c>
+      <c r="E37">
+        <f>LN(D37/D36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>28.16464424133301</v>
+      </c>
+      <c r="C38" t="n">
+        <v>5.518499851226807</v>
+      </c>
+      <c r="D38">
+        <f>B38/C38</f>
+        <v/>
+      </c>
+      <c r="E38">
+        <f>LN(D38/D37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025-12-19</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>28.26490783691406</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5.521299839019775</v>
+      </c>
+      <c r="D39">
+        <f>B39/C39</f>
+        <v/>
+      </c>
+      <c r="E39">
+        <f>LN(D39/D38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>28.34694290161133</v>
+      </c>
+      <c r="C40" t="n">
+        <v>5.53980016708374</v>
+      </c>
+      <c r="D40">
+        <f>B40/C40</f>
+        <v/>
+      </c>
+      <c r="E40">
+        <f>LN(D40/D39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025-12-23</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>28.4993839263916</v>
+      </c>
+      <c r="C41" t="n">
+        <v>5.590000152587891</v>
+      </c>
+      <c r="D41">
+        <f>B41/C41</f>
+        <v/>
+      </c>
+      <c r="E41">
+        <f>LN(D41/D40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>28.59341049194336</v>
+      </c>
+      <c r="C42" t="n">
+        <v>5.519499778747559</v>
+      </c>
+      <c r="D42">
+        <f>B42/C42</f>
+        <v/>
+      </c>
+      <c r="E42">
+        <f>LN(D42/D41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>28.89429473876953</v>
+      </c>
+      <c r="C43" t="n">
+        <v>5.542500019073486</v>
+      </c>
+      <c r="D43">
+        <f>B43/C43</f>
+        <v/>
+      </c>
+      <c r="E43">
+        <f>LN(D43/D42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>28.97891998291016</v>
+      </c>
+      <c r="C44" t="n">
+        <v>5.569099903106689</v>
+      </c>
+      <c r="D44">
+        <f>B44/C44</f>
+        <v/>
+      </c>
+      <c r="E44">
+        <f>LN(D44/D43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>28.87549018859863</v>
+      </c>
+      <c r="C45" t="n">
+        <v>5.517000198364258</v>
+      </c>
+      <c r="D45">
+        <f>B45/C45</f>
+        <v/>
+      </c>
+      <c r="E45">
+        <f>LN(D45/D44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>28.39595603942871</v>
+      </c>
+      <c r="C46" t="n">
+        <v>5.421599864959717</v>
+      </c>
+      <c r="D46">
+        <f>B46/C46</f>
+        <v/>
+      </c>
+      <c r="E46">
+        <f>LN(D46/D45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>27.86940765380859</v>
+      </c>
+      <c r="C47" t="n">
+        <v>5.40749979019165</v>
+      </c>
+      <c r="D47">
+        <f>B47/C47</f>
+        <v/>
+      </c>
+      <c r="E47">
+        <f>LN(D47/D46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>28.04805755615234</v>
+      </c>
+      <c r="C48" t="n">
+        <v>5.372000217437744</v>
+      </c>
+      <c r="D48">
+        <f>B48/C48</f>
+        <v/>
+      </c>
+      <c r="E48">
+        <f>LN(D48/D47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>28.39595603942871</v>
+      </c>
+      <c r="C49" t="n">
+        <v>5.383900165557861</v>
+      </c>
+      <c r="D49">
+        <f>B49/C49</f>
+        <v/>
+      </c>
+      <c r="E49">
+        <f>LN(D49/D48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>28.48998069763184</v>
+      </c>
+      <c r="C50" t="n">
+        <v>5.386600017547607</v>
+      </c>
+      <c r="D50">
+        <f>B50/C50</f>
+        <v/>
+      </c>
+      <c r="E50">
+        <f>LN(D50/D49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>28.5463981628418</v>
+      </c>
+      <c r="C51" t="n">
+        <v>5.370299816131592</v>
+      </c>
+      <c r="D51">
+        <f>B51/C51</f>
+        <v/>
+      </c>
+      <c r="E51">
+        <f>LN(D51/D50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>29.2798023223877</v>
+      </c>
+      <c r="C52" t="n">
+        <v>5.373700141906738</v>
+      </c>
+      <c r="D52">
+        <f>B52/C52</f>
+        <v/>
+      </c>
+      <c r="E52">
+        <f>LN(D52/D51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>30.07902717590332</v>
+      </c>
+      <c r="C53" t="n">
+        <v>5.371300220489502</v>
+      </c>
+      <c r="D53">
+        <f>B53/C53</f>
+        <v/>
+      </c>
+      <c r="E53">
+        <f>LN(D53/D52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>29.89097595214844</v>
+      </c>
+      <c r="C54" t="n">
+        <v>5.396100044250488</v>
+      </c>
+      <c r="D54">
+        <f>B54/C54</f>
+        <v/>
+      </c>
+      <c r="E54">
+        <f>LN(D54/D53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>30.12604141235352</v>
+      </c>
+      <c r="C55" t="n">
+        <v>5.367899894714355</v>
+      </c>
+      <c r="D55">
+        <f>B55/C55</f>
+        <v/>
+      </c>
+      <c r="E55">
+        <f>LN(D55/D54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>30.24827194213867</v>
+      </c>
+      <c r="C56" t="n">
+        <v>5.367700099945068</v>
+      </c>
+      <c r="D56">
+        <f>B56/C56</f>
+        <v/>
+      </c>
+      <c r="E56">
+        <f>LN(D56/D55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>30.36110687255859</v>
+      </c>
+      <c r="C57" t="n">
+        <v>5.36870002746582</v>
+      </c>
+      <c r="D57">
+        <f>B57/C57</f>
+        <v/>
+      </c>
+      <c r="E57">
+        <f>LN(D57/D56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>31.43300819396973</v>
+      </c>
+      <c r="C58" t="n">
+        <v>5.374300003051758</v>
+      </c>
+      <c r="D58">
+        <f>B58/C58</f>
+        <v/>
+      </c>
+      <c r="E58">
+        <f>LN(D58/D57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>31.57404708862305</v>
+      </c>
+      <c r="C59" t="n">
+        <v>5.31879997253418</v>
+      </c>
+      <c r="D59">
+        <f>B59/C59</f>
+        <v/>
+      </c>
+      <c r="E59">
+        <f>LN(D59/D58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>32.94683456420898</v>
+      </c>
+      <c r="C60" t="n">
+        <v>5.283699989318848</v>
+      </c>
+      <c r="D60">
+        <f>B60/C60</f>
+        <v/>
+      </c>
+      <c r="E60">
+        <f>LN(D60/D59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>33.24771499633789</v>
+      </c>
+      <c r="C61" t="n">
+        <v>5.288899898529053</v>
+      </c>
+      <c r="D61">
+        <f>B61/C61</f>
+        <v/>
+      </c>
+      <c r="E61">
+        <f>LN(D61/D60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>33.97171783447266</v>
+      </c>
+      <c r="C62" t="n">
+        <v>5.279099941253662</v>
+      </c>
+      <c r="D62">
+        <f>B62/C62</f>
+        <v/>
+      </c>
+      <c r="E62">
+        <f>LN(D62/D61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>35.10943603515625</v>
+      </c>
+      <c r="C63" t="n">
+        <v>5.183599948883057</v>
+      </c>
+      <c r="D63">
+        <f>B63/C63</f>
+        <v/>
+      </c>
+      <c r="E63">
+        <f>LN(D63/D62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>35.44793319702148</v>
+      </c>
+      <c r="C64" t="n">
+        <v>5.197100162506104</v>
+      </c>
+      <c r="D64">
+        <f>B64/C64</f>
+        <v/>
+      </c>
+      <c r="E64">
+        <f>LN(D64/D63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>35.50434494018555</v>
+      </c>
+      <c r="C65" t="n">
+        <v>5.189199924468994</v>
+      </c>
+      <c r="D65">
+        <f>B65/C65</f>
+        <v/>
+      </c>
+      <c r="E65">
+        <f>LN(D65/D64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>35.01541137695312</v>
+      </c>
+      <c r="C66" t="n">
+        <v>5.255000114440918</v>
+      </c>
+      <c r="D66">
+        <f>B66/C66</f>
+        <v/>
+      </c>
+      <c r="E66">
+        <f>LN(D66/D65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>35.33510208129883</v>
+      </c>
+      <c r="C67" t="n">
+        <v>5.259399890899658</v>
+      </c>
+      <c r="D67">
+        <f>B67/C67</f>
+        <v/>
+      </c>
+      <c r="E67">
+        <f>LN(D67/D66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>35.27868270874023</v>
+      </c>
+      <c r="C68" t="n">
+        <v>5.237500190734863</v>
+      </c>
+      <c r="D68">
+        <f>B68/C68</f>
+        <v/>
+      </c>
+      <c r="E68">
+        <f>LN(D68/D67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>34.78974533081055</v>
+      </c>
+      <c r="C69" t="n">
+        <v>5.23799991607666</v>
+      </c>
+      <c r="D69">
+        <f>B69/C69</f>
+        <v/>
+      </c>
+      <c r="E69">
+        <f>LN(D69/D68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>34.46065521240234</v>
+      </c>
+      <c r="C70" t="n">
+        <v>5.270500183105469</v>
+      </c>
+      <c r="D70">
+        <f>B70/C70</f>
+        <v/>
+      </c>
+      <c r="E70">
+        <f>LN(D70/D69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>35.09063339233398</v>
+      </c>
+      <c r="C71" t="n">
+        <v>5.21589994430542</v>
+      </c>
+      <c r="D71">
+        <f>B71/C71</f>
+        <v/>
+      </c>
+      <c r="E71">
+        <f>LN(D71/D70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>35.11883926391602</v>
+      </c>
+      <c r="C72" t="n">
+        <v>5.19159984588623</v>
+      </c>
+      <c r="D72">
+        <f>B72/C72</f>
+        <v/>
+      </c>
+      <c r="E72">
+        <f>LN(D72/D71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>35.80523300170898</v>
+      </c>
+      <c r="C73" t="n">
+        <v>5.196199893951416</v>
+      </c>
+      <c r="D73">
+        <f>B73/C73</f>
+        <v/>
+      </c>
+      <c r="E73">
+        <f>LN(D73/D72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>34.89317321777344</v>
+      </c>
+      <c r="C74" t="n">
+        <v>5.198699951171875</v>
+      </c>
+      <c r="D74">
+        <f>B74/C74</f>
+        <v/>
+      </c>
+      <c r="E74">
+        <f>LN(D74/D73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>34.68631744384766</v>
+      </c>
+      <c r="C75" t="n">
+        <v>5.213900089263916</v>
+      </c>
+      <c r="D75">
+        <f>B75/C75</f>
+        <v/>
+      </c>
+      <c r="E75">
+        <f>LN(D75/D74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>34.9683952331543</v>
+      </c>
+      <c r="C76" t="n">
+        <v>5.220499992370605</v>
+      </c>
+      <c r="D76">
+        <f>B76/C76</f>
+        <v/>
+      </c>
+      <c r="E76">
+        <f>LN(D76/D75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>35.55136108398438</v>
+      </c>
+      <c r="C77" t="n">
+        <v>5.234399795532227</v>
+      </c>
+      <c r="D77">
+        <f>B77/C77</f>
+        <v/>
+      </c>
+      <c r="E77">
+        <f>LN(D77/D76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>35.70180130004883</v>
+      </c>
+      <c r="C78" t="n">
+        <v>5.208799839019775</v>
+      </c>
+      <c r="D78">
+        <f>B78/C78</f>
+        <v/>
+      </c>
+      <c r="E78">
+        <f>LN(D78/D77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>36.28476715087891</v>
+      </c>
+      <c r="C79" t="n">
+        <v>5.176499843597412</v>
+      </c>
+      <c r="D79">
+        <f>B79/C79</f>
+        <v/>
+      </c>
+      <c r="E79">
+        <f>LN(D79/D78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>37.20622634887695</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5.170899868011475</v>
+      </c>
+      <c r="D80">
+        <f>B80/C80</f>
+        <v/>
+      </c>
+      <c r="E80">
+        <f>LN(D80/D79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>37.20622634887695</v>
+      </c>
+      <c r="C81" t="n">
+        <v>5.151999950408936</v>
+      </c>
+      <c r="D81">
+        <f>B81/C81</f>
+        <v/>
+      </c>
+      <c r="E81">
+        <f>LN(D81/D80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>37.24383544921875</v>
+      </c>
+      <c r="C82" t="n">
+        <v>5.124199867248535</v>
+      </c>
+      <c r="D82">
+        <f>B82/C82</f>
+        <v/>
+      </c>
+      <c r="E82">
+        <f>LN(D82/D81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>36.98056030273438</v>
+      </c>
+      <c r="C83" t="n">
+        <v>5.136600017547607</v>
+      </c>
+      <c r="D83">
+        <f>B83/C83</f>
+        <v/>
+      </c>
+      <c r="E83">
+        <f>LN(D83/D82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>38.67303466796875</v>
+      </c>
+      <c r="C84" t="n">
+        <v>5.129600048065186</v>
+      </c>
+      <c r="D84">
+        <f>B84/C84</f>
+        <v/>
+      </c>
+      <c r="E84">
+        <f>LN(D84/D83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>38.50378799438477</v>
+      </c>
+      <c r="C85" t="n">
+        <v>5.170300006866455</v>
+      </c>
+      <c r="D85">
+        <f>B85/C85</f>
+        <v/>
+      </c>
+      <c r="E85">
+        <f>LN(D85/D84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>38.08066940307617</v>
+      </c>
+      <c r="C86" t="n">
+        <v>5.277299880981445</v>
+      </c>
+      <c r="D86">
+        <f>B86/C86</f>
+        <v/>
+      </c>
+      <c r="E86">
+        <f>LN(D86/D85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>38.25931930541992</v>
+      </c>
+      <c r="C87" t="n">
+        <v>5.230100154876709</v>
+      </c>
+      <c r="D87">
+        <f>B87/C87</f>
+        <v/>
+      </c>
+      <c r="E87">
+        <f>LN(D87/D86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>39.64150619506836</v>
+      </c>
+      <c r="C88" t="n">
+        <v>5.263400077819824</v>
+      </c>
+      <c r="D88">
+        <f>B88/C88</f>
+        <v/>
+      </c>
+      <c r="E88">
+        <f>LN(D88/D87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>40.58177185058594</v>
+      </c>
+      <c r="C89" t="n">
+        <v>5.243500232696533</v>
+      </c>
+      <c r="D89">
+        <f>B89/C89</f>
+        <v/>
+      </c>
+      <c r="E89">
+        <f>LN(D89/D88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>40.36550903320312</v>
+      </c>
+      <c r="C90" t="n">
+        <v>5.205299854278564</v>
+      </c>
+      <c r="D90">
+        <f>B90/C90</f>
+        <v/>
+      </c>
+      <c r="E90">
+        <f>LN(D90/D89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>42.12380218505859</v>
+      </c>
+      <c r="C91" t="n">
+        <v>5.162399768829346</v>
+      </c>
+      <c r="D91">
+        <f>B91/C91</f>
+        <v/>
+      </c>
+      <c r="E91">
+        <f>LN(D91/D90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>42.31185913085938</v>
+      </c>
+      <c r="C92" t="n">
+        <v>5.151400089263916</v>
+      </c>
+      <c r="D92">
+        <f>B92/C92</f>
+        <v/>
+      </c>
+      <c r="E92">
+        <f>LN(D92/D91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>42.00156784057617</v>
+      </c>
+      <c r="C93" t="n">
+        <v>5.243899822235107</v>
+      </c>
+      <c r="D93">
+        <f>B93/C93</f>
+        <v/>
+      </c>
+      <c r="E93">
+        <f>LN(D93/D92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>43.1204833984375</v>
+      </c>
+      <c r="C94" t="n">
+        <v>5.329100131988525</v>
+      </c>
+      <c r="D94">
+        <f>B94/C94</f>
+        <v/>
+      </c>
+      <c r="E94">
+        <f>LN(D94/D93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>43.60941696166992</v>
+      </c>
+      <c r="C95" t="n">
+        <v>5.233399868011475</v>
+      </c>
+      <c r="D95">
+        <f>B95/C95</f>
+        <v/>
+      </c>
+      <c r="E95">
+        <f>LN(D95/D94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>44.19237899780273</v>
+      </c>
+      <c r="C96" t="n">
+        <v>5.19290018081665</v>
+      </c>
+      <c r="D96">
+        <f>B96/C96</f>
+        <v/>
+      </c>
+      <c r="E96">
+        <f>LN(D96/D95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>43.98552322387695</v>
+      </c>
+      <c r="C97" t="n">
+        <v>5.262100219726562</v>
+      </c>
+      <c r="D97">
+        <f>B97/C97</f>
+        <v/>
+      </c>
+      <c r="E97">
+        <f>LN(D97/D96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>42.94182586669922</v>
+      </c>
+      <c r="C98" t="n">
+        <v>5.219900131225586</v>
+      </c>
+      <c r="D98">
+        <f>B98/C98</f>
+        <v/>
+      </c>
+      <c r="E98">
+        <f>LN(D98/D97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>43.28032684326172</v>
+      </c>
+      <c r="C99" t="n">
+        <v>5.31190013885498</v>
+      </c>
+      <c r="D99">
+        <f>B99/C99</f>
+        <v/>
+      </c>
+      <c r="E99">
+        <f>LN(D99/D98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>44.44625473022461</v>
+      </c>
+      <c r="C100" t="n">
+        <v>5.232900142669678</v>
+      </c>
+      <c r="D100">
+        <f>B100/C100</f>
+        <v/>
+      </c>
+      <c r="E100">
+        <f>LN(D100/D99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>44.66250991821289</v>
+      </c>
+      <c r="C101" t="n">
+        <v>5.232600212097168</v>
+      </c>
+      <c r="D101">
+        <f>B101/C101</f>
+        <v/>
+      </c>
+      <c r="E101">
+        <f>LN(D101/D100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>45.15144729614258</v>
+      </c>
+      <c r="C102" t="n">
+        <v>5.236800193786621</v>
+      </c>
+      <c r="D102">
+        <f>B102/C102</f>
+        <v/>
+      </c>
+      <c r="E102">
+        <f>LN(D102/D101)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>46.45841598510742</v>
+      </c>
+      <c r="C103" t="n">
+        <v>5.235099792480469</v>
+      </c>
+      <c r="D103">
+        <f>B103/C103</f>
+        <v/>
+      </c>
+      <c r="E103">
+        <f>LN(D103/D102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>46.702880859375</v>
+      </c>
+      <c r="C104" t="n">
+        <v>5.263999938964844</v>
+      </c>
+      <c r="D104">
+        <f>B104/C104</f>
+        <v/>
+      </c>
+      <c r="E104">
+        <f>LN(D104/D103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>45.76261901855469</v>
+      </c>
+      <c r="C105" t="n">
+        <v>5.192800045013428</v>
+      </c>
+      <c r="D105">
+        <f>B105/C105</f>
+        <v/>
+      </c>
+      <c r="E105">
+        <f>LN(D105/D104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>44.54027557373047</v>
+      </c>
+      <c r="C106" t="n">
+        <v>5.154500007629395</v>
+      </c>
+      <c r="D106">
+        <f>B106/C106</f>
+        <v/>
+      </c>
+      <c r="E106">
+        <f>LN(D106/D105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>45.27368545532227</v>
+      </c>
+      <c r="C107" t="n">
+        <v>5.156400203704834</v>
+      </c>
+      <c r="D107">
+        <f>B107/C107</f>
+        <v/>
+      </c>
+      <c r="E107">
+        <f>LN(D107/D106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>46.0164909362793</v>
+      </c>
+      <c r="C108" t="n">
+        <v>5.138299942016602</v>
+      </c>
+      <c r="D108">
+        <f>B108/C108</f>
+        <v/>
+      </c>
+      <c r="E108">
+        <f>LN(D108/D107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>45.61217880249023</v>
+      </c>
+      <c r="C109" t="n">
+        <v>5.150599956512451</v>
+      </c>
+      <c r="D109">
+        <f>B109/C109</f>
+        <v/>
+      </c>
+      <c r="E109">
+        <f>LN(D109/D108)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>43.82567977905273</v>
+      </c>
+      <c r="C110" t="n">
+        <v>5.100200176239014</v>
+      </c>
+      <c r="D110">
+        <f>B110/C110</f>
+        <v/>
+      </c>
+      <c r="E110">
+        <f>LN(D110/D109)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>45.03861999511719</v>
+      </c>
+      <c r="C111" t="n">
+        <v>5.095799922943115</v>
+      </c>
+      <c r="D111">
+        <f>B111/C111</f>
+        <v/>
+      </c>
+      <c r="E111">
+        <f>LN(D111/D110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>46.10111618041992</v>
+      </c>
+      <c r="C112" t="n">
+        <v>5.095799922943115</v>
+      </c>
+      <c r="D112">
+        <f>B112/C112</f>
+        <v/>
+      </c>
+      <c r="E112">
+        <f>LN(D112/D111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>46.80630874633789</v>
+      </c>
+      <c r="C113" t="n">
+        <v>4.994400024414062</v>
+      </c>
+      <c r="D113">
+        <f>B113/C113</f>
+        <v/>
+      </c>
+      <c r="E113">
+        <f>LN(D113/D112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>45.01981353759766</v>
+      </c>
+      <c r="C114" t="n">
+        <v>4.984799861907959</v>
+      </c>
+      <c r="D114">
+        <f>B114/C114</f>
+        <v/>
+      </c>
+      <c r="E114">
+        <f>LN(D114/D113)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>44.08895492553711</v>
+      </c>
+      <c r="C115" t="n">
+        <v>4.992400169372559</v>
+      </c>
+      <c r="D115">
+        <f>B115/C115</f>
+        <v/>
+      </c>
+      <c r="E115">
+        <f>LN(D115/D114)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>45.67799758911133</v>
+      </c>
+      <c r="C116" t="n">
+        <v>4.987090110778809</v>
+      </c>
+      <c r="D116">
+        <f>B116/C116</f>
+        <v/>
+      </c>
+      <c r="E116">
+        <f>LN(D116/D115)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>43.45897674560547</v>
+      </c>
+      <c r="C117" t="n">
+        <v>4.987090110778809</v>
+      </c>
+      <c r="D117">
+        <f>B117/C117</f>
+        <v/>
+      </c>
+      <c r="E117">
+        <f>LN(D117/D116)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>44.21118927001953</v>
+      </c>
+      <c r="C118" t="n">
+        <v>4.952400207519531</v>
+      </c>
+      <c r="D118">
+        <f>B118/C118</f>
+        <v/>
+      </c>
+      <c r="E118">
+        <f>LN(D118/D117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>44.82235336303711</v>
+      </c>
+      <c r="C119" t="n">
+        <v>4.984899997711182</v>
+      </c>
+      <c r="D119">
+        <f>B119/C119</f>
+        <v/>
+      </c>
+      <c r="E119">
+        <f>LN(D119/D118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>45.54999542236328</v>
+      </c>
+      <c r="C120" t="n">
+        <v>5.030799865722656</v>
+      </c>
+      <c r="D120">
+        <f>B120/C120</f>
+        <v/>
+      </c>
+      <c r="E120">
+        <f>LN(D120/D119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>44.96834564208984</v>
+      </c>
+      <c r="C121" t="n">
+        <v>5.030799865722656</v>
+      </c>
+      <c r="D121">
+        <f>B121/C121</f>
+        <v/>
+      </c>
+      <c r="E121">
+        <f>LN(D121/D120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>45.16858291625977</v>
+      </c>
+      <c r="C122" t="n">
+        <v>4.999599933624268</v>
+      </c>
+      <c r="D122">
+        <f>B122/C122</f>
+        <v/>
+      </c>
+      <c r="E122">
+        <f>LN(D122/D121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>45.31161880493164</v>
+      </c>
+      <c r="C123" t="n">
+        <v>4.99429988861084</v>
+      </c>
+      <c r="D123">
+        <f>B123/C123</f>
+        <v/>
+      </c>
+      <c r="E123">
+        <f>LN(D123/D122)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>46.68469619750977</v>
+      </c>
+      <c r="C124" t="n">
+        <v>5.017499923706055</v>
+      </c>
+      <c r="D124">
+        <f>B124/C124</f>
+        <v/>
+      </c>
+      <c r="E124">
+        <f>LN(D124/D123)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>46.79911804199219</v>
+      </c>
+      <c r="C125" t="n">
+        <v>4.969500064849854</v>
+      </c>
+      <c r="D125">
+        <f>B125/C125</f>
+        <v/>
+      </c>
+      <c r="E125">
+        <f>LN(D125/D124)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>47.04703903198242</v>
+      </c>
+      <c r="C126" t="n">
+        <v>4.984799861907959</v>
+      </c>
+      <c r="D126">
+        <f>B126/C126</f>
+        <v/>
+      </c>
+      <c r="E126">
+        <f>LN(D126/D125)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>46.39863967895508</v>
+      </c>
+      <c r="C127" t="n">
+        <v>4.927299976348877</v>
+      </c>
+      <c r="D127">
+        <f>B127/C127</f>
+        <v/>
+      </c>
+      <c r="E127">
+        <f>LN(D127/D126)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>45.07323455810547</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4.932271957397461</v>
+      </c>
+      <c r="D128">
+        <f>B128/C128</f>
+        <v/>
+      </c>
+      <c r="E128">
+        <f>LN(D128/D127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>44.0720329284668</v>
+      </c>
+      <c r="C129" t="n">
+        <v>4.944900035858154</v>
+      </c>
+      <c r="D129">
+        <f>B129/C129</f>
+        <v/>
+      </c>
+      <c r="E129">
+        <f>LN(D129/D128)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>43.54758834838867</v>
+      </c>
+      <c r="C130" t="n">
+        <v>4.944900035858154</v>
+      </c>
+      <c r="D130">
+        <f>B130/C130</f>
+        <v/>
+      </c>
+      <c r="E130">
+        <f>LN(D130/D129)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>44.27227020263672</v>
+      </c>
+      <c r="C131" t="n">
+        <v>4.906400203704834</v>
+      </c>
+      <c r="D131">
+        <f>B131/C131</f>
+        <v/>
+      </c>
+      <c r="E131">
+        <f>LN(D131/D130)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>43.55712509155273</v>
+      </c>
+      <c r="C132" t="n">
+        <v>4.9096999168396</v>
+      </c>
+      <c r="D132">
+        <f>B132/C132</f>
+        <v/>
+      </c>
+      <c r="E132">
+        <f>LN(D132/D131)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>42.49871063232422</v>
+      </c>
+      <c r="C133" t="n">
+        <v>5.024899959564209</v>
+      </c>
+      <c r="D133">
+        <f>B133/C133</f>
+        <v/>
+      </c>
+      <c r="E133">
+        <f>LN(D133/D132)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>42.90872573852539</v>
+      </c>
+      <c r="C134" t="n">
+        <v>5.00409984588623</v>
+      </c>
+      <c r="D134">
+        <f>B134/C134</f>
+        <v/>
+      </c>
+      <c r="E134">
+        <f>LN(D134/D133)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>43.35688400268555</v>
+      </c>
+      <c r="C135" t="n">
+        <v>5.00409984588623</v>
+      </c>
+      <c r="D135">
+        <f>B135/C135</f>
+        <v/>
+      </c>
+      <c r="E135">
+        <f>LN(D135/D134)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>44.28180694580078</v>
+      </c>
+      <c r="C136" t="n">
+        <v>5.005624771118164</v>
+      </c>
+      <c r="D136">
+        <f>B136/C136</f>
+        <v/>
+      </c>
+      <c r="E136">
+        <f>LN(D136/D135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>43.94807434082031</v>
+      </c>
+      <c r="C137" t="n">
+        <v>5.058199882507324</v>
+      </c>
+      <c r="D137">
+        <f>B137/C137</f>
+        <v/>
+      </c>
+      <c r="E137">
+        <f>LN(D137/D136)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>42.52731704711914</v>
+      </c>
+      <c r="C138" t="n">
+        <v>5.01170015335083</v>
+      </c>
+      <c r="D138">
+        <f>B138/C138</f>
+        <v/>
+      </c>
+      <c r="E138">
+        <f>LN(D138/D137)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>42.86105346679688</v>
+      </c>
+      <c r="C139" t="n">
+        <v>5.017099857330322</v>
+      </c>
+      <c r="D139">
+        <f>B139/C139</f>
+        <v/>
+      </c>
+      <c r="E139">
+        <f>LN(D139/D138)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>42.41289138793945</v>
+      </c>
+      <c r="C140" t="n">
+        <v>5.017099857330322</v>
+      </c>
+      <c r="D140">
+        <f>B140/C140</f>
+        <v/>
+      </c>
+      <c r="E140">
+        <f>LN(D140/D139)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>41.38308334350586</v>
+      </c>
+      <c r="C141" t="n">
+        <v>5.01039981842041</v>
+      </c>
+      <c r="D141">
+        <f>B141/C141</f>
+        <v/>
+      </c>
+      <c r="E141">
+        <f>LN(D141/D140)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>41.42122268676758</v>
+      </c>
+      <c r="C142" t="n">
+        <v>5.04449987411499</v>
+      </c>
+      <c r="D142">
+        <f>B142/C142</f>
+        <v/>
+      </c>
+      <c r="E142">
+        <f>LN(D142/D141)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>40.83003616333008</v>
+      </c>
+      <c r="C143" t="n">
+        <v>5.07289981842041</v>
+      </c>
+      <c r="D143">
+        <f>B143/C143</f>
+        <v/>
+      </c>
+      <c r="E143">
+        <f>LN(D143/D142)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>40.53444290161133</v>
+      </c>
+      <c r="C144" t="n">
+        <v>5.051700115203857</v>
+      </c>
+      <c r="D144">
+        <f>B144/C144</f>
+        <v/>
+      </c>
+      <c r="E144">
+        <f>LN(D144/D143)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>40.04814529418945</v>
+      </c>
+      <c r="C145" t="n">
+        <v>5.051700115203857</v>
+      </c>
+      <c r="D145">
+        <f>B145/C145</f>
+        <v/>
+      </c>
+      <c r="E145">
+        <f>LN(D145/D144)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>40.40094757080078</v>
+      </c>
+      <c r="C146" t="n">
+        <v>5.038599967956543</v>
+      </c>
+      <c r="D146">
+        <f>B146/C146</f>
+        <v/>
+      </c>
+      <c r="E146">
+        <f>LN(D146/D145)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>40.30493545532227</v>
+      </c>
+      <c r="C147" t="n">
+        <v>5.020699977874756</v>
+      </c>
+      <c r="D147">
+        <f>B147/C147</f>
+        <v/>
+      </c>
+      <c r="E147">
+        <f>LN(D147/D146)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>39.99467468261719</v>
+      </c>
+      <c r="C148" t="n">
+        <v>5.077400207519531</v>
+      </c>
+      <c r="D148">
+        <f>B148/C148</f>
+        <v/>
+      </c>
+      <c r="E148">
+        <f>LN(D148/D147)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>39.6456298828125</v>
+      </c>
+      <c r="C149" t="n">
+        <v>5.060699939727783</v>
+      </c>
+      <c r="D149">
+        <f>B149/C149</f>
+        <v/>
+      </c>
+      <c r="E149">
+        <f>LN(D149/D148)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>39.96559143066406</v>
+      </c>
+      <c r="C150" t="n">
+        <v>5.203100204467773</v>
+      </c>
+      <c r="D150">
+        <f>B150/C150</f>
+        <v/>
+      </c>
+      <c r="E150">
+        <f>LN(D150/D149)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>39.91710662841797</v>
+      </c>
+      <c r="C151" t="n">
+        <v>5.190100193023682</v>
+      </c>
+      <c r="D151">
+        <f>B151/C151</f>
+        <v/>
+      </c>
+      <c r="E151">
+        <f>LN(D151/D150)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>40.38250350952148</v>
+      </c>
+      <c r="C152" t="n">
+        <v>5.192100048065186</v>
+      </c>
+      <c r="D152">
+        <f>B152/C152</f>
+        <v/>
+      </c>
+      <c r="E152">
+        <f>LN(D152/D151)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>40.48915481567383</v>
+      </c>
+      <c r="C153" t="n">
+        <v>5.113800048828125</v>
+      </c>
+      <c r="D153">
+        <f>B153/C153</f>
+        <v/>
+      </c>
+      <c r="E153">
+        <f>LN(D153/D152)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>39.92680740356445</v>
+      </c>
+      <c r="C154" t="n">
+        <v>5.113800048828125</v>
+      </c>
+      <c r="D154">
+        <f>B154/C154</f>
+        <v/>
+      </c>
+      <c r="E154">
+        <f>LN(D154/D153)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>37.87132263183594</v>
+      </c>
+      <c r="C155" t="n">
+        <v>5.075099945068359</v>
+      </c>
+      <c r="D155">
+        <f>B155/C155</f>
+        <v/>
+      </c>
+      <c r="E155">
+        <f>LN(D155/D154)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>37.36714935302734</v>
+      </c>
+      <c r="C156" t="n">
+        <v>5.101900100708008</v>
+      </c>
+      <c r="D156">
+        <f>B156/C156</f>
+        <v/>
+      </c>
+      <c r="E156">
+        <f>LN(D156/D155)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>37.39623260498047</v>
+      </c>
+      <c r="C157" t="n">
+        <v>5.122099876403809</v>
+      </c>
+      <c r="D157">
+        <f>B157/C157</f>
+        <v/>
+      </c>
+      <c r="E157">
+        <f>LN(D157/D156)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>37.66770935058594</v>
+      </c>
+      <c r="C158" t="n">
+        <v>5.18149995803833</v>
+      </c>
+      <c r="D158">
+        <f>B158/C158</f>
+        <v/>
+      </c>
+      <c r="E158">
+        <f>LN(D158/D157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>37.61923217773438</v>
+      </c>
+      <c r="C159" t="n">
+        <v>5.18149995803833</v>
+      </c>
+      <c r="D159">
+        <f>B159/C159</f>
+        <v/>
+      </c>
+      <c r="E159">
+        <f>LN(D159/D158)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>37.97797393798828</v>
+      </c>
+      <c r="C160" t="n">
+        <v>5.156499862670898</v>
+      </c>
+      <c r="D160">
+        <f>B160/C160</f>
+        <v/>
+      </c>
+      <c r="E160">
+        <f>LN(D160/D159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>38.13310623168945</v>
+      </c>
+      <c r="C161" t="n">
+        <v>5.197700023651123</v>
+      </c>
+      <c r="D161">
+        <f>B161/C161</f>
+        <v/>
+      </c>
+      <c r="E161">
+        <f>LN(D161/D160)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>37.124755859375</v>
+      </c>
+      <c r="C162" t="n">
+        <v>5.207499980926514</v>
+      </c>
+      <c r="D162">
+        <f>B162/C162</f>
+        <v/>
+      </c>
+      <c r="E162">
+        <f>LN(D162/D161)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>37.27988815307617</v>
+      </c>
+      <c r="C163" t="n">
+        <v>5.194099903106689</v>
+      </c>
+      <c r="D163">
+        <f>B163/C163</f>
+        <v/>
+      </c>
+      <c r="E163">
+        <f>LN(D163/D162)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>36.90175628662109</v>
+      </c>
+      <c r="C164" t="n">
+        <v>5.194099903106689</v>
+      </c>
+      <c r="D164">
+        <f>B164/C164</f>
+        <v/>
+      </c>
+      <c r="E164">
+        <f>LN(D164/D163)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>36.97932052612305</v>
+      </c>
+      <c r="C165" t="n">
+        <v>5.181787014007568</v>
+      </c>
+      <c r="D165">
+        <f>B165/C165</f>
+        <v/>
+      </c>
+      <c r="E165">
+        <f>LN(D165/D164)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>36.64966583251953</v>
+      </c>
+      <c r="C166" t="n">
+        <v>5.174699783325195</v>
+      </c>
+      <c r="D166">
+        <f>B166/C166</f>
+        <v/>
+      </c>
+      <c r="E166">
+        <f>LN(D166/D165)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>36.67875671386719</v>
+      </c>
+      <c r="C167" t="n">
+        <v>5.220600128173828</v>
+      </c>
+      <c r="D167">
+        <f>B167/C167</f>
+        <v/>
+      </c>
+      <c r="E167">
+        <f>LN(D167/D166)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>36.8047981262207</v>
+      </c>
+      <c r="C168" t="n">
+        <v>5.2221999168396</v>
+      </c>
+      <c r="D168">
+        <f>B168/C168</f>
+        <v/>
+      </c>
+      <c r="E168">
+        <f>LN(D168/D167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>37.08597183227539</v>
+      </c>
+      <c r="C169" t="n">
+        <v>5.2221999168396</v>
+      </c>
+      <c r="D169">
+        <f>B169/C169</f>
+        <v/>
+      </c>
+      <c r="E169">
+        <f>LN(D169/D168)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>36.62057876586914</v>
+      </c>
+      <c r="C170" t="n">
+        <v>5.143599987030029</v>
+      </c>
+      <c r="D170">
+        <f>B170/C170</f>
+        <v/>
+      </c>
+      <c r="E170">
+        <f>LN(D170/D169)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>37.27018737792969</v>
+      </c>
+      <c r="C171" t="n">
+        <v>5.170899868011475</v>
+      </c>
+      <c r="D171">
+        <f>B171/C171</f>
+        <v/>
+      </c>
+      <c r="E171">
+        <f>LN(D171/D170)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>38.44336700439453</v>
+      </c>
+      <c r="C172" t="n">
+        <v>5.16349983215332</v>
+      </c>
+      <c r="D172">
+        <f>B172/C172</f>
+        <v/>
+      </c>
+      <c r="E172">
+        <f>LN(D172/D171)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>38.01675796508789</v>
+      </c>
+      <c r="C173" t="n">
+        <v>5.133900165557861</v>
+      </c>
+      <c r="D173">
+        <f>B173/C173</f>
+        <v/>
+      </c>
+      <c r="E173">
+        <f>LN(D173/D172)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>38.44336700439453</v>
+      </c>
+      <c r="C174" t="n">
+        <v>5.133900165557861</v>
+      </c>
+      <c r="D174">
+        <f>B174/C174</f>
+        <v/>
+      </c>
+      <c r="E174">
+        <f>LN(D174/D173)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>39.42263031005859</v>
+      </c>
+      <c r="C175" t="n">
+        <v>5.147900104522705</v>
+      </c>
+      <c r="D175">
+        <f>B175/C175</f>
+        <v/>
+      </c>
+      <c r="E175">
+        <f>LN(D175/D174)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>39.42263031005859</v>
+      </c>
+      <c r="C176" t="n">
+        <v>5.087900161743164</v>
+      </c>
+      <c r="D176">
+        <f>B176/C176</f>
+        <v/>
+      </c>
+      <c r="E176">
+        <f>LN(D176/D175)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>39.35475921630859</v>
+      </c>
+      <c r="C177" t="n">
+        <v>5.09089994430542</v>
+      </c>
+      <c r="D177">
+        <f>B177/C177</f>
+        <v/>
+      </c>
+      <c r="E177">
+        <f>LN(D177/D176)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>38.67606353759766</v>
+      </c>
+      <c r="C178" t="n">
+        <v>5.11359977722168</v>
+      </c>
+      <c r="D178">
+        <f>B178/C178</f>
+        <v/>
+      </c>
+      <c r="E178">
+        <f>LN(D178/D177)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>39.65532684326172</v>
+      </c>
+      <c r="C179" t="n">
+        <v>5.11359977722168</v>
+      </c>
+      <c r="D179">
+        <f>B179/C179</f>
+        <v/>
+      </c>
+      <c r="E179">
+        <f>LN(D179/D178)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>39.89772033691406</v>
+      </c>
+      <c r="C180" t="n">
+        <v>5.104400157928467</v>
+      </c>
+      <c r="D180">
+        <f>B180/C180</f>
+        <v/>
+      </c>
+      <c r="E180">
+        <f>LN(D180/D179)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>40.39219665527344</v>
+      </c>
+      <c r="C181" t="n">
+        <v>5.087500095367432</v>
+      </c>
+      <c r="D181">
+        <f>B181/C181</f>
+        <v/>
+      </c>
+      <c r="E181">
+        <f>LN(D181/D180)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>41.28420257568359</v>
+      </c>
+      <c r="C182" t="n">
+        <v>5.062488079071045</v>
+      </c>
+      <c r="D182">
+        <f>B182/C182</f>
+        <v/>
+      </c>
+      <c r="E182">
+        <f>LN(D182/D181)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>41.64294052124023</v>
+      </c>
+      <c r="C183" t="n">
+        <v>5.09689998626709</v>
+      </c>
+      <c r="D183">
+        <f>B183/C183</f>
+        <v/>
+      </c>
+      <c r="E183">
+        <f>LN(D183/D182)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>40.92546081542969</v>
+      </c>
+      <c r="C184" t="n">
+        <v>5.09689998626709</v>
+      </c>
+      <c r="D184">
+        <f>B184/C184</f>
+        <v/>
+      </c>
+      <c r="E184">
+        <f>LN(D184/D183)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>39.76197814941406</v>
+      </c>
+      <c r="C185" t="n">
+        <v>5.123025894165039</v>
+      </c>
+      <c r="D185">
+        <f>B185/C185</f>
+        <v/>
+      </c>
+      <c r="E185">
+        <f>LN(D185/D184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>39.95589065551758</v>
+      </c>
+      <c r="C186" t="n">
+        <v>5.137100219726562</v>
+      </c>
+      <c r="D186">
+        <f>B186/C186</f>
+        <v/>
+      </c>
+      <c r="E186">
+        <f>LN(D186/D185)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>40.72185134887695</v>
+      </c>
+      <c r="C187" t="n">
+        <v>5.127099990844727</v>
+      </c>
+      <c r="D187">
+        <f>B187/C187</f>
+        <v/>
+      </c>
+      <c r="E187">
+        <f>LN(D187/D186)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>41.53628921508789</v>
+      </c>
+      <c r="C188" t="n">
+        <v>5.078100204467773</v>
+      </c>
+      <c r="D188">
+        <f>B188/C188</f>
+        <v/>
+      </c>
+      <c r="E188">
+        <f>LN(D188/D187)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>42.09863662719727</v>
+      </c>
+      <c r="C189" t="n">
+        <v>5.078100204467773</v>
+      </c>
+      <c r="D189">
+        <f>B189/C189</f>
+        <v/>
+      </c>
+      <c r="E189">
+        <f>LN(D189/D188)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>41.73989868164062</v>
+      </c>
+      <c r="C190" t="n">
+        <v>5.10290002822876</v>
+      </c>
+      <c r="D190">
+        <f>B190/C190</f>
+        <v/>
+      </c>
+      <c r="E190">
+        <f>LN(D190/D189)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>41.20663452148438</v>
+      </c>
+      <c r="C191" t="n">
+        <v>5.143700122833252</v>
+      </c>
+      <c r="D191">
+        <f>B191/C191</f>
+        <v/>
+      </c>
+      <c r="E191">
+        <f>LN(D191/D190)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>40.65398025512695</v>
+      </c>
+      <c r="C192" t="n">
+        <v>5.138500213623047</v>
+      </c>
+      <c r="D192">
+        <f>B192/C192</f>
+        <v/>
+      </c>
+      <c r="E192">
+        <f>LN(D192/D191)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>40.84789657592773</v>
+      </c>
+      <c r="C193" t="n">
+        <v>5.121799945831299</v>
+      </c>
+      <c r="D193">
+        <f>B193/C193</f>
+        <v/>
+      </c>
+      <c r="E193">
+        <f>LN(D193/D192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>39.62623977661133</v>
+      </c>
+      <c r="C194" t="n">
+        <v>5.121799945831299</v>
+      </c>
+      <c r="D194">
+        <f>B194/C194</f>
+        <v/>
+      </c>
+      <c r="E194">
+        <f>LN(D194/D193)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>40.94485092163086</v>
+      </c>
+      <c r="C195" t="n">
+        <v>5.105999946594238</v>
+      </c>
+      <c r="D195">
+        <f>B195/C195</f>
+        <v/>
+      </c>
+      <c r="E195">
+        <f>LN(D195/D194)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>40.39219665527344</v>
+      </c>
+      <c r="C196" t="n">
+        <v>5.173500061035156</v>
+      </c>
+      <c r="D196">
+        <f>B196/C196</f>
+        <v/>
+      </c>
+      <c r="E196">
+        <f>LN(D196/D195)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>40.18859100341797</v>
+      </c>
+      <c r="C197" t="n">
+        <v>5.195400238037109</v>
+      </c>
+      <c r="D197">
+        <f>B197/C197</f>
+        <v/>
+      </c>
+      <c r="E197">
+        <f>LN(D197/D196)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>40.62489700317383</v>
+      </c>
+      <c r="C198" t="n">
+        <v>5.19980001449585</v>
+      </c>
+      <c r="D198">
+        <f>B198/C198</f>
+        <v/>
+      </c>
+      <c r="E198">
+        <f>LN(D198/D197)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>40.80911254882812</v>
+      </c>
+      <c r="C199" t="n">
+        <v>5.19980001449585</v>
+      </c>
+      <c r="D199">
+        <f>B199/C199</f>
+        <v/>
+      </c>
+      <c r="E199">
+        <f>LN(D199/D198)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>41.17755126953125</v>
+      </c>
+      <c r="C200" t="n">
+        <v>5.202499866485596</v>
+      </c>
+      <c r="D200">
+        <f>B200/C200</f>
+        <v/>
+      </c>
+      <c r="E200">
+        <f>LN(D200/D199)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>41.30359268188477</v>
+      </c>
+      <c r="C201" t="n">
+        <v>5.214300155639648</v>
+      </c>
+      <c r="D201">
+        <f>B201/C201</f>
+        <v/>
+      </c>
+      <c r="E201">
+        <f>LN(D201/D200)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>41.79807281494141</v>
+      </c>
+      <c r="C202" t="n">
+        <v>5.176700115203857</v>
+      </c>
+      <c r="D202">
+        <f>B202/C202</f>
+        <v/>
+      </c>
+      <c r="E202">
+        <f>LN(D202/D201)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>42.97124862670898</v>
+      </c>
+      <c r="C203" t="n">
+        <v>5.193099975585938</v>
+      </c>
+      <c r="D203">
+        <f>B203/C203</f>
+        <v/>
+      </c>
+      <c r="E203">
+        <f>LN(D203/D202)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>42.95185852050781</v>
+      </c>
+      <c r="C204" t="n">
+        <v>5.193099975585938</v>
+      </c>
+      <c r="D204">
+        <f>B204/C204</f>
+        <v/>
+      </c>
+      <c r="E204">
+        <f>LN(D204/D203)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>42.11000061035156</v>
+      </c>
+      <c r="C205" t="n">
+        <v>5.154300212860107</v>
+      </c>
+      <c r="D205">
+        <f>B205/C205</f>
+        <v/>
+      </c>
+      <c r="E205">
+        <f>LN(D205/D204)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>41.34999847412109</v>
+      </c>
+      <c r="C206" t="n">
+        <v>5.146399974822998</v>
+      </c>
+      <c r="D206">
+        <f>B206/C206</f>
+        <v/>
+      </c>
+      <c r="E206">
+        <f>LN(D206/D205)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>41.45000076293945</v>
+      </c>
+      <c r="C207" t="n">
+        <v>5.14739990234375</v>
+      </c>
+      <c r="D207">
+        <f>B207/C207</f>
+        <v/>
+      </c>
+      <c r="E207">
+        <f>LN(D207/D206)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>42.70000076293945</v>
+      </c>
+      <c r="C208" t="n">
+        <v>5.161099910736084</v>
+      </c>
+      <c r="D208">
+        <f>B208/C208</f>
+        <v/>
+      </c>
+      <c r="E208">
+        <f>LN(D208/D207)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>43.54999923706055</v>
+      </c>
+      <c r="C209" t="n">
+        <v>5.161099910736084</v>
+      </c>
+      <c r="D209">
+        <f>B209/C209</f>
+        <v/>
+      </c>
+      <c r="E209">
+        <f>LN(D209/D208)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>45.02000045776367</v>
+      </c>
+      <c r="C210" t="n">
+        <v>5.181700229644775</v>
+      </c>
+      <c r="D210">
+        <f>B210/C210</f>
+        <v/>
+      </c>
+      <c r="E210">
+        <f>LN(D210/D209)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>46.86999893188477</v>
+      </c>
+      <c r="C211" t="n">
+        <v>5.152200222015381</v>
+      </c>
+      <c r="D211">
+        <f>B211/C211</f>
+        <v/>
+      </c>
+      <c r="E211">
+        <f>LN(D211/D210)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>48.20000076293945</v>
+      </c>
+      <c r="C212" t="n">
+        <v>5.092700004577637</v>
+      </c>
+      <c r="D212">
+        <f>B212/C212</f>
+        <v/>
+      </c>
+      <c r="E212">
+        <f>LN(D212/D211)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>47.56000137329102</v>
+      </c>
+      <c r="C213" t="n">
+        <v>5.10099983215332</v>
+      </c>
+      <c r="D213">
+        <f>B213/C213</f>
+        <v/>
+      </c>
+      <c r="E213">
+        <f>LN(D213/D212)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>47.11000061035156</v>
+      </c>
+      <c r="C214" t="n">
+        <v>5.10099983215332</v>
+      </c>
+      <c r="D214">
+        <f>B214/C214</f>
+        <v/>
+      </c>
+      <c r="E214">
+        <f>LN(D214/D213)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>48.09000015258789</v>
+      </c>
+      <c r="C215" t="n">
+        <v>5.084799766540527</v>
+      </c>
+      <c r="D215">
+        <f>B215/C215</f>
+        <v/>
+      </c>
+      <c r="E215">
+        <f>LN(D215/D214)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>48.41999816894531</v>
+      </c>
+      <c r="C216" t="n">
+        <v>5.103400230407715</v>
+      </c>
+      <c r="D216">
+        <f>B216/C216</f>
+        <v/>
+      </c>
+      <c r="E216">
+        <f>LN(D216/D215)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>49.11999893188477</v>
+      </c>
+      <c r="C217" t="n">
+        <v>5.102799892425537</v>
+      </c>
+      <c r="D217">
+        <f>B217/C217</f>
+        <v/>
+      </c>
+      <c r="E217">
+        <f>LN(D217/D216)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>49</v>
+      </c>
+      <c r="C218" t="n">
+        <v>5.102799892425537</v>
+      </c>
+      <c r="D218">
+        <f>B218/C218</f>
+        <v/>
+      </c>
+      <c r="E218">
+        <f>LN(D218/D217)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>48.91999816894531</v>
+      </c>
+      <c r="C219" t="n">
+        <v>5.138000011444092</v>
+      </c>
+      <c r="D219">
+        <f>B219/C219</f>
+        <v/>
+      </c>
+      <c r="E219">
+        <f>LN(D219/D218)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>50.43000030517578</v>
+      </c>
+      <c r="C220" t="n">
+        <v>5.142899990081787</v>
+      </c>
+      <c r="D220">
+        <f>B220/C220</f>
+        <v/>
+      </c>
+      <c r="E220">
+        <f>LN(D220/D219)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>48.65000152587891</v>
+      </c>
+      <c r="C221" t="n">
+        <v>5.150899887084961</v>
+      </c>
+      <c r="D221">
+        <f>B221/C221</f>
+        <v/>
+      </c>
+      <c r="E221">
+        <f>LN(D221/D220)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>48.61000061035156</v>
+      </c>
+      <c r="C222" t="n">
+        <v>5.124100208282471</v>
+      </c>
+      <c r="D222">
+        <f>B222/C222</f>
+        <v/>
+      </c>
+      <c r="E222">
+        <f>LN(D222/D221)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="C223" t="n">
+        <v>5.124100208282471</v>
+      </c>
+      <c r="D223">
+        <f>B223/C223</f>
+        <v/>
+      </c>
+      <c r="E223">
+        <f>LN(D223/D222)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>48</v>
+      </c>
+      <c r="C224" t="n">
+        <v>5.110400199890137</v>
+      </c>
+      <c r="D224">
+        <f>B224/C224</f>
+        <v/>
+      </c>
+      <c r="E224">
+        <f>LN(D224/D223)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>48.34999847412109</v>
+      </c>
+      <c r="C225" t="n">
+        <v>5.099899768829346</v>
+      </c>
+      <c r="D225">
+        <f>B225/C225</f>
+        <v/>
+      </c>
+      <c r="E225">
+        <f>LN(D225/D224)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>49.59999847412109</v>
+      </c>
+      <c r="C226" t="n">
+        <v>5.164299964904785</v>
+      </c>
+      <c r="D226">
+        <f>B226/C226</f>
+        <v/>
+      </c>
+      <c r="E226">
+        <f>LN(D226/D225)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>49.2599983215332</v>
+      </c>
+      <c r="C227" t="n">
+        <v>5.190499782562256</v>
+      </c>
+      <c r="D227">
+        <f>B227/C227</f>
+        <v/>
+      </c>
+      <c r="E227">
+        <f>LN(D227/D226)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>48.06999969482422</v>
+      </c>
+      <c r="C228" t="n">
+        <v>5.190499782562256</v>
+      </c>
+      <c r="D228">
+        <f>B228/C228</f>
+        <v/>
+      </c>
+      <c r="E228">
+        <f>LN(D228/D227)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>48.72000122070312</v>
+      </c>
+      <c r="C229" t="n">
+        <v>5.222899913787842</v>
+      </c>
+      <c r="D229">
+        <f>B229/C229</f>
+        <v/>
+      </c>
+      <c r="E229">
+        <f>LN(D229/D228)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>49.09999847412109</v>
+      </c>
+      <c r="C230" t="n">
+        <v>5.202899932861328</v>
+      </c>
+      <c r="D230">
+        <f>B230/C230</f>
+        <v/>
+      </c>
+      <c r="E230">
+        <f>LN(D230/D229)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>49.11999893188477</v>
+      </c>
+      <c r="C231" t="n">
+        <v>5.179100036621094</v>
+      </c>
+      <c r="D231">
+        <f>B231/C231</f>
+        <v/>
+      </c>
+      <c r="E231">
+        <f>LN(D231/D230)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>49.90000152587891</v>
+      </c>
+      <c r="C232" t="n">
+        <v>5.222599983215332</v>
+      </c>
+      <c r="D232">
+        <f>B232/C232</f>
+        <v/>
+      </c>
+      <c r="E232">
+        <f>LN(D232/D231)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>51.16999816894531</v>
+      </c>
+      <c r="C233" t="n">
+        <v>5.222599983215332</v>
+      </c>
+      <c r="D233">
+        <f>B233/C233</f>
+        <v/>
+      </c>
+      <c r="E233">
+        <f>LN(D233/D232)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>55.36000061035156</v>
+      </c>
+      <c r="C234" t="n">
+        <v>4.996699810028076</v>
+      </c>
+      <c r="D234">
+        <f>B234/C234</f>
+        <v/>
+      </c>
+      <c r="E234">
+        <f>LN(D234/D233)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>53.81999969482422</v>
+      </c>
+      <c r="C235" t="n">
+        <v>4.981400012969971</v>
+      </c>
+      <c r="D235">
+        <f>B235/C235</f>
+        <v/>
+      </c>
+      <c r="E235">
+        <f>LN(D235/D234)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>54.33000183105469</v>
+      </c>
+      <c r="C236" t="n">
+        <v>5.019199848175049</v>
+      </c>
+      <c r="D236">
+        <f>B236/C236</f>
+        <v/>
+      </c>
+      <c r="E236">
+        <f>LN(D236/D235)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>55.47999954223633</v>
+      </c>
+      <c r="C237" t="n">
+        <v>5.0177001953125</v>
+      </c>
+      <c r="D237">
+        <f>B237/C237</f>
+        <v/>
+      </c>
+      <c r="E237">
+        <f>LN(D237/D236)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>56</v>
+      </c>
+      <c r="C238" t="n">
+        <v>5.0177001953125</v>
+      </c>
+      <c r="D238">
+        <f>B238/C238</f>
+        <v/>
+      </c>
+      <c r="E238">
+        <f>LN(D238/D237)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>56.84999847412109</v>
+      </c>
+      <c r="C239" t="n">
+        <v>5.025800228118896</v>
+      </c>
+      <c r="D239">
+        <f>B239/C239</f>
+        <v/>
+      </c>
+      <c r="E239">
+        <f>LN(D239/D238)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>58.11000061035156</v>
+      </c>
+      <c r="C240" t="n">
+        <v>5.03950023651123</v>
+      </c>
+      <c r="D240">
+        <f>B240/C240</f>
+        <v/>
+      </c>
+      <c r="E240">
+        <f>LN(D240/D239)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>57.36000061035156</v>
+      </c>
+      <c r="C241" t="n">
+        <v>5.09660005569458</v>
+      </c>
+      <c r="D241">
+        <f>B241/C241</f>
+        <v/>
+      </c>
+      <c r="E241">
+        <f>LN(D241/D240)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>59.68000030517578</v>
+      </c>
+      <c r="C242" t="n">
+        <v>5.09660005569458</v>
+      </c>
+      <c r="D242">
+        <f>B242/C242</f>
+        <v/>
+      </c>
+      <c r="E242">
+        <f>LN(D242/D241)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>58</v>
+      </c>
+      <c r="C243" t="n">
+        <v>5.037000179290771</v>
+      </c>
+      <c r="D243">
+        <f>B243/C243</f>
+        <v/>
+      </c>
+      <c r="E243">
+        <f>LN(D243/D242)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>58.20999908447266</v>
+      </c>
+      <c r="C244" t="n">
+        <v>5.02269983291626</v>
+      </c>
+      <c r="D244">
+        <f>B244/C244</f>
+        <v/>
+      </c>
+      <c r="E244">
+        <f>LN(D244/D243)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>57.75</v>
+      </c>
+      <c r="C245" t="n">
+        <v>5.02039098739624</v>
+      </c>
+      <c r="D245">
+        <f>B245/C245</f>
+        <v/>
+      </c>
+      <c r="E245">
+        <f>LN(D245/D244)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>57.83000183105469</v>
+      </c>
+      <c r="C246" t="n">
+        <v>5.049900054931641</v>
+      </c>
+      <c r="D246">
+        <f>B246/C246</f>
+        <v/>
+      </c>
+      <c r="E246">
+        <f>LN(D246/D245)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>58.68000030517578</v>
+      </c>
+      <c r="C247" t="n">
+        <v>5.049900054931641</v>
+      </c>
+      <c r="D247">
+        <f>B247/C247</f>
+        <v/>
+      </c>
+      <c r="E247">
+        <f>LN(D247/D246)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>53.88000106811523</v>
+      </c>
+      <c r="C248" t="n">
+        <v>4.96019983291626</v>
+      </c>
+      <c r="D248">
+        <f>B248/C248</f>
+        <v/>
+      </c>
+      <c r="E248">
+        <f>LN(D248/D247)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>52.79000091552734</v>
+      </c>
+      <c r="C249" t="n">
+        <v>5.372600078582764</v>
+      </c>
+      <c r="D249">
+        <f>B249/C249</f>
+        <v/>
+      </c>
+      <c r="E249">
+        <f>LN(D249/D248)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>52.5099983215332</v>
+      </c>
+      <c r="C250" t="n">
+        <v>5.350299835205078</v>
+      </c>
+      <c r="D250">
+        <f>B250/C250</f>
+        <v/>
+      </c>
+      <c r="E250">
+        <f>LN(D250/D249)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6126,7 +11477,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-28 23:18 UTC</t>
+          <t>Snapshot as of 2026-10-29 01:48 UTC</t>
         </is>
       </c>
     </row>

--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-29 01:48 UTC</t>
+          <t>Snapshot as of 2026-10-29 18:25 UTC</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H250"/>
+  <dimension ref="A1:H249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5863,11 +5863,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.33520317077637</v>
+        <v>27.36254692077637</v>
       </c>
       <c r="C2" t="n">
         <v>5.357399940490723</v>
@@ -5882,21 +5882,21 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D250/D45-1)*100</f>
+        <f>(D249/D44-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.36254692077637</v>
+        <v>27.24405288696289</v>
       </c>
       <c r="C3" t="n">
-        <v>5.357399940490723</v>
+        <v>5.357800006866455</v>
       </c>
       <c r="D3">
         <f>B3/C3</f>
@@ -5912,21 +5912,21 @@
         </is>
       </c>
       <c r="H3">
-        <f>(D250/D2-1)*100</f>
+        <f>(D249/D2-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.24405288696289</v>
+        <v>27.11644744873047</v>
       </c>
       <c r="C4" t="n">
-        <v>5.357800006866455</v>
+        <v>5.381999969482422</v>
       </c>
       <c r="D4">
         <f>B4/C4</f>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="H4">
-        <f>(COUNT(D2:D250)-1)/((DATEVALUE(A250)-DATEVALUE(A2))/365.25)</f>
+        <f>(COUNT(D2:D249)-1)/((DATEVALUE(A249)-DATEVALUE(A2))/365.25)</f>
         <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.11644554138184</v>
+        <v>27.43546485900879</v>
       </c>
       <c r="C5" t="n">
-        <v>5.381999969482422</v>
+        <v>5.374599933624268</v>
       </c>
       <c r="D5">
         <f>B5/C5</f>
@@ -5972,21 +5972,21 @@
         </is>
       </c>
       <c r="H5">
-        <f>STDEV.S(E3:E250)*SQRT(H4)*100</f>
+        <f>STDEV.S(E3:E249)*SQRT(H4)*100</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.43546676635742</v>
+        <v>27.57218360900879</v>
       </c>
       <c r="C6" t="n">
-        <v>5.374599933624268</v>
+        <v>5.354899883270264</v>
       </c>
       <c r="D6">
         <f>B6/C6</f>
@@ -6000,14 +6000,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>27.57218551635742</v>
+        <v>28.11907386779785</v>
       </c>
       <c r="C7" t="n">
-        <v>5.354899883270264</v>
+        <v>5.395899772644043</v>
       </c>
       <c r="D7">
         <f>B7/C7</f>
@@ -6029,14 +6029,14 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.11907196044922</v>
+        <v>28.26490783691406</v>
       </c>
       <c r="C8" t="n">
-        <v>5.395899772644043</v>
+        <v>5.35860013961792</v>
       </c>
       <c r="D8">
         <f>B8/C8</f>
@@ -6052,20 +6052,20 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>92.35155499432163</v>
+        <v>92.15964279874942</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28.26490783691406</v>
+        <v>29.33133697509766</v>
       </c>
       <c r="C9" t="n">
-        <v>5.35860013961792</v>
+        <v>5.349500179290771</v>
       </c>
       <c r="D9">
         <f>B9/C9</f>
@@ -6081,20 +6081,20 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>34.39185795373886</v>
+        <v>34.43895459009657</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29.33133697509766</v>
+        <v>29.49540328979492</v>
       </c>
       <c r="C10" t="n">
-        <v>5.349500179290771</v>
+        <v>5.330900192260742</v>
       </c>
       <c r="D10">
         <f>B10/C10</f>
@@ -6108,14 +6108,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.49540519714355</v>
+        <v>30.26104545593262</v>
       </c>
       <c r="C11" t="n">
-        <v>5.330900192260742</v>
+        <v>5.289700031280518</v>
       </c>
       <c r="D11">
         <f>B11/C11</f>
@@ -6127,21 +6127,21 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-29 01:48 UTC</t>
+          <t>Snapshot as of 2026-10-29 18:25 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.26104354858398</v>
+        <v>29.48628616333008</v>
       </c>
       <c r="C12" t="n">
-        <v>5.289700031280518</v>
+        <v>5.270699977874756</v>
       </c>
       <c r="D12">
         <f>B12/C12</f>
@@ -6155,14 +6155,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29.48628425598145</v>
+        <v>29.6138973236084</v>
       </c>
       <c r="C13" t="n">
-        <v>5.270699977874756</v>
+        <v>5.291299819946289</v>
       </c>
       <c r="D13">
         <f>B13/C13</f>
@@ -6176,14 +6176,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.61389541625977</v>
+        <v>29.80530738830566</v>
       </c>
       <c r="C14" t="n">
-        <v>5.291299819946289</v>
+        <v>5.296500205993652</v>
       </c>
       <c r="D14">
         <f>B14/C14</f>
@@ -6197,14 +6197,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.8053035736084</v>
+        <v>29.96936988830566</v>
       </c>
       <c r="C15" t="n">
-        <v>5.296500205993652</v>
+        <v>5.295599937438965</v>
       </c>
       <c r="D15">
         <f>B15/C15</f>
@@ -6218,14 +6218,14 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29.9693717956543</v>
+        <v>30.06963539123535</v>
       </c>
       <c r="C16" t="n">
-        <v>5.295599937438965</v>
+        <v>5.329500198364258</v>
       </c>
       <c r="D16">
         <f>B16/C16</f>
@@ -6239,14 +6239,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.06963539123535</v>
+        <v>29.91468238830566</v>
       </c>
       <c r="C17" t="n">
-        <v>5.329500198364258</v>
+        <v>5.321499824523926</v>
       </c>
       <c r="D17">
         <f>B17/C17</f>
@@ -6260,14 +6260,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29.9146842956543</v>
+        <v>29.68681335449219</v>
       </c>
       <c r="C18" t="n">
-        <v>5.321499824523926</v>
+        <v>5.332300186157227</v>
       </c>
       <c r="D18">
         <f>B18/C18</f>
@@ -6281,14 +6281,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29.68681144714355</v>
+        <v>29.65946769714355</v>
       </c>
       <c r="C19" t="n">
-        <v>5.332300186157227</v>
+        <v>5.402100086212158</v>
       </c>
       <c r="D19">
         <f>B19/C19</f>
@@ -6302,14 +6302,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29.65946960449219</v>
+        <v>29.42248344421387</v>
       </c>
       <c r="C20" t="n">
-        <v>5.402100086212158</v>
+        <v>5.386799812316895</v>
       </c>
       <c r="D20">
         <f>B20/C20</f>
@@ -6323,14 +6323,14 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29.42248344421387</v>
+        <v>29.37691116333008</v>
       </c>
       <c r="C21" t="n">
-        <v>5.386799812316895</v>
+        <v>5.37939977645874</v>
       </c>
       <c r="D21">
         <f>B21/C21</f>
@@ -6344,14 +6344,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.37690925598145</v>
+        <v>29.53186225891113</v>
       </c>
       <c r="C22" t="n">
-        <v>5.37939977645874</v>
+        <v>5.33080005645752</v>
       </c>
       <c r="D22">
         <f>B22/C22</f>
@@ -6365,14 +6365,14 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29.53186416625977</v>
+        <v>28.97586250305176</v>
       </c>
       <c r="C23" t="n">
-        <v>5.33080005645752</v>
+        <v>5.355400085449219</v>
       </c>
       <c r="D23">
         <f>B23/C23</f>
@@ -6386,14 +6386,14 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28.97586441040039</v>
+        <v>29.03055000305176</v>
       </c>
       <c r="C24" t="n">
-        <v>5.355400085449219</v>
+        <v>5.335400104522705</v>
       </c>
       <c r="D24">
         <f>B24/C24</f>
@@ -6407,14 +6407,14 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.03055000305176</v>
+        <v>29.23107528686523</v>
       </c>
       <c r="C25" t="n">
-        <v>5.335400104522705</v>
+        <v>5.355800151824951</v>
       </c>
       <c r="D25">
         <f>B25/C25</f>
@@ -6428,14 +6428,14 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.2310733795166</v>
+        <v>29.44983100891113</v>
       </c>
       <c r="C26" t="n">
-        <v>5.355800151824951</v>
+        <v>5.326300144195557</v>
       </c>
       <c r="D26">
         <f>B26/C26</f>
@@ -6449,14 +6449,14 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>29.4498291015625</v>
+        <v>29.6412410736084</v>
       </c>
       <c r="C27" t="n">
-        <v>5.326300144195557</v>
+        <v>5.306099891662598</v>
       </c>
       <c r="D27">
         <f>B27/C27</f>
@@ -6470,14 +6470,14 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29.64123916625977</v>
+        <v>28.59304046630859</v>
       </c>
       <c r="C28" t="n">
-        <v>5.306099891662598</v>
+        <v>5.309299945831299</v>
       </c>
       <c r="D28">
         <f>B28/C28</f>
@@ -6491,14 +6491,14 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28.59304237365723</v>
+        <v>28.85736846923828</v>
       </c>
       <c r="C29" t="n">
-        <v>5.309299945831299</v>
+        <v>5.43809986114502</v>
       </c>
       <c r="D29">
         <f>B29/C29</f>
@@ -6512,14 +6512,14 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28.85736846923828</v>
+        <v>29.03966522216797</v>
       </c>
       <c r="C30" t="n">
-        <v>5.43809986114502</v>
+        <v>5.429999828338623</v>
       </c>
       <c r="D30">
         <f>B30/C30</f>
@@ -6533,14 +6533,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29.03966522216797</v>
+        <v>29.11258316040039</v>
       </c>
       <c r="C31" t="n">
-        <v>5.429999828338623</v>
+        <v>5.43149995803833</v>
       </c>
       <c r="D31">
         <f>B31/C31</f>
@@ -6554,14 +6554,14 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.11258316040039</v>
+        <v>28.62950134277344</v>
       </c>
       <c r="C32" t="n">
-        <v>5.43149995803833</v>
+        <v>5.469799995422363</v>
       </c>
       <c r="D32">
         <f>B32/C32</f>
@@ -6575,14 +6575,14 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28.6294994354248</v>
+        <v>28.79356575012207</v>
       </c>
       <c r="C33" t="n">
-        <v>5.469799995422363</v>
+        <v>5.405499935150146</v>
       </c>
       <c r="D33">
         <f>B33/C33</f>
@@ -6596,14 +6596,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28.79356575012207</v>
+        <v>28.89382934570312</v>
       </c>
       <c r="C34" t="n">
-        <v>5.405499935150146</v>
+        <v>5.418200016021729</v>
       </c>
       <c r="D34">
         <f>B34/C34</f>
@@ -6617,14 +6617,14 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28.89382934570312</v>
+        <v>28.01880836486816</v>
       </c>
       <c r="C35" t="n">
-        <v>5.418200016021729</v>
+        <v>5.413400173187256</v>
       </c>
       <c r="D35">
         <f>B35/C35</f>
@@ -6638,14 +6638,14 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.0188102722168</v>
+        <v>28.32871055603027</v>
       </c>
       <c r="C36" t="n">
-        <v>5.413400173187256</v>
+        <v>5.507500171661377</v>
       </c>
       <c r="D36">
         <f>B36/C36</f>
@@ -6659,14 +6659,14 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.32871055603027</v>
+        <v>28.16464614868164</v>
       </c>
       <c r="C37" t="n">
-        <v>5.507500171661377</v>
+        <v>5.518499851226807</v>
       </c>
       <c r="D37">
         <f>B37/C37</f>
@@ -6680,14 +6680,14 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28.16464424133301</v>
+        <v>28.26490783691406</v>
       </c>
       <c r="C38" t="n">
-        <v>5.518499851226807</v>
+        <v>5.521299839019775</v>
       </c>
       <c r="D38">
         <f>B38/C38</f>
@@ -6701,14 +6701,14 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.26490783691406</v>
+        <v>28.3469409942627</v>
       </c>
       <c r="C39" t="n">
-        <v>5.521299839019775</v>
+        <v>5.53980016708374</v>
       </c>
       <c r="D39">
         <f>B39/C39</f>
@@ -6722,14 +6722,14 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.34694290161133</v>
+        <v>28.4993839263916</v>
       </c>
       <c r="C40" t="n">
-        <v>5.53980016708374</v>
+        <v>5.590000152587891</v>
       </c>
       <c r="D40">
         <f>B40/C40</f>
@@ -6743,14 +6743,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>28.4993839263916</v>
+        <v>28.59341049194336</v>
       </c>
       <c r="C41" t="n">
-        <v>5.590000152587891</v>
+        <v>5.519499778747559</v>
       </c>
       <c r="D41">
         <f>B41/C41</f>
@@ -6764,14 +6764,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>28.59341049194336</v>
+        <v>28.89429473876953</v>
       </c>
       <c r="C42" t="n">
-        <v>5.519499778747559</v>
+        <v>5.542500019073486</v>
       </c>
       <c r="D42">
         <f>B42/C42</f>
@@ -6785,14 +6785,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.89429473876953</v>
+        <v>28.97891807556152</v>
       </c>
       <c r="C43" t="n">
-        <v>5.542500019073486</v>
+        <v>5.569099903106689</v>
       </c>
       <c r="D43">
         <f>B43/C43</f>
@@ -6806,14 +6806,14 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28.97891998291016</v>
+        <v>28.87548828125</v>
       </c>
       <c r="C44" t="n">
-        <v>5.569099903106689</v>
+        <v>5.517000198364258</v>
       </c>
       <c r="D44">
         <f>B44/C44</f>
@@ -6827,14 +6827,14 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.87549018859863</v>
+        <v>28.39595603942871</v>
       </c>
       <c r="C45" t="n">
-        <v>5.517000198364258</v>
+        <v>5.421599864959717</v>
       </c>
       <c r="D45">
         <f>B45/C45</f>
@@ -6848,14 +6848,14 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>28.39595603942871</v>
+        <v>27.86940574645996</v>
       </c>
       <c r="C46" t="n">
-        <v>5.421599864959717</v>
+        <v>5.40749979019165</v>
       </c>
       <c r="D46">
         <f>B46/C46</f>
@@ -6869,14 +6869,14 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>27.86940765380859</v>
+        <v>28.04805755615234</v>
       </c>
       <c r="C47" t="n">
-        <v>5.40749979019165</v>
+        <v>5.372000217437744</v>
       </c>
       <c r="D47">
         <f>B47/C47</f>
@@ -6890,14 +6890,14 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28.04805755615234</v>
+        <v>28.39595603942871</v>
       </c>
       <c r="C48" t="n">
-        <v>5.372000217437744</v>
+        <v>5.383900165557861</v>
       </c>
       <c r="D48">
         <f>B48/C48</f>
@@ -6911,14 +6911,14 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28.39595603942871</v>
+        <v>28.48998260498047</v>
       </c>
       <c r="C49" t="n">
-        <v>5.383900165557861</v>
+        <v>5.386600017547607</v>
       </c>
       <c r="D49">
         <f>B49/C49</f>
@@ -6932,14 +6932,14 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.48998069763184</v>
+        <v>28.54639625549316</v>
       </c>
       <c r="C50" t="n">
-        <v>5.386600017547607</v>
+        <v>5.370299816131592</v>
       </c>
       <c r="D50">
         <f>B50/C50</f>
@@ -6953,14 +6953,14 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28.5463981628418</v>
+        <v>29.2798023223877</v>
       </c>
       <c r="C51" t="n">
-        <v>5.370299816131592</v>
+        <v>5.373700141906738</v>
       </c>
       <c r="D51">
         <f>B51/C51</f>
@@ -6974,14 +6974,14 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29.2798023223877</v>
+        <v>30.07902717590332</v>
       </c>
       <c r="C52" t="n">
-        <v>5.373700141906738</v>
+        <v>5.371300220489502</v>
       </c>
       <c r="D52">
         <f>B52/C52</f>
@@ -6995,14 +6995,14 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>30.07902717590332</v>
+        <v>29.89097595214844</v>
       </c>
       <c r="C53" t="n">
-        <v>5.371300220489502</v>
+        <v>5.396100044250488</v>
       </c>
       <c r="D53">
         <f>B53/C53</f>
@@ -7016,14 +7016,14 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29.89097595214844</v>
+        <v>30.12603950500488</v>
       </c>
       <c r="C54" t="n">
-        <v>5.396100044250488</v>
+        <v>5.367899894714355</v>
       </c>
       <c r="D54">
         <f>B54/C54</f>
@@ -7037,14 +7037,14 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>30.12604141235352</v>
+        <v>30.24827003479004</v>
       </c>
       <c r="C55" t="n">
-        <v>5.367899894714355</v>
+        <v>5.367700099945068</v>
       </c>
       <c r="D55">
         <f>B55/C55</f>
@@ -7058,14 +7058,14 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>30.24827194213867</v>
+        <v>30.36110687255859</v>
       </c>
       <c r="C56" t="n">
-        <v>5.367700099945068</v>
+        <v>5.36870002746582</v>
       </c>
       <c r="D56">
         <f>B56/C56</f>
@@ -7079,14 +7079,14 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>30.36110687255859</v>
+        <v>31.43300437927246</v>
       </c>
       <c r="C57" t="n">
-        <v>5.36870002746582</v>
+        <v>5.374300003051758</v>
       </c>
       <c r="D57">
         <f>B57/C57</f>
@@ -7100,14 +7100,14 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31.43300819396973</v>
+        <v>31.57404708862305</v>
       </c>
       <c r="C58" t="n">
-        <v>5.374300003051758</v>
+        <v>5.31879997253418</v>
       </c>
       <c r="D58">
         <f>B58/C58</f>
@@ -7121,14 +7121,14 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31.57404708862305</v>
+        <v>32.94683456420898</v>
       </c>
       <c r="C59" t="n">
-        <v>5.31879997253418</v>
+        <v>5.283699989318848</v>
       </c>
       <c r="D59">
         <f>B59/C59</f>
@@ -7142,14 +7142,14 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32.94683456420898</v>
+        <v>33.24771499633789</v>
       </c>
       <c r="C60" t="n">
-        <v>5.283699989318848</v>
+        <v>5.288899898529053</v>
       </c>
       <c r="D60">
         <f>B60/C60</f>
@@ -7163,14 +7163,14 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>33.24771499633789</v>
+        <v>33.97171783447266</v>
       </c>
       <c r="C61" t="n">
-        <v>5.288899898529053</v>
+        <v>5.279099941253662</v>
       </c>
       <c r="D61">
         <f>B61/C61</f>
@@ -7184,14 +7184,14 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>33.97171783447266</v>
+        <v>35.10943603515625</v>
       </c>
       <c r="C62" t="n">
-        <v>5.279099941253662</v>
+        <v>5.183599948883057</v>
       </c>
       <c r="D62">
         <f>B62/C62</f>
@@ -7205,14 +7205,14 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>35.10943603515625</v>
+        <v>35.44792938232422</v>
       </c>
       <c r="C63" t="n">
-        <v>5.183599948883057</v>
+        <v>5.197100162506104</v>
       </c>
       <c r="D63">
         <f>B63/C63</f>
@@ -7226,14 +7226,14 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>35.44793319702148</v>
+        <v>35.50434494018555</v>
       </c>
       <c r="C64" t="n">
-        <v>5.197100162506104</v>
+        <v>5.189199924468994</v>
       </c>
       <c r="D64">
         <f>B64/C64</f>
@@ -7247,14 +7247,14 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>35.50434494018555</v>
+        <v>35.01540756225586</v>
       </c>
       <c r="C65" t="n">
-        <v>5.189199924468994</v>
+        <v>5.255000114440918</v>
       </c>
       <c r="D65">
         <f>B65/C65</f>
@@ -7268,14 +7268,14 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>35.01541137695312</v>
+        <v>35.33510208129883</v>
       </c>
       <c r="C66" t="n">
-        <v>5.255000114440918</v>
+        <v>5.259399890899658</v>
       </c>
       <c r="D66">
         <f>B66/C66</f>
@@ -7289,14 +7289,14 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>35.33510208129883</v>
+        <v>35.2786865234375</v>
       </c>
       <c r="C67" t="n">
-        <v>5.259399890899658</v>
+        <v>5.237500190734863</v>
       </c>
       <c r="D67">
         <f>B67/C67</f>
@@ -7310,14 +7310,14 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>35.27868270874023</v>
+        <v>34.78974533081055</v>
       </c>
       <c r="C68" t="n">
-        <v>5.237500190734863</v>
+        <v>5.23799991607666</v>
       </c>
       <c r="D68">
         <f>B68/C68</f>
@@ -7331,14 +7331,14 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>34.78974533081055</v>
+        <v>34.46065521240234</v>
       </c>
       <c r="C69" t="n">
-        <v>5.23799991607666</v>
+        <v>5.270500183105469</v>
       </c>
       <c r="D69">
         <f>B69/C69</f>
@@ -7352,14 +7352,14 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>34.46065521240234</v>
+        <v>35.09062957763672</v>
       </c>
       <c r="C70" t="n">
-        <v>5.270500183105469</v>
+        <v>5.21589994430542</v>
       </c>
       <c r="D70">
         <f>B70/C70</f>
@@ -7373,14 +7373,14 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>35.09063339233398</v>
+        <v>35.11883544921875</v>
       </c>
       <c r="C71" t="n">
-        <v>5.21589994430542</v>
+        <v>5.19159984588623</v>
       </c>
       <c r="D71">
         <f>B71/C71</f>
@@ -7394,14 +7394,14 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>35.11883926391602</v>
+        <v>35.80522918701172</v>
       </c>
       <c r="C72" t="n">
-        <v>5.19159984588623</v>
+        <v>5.196199893951416</v>
       </c>
       <c r="D72">
         <f>B72/C72</f>
@@ -7415,14 +7415,14 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>35.80523300170898</v>
+        <v>34.89317321777344</v>
       </c>
       <c r="C73" t="n">
-        <v>5.196199893951416</v>
+        <v>5.198699951171875</v>
       </c>
       <c r="D73">
         <f>B73/C73</f>
@@ -7436,14 +7436,14 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>34.89317321777344</v>
+        <v>34.68631362915039</v>
       </c>
       <c r="C74" t="n">
-        <v>5.198699951171875</v>
+        <v>5.213900089263916</v>
       </c>
       <c r="D74">
         <f>B74/C74</f>
@@ -7457,14 +7457,14 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>34.68631744384766</v>
+        <v>34.9683952331543</v>
       </c>
       <c r="C75" t="n">
-        <v>5.213900089263916</v>
+        <v>5.220499992370605</v>
       </c>
       <c r="D75">
         <f>B75/C75</f>
@@ -7478,14 +7478,14 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>34.9683952331543</v>
+        <v>35.55135726928711</v>
       </c>
       <c r="C76" t="n">
-        <v>5.220499992370605</v>
+        <v>5.234399795532227</v>
       </c>
       <c r="D76">
         <f>B76/C76</f>
@@ -7499,14 +7499,14 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>35.55136108398438</v>
+        <v>35.70180130004883</v>
       </c>
       <c r="C77" t="n">
-        <v>5.234399795532227</v>
+        <v>5.208799839019775</v>
       </c>
       <c r="D77">
         <f>B77/C77</f>
@@ -7520,14 +7520,14 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>35.70180130004883</v>
+        <v>36.28476715087891</v>
       </c>
       <c r="C78" t="n">
-        <v>5.208799839019775</v>
+        <v>5.176499843597412</v>
       </c>
       <c r="D78">
         <f>B78/C78</f>
@@ -7541,14 +7541,14 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>36.28476715087891</v>
+        <v>37.20622253417969</v>
       </c>
       <c r="C79" t="n">
-        <v>5.176499843597412</v>
+        <v>5.170899868011475</v>
       </c>
       <c r="D79">
         <f>B79/C79</f>
@@ -7562,14 +7562,14 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>37.20622634887695</v>
+        <v>37.20622253417969</v>
       </c>
       <c r="C80" t="n">
-        <v>5.170899868011475</v>
+        <v>5.151999950408936</v>
       </c>
       <c r="D80">
         <f>B80/C80</f>
@@ -7583,14 +7583,14 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>37.20622634887695</v>
+        <v>37.24383544921875</v>
       </c>
       <c r="C81" t="n">
-        <v>5.151999950408936</v>
+        <v>5.124199867248535</v>
       </c>
       <c r="D81">
         <f>B81/C81</f>
@@ -7604,14 +7604,14 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37.24383544921875</v>
+        <v>36.98056030273438</v>
       </c>
       <c r="C82" t="n">
-        <v>5.124199867248535</v>
+        <v>5.136600017547607</v>
       </c>
       <c r="D82">
         <f>B82/C82</f>
@@ -7625,14 +7625,14 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>36.98056030273438</v>
+        <v>38.67303466796875</v>
       </c>
       <c r="C83" t="n">
-        <v>5.136600017547607</v>
+        <v>5.129600048065186</v>
       </c>
       <c r="D83">
         <f>B83/C83</f>
@@ -7646,14 +7646,14 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>38.67303466796875</v>
+        <v>38.5037841796875</v>
       </c>
       <c r="C84" t="n">
-        <v>5.129600048065186</v>
+        <v>5.170300006866455</v>
       </c>
       <c r="D84">
         <f>B84/C84</f>
@@ -7667,14 +7667,14 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>38.50378799438477</v>
+        <v>38.08066940307617</v>
       </c>
       <c r="C85" t="n">
-        <v>5.170300006866455</v>
+        <v>5.277299880981445</v>
       </c>
       <c r="D85">
         <f>B85/C85</f>
@@ -7688,14 +7688,14 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>38.08066940307617</v>
+        <v>38.25931549072266</v>
       </c>
       <c r="C86" t="n">
-        <v>5.277299880981445</v>
+        <v>5.230100154876709</v>
       </c>
       <c r="D86">
         <f>B86/C86</f>
@@ -7709,14 +7709,14 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>38.25931930541992</v>
+        <v>39.64150619506836</v>
       </c>
       <c r="C87" t="n">
-        <v>5.230100154876709</v>
+        <v>5.263400077819824</v>
       </c>
       <c r="D87">
         <f>B87/C87</f>
@@ -7730,14 +7730,14 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>39.64150619506836</v>
+        <v>40.58176803588867</v>
       </c>
       <c r="C88" t="n">
-        <v>5.263400077819824</v>
+        <v>5.243500232696533</v>
       </c>
       <c r="D88">
         <f>B88/C88</f>
@@ -7751,14 +7751,14 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>40.58177185058594</v>
+        <v>40.36550903320312</v>
       </c>
       <c r="C89" t="n">
-        <v>5.243500232696533</v>
+        <v>5.205299854278564</v>
       </c>
       <c r="D89">
         <f>B89/C89</f>
@@ -7772,14 +7772,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>40.36550903320312</v>
+        <v>42.12380218505859</v>
       </c>
       <c r="C90" t="n">
-        <v>5.205299854278564</v>
+        <v>5.162399768829346</v>
       </c>
       <c r="D90">
         <f>B90/C90</f>
@@ -7793,14 +7793,14 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>42.12380218505859</v>
+        <v>42.31185150146484</v>
       </c>
       <c r="C91" t="n">
-        <v>5.162399768829346</v>
+        <v>5.151400089263916</v>
       </c>
       <c r="D91">
         <f>B91/C91</f>
@@ -7814,14 +7814,14 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>42.31185913085938</v>
+        <v>42.00156784057617</v>
       </c>
       <c r="C92" t="n">
-        <v>5.151400089263916</v>
+        <v>5.243899822235107</v>
       </c>
       <c r="D92">
         <f>B92/C92</f>
@@ -7835,14 +7835,14 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>42.00156784057617</v>
+        <v>43.12047958374023</v>
       </c>
       <c r="C93" t="n">
-        <v>5.243899822235107</v>
+        <v>5.329100131988525</v>
       </c>
       <c r="D93">
         <f>B93/C93</f>
@@ -7856,14 +7856,14 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>43.1204833984375</v>
+        <v>43.60942077636719</v>
       </c>
       <c r="C94" t="n">
-        <v>5.329100131988525</v>
+        <v>5.233399868011475</v>
       </c>
       <c r="D94">
         <f>B94/C94</f>
@@ -7877,14 +7877,14 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>43.60941696166992</v>
+        <v>44.19237899780273</v>
       </c>
       <c r="C95" t="n">
-        <v>5.233399868011475</v>
+        <v>5.19290018081665</v>
       </c>
       <c r="D95">
         <f>B95/C95</f>
@@ -7898,14 +7898,14 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>44.19237899780273</v>
+        <v>43.98551940917969</v>
       </c>
       <c r="C96" t="n">
-        <v>5.19290018081665</v>
+        <v>5.262100219726562</v>
       </c>
       <c r="D96">
         <f>B96/C96</f>
@@ -7919,14 +7919,14 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>43.98552322387695</v>
+        <v>42.94182968139648</v>
       </c>
       <c r="C97" t="n">
-        <v>5.262100219726562</v>
+        <v>5.219900131225586</v>
       </c>
       <c r="D97">
         <f>B97/C97</f>
@@ -7940,14 +7940,14 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>42.94182586669922</v>
+        <v>43.28032684326172</v>
       </c>
       <c r="C98" t="n">
-        <v>5.219900131225586</v>
+        <v>5.31190013885498</v>
       </c>
       <c r="D98">
         <f>B98/C98</f>
@@ -7961,14 +7961,14 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>43.28032684326172</v>
+        <v>44.44625091552734</v>
       </c>
       <c r="C99" t="n">
-        <v>5.31190013885498</v>
+        <v>5.232900142669678</v>
       </c>
       <c r="D99">
         <f>B99/C99</f>
@@ -7982,14 +7982,14 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>44.44625473022461</v>
+        <v>44.66250991821289</v>
       </c>
       <c r="C100" t="n">
-        <v>5.232900142669678</v>
+        <v>5.232600212097168</v>
       </c>
       <c r="D100">
         <f>B100/C100</f>
@@ -8003,14 +8003,14 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>44.66250991821289</v>
+        <v>45.15145111083984</v>
       </c>
       <c r="C101" t="n">
-        <v>5.232600212097168</v>
+        <v>5.236800193786621</v>
       </c>
       <c r="D101">
         <f>B101/C101</f>
@@ -8024,14 +8024,14 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>45.15144729614258</v>
+        <v>46.45841598510742</v>
       </c>
       <c r="C102" t="n">
-        <v>5.236800193786621</v>
+        <v>5.235099792480469</v>
       </c>
       <c r="D102">
         <f>B102/C102</f>
@@ -8045,14 +8045,14 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>46.45841598510742</v>
+        <v>46.702880859375</v>
       </c>
       <c r="C103" t="n">
-        <v>5.235099792480469</v>
+        <v>5.263999938964844</v>
       </c>
       <c r="D103">
         <f>B103/C103</f>
@@ -8066,14 +8066,14 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>46.702880859375</v>
+        <v>45.76261901855469</v>
       </c>
       <c r="C104" t="n">
-        <v>5.263999938964844</v>
+        <v>5.192800045013428</v>
       </c>
       <c r="D104">
         <f>B104/C104</f>
@@ -8087,14 +8087,14 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>45.76261901855469</v>
+        <v>44.54027557373047</v>
       </c>
       <c r="C105" t="n">
-        <v>5.192800045013428</v>
+        <v>5.154500007629395</v>
       </c>
       <c r="D105">
         <f>B105/C105</f>
@@ -8108,14 +8108,14 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>44.54027557373047</v>
+        <v>45.27368545532227</v>
       </c>
       <c r="C106" t="n">
-        <v>5.154500007629395</v>
+        <v>5.156400203704834</v>
       </c>
       <c r="D106">
         <f>B106/C106</f>
@@ -8129,14 +8129,14 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>45.27368545532227</v>
+        <v>46.0164909362793</v>
       </c>
       <c r="C107" t="n">
-        <v>5.156400203704834</v>
+        <v>5.138299942016602</v>
       </c>
       <c r="D107">
         <f>B107/C107</f>
@@ -8150,14 +8150,14 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>46.0164909362793</v>
+        <v>45.61217498779297</v>
       </c>
       <c r="C108" t="n">
-        <v>5.138299942016602</v>
+        <v>5.150599956512451</v>
       </c>
       <c r="D108">
         <f>B108/C108</f>
@@ -8171,14 +8171,14 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>45.61217880249023</v>
+        <v>43.82567596435547</v>
       </c>
       <c r="C109" t="n">
-        <v>5.150599956512451</v>
+        <v>5.100200176239014</v>
       </c>
       <c r="D109">
         <f>B109/C109</f>
@@ -8192,14 +8192,14 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>43.82567977905273</v>
+        <v>45.03861999511719</v>
       </c>
       <c r="C110" t="n">
-        <v>5.100200176239014</v>
+        <v>5.095799922943115</v>
       </c>
       <c r="D110">
         <f>B110/C110</f>
@@ -8213,11 +8213,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>45.03861999511719</v>
+        <v>46.10111618041992</v>
       </c>
       <c r="C111" t="n">
         <v>5.095799922943115</v>
@@ -8234,14 +8234,14 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>46.10111618041992</v>
+        <v>46.80630874633789</v>
       </c>
       <c r="C112" t="n">
-        <v>5.095799922943115</v>
+        <v>4.994400024414062</v>
       </c>
       <c r="D112">
         <f>B112/C112</f>
@@ -8255,14 +8255,14 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>46.80630874633789</v>
+        <v>45.01980972290039</v>
       </c>
       <c r="C113" t="n">
-        <v>4.994400024414062</v>
+        <v>4.984799861907959</v>
       </c>
       <c r="D113">
         <f>B113/C113</f>
@@ -8276,14 +8276,14 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>45.01981353759766</v>
+        <v>44.08895111083984</v>
       </c>
       <c r="C114" t="n">
-        <v>4.984799861907959</v>
+        <v>4.992400169372559</v>
       </c>
       <c r="D114">
         <f>B114/C114</f>
@@ -8297,14 +8297,14 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>44.08895492553711</v>
+        <v>45.67800140380859</v>
       </c>
       <c r="C115" t="n">
-        <v>4.992400169372559</v>
+        <v>4.987090110778809</v>
       </c>
       <c r="D115">
         <f>B115/C115</f>
@@ -8318,11 +8318,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>45.67799758911133</v>
+        <v>43.45897674560547</v>
       </c>
       <c r="C116" t="n">
         <v>4.987090110778809</v>
@@ -8339,14 +8339,14 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>43.45897674560547</v>
+        <v>44.21118545532227</v>
       </c>
       <c r="C117" t="n">
-        <v>4.987090110778809</v>
+        <v>4.952400207519531</v>
       </c>
       <c r="D117">
         <f>B117/C117</f>
@@ -8360,14 +8360,14 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>44.21118927001953</v>
+        <v>44.82235717773438</v>
       </c>
       <c r="C118" t="n">
-        <v>4.952400207519531</v>
+        <v>4.984899997711182</v>
       </c>
       <c r="D118">
         <f>B118/C118</f>
@@ -8381,14 +8381,14 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>44.82235336303711</v>
+        <v>45.54999542236328</v>
       </c>
       <c r="C119" t="n">
-        <v>4.984899997711182</v>
+        <v>5.030799865722656</v>
       </c>
       <c r="D119">
         <f>B119/C119</f>
@@ -8402,11 +8402,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>45.54999542236328</v>
+        <v>44.96834564208984</v>
       </c>
       <c r="C120" t="n">
         <v>5.030799865722656</v>
@@ -8423,14 +8423,14 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>44.96834564208984</v>
+        <v>45.16858291625977</v>
       </c>
       <c r="C121" t="n">
-        <v>5.030799865722656</v>
+        <v>4.999599933624268</v>
       </c>
       <c r="D121">
         <f>B121/C121</f>
@@ -8444,14 +8444,14 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>45.16858291625977</v>
+        <v>45.31161880493164</v>
       </c>
       <c r="C122" t="n">
-        <v>4.999599933624268</v>
+        <v>4.99429988861084</v>
       </c>
       <c r="D122">
         <f>B122/C122</f>
@@ -8465,14 +8465,14 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>45.31161880493164</v>
+        <v>46.68469619750977</v>
       </c>
       <c r="C123" t="n">
-        <v>4.99429988861084</v>
+        <v>5.017499923706055</v>
       </c>
       <c r="D123">
         <f>B123/C123</f>
@@ -8486,14 +8486,14 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>46.68469619750977</v>
+        <v>46.79911804199219</v>
       </c>
       <c r="C124" t="n">
-        <v>5.017499923706055</v>
+        <v>4.969500064849854</v>
       </c>
       <c r="D124">
         <f>B124/C124</f>
@@ -8507,14 +8507,14 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>46.79911804199219</v>
+        <v>47.04703903198242</v>
       </c>
       <c r="C125" t="n">
-        <v>4.969500064849854</v>
+        <v>4.984799861907959</v>
       </c>
       <c r="D125">
         <f>B125/C125</f>
@@ -8528,14 +8528,14 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>47.04703903198242</v>
+        <v>46.39863967895508</v>
       </c>
       <c r="C126" t="n">
-        <v>4.984799861907959</v>
+        <v>4.927299976348877</v>
       </c>
       <c r="D126">
         <f>B126/C126</f>
@@ -8549,14 +8549,14 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>46.39863967895508</v>
+        <v>45.07323455810547</v>
       </c>
       <c r="C127" t="n">
-        <v>4.927299976348877</v>
+        <v>4.932271957397461</v>
       </c>
       <c r="D127">
         <f>B127/C127</f>
@@ -8570,14 +8570,14 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>45.07323455810547</v>
+        <v>44.0720329284668</v>
       </c>
       <c r="C128" t="n">
-        <v>4.932271957397461</v>
+        <v>4.944900035858154</v>
       </c>
       <c r="D128">
         <f>B128/C128</f>
@@ -8591,11 +8591,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>44.0720329284668</v>
+        <v>43.54758834838867</v>
       </c>
       <c r="C129" t="n">
         <v>4.944900035858154</v>
@@ -8612,14 +8612,14 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>43.54758834838867</v>
+        <v>44.27227020263672</v>
       </c>
       <c r="C130" t="n">
-        <v>4.944900035858154</v>
+        <v>4.906400203704834</v>
       </c>
       <c r="D130">
         <f>B130/C130</f>
@@ -8633,14 +8633,14 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>44.27227020263672</v>
+        <v>43.55712509155273</v>
       </c>
       <c r="C131" t="n">
-        <v>4.906400203704834</v>
+        <v>4.9096999168396</v>
       </c>
       <c r="D131">
         <f>B131/C131</f>
@@ -8654,14 +8654,14 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>43.55712509155273</v>
+        <v>42.49871063232422</v>
       </c>
       <c r="C132" t="n">
-        <v>4.9096999168396</v>
+        <v>5.024899959564209</v>
       </c>
       <c r="D132">
         <f>B132/C132</f>
@@ -8675,14 +8675,14 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>42.49871063232422</v>
+        <v>42.90872573852539</v>
       </c>
       <c r="C133" t="n">
-        <v>5.024899959564209</v>
+        <v>5.00409984588623</v>
       </c>
       <c r="D133">
         <f>B133/C133</f>
@@ -8696,11 +8696,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>42.90872573852539</v>
+        <v>43.35688400268555</v>
       </c>
       <c r="C134" t="n">
         <v>5.00409984588623</v>
@@ -8717,14 +8717,14 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>43.35688400268555</v>
+        <v>44.28180694580078</v>
       </c>
       <c r="C135" t="n">
-        <v>5.00409984588623</v>
+        <v>5.005624771118164</v>
       </c>
       <c r="D135">
         <f>B135/C135</f>
@@ -8738,14 +8738,14 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>44.28180694580078</v>
+        <v>43.94807434082031</v>
       </c>
       <c r="C136" t="n">
-        <v>5.005624771118164</v>
+        <v>5.058199882507324</v>
       </c>
       <c r="D136">
         <f>B136/C136</f>
@@ -8759,14 +8759,14 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>43.94807434082031</v>
+        <v>42.52731704711914</v>
       </c>
       <c r="C137" t="n">
-        <v>5.058199882507324</v>
+        <v>5.01170015335083</v>
       </c>
       <c r="D137">
         <f>B137/C137</f>
@@ -8780,14 +8780,14 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>42.52731704711914</v>
+        <v>42.86105346679688</v>
       </c>
       <c r="C138" t="n">
-        <v>5.01170015335083</v>
+        <v>5.017099857330322</v>
       </c>
       <c r="D138">
         <f>B138/C138</f>
@@ -8801,11 +8801,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>42.86105346679688</v>
+        <v>42.41289138793945</v>
       </c>
       <c r="C139" t="n">
         <v>5.017099857330322</v>
@@ -8822,14 +8822,14 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>42.41289138793945</v>
+        <v>41.38308334350586</v>
       </c>
       <c r="C140" t="n">
-        <v>5.017099857330322</v>
+        <v>5.01039981842041</v>
       </c>
       <c r="D140">
         <f>B140/C140</f>
@@ -8843,14 +8843,14 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>41.38308334350586</v>
+        <v>41.42122268676758</v>
       </c>
       <c r="C141" t="n">
-        <v>5.01039981842041</v>
+        <v>5.04449987411499</v>
       </c>
       <c r="D141">
         <f>B141/C141</f>
@@ -8864,14 +8864,14 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>41.42122268676758</v>
+        <v>40.83003616333008</v>
       </c>
       <c r="C142" t="n">
-        <v>5.04449987411499</v>
+        <v>5.07289981842041</v>
       </c>
       <c r="D142">
         <f>B142/C142</f>
@@ -8885,14 +8885,14 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>40.83003616333008</v>
+        <v>40.53444290161133</v>
       </c>
       <c r="C143" t="n">
-        <v>5.07289981842041</v>
+        <v>5.051700115203857</v>
       </c>
       <c r="D143">
         <f>B143/C143</f>
@@ -8906,11 +8906,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>40.53444290161133</v>
+        <v>40.04814529418945</v>
       </c>
       <c r="C144" t="n">
         <v>5.051700115203857</v>
@@ -8927,14 +8927,14 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>40.04814529418945</v>
+        <v>40.40094757080078</v>
       </c>
       <c r="C145" t="n">
-        <v>5.051700115203857</v>
+        <v>5.038599967956543</v>
       </c>
       <c r="D145">
         <f>B145/C145</f>
@@ -8948,14 +8948,14 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>40.40094757080078</v>
+        <v>40.30493545532227</v>
       </c>
       <c r="C146" t="n">
-        <v>5.038599967956543</v>
+        <v>5.020699977874756</v>
       </c>
       <c r="D146">
         <f>B146/C146</f>
@@ -8969,14 +8969,14 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>40.30493545532227</v>
+        <v>39.99467468261719</v>
       </c>
       <c r="C147" t="n">
-        <v>5.020699977874756</v>
+        <v>5.077400207519531</v>
       </c>
       <c r="D147">
         <f>B147/C147</f>
@@ -8990,14 +8990,14 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>39.99467468261719</v>
+        <v>39.6456298828125</v>
       </c>
       <c r="C148" t="n">
-        <v>5.077400207519531</v>
+        <v>5.060699939727783</v>
       </c>
       <c r="D148">
         <f>B148/C148</f>
@@ -9011,14 +9011,14 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>39.6456298828125</v>
+        <v>39.96559143066406</v>
       </c>
       <c r="C149" t="n">
-        <v>5.060699939727783</v>
+        <v>5.203100204467773</v>
       </c>
       <c r="D149">
         <f>B149/C149</f>
@@ -9032,14 +9032,14 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>39.96559143066406</v>
+        <v>39.91710662841797</v>
       </c>
       <c r="C150" t="n">
-        <v>5.203100204467773</v>
+        <v>5.190100193023682</v>
       </c>
       <c r="D150">
         <f>B150/C150</f>
@@ -9053,14 +9053,14 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>39.91710662841797</v>
+        <v>40.38250350952148</v>
       </c>
       <c r="C151" t="n">
-        <v>5.190100193023682</v>
+        <v>5.192100048065186</v>
       </c>
       <c r="D151">
         <f>B151/C151</f>
@@ -9074,14 +9074,14 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>40.38250350952148</v>
+        <v>40.48915481567383</v>
       </c>
       <c r="C152" t="n">
-        <v>5.192100048065186</v>
+        <v>5.113800048828125</v>
       </c>
       <c r="D152">
         <f>B152/C152</f>
@@ -9095,11 +9095,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>40.48915481567383</v>
+        <v>39.92680740356445</v>
       </c>
       <c r="C153" t="n">
         <v>5.113800048828125</v>
@@ -9116,14 +9116,14 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>39.92680740356445</v>
+        <v>37.87132263183594</v>
       </c>
       <c r="C154" t="n">
-        <v>5.113800048828125</v>
+        <v>5.075099945068359</v>
       </c>
       <c r="D154">
         <f>B154/C154</f>
@@ -9137,14 +9137,14 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>37.87132263183594</v>
+        <v>37.36714935302734</v>
       </c>
       <c r="C155" t="n">
-        <v>5.075099945068359</v>
+        <v>5.101900100708008</v>
       </c>
       <c r="D155">
         <f>B155/C155</f>
@@ -9158,14 +9158,14 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>37.36714935302734</v>
+        <v>37.39623260498047</v>
       </c>
       <c r="C156" t="n">
-        <v>5.101900100708008</v>
+        <v>5.122099876403809</v>
       </c>
       <c r="D156">
         <f>B156/C156</f>
@@ -9179,14 +9179,14 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>37.39623260498047</v>
+        <v>37.66770935058594</v>
       </c>
       <c r="C157" t="n">
-        <v>5.122099876403809</v>
+        <v>5.18149995803833</v>
       </c>
       <c r="D157">
         <f>B157/C157</f>
@@ -9200,11 +9200,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>37.66770935058594</v>
+        <v>37.61923217773438</v>
       </c>
       <c r="C158" t="n">
         <v>5.18149995803833</v>
@@ -9221,14 +9221,14 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>37.61923217773438</v>
+        <v>37.97797393798828</v>
       </c>
       <c r="C159" t="n">
-        <v>5.18149995803833</v>
+        <v>5.156499862670898</v>
       </c>
       <c r="D159">
         <f>B159/C159</f>
@@ -9242,14 +9242,14 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>37.97797393798828</v>
+        <v>38.13310623168945</v>
       </c>
       <c r="C160" t="n">
-        <v>5.156499862670898</v>
+        <v>5.197700023651123</v>
       </c>
       <c r="D160">
         <f>B160/C160</f>
@@ -9263,14 +9263,14 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>38.13310623168945</v>
+        <v>37.124755859375</v>
       </c>
       <c r="C161" t="n">
-        <v>5.197700023651123</v>
+        <v>5.207499980926514</v>
       </c>
       <c r="D161">
         <f>B161/C161</f>
@@ -9284,14 +9284,14 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>37.124755859375</v>
+        <v>37.27988815307617</v>
       </c>
       <c r="C162" t="n">
-        <v>5.207499980926514</v>
+        <v>5.194099903106689</v>
       </c>
       <c r="D162">
         <f>B162/C162</f>
@@ -9305,11 +9305,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>37.27988815307617</v>
+        <v>36.90175628662109</v>
       </c>
       <c r="C163" t="n">
         <v>5.194099903106689</v>
@@ -9326,14 +9326,14 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>36.90175628662109</v>
+        <v>36.97932052612305</v>
       </c>
       <c r="C164" t="n">
-        <v>5.194099903106689</v>
+        <v>5.181787014007568</v>
       </c>
       <c r="D164">
         <f>B164/C164</f>
@@ -9347,14 +9347,14 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>36.97932052612305</v>
+        <v>36.64966583251953</v>
       </c>
       <c r="C165" t="n">
-        <v>5.181787014007568</v>
+        <v>5.174699783325195</v>
       </c>
       <c r="D165">
         <f>B165/C165</f>
@@ -9368,14 +9368,14 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>36.64966583251953</v>
+        <v>36.67875671386719</v>
       </c>
       <c r="C166" t="n">
-        <v>5.174699783325195</v>
+        <v>5.220600128173828</v>
       </c>
       <c r="D166">
         <f>B166/C166</f>
@@ -9389,14 +9389,14 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>36.67875671386719</v>
+        <v>36.8047981262207</v>
       </c>
       <c r="C167" t="n">
-        <v>5.220600128173828</v>
+        <v>5.2221999168396</v>
       </c>
       <c r="D167">
         <f>B167/C167</f>
@@ -9410,11 +9410,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>36.8047981262207</v>
+        <v>37.08597183227539</v>
       </c>
       <c r="C168" t="n">
         <v>5.2221999168396</v>
@@ -9431,14 +9431,14 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>37.08597183227539</v>
+        <v>36.62057876586914</v>
       </c>
       <c r="C169" t="n">
-        <v>5.2221999168396</v>
+        <v>5.143599987030029</v>
       </c>
       <c r="D169">
         <f>B169/C169</f>
@@ -9452,14 +9452,14 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>36.62057876586914</v>
+        <v>37.27018737792969</v>
       </c>
       <c r="C170" t="n">
-        <v>5.143599987030029</v>
+        <v>5.170899868011475</v>
       </c>
       <c r="D170">
         <f>B170/C170</f>
@@ -9473,14 +9473,14 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>37.27018737792969</v>
+        <v>38.44336700439453</v>
       </c>
       <c r="C171" t="n">
-        <v>5.170899868011475</v>
+        <v>5.16349983215332</v>
       </c>
       <c r="D171">
         <f>B171/C171</f>
@@ -9494,14 +9494,14 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>38.44336700439453</v>
+        <v>38.01675796508789</v>
       </c>
       <c r="C172" t="n">
-        <v>5.16349983215332</v>
+        <v>5.133900165557861</v>
       </c>
       <c r="D172">
         <f>B172/C172</f>
@@ -9515,11 +9515,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>38.01675796508789</v>
+        <v>38.44336700439453</v>
       </c>
       <c r="C173" t="n">
         <v>5.133900165557861</v>
@@ -9536,14 +9536,14 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>38.44336700439453</v>
+        <v>39.42263031005859</v>
       </c>
       <c r="C174" t="n">
-        <v>5.133900165557861</v>
+        <v>5.147900104522705</v>
       </c>
       <c r="D174">
         <f>B174/C174</f>
@@ -9557,14 +9557,14 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B175" t="n">
         <v>39.42263031005859</v>
       </c>
       <c r="C175" t="n">
-        <v>5.147900104522705</v>
+        <v>5.087900161743164</v>
       </c>
       <c r="D175">
         <f>B175/C175</f>
@@ -9578,14 +9578,14 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>39.42263031005859</v>
+        <v>39.35475921630859</v>
       </c>
       <c r="C176" t="n">
-        <v>5.087900161743164</v>
+        <v>5.09089994430542</v>
       </c>
       <c r="D176">
         <f>B176/C176</f>
@@ -9599,14 +9599,14 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>39.35475921630859</v>
+        <v>38.67606353759766</v>
       </c>
       <c r="C177" t="n">
-        <v>5.09089994430542</v>
+        <v>5.11359977722168</v>
       </c>
       <c r="D177">
         <f>B177/C177</f>
@@ -9620,11 +9620,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>38.67606353759766</v>
+        <v>39.65532684326172</v>
       </c>
       <c r="C178" t="n">
         <v>5.11359977722168</v>
@@ -9641,14 +9641,14 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>39.65532684326172</v>
+        <v>39.89772033691406</v>
       </c>
       <c r="C179" t="n">
-        <v>5.11359977722168</v>
+        <v>5.104400157928467</v>
       </c>
       <c r="D179">
         <f>B179/C179</f>
@@ -9662,14 +9662,14 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>39.89772033691406</v>
+        <v>40.39219665527344</v>
       </c>
       <c r="C180" t="n">
-        <v>5.104400157928467</v>
+        <v>5.087500095367432</v>
       </c>
       <c r="D180">
         <f>B180/C180</f>
@@ -9683,14 +9683,14 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>40.39219665527344</v>
+        <v>41.28420257568359</v>
       </c>
       <c r="C181" t="n">
-        <v>5.087500095367432</v>
+        <v>5.062488079071045</v>
       </c>
       <c r="D181">
         <f>B181/C181</f>
@@ -9704,14 +9704,14 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>41.28420257568359</v>
+        <v>41.64294052124023</v>
       </c>
       <c r="C182" t="n">
-        <v>5.062488079071045</v>
+        <v>5.09689998626709</v>
       </c>
       <c r="D182">
         <f>B182/C182</f>
@@ -9725,11 +9725,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>41.64294052124023</v>
+        <v>40.92546081542969</v>
       </c>
       <c r="C183" t="n">
         <v>5.09689998626709</v>
@@ -9746,14 +9746,14 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>40.92546081542969</v>
+        <v>39.76197814941406</v>
       </c>
       <c r="C184" t="n">
-        <v>5.09689998626709</v>
+        <v>5.123025894165039</v>
       </c>
       <c r="D184">
         <f>B184/C184</f>
@@ -9767,14 +9767,14 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>39.76197814941406</v>
+        <v>39.95589065551758</v>
       </c>
       <c r="C185" t="n">
-        <v>5.123025894165039</v>
+        <v>5.137100219726562</v>
       </c>
       <c r="D185">
         <f>B185/C185</f>
@@ -9788,14 +9788,14 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>39.95589065551758</v>
+        <v>40.72185134887695</v>
       </c>
       <c r="C186" t="n">
-        <v>5.137100219726562</v>
+        <v>5.127099990844727</v>
       </c>
       <c r="D186">
         <f>B186/C186</f>
@@ -9809,14 +9809,14 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>40.72185134887695</v>
+        <v>41.53628921508789</v>
       </c>
       <c r="C187" t="n">
-        <v>5.127099990844727</v>
+        <v>5.078100204467773</v>
       </c>
       <c r="D187">
         <f>B187/C187</f>
@@ -9830,11 +9830,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>41.53628921508789</v>
+        <v>42.09863662719727</v>
       </c>
       <c r="C188" t="n">
         <v>5.078100204467773</v>
@@ -9851,14 +9851,14 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>42.09863662719727</v>
+        <v>41.73989868164062</v>
       </c>
       <c r="C189" t="n">
-        <v>5.078100204467773</v>
+        <v>5.10290002822876</v>
       </c>
       <c r="D189">
         <f>B189/C189</f>
@@ -9872,14 +9872,14 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>41.73989868164062</v>
+        <v>41.20663452148438</v>
       </c>
       <c r="C190" t="n">
-        <v>5.10290002822876</v>
+        <v>5.143700122833252</v>
       </c>
       <c r="D190">
         <f>B190/C190</f>
@@ -9893,14 +9893,14 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>41.20663452148438</v>
+        <v>40.65398025512695</v>
       </c>
       <c r="C191" t="n">
-        <v>5.143700122833252</v>
+        <v>5.138500213623047</v>
       </c>
       <c r="D191">
         <f>B191/C191</f>
@@ -9914,14 +9914,14 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>40.65398025512695</v>
+        <v>40.84789657592773</v>
       </c>
       <c r="C192" t="n">
-        <v>5.138500213623047</v>
+        <v>5.121799945831299</v>
       </c>
       <c r="D192">
         <f>B192/C192</f>
@@ -9935,11 +9935,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>40.84789657592773</v>
+        <v>39.62623977661133</v>
       </c>
       <c r="C193" t="n">
         <v>5.121799945831299</v>
@@ -9956,14 +9956,14 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>39.62623977661133</v>
+        <v>40.94485092163086</v>
       </c>
       <c r="C194" t="n">
-        <v>5.121799945831299</v>
+        <v>5.105999946594238</v>
       </c>
       <c r="D194">
         <f>B194/C194</f>
@@ -9977,14 +9977,14 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>40.94485092163086</v>
+        <v>40.39219665527344</v>
       </c>
       <c r="C195" t="n">
-        <v>5.105999946594238</v>
+        <v>5.173500061035156</v>
       </c>
       <c r="D195">
         <f>B195/C195</f>
@@ -9998,14 +9998,14 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>40.39219665527344</v>
+        <v>40.18859100341797</v>
       </c>
       <c r="C196" t="n">
-        <v>5.173500061035156</v>
+        <v>5.195400238037109</v>
       </c>
       <c r="D196">
         <f>B196/C196</f>
@@ -10019,14 +10019,14 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>40.18859100341797</v>
+        <v>40.62489700317383</v>
       </c>
       <c r="C197" t="n">
-        <v>5.195400238037109</v>
+        <v>5.19980001449585</v>
       </c>
       <c r="D197">
         <f>B197/C197</f>
@@ -10040,11 +10040,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>40.62489700317383</v>
+        <v>40.80911254882812</v>
       </c>
       <c r="C198" t="n">
         <v>5.19980001449585</v>
@@ -10061,14 +10061,14 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>40.80911254882812</v>
+        <v>41.17755126953125</v>
       </c>
       <c r="C199" t="n">
-        <v>5.19980001449585</v>
+        <v>5.202499866485596</v>
       </c>
       <c r="D199">
         <f>B199/C199</f>
@@ -10082,14 +10082,14 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>41.17755126953125</v>
+        <v>41.30359268188477</v>
       </c>
       <c r="C200" t="n">
-        <v>5.202499866485596</v>
+        <v>5.214300155639648</v>
       </c>
       <c r="D200">
         <f>B200/C200</f>
@@ -10103,14 +10103,14 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>41.30359268188477</v>
+        <v>41.79807281494141</v>
       </c>
       <c r="C201" t="n">
-        <v>5.214300155639648</v>
+        <v>5.176700115203857</v>
       </c>
       <c r="D201">
         <f>B201/C201</f>
@@ -10124,14 +10124,14 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>41.79807281494141</v>
+        <v>42.97124862670898</v>
       </c>
       <c r="C202" t="n">
-        <v>5.176700115203857</v>
+        <v>5.193099975585938</v>
       </c>
       <c r="D202">
         <f>B202/C202</f>
@@ -10145,11 +10145,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>42.97124862670898</v>
+        <v>42.95185852050781</v>
       </c>
       <c r="C203" t="n">
         <v>5.193099975585938</v>
@@ -10166,14 +10166,14 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>42.95185852050781</v>
+        <v>42.11000061035156</v>
       </c>
       <c r="C204" t="n">
-        <v>5.193099975585938</v>
+        <v>5.154300212860107</v>
       </c>
       <c r="D204">
         <f>B204/C204</f>
@@ -10187,14 +10187,14 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>42.11000061035156</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="C205" t="n">
-        <v>5.154300212860107</v>
+        <v>5.146399974822998</v>
       </c>
       <c r="D205">
         <f>B205/C205</f>
@@ -10208,14 +10208,14 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>41.34999847412109</v>
+        <v>41.45000076293945</v>
       </c>
       <c r="C206" t="n">
-        <v>5.146399974822998</v>
+        <v>5.14739990234375</v>
       </c>
       <c r="D206">
         <f>B206/C206</f>
@@ -10229,14 +10229,14 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>41.45000076293945</v>
+        <v>42.70000076293945</v>
       </c>
       <c r="C207" t="n">
-        <v>5.14739990234375</v>
+        <v>5.161099910736084</v>
       </c>
       <c r="D207">
         <f>B207/C207</f>
@@ -10250,11 +10250,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>42.70000076293945</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="C208" t="n">
         <v>5.161099910736084</v>
@@ -10271,14 +10271,14 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>43.54999923706055</v>
+        <v>45.02000045776367</v>
       </c>
       <c r="C209" t="n">
-        <v>5.161099910736084</v>
+        <v>5.181700229644775</v>
       </c>
       <c r="D209">
         <f>B209/C209</f>
@@ -10292,14 +10292,14 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>45.02000045776367</v>
+        <v>46.86999893188477</v>
       </c>
       <c r="C210" t="n">
-        <v>5.181700229644775</v>
+        <v>5.152200222015381</v>
       </c>
       <c r="D210">
         <f>B210/C210</f>
@@ -10313,14 +10313,14 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>46.86999893188477</v>
+        <v>48.20000076293945</v>
       </c>
       <c r="C211" t="n">
-        <v>5.152200222015381</v>
+        <v>5.092700004577637</v>
       </c>
       <c r="D211">
         <f>B211/C211</f>
@@ -10334,14 +10334,14 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>48.20000076293945</v>
+        <v>47.56000137329102</v>
       </c>
       <c r="C212" t="n">
-        <v>5.092700004577637</v>
+        <v>5.10099983215332</v>
       </c>
       <c r="D212">
         <f>B212/C212</f>
@@ -10355,11 +10355,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>47.56000137329102</v>
+        <v>47.11000061035156</v>
       </c>
       <c r="C213" t="n">
         <v>5.10099983215332</v>
@@ -10376,14 +10376,14 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>47.11000061035156</v>
+        <v>48.09000015258789</v>
       </c>
       <c r="C214" t="n">
-        <v>5.10099983215332</v>
+        <v>5.084799766540527</v>
       </c>
       <c r="D214">
         <f>B214/C214</f>
@@ -10397,14 +10397,14 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>48.09000015258789</v>
+        <v>48.41999816894531</v>
       </c>
       <c r="C215" t="n">
-        <v>5.084799766540527</v>
+        <v>5.103400230407715</v>
       </c>
       <c r="D215">
         <f>B215/C215</f>
@@ -10418,14 +10418,14 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>48.41999816894531</v>
+        <v>49.11999893188477</v>
       </c>
       <c r="C216" t="n">
-        <v>5.103400230407715</v>
+        <v>5.102799892425537</v>
       </c>
       <c r="D216">
         <f>B216/C216</f>
@@ -10439,11 +10439,11 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>49.11999893188477</v>
+        <v>49</v>
       </c>
       <c r="C217" t="n">
         <v>5.102799892425537</v>
@@ -10460,14 +10460,14 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>49</v>
+        <v>48.91999816894531</v>
       </c>
       <c r="C218" t="n">
-        <v>5.102799892425537</v>
+        <v>5.138000011444092</v>
       </c>
       <c r="D218">
         <f>B218/C218</f>
@@ -10481,14 +10481,14 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>48.91999816894531</v>
+        <v>50.43000030517578</v>
       </c>
       <c r="C219" t="n">
-        <v>5.138000011444092</v>
+        <v>5.142899990081787</v>
       </c>
       <c r="D219">
         <f>B219/C219</f>
@@ -10502,14 +10502,14 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>50.43000030517578</v>
+        <v>48.65000152587891</v>
       </c>
       <c r="C220" t="n">
-        <v>5.142899990081787</v>
+        <v>5.150899887084961</v>
       </c>
       <c r="D220">
         <f>B220/C220</f>
@@ -10523,14 +10523,14 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>48.65000152587891</v>
+        <v>48.61000061035156</v>
       </c>
       <c r="C221" t="n">
-        <v>5.150899887084961</v>
+        <v>5.124100208282471</v>
       </c>
       <c r="D221">
         <f>B221/C221</f>
@@ -10544,11 +10544,11 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>48.61000061035156</v>
+        <v>48.5</v>
       </c>
       <c r="C222" t="n">
         <v>5.124100208282471</v>
@@ -10565,14 +10565,14 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="C223" t="n">
-        <v>5.124100208282471</v>
+        <v>5.110400199890137</v>
       </c>
       <c r="D223">
         <f>B223/C223</f>
@@ -10586,14 +10586,14 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>48</v>
+        <v>48.34999847412109</v>
       </c>
       <c r="C224" t="n">
-        <v>5.110400199890137</v>
+        <v>5.099899768829346</v>
       </c>
       <c r="D224">
         <f>B224/C224</f>
@@ -10607,14 +10607,14 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>48.34999847412109</v>
+        <v>49.59999847412109</v>
       </c>
       <c r="C225" t="n">
-        <v>5.099899768829346</v>
+        <v>5.164299964904785</v>
       </c>
       <c r="D225">
         <f>B225/C225</f>
@@ -10628,14 +10628,14 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>49.59999847412109</v>
+        <v>49.2599983215332</v>
       </c>
       <c r="C226" t="n">
-        <v>5.164299964904785</v>
+        <v>5.190499782562256</v>
       </c>
       <c r="D226">
         <f>B226/C226</f>
@@ -10649,11 +10649,11 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>49.2599983215332</v>
+        <v>48.06999969482422</v>
       </c>
       <c r="C227" t="n">
         <v>5.190499782562256</v>
@@ -10670,14 +10670,14 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>48.06999969482422</v>
+        <v>48.72000122070312</v>
       </c>
       <c r="C228" t="n">
-        <v>5.190499782562256</v>
+        <v>5.222899913787842</v>
       </c>
       <c r="D228">
         <f>B228/C228</f>
@@ -10691,14 +10691,14 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>48.72000122070312</v>
+        <v>49.09999847412109</v>
       </c>
       <c r="C229" t="n">
-        <v>5.222899913787842</v>
+        <v>5.202899932861328</v>
       </c>
       <c r="D229">
         <f>B229/C229</f>
@@ -10712,14 +10712,14 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>49.09999847412109</v>
+        <v>49.11999893188477</v>
       </c>
       <c r="C230" t="n">
-        <v>5.202899932861328</v>
+        <v>5.179100036621094</v>
       </c>
       <c r="D230">
         <f>B230/C230</f>
@@ -10733,14 +10733,14 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>49.11999893188477</v>
+        <v>49.90000152587891</v>
       </c>
       <c r="C231" t="n">
-        <v>5.179100036621094</v>
+        <v>5.222599983215332</v>
       </c>
       <c r="D231">
         <f>B231/C231</f>
@@ -10754,11 +10754,11 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>49.90000152587891</v>
+        <v>51.16999816894531</v>
       </c>
       <c r="C232" t="n">
         <v>5.222599983215332</v>
@@ -10775,14 +10775,14 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>51.16999816894531</v>
+        <v>55.36000061035156</v>
       </c>
       <c r="C233" t="n">
-        <v>5.222599983215332</v>
+        <v>4.996699810028076</v>
       </c>
       <c r="D233">
         <f>B233/C233</f>
@@ -10796,14 +10796,14 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>55.36000061035156</v>
+        <v>53.81999969482422</v>
       </c>
       <c r="C234" t="n">
-        <v>4.996699810028076</v>
+        <v>4.981400012969971</v>
       </c>
       <c r="D234">
         <f>B234/C234</f>
@@ -10817,14 +10817,14 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>53.81999969482422</v>
+        <v>54.33000183105469</v>
       </c>
       <c r="C235" t="n">
-        <v>4.981400012969971</v>
+        <v>5.019199848175049</v>
       </c>
       <c r="D235">
         <f>B235/C235</f>
@@ -10838,14 +10838,14 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>54.33000183105469</v>
+        <v>55.47999954223633</v>
       </c>
       <c r="C236" t="n">
-        <v>5.019199848175049</v>
+        <v>5.0177001953125</v>
       </c>
       <c r="D236">
         <f>B236/C236</f>
@@ -10859,11 +10859,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>55.47999954223633</v>
+        <v>56</v>
       </c>
       <c r="C237" t="n">
         <v>5.0177001953125</v>
@@ -10880,14 +10880,14 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>56</v>
+        <v>56.84999847412109</v>
       </c>
       <c r="C238" t="n">
-        <v>5.0177001953125</v>
+        <v>5.025800228118896</v>
       </c>
       <c r="D238">
         <f>B238/C238</f>
@@ -10901,14 +10901,14 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>56.84999847412109</v>
+        <v>58.11000061035156</v>
       </c>
       <c r="C239" t="n">
-        <v>5.025800228118896</v>
+        <v>5.03950023651123</v>
       </c>
       <c r="D239">
         <f>B239/C239</f>
@@ -10922,14 +10922,14 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>58.11000061035156</v>
+        <v>57.36000061035156</v>
       </c>
       <c r="C240" t="n">
-        <v>5.03950023651123</v>
+        <v>5.09660005569458</v>
       </c>
       <c r="D240">
         <f>B240/C240</f>
@@ -10943,11 +10943,11 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>57.36000061035156</v>
+        <v>59.68000030517578</v>
       </c>
       <c r="C241" t="n">
         <v>5.09660005569458</v>
@@ -10964,14 +10964,14 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>59.68000030517578</v>
+        <v>58</v>
       </c>
       <c r="C242" t="n">
-        <v>5.09660005569458</v>
+        <v>5.037000179290771</v>
       </c>
       <c r="D242">
         <f>B242/C242</f>
@@ -10985,14 +10985,14 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>58</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="C243" t="n">
-        <v>5.037000179290771</v>
+        <v>5.02269983291626</v>
       </c>
       <c r="D243">
         <f>B243/C243</f>
@@ -11006,14 +11006,14 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>58.20999908447266</v>
+        <v>57.75</v>
       </c>
       <c r="C244" t="n">
-        <v>5.02269983291626</v>
+        <v>5.02039098739624</v>
       </c>
       <c r="D244">
         <f>B244/C244</f>
@@ -11027,14 +11027,14 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>57.75</v>
+        <v>57.83000183105469</v>
       </c>
       <c r="C245" t="n">
-        <v>5.02039098739624</v>
+        <v>5.049900054931641</v>
       </c>
       <c r="D245">
         <f>B245/C245</f>
@@ -11048,11 +11048,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>57.83000183105469</v>
+        <v>58.68000030517578</v>
       </c>
       <c r="C246" t="n">
         <v>5.049900054931641</v>
@@ -11069,14 +11069,14 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>58.68000030517578</v>
+        <v>53.88000106811523</v>
       </c>
       <c r="C247" t="n">
-        <v>5.049900054931641</v>
+        <v>4.96019983291626</v>
       </c>
       <c r="D247">
         <f>B247/C247</f>
@@ -11090,14 +11090,14 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>53.88000106811523</v>
+        <v>52.79000091552734</v>
       </c>
       <c r="C248" t="n">
-        <v>4.96019983291626</v>
+        <v>5.372600078582764</v>
       </c>
       <c r="D248">
         <f>B248/C248</f>
@@ -11111,14 +11111,14 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>52.79000091552734</v>
+        <v>52.5099983215332</v>
       </c>
       <c r="C249" t="n">
-        <v>5.372600078582764</v>
+        <v>5.350299835205078</v>
       </c>
       <c r="D249">
         <f>B249/C249</f>
@@ -11126,27 +11126,6 @@
       </c>
       <c r="E249">
         <f>LN(D249/D248)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B250" t="n">
-        <v>52.5099983215332</v>
-      </c>
-      <c r="C250" t="n">
-        <v>5.350299835205078</v>
-      </c>
-      <c r="D250">
-        <f>B250/C250</f>
-        <v/>
-      </c>
-      <c r="E250">
-        <f>LN(D250/D249)</f>
         <v/>
       </c>
     </row>
@@ -11477,7 +11456,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-29 01:48 UTC</t>
+          <t>Snapshot as of 2026-10-29 18:25 UTC</t>
         </is>
       </c>
     </row>

--- a/research/verification.xlsx
+++ b/research/verification.xlsx
@@ -471,11 +471,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>264.3299865722656</v>
+        <v>254.8399963378906</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -490,18 +490,18 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D252/D46-1)*100</f>
+        <f>(D252/D45-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>254.8399963378906</v>
+        <v>256.1199951171875</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -527,11 +527,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>256.1199951171875</v>
+        <v>259.6499938964844</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -557,11 +557,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>259.6499938964844</v>
+        <v>250.0500030517578</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -587,11 +587,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>250.0500030517578</v>
+        <v>256.3299865722656</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -608,11 +608,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>256.3299865722656</v>
+        <v>237.6999969482422</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -631,17 +631,17 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>158.8445876403992</v>
+        <v>153.465789591444</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>237.6999969482422</v>
+        <v>233.5399932861328</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -660,17 +660,17 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>118.8325199561155</v>
+        <v>122.2649505572123</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233.5399932861328</v>
+        <v>243.9799957275391</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -689,17 +689,17 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>67.73061674943405</v>
+        <v>67.65662520929743</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>243.9799957275391</v>
+        <v>237.5200042724609</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -716,11 +716,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>237.5200042724609</v>
+        <v>258.8900146484375</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -735,18 +735,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-29 18:25 UTC</t>
+          <t>Snapshot as of 2026-10-30 01:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>258.8900146484375</v>
+        <v>247.9600067138672</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -763,11 +763,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>247.9600067138672</v>
+        <v>246.8099975585938</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -784,11 +784,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>246.8099975585938</v>
+        <v>240.5200042724609</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -805,11 +805,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>240.5200042724609</v>
+        <v>230.2899932861328</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -826,11 +826,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>230.2899932861328</v>
+        <v>223.5500030517578</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -847,11 +847,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>223.5500030517578</v>
+        <v>206.0200042724609</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -868,11 +868,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>206.0200042724609</v>
+        <v>203.7799987792969</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -889,11 +889,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>203.7799987792969</v>
+        <v>215.0500030517578</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -910,11 +910,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>215.0500030517578</v>
+        <v>206.1300048828125</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -931,11 +931,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>206.1300048828125</v>
+        <v>214.2400054931641</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -952,11 +952,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>214.2400054931641</v>
+        <v>217.5299987792969</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -973,11 +973,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>217.5299987792969</v>
+        <v>219.7599945068359</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -994,11 +994,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>219.7599945068359</v>
+        <v>215.2400054931641</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1015,11 +1015,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>215.2400054931641</v>
+        <v>217.6000061035156</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1036,11 +1036,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>217.6000061035156</v>
+        <v>215.9799957275391</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1057,11 +1057,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>215.9799957275391</v>
+        <v>217.9700012207031</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -1078,11 +1078,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>217.9700012207031</v>
+        <v>221.1100006103516</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -1099,11 +1099,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>221.1100006103516</v>
+        <v>221.6199951171875</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -1120,11 +1120,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>221.6199951171875</v>
+        <v>221.4199981689453</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1141,11 +1141,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>221.4199981689453</v>
+        <v>221.4299926757812</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -1162,11 +1162,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>221.4299926757812</v>
+        <v>210.7799987792969</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -1183,11 +1183,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>210.7799987792969</v>
+        <v>207.5800018310547</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -1204,11 +1204,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>207.5800018310547</v>
+        <v>209.1699981689453</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -1225,11 +1225,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>209.1699981689453</v>
+        <v>198.1100006103516</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -1246,11 +1246,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>198.1100006103516</v>
+        <v>201.0599975585938</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -1267,11 +1267,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>201.0599975585938</v>
+        <v>213.4299926757812</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -1288,11 +1288,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>213.4299926757812</v>
+        <v>214.9499969482422</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -1309,11 +1309,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>214.9499969482422</v>
+        <v>214.8999938964844</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -1330,11 +1330,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>214.8999938964844</v>
+        <v>215.0399932861328</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -1351,11 +1351,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>215.0399932861328</v>
+        <v>214.9900054931641</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -1372,11 +1372,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>214.9900054931641</v>
+        <v>215.6100006103516</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -1393,11 +1393,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>215.6100006103516</v>
+        <v>215.3399963378906</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -1414,11 +1414,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>215.3399963378906</v>
+        <v>214.1600036621094</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -1435,11 +1435,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>214.1600036621094</v>
+        <v>223.4700012207031</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -1456,11 +1456,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>223.4700012207031</v>
+        <v>221.0800018310547</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -1477,11 +1477,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>221.0800018310547</v>
+        <v>214.3500061035156</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -1498,11 +1498,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>214.3500061035156</v>
+        <v>210.0200042724609</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -1519,11 +1519,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>210.0200042724609</v>
+        <v>204.6799926757812</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -1540,11 +1540,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>204.6799926757812</v>
+        <v>203.1699981689453</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -1561,11 +1561,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>203.1699981689453</v>
+        <v>207.6900024414062</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -1582,11 +1582,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>207.6900024414062</v>
+        <v>220.9700012207031</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -1603,11 +1603,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>220.9700012207031</v>
+        <v>223.6000061035156</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -1624,11 +1624,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>223.6000061035156</v>
+        <v>227.9199981689453</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -1645,11 +1645,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>227.9199981689453</v>
+        <v>231.8300018310547</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -1666,11 +1666,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>231.8300018310547</v>
+        <v>231.9199981689453</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -1687,11 +1687,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>231.9199981689453</v>
+        <v>249.8000030517578</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -1708,11 +1708,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>249.8000030517578</v>
+        <v>253.7299957275391</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -1729,11 +1729,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>253.7299957275391</v>
+        <v>259.6799926757812</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -1750,11 +1750,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>259.6799926757812</v>
+        <v>251.3099975585938</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -1771,11 +1771,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>251.3099975585938</v>
+        <v>252.0299987792969</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -1792,11 +1792,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>252.0299987792969</v>
+        <v>252.7400054931641</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -1813,11 +1813,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>252.7400054931641</v>
+        <v>252.1799926757812</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -1834,11 +1834,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>252.1799926757812</v>
+        <v>236.7299957275391</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -1855,11 +1855,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>236.7299957275391</v>
+        <v>246.2700042724609</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -1876,11 +1876,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>246.2700042724609</v>
+        <v>242.1100006103516</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -1897,11 +1897,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>242.1100006103516</v>
+        <v>200.1900024414062</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -1918,11 +1918,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>200.1900024414062</v>
+        <v>192.5</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -1939,11 +1939,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>192.5</v>
+        <v>208.4400024414062</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -1960,11 +1960,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>208.4400024414062</v>
+        <v>216</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -1981,11 +1981,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>216</v>
+        <v>213.5700073242188</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -2002,11 +2002,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>213.5700073242188</v>
+        <v>213.5800018310547</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
@@ -2023,11 +2023,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>213.5800018310547</v>
+        <v>205.9400024414062</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
@@ -2044,11 +2044,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>205.9400024414062</v>
+        <v>207.3200073242188</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
@@ -2065,11 +2065,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>207.3200073242188</v>
+        <v>203.0800018310547</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -2086,11 +2086,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>203.0800018310547</v>
+        <v>200.1199951171875</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
@@ -2107,11 +2107,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>200.1199951171875</v>
+        <v>203.3699951171875</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -2128,11 +2128,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>203.3699951171875</v>
+        <v>200.1499938964844</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -2149,11 +2149,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>200.1499938964844</v>
+        <v>196.6000061035156</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -2170,11 +2170,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>196.6000061035156</v>
+        <v>213.8399963378906</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -2191,11 +2191,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>213.8399963378906</v>
+        <v>210.8600006103516</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -2212,11 +2212,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>210.8600006103516</v>
+        <v>203.6799926757812</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -2233,11 +2233,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>203.6799926757812</v>
+        <v>200.2100067138672</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -2254,11 +2254,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>200.2100067138672</v>
+        <v>198.6199951171875</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
@@ -2275,11 +2275,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>198.6199951171875</v>
+        <v>190.9499969482422</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -2296,11 +2296,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>190.9499969482422</v>
+        <v>202.0700073242188</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -2317,11 +2317,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>202.0700073242188</v>
+        <v>199.4499969482422</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
@@ -2338,11 +2338,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>199.4499969482422</v>
+        <v>192.4299926757812</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -2359,11 +2359,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>192.4299926757812</v>
+        <v>202.6799926757812</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
@@ -2380,11 +2380,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>202.6799926757812</v>
+        <v>203.2299957275391</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -2401,11 +2401,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>203.2299957275391</v>
+        <v>204.8300018310547</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -2422,11 +2422,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>204.8300018310547</v>
+        <v>197.7400054931641</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -2443,11 +2443,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>197.7400054931641</v>
+        <v>193.3899993896484</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -2464,11 +2464,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>193.3899993896484</v>
+        <v>196.5800018310547</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -2485,11 +2485,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>196.5800018310547</v>
+        <v>196.3099975585938</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
@@ -2506,11 +2506,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>196.3099975585938</v>
+        <v>199.4600067138672</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -2527,11 +2527,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>199.4600067138672</v>
+        <v>205.2700042724609</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -2548,11 +2548,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>205.2700042724609</v>
+        <v>201.3300018310547</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
@@ -2569,11 +2569,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>201.3300018310547</v>
+        <v>202.6799926757812</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
@@ -2590,11 +2590,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>202.6799926757812</v>
+        <v>205.3699951171875</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -2611,11 +2611,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>205.3699951171875</v>
+        <v>220.2700042724609</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -2632,11 +2632,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>220.2700042724609</v>
+        <v>203.7700042724609</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
@@ -2653,11 +2653,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>203.7700042724609</v>
+        <v>201.9900054931641</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -2674,11 +2674,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>201.9900054931641</v>
+        <v>196.0399932861328</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
@@ -2695,11 +2695,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>196.0399932861328</v>
+        <v>203.4299926757812</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
@@ -2716,11 +2716,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>203.4299926757812</v>
+        <v>210.2100067138672</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
@@ -2737,11 +2737,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>210.2100067138672</v>
+        <v>217.5</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -2758,11 +2758,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>217.5</v>
+        <v>220.1799926757812</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
@@ -2779,11 +2779,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>220.1799926757812</v>
+        <v>221.5299987792969</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
@@ -2800,11 +2800,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>221.5299987792969</v>
+        <v>231.8200073242188</v>
       </c>
       <c r="C110" t="n">
         <v>1</v>
@@ -2821,11 +2821,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>231.8200073242188</v>
+        <v>236.6399993896484</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
@@ -2842,11 +2842,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>236.6399993896484</v>
+        <v>245.0399932861328</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
@@ -2863,11 +2863,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>245.0399932861328</v>
+        <v>246.8300018310547</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
@@ -2884,11 +2884,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>246.8300018310547</v>
+        <v>255.0700073242188</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -2905,11 +2905,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>255.0700073242188</v>
+        <v>258.1199951171875</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -2926,11 +2926,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>258.1199951171875</v>
+        <v>278.260009765625</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
@@ -2947,11 +2947,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>278.260009765625</v>
+        <v>278.3900146484375</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
@@ -2968,11 +2968,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>278.3900146484375</v>
+        <v>274.9500122070312</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
@@ -2989,11 +2989,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>274.9500122070312</v>
+        <v>284.489990234375</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -3010,11 +3010,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>284.489990234375</v>
+        <v>303.4599914550781</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -3031,11 +3031,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>303.4599914550781</v>
+        <v>305.3299865722656</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
@@ -3052,11 +3052,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>305.3299865722656</v>
+        <v>347.8099975585938</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
@@ -3073,11 +3073,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>347.8099975585938</v>
+        <v>334.6300048828125</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -3094,11 +3094,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>334.6300048828125</v>
+        <v>323.2099914550781</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -3115,11 +3115,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>323.2099914550781</v>
+        <v>337.1099853515625</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -3136,11 +3136,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>337.1099853515625</v>
+        <v>354.489990234375</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -3157,11 +3157,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>354.489990234375</v>
+        <v>360.5400085449219</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -3178,11 +3178,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>360.5400085449219</v>
+        <v>341.5400085449219</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
@@ -3199,11 +3199,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>341.5400085449219</v>
+        <v>355.260009765625</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -3220,11 +3220,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>355.260009765625</v>
+        <v>421.3900146484375</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -3241,11 +3241,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>421.3900146484375</v>
+        <v>408.4599914550781</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -3262,11 +3262,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>408.4599914550781</v>
+        <v>455.1900024414062</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
@@ -3283,11 +3283,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>455.1900024414062</v>
+        <v>458.7900085449219</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -3304,11 +3304,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>458.7900085449219</v>
+        <v>448.2900085449219</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
@@ -3325,11 +3325,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>448.2900085449219</v>
+        <v>445.5</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
@@ -3346,11 +3346,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>445.5</v>
+        <v>449.7000122070312</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -3367,11 +3367,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>449.7000122070312</v>
+        <v>424.1000061035156</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
@@ -3388,11 +3388,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>424.1000061035156</v>
+        <v>420.989990234375</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
@@ -3409,11 +3409,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>420.989990234375</v>
+        <v>414.0499877929688</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
@@ -3430,11 +3430,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>414.0499877929688</v>
+        <v>447.5799865722656</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -3451,11 +3451,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>447.5799865722656</v>
+        <v>449.5899963378906</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
@@ -3472,11 +3472,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>449.5899963378906</v>
+        <v>467.510009765625</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
@@ -3493,11 +3493,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>467.510009765625</v>
+        <v>503.8900146484375</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -3514,11 +3514,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>503.8900146484375</v>
+        <v>495.5400085449219</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
@@ -3535,11 +3535,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>495.5400085449219</v>
+        <v>518.0900268554688</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
@@ -3556,11 +3556,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>518.0900268554688</v>
+        <v>516.0999755859375</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
@@ -3577,11 +3577,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>516.0999755859375</v>
+        <v>510.1300048828125</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
@@ -3598,11 +3598,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>510.1300048828125</v>
+        <v>521.5399780273438</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
@@ -3619,11 +3619,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>521.5399780273438</v>
+        <v>542.52001953125</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
@@ -3640,11 +3640,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>542.52001953125</v>
+        <v>523.2000122070312</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -3661,11 +3661,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>523.2000122070312</v>
+        <v>466.3800048828125</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -3682,11 +3682,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>466.3800048828125</v>
+        <v>490.3299865722656</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -3703,11 +3703,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>490.3299865722656</v>
+        <v>475.510009765625</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
@@ -3724,11 +3724,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>475.510009765625</v>
+        <v>452.3999938964844</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
@@ -3745,11 +3745,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>452.3999938964844</v>
+        <v>488.4500122070312</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
@@ -3766,11 +3766,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>488.4500122070312</v>
+        <v>511.5700073242188</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
@@ -3787,11 +3787,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>511.5700073242188</v>
+        <v>547.260009765625</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -3808,11 +3808,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>547.260009765625</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -3829,11 +3829,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>507.2900085449219</v>
+        <v>512.47998046875</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
@@ -3850,11 +3850,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>512.47998046875</v>
+        <v>537.3699951171875</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
@@ -3871,11 +3871,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>537.3699951171875</v>
+        <v>551.6300048828125</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -3892,11 +3892,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>551.6300048828125</v>
+        <v>519.8499755859375</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -3913,11 +3913,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>519.8499755859375</v>
+        <v>519.739990234375</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -3934,11 +3934,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>519.739990234375</v>
+        <v>532.5700073242188</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
@@ -3955,11 +3955,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>532.5700073242188</v>
+        <v>521.5800170898438</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -3976,11 +3976,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>521.5800170898438</v>
+        <v>539.489990234375</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
@@ -3997,11 +3997,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>539.489990234375</v>
+        <v>580.9099731445312</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
@@ -4018,11 +4018,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>580.9099731445312</v>
+        <v>540.8800048828125</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
@@ -4039,11 +4039,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>540.8800048828125</v>
+        <v>517.8200073242188</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
@@ -4060,11 +4060,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>517.8200073242188</v>
+        <v>552.0499877929688</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
@@ -4081,11 +4081,11 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>552.0499877929688</v>
+        <v>516.1099853515625</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -4102,11 +4102,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>516.1099853515625</v>
+        <v>517.4099731445312</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
@@ -4123,11 +4123,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>517.4099731445312</v>
+        <v>546.719970703125</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
@@ -4144,11 +4144,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>546.719970703125</v>
+        <v>557.8900146484375</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
@@ -4165,11 +4165,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>557.8900146484375</v>
+        <v>534.3900146484375</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
@@ -4186,11 +4186,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>534.3900146484375</v>
+        <v>548.1300048828125</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
@@ -4207,11 +4207,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>548.1300048828125</v>
+        <v>529.1400146484375</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
@@ -4228,11 +4228,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>529.1400146484375</v>
+        <v>500.9400024414062</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
@@ -4249,11 +4249,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>500.9400024414062</v>
+        <v>495.760009765625</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
@@ -4270,11 +4270,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>495.760009765625</v>
+        <v>503.5700073242188</v>
       </c>
       <c r="C180" t="n">
         <v>1</v>
@@ -4291,11 +4291,11 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>503.5700073242188</v>
+        <v>544.4299926757812</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
@@ -4312,11 +4312,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>544.4299926757812</v>
+        <v>552.3300170898438</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -4333,11 +4333,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>552.3300170898438</v>
+        <v>539.6900024414062</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
@@ -4354,11 +4354,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>539.6900024414062</v>
+        <v>521.9500122070312</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
@@ -4375,11 +4375,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>521.9500122070312</v>
+        <v>494.9500122070312</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -4396,11 +4396,11 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>494.9500122070312</v>
+        <v>454.6199951171875</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
@@ -4417,11 +4417,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>454.6199951171875</v>
+        <v>429.5599975585938</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
@@ -4438,11 +4438,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>429.5599975585938</v>
+        <v>485.3900146484375</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -4459,11 +4459,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>485.3900146484375</v>
+        <v>476.1499938964844</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
@@ -4480,11 +4480,11 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>476.1499938964844</v>
+        <v>484.6400146484375</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -4501,11 +4501,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>484.6400146484375</v>
+        <v>518.5800170898438</v>
       </c>
       <c r="C191" t="n">
         <v>1</v>
@@ -4522,11 +4522,11 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>518.5800170898438</v>
+        <v>482.0499877929688</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
@@ -4543,11 +4543,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>482.0499877929688</v>
+        <v>489.2799987792969</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
@@ -4564,11 +4564,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>489.2799987792969</v>
+        <v>483.3599853515625</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -4585,11 +4585,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>483.3599853515625</v>
+        <v>469.5599975585938</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
@@ -4606,11 +4606,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>469.5599975585938</v>
+        <v>474.3200073242188</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
@@ -4627,11 +4627,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>474.3200073242188</v>
+        <v>482.9299926757812</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -4648,11 +4648,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>482.9299926757812</v>
+        <v>483.010009765625</v>
       </c>
       <c r="C198" t="n">
         <v>1</v>
@@ -4669,11 +4669,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>483.010009765625</v>
+        <v>514.3900146484375</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
@@ -4690,11 +4690,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>514.3900146484375</v>
+        <v>506</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
@@ -4711,11 +4711,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>506</v>
+        <v>484.3900146484375</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
@@ -4732,11 +4732,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>484.3900146484375</v>
+        <v>466.4200134277344</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
@@ -4753,11 +4753,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>466.4200134277344</v>
+        <v>469.4599914550781</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
@@ -4774,11 +4774,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>469.4599914550781</v>
+        <v>473.25</v>
       </c>
       <c r="C204" t="n">
         <v>1</v>
@@ -4795,11 +4795,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>473.25</v>
+        <v>456.75</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
@@ -4816,11 +4816,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>456.75</v>
+        <v>479.1799926757812</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
@@ -4837,11 +4837,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>479.1799926757812</v>
+        <v>480.9299926757812</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
@@ -4858,11 +4858,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>480.9299926757812</v>
+        <v>476.6700134277344</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
@@ -4879,11 +4879,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>476.6700134277344</v>
+        <v>465.5799865722656</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
@@ -4900,11 +4900,11 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>465.5799865722656</v>
+        <v>470.7200012207031</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
@@ -4921,11 +4921,11 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>470.7200012207031</v>
+        <v>459.6099853515625</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
@@ -4942,11 +4942,11 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>459.6099853515625</v>
+        <v>457.0599975585938</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
@@ -4963,11 +4963,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>457.0599975585938</v>
+        <v>456.1600036621094</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
@@ -4984,11 +4984,11 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>456.1600036621094</v>
+        <v>477.5700073242188</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
@@ -5005,11 +5005,11 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>477.5700073242188</v>
+        <v>505.739990234375</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
@@ -5026,11 +5026,11 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>505.739990234375</v>
+        <v>521.0999755859375</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
@@ -5047,11 +5047,11 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>521.0999755859375</v>
+        <v>503.6000061035156</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
@@ -5068,11 +5068,11 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>503.6000061035156</v>
+        <v>516.1300048828125</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
@@ -5089,11 +5089,11 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>516.1300048828125</v>
+        <v>493.4100036621094</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
@@ -5110,11 +5110,11 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>493.4100036621094</v>
+        <v>504.2000122070312</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
@@ -5131,11 +5131,11 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>504.2000122070312</v>
+        <v>512.5</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
@@ -5152,11 +5152,11 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>512.5</v>
+        <v>545.0900268554688</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
@@ -5173,11 +5173,11 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>545.0900268554688</v>
+        <v>559.8200073242188</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
@@ -5194,11 +5194,11 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>559.8200073242188</v>
+        <v>615.52001953125</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
@@ -5215,11 +5215,11 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>615.52001953125</v>
+        <v>623.77001953125</v>
       </c>
       <c r="C225" t="n">
         <v>1</v>
@@ -5236,11 +5236,11 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>623.77001953125</v>
+        <v>614.6099853515625</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
@@ -5257,11 +5257,11 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>614.6099853515625</v>
+        <v>629.260009765625</v>
       </c>
       <c r="C227" t="n">
         <v>1</v>
@@ -5278,11 +5278,11 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>629.260009765625</v>
+        <v>630.6300048828125</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
@@ -5299,11 +5299,11 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>630.6300048828125</v>
+        <v>607.8699951171875</v>
       </c>
       <c r="C229" t="n">
         <v>1</v>
@@ -5320,11 +5320,11 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>607.8699951171875</v>
+        <v>607.5700073242188</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
@@ -5341,11 +5341,11 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>607.5700073242188</v>
+        <v>611.760009765625</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
@@ -5362,11 +5362,11 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>611.760009765625</v>
+        <v>615.72998046875</v>
       </c>
       <c r="C232" t="n">
         <v>1</v>
@@ -5383,11 +5383,11 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>615.72998046875</v>
+        <v>633.9099731445312</v>
       </c>
       <c r="C233" t="n">
         <v>1</v>
@@ -5404,11 +5404,11 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>633.9099731445312</v>
+        <v>631.75</v>
       </c>
       <c r="C234" t="n">
         <v>1</v>
@@ -5425,11 +5425,11 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>631.75</v>
+        <v>649.4199829101562</v>
       </c>
       <c r="C235" t="n">
         <v>1</v>
@@ -5446,11 +5446,11 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>649.4199829101562</v>
+        <v>645.8599853515625</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
@@ -5467,11 +5467,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>645.8599853515625</v>
+        <v>620.6799926757812</v>
       </c>
       <c r="C237" t="n">
         <v>1</v>
@@ -5488,11 +5488,11 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>620.6799926757812</v>
+        <v>608.0999755859375</v>
       </c>
       <c r="C238" t="n">
         <v>1</v>
@@ -5509,11 +5509,11 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>608.0999755859375</v>
+        <v>594.239990234375</v>
       </c>
       <c r="C239" t="n">
         <v>1</v>
@@ -5530,11 +5530,11 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>594.239990234375</v>
+        <v>605.530029296875</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
@@ -5551,11 +5551,11 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>605.530029296875</v>
+        <v>570.8200073242188</v>
       </c>
       <c r="C241" t="n">
         <v>1</v>
@@ -5572,11 +5572,11 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>570.8200073242188</v>
+        <v>562.22998046875</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
@@ -5593,11 +5593,11 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>562.22998046875</v>
+        <v>528.75</v>
       </c>
       <c r="C243" t="n">
         <v>1</v>
@@ -5614,11 +5614,11 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>528.75</v>
+        <v>538.0499877929688</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
@@ -5635,11 +5635,11 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>538.0499877929688</v>
+        <v>534.739990234375</v>
       </c>
       <c r="C245" t="n">
         <v>1</v>
@@ -5656,11 +5656,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>534.739990234375</v>
+        <v>552.719970703125</v>
       </c>
       <c r="C246" t="n">
         <v>1</v>
@@ -5677,11 +5677,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>552.719970703125</v>
+        <v>507.9299926757812</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
@@ -5698,11 +5698,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>507.9299926757812</v>
+        <v>516.7899780273438</v>
       </c>
       <c r="C248" t="n">
         <v>1</v>
@@ -5719,11 +5719,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>516.7899780273438</v>
+        <v>531.280029296875</v>
       </c>
       <c r="C249" t="n">
         <v>1</v>
@@ -5740,11 +5740,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>531.280029296875</v>
+        <v>560.260009765625</v>
       </c>
       <c r="C250" t="n">
         <v>1</v>
@@ -5761,11 +5761,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>560.260009765625</v>
+        <v>578.4400024414062</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>
@@ -5782,11 +5782,11 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>578.4400024414062</v>
+        <v>566.4199829101562</v>
       </c>
       <c r="C252" t="n">
         <v>1</v>
@@ -5811,7 +5811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5867,10 +5867,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.36254692077637</v>
+        <v>27.36254501342773</v>
       </c>
       <c r="C2" t="n">
-        <v>5.357399940490723</v>
+        <v>5.357800006866455</v>
       </c>
       <c r="D2">
         <f>B2/C2</f>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D249/D44-1)*100</f>
+        <f>(D250/D44-1)*100</f>
         <v/>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>27.24405288696289</v>
+        <v>27.24405097961426</v>
       </c>
       <c r="C3" t="n">
         <v>5.357800006866455</v>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="H3">
-        <f>(D249/D2-1)*100</f>
+        <f>(D250/D2-1)*100</f>
         <v/>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
         </is>
       </c>
       <c r="H4">
-        <f>(COUNT(D2:D249)-1)/((DATEVALUE(A249)-DATEVALUE(A2))/365.25)</f>
+        <f>(COUNT(D2:D250)-1)/((DATEVALUE(A250)-DATEVALUE(A2))/365.25)</f>
         <v/>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
         </is>
       </c>
       <c r="H5">
-        <f>STDEV.S(E3:E249)*SQRT(H4)*100</f>
+        <f>STDEV.S(E3:E250)*SQRT(H4)*100</f>
         <v/>
       </c>
     </row>
@@ -5983,7 +5983,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.57218360900879</v>
+        <v>27.57218551635742</v>
       </c>
       <c r="C6" t="n">
         <v>5.354899883270264</v>
@@ -6004,7 +6004,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28.11907386779785</v>
+        <v>28.11907196044922</v>
       </c>
       <c r="C7" t="n">
         <v>5.395899772644043</v>
@@ -6023,7 +6023,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>87.51557884207661</v>
+        <v>86.56198040609982</v>
       </c>
     </row>
     <row r="8">
@@ -6033,7 +6033,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.26490783691406</v>
+        <v>28.2649097442627</v>
       </c>
       <c r="C8" t="n">
         <v>5.35860013961792</v>
@@ -6052,7 +6052,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>92.15964279874942</v>
+        <v>91.19670154311741</v>
       </c>
     </row>
     <row r="9">
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29.33133697509766</v>
+        <v>29.33133506774902</v>
       </c>
       <c r="C9" t="n">
         <v>5.349500179290771</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>34.43895459009657</v>
+        <v>34.40004387325227</v>
       </c>
     </row>
     <row r="10">
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29.49540328979492</v>
+        <v>29.49540519714355</v>
       </c>
       <c r="C10" t="n">
         <v>5.330900192260742</v>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-29 18:25 UTC</t>
+          <t>Snapshot as of 2026-10-30 01:58 UTC</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.80530738830566</v>
+        <v>29.8053035736084</v>
       </c>
       <c r="C14" t="n">
         <v>5.296500205993652</v>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.96936988830566</v>
+        <v>29.9693717956543</v>
       </c>
       <c r="C15" t="n">
         <v>5.295599937438965</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>30.06963539123535</v>
+        <v>30.06963348388672</v>
       </c>
       <c r="C16" t="n">
         <v>5.329500198364258</v>
@@ -6264,7 +6264,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29.68681335449219</v>
+        <v>29.68681144714355</v>
       </c>
       <c r="C18" t="n">
         <v>5.332300186157227</v>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29.65946769714355</v>
+        <v>29.65946960449219</v>
       </c>
       <c r="C19" t="n">
         <v>5.402100086212158</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29.37691116333008</v>
+        <v>29.37691307067871</v>
       </c>
       <c r="C21" t="n">
         <v>5.37939977645874</v>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.53186225891113</v>
+        <v>29.53186416625977</v>
       </c>
       <c r="C22" t="n">
         <v>5.33080005645752</v>
@@ -6411,7 +6411,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29.23107528686523</v>
+        <v>29.23107147216797</v>
       </c>
       <c r="C25" t="n">
         <v>5.355800151824951</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.44983100891113</v>
+        <v>29.4498291015625</v>
       </c>
       <c r="C26" t="n">
         <v>5.326300144195557</v>
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.59304046630859</v>
+        <v>28.59304237365723</v>
       </c>
       <c r="C28" t="n">
         <v>5.309299945831299</v>
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28.62950134277344</v>
+        <v>28.6294994354248</v>
       </c>
       <c r="C32" t="n">
         <v>5.469799995422363</v>
@@ -6600,7 +6600,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28.89382934570312</v>
+        <v>28.89382743835449</v>
       </c>
       <c r="C34" t="n">
         <v>5.418200016021729</v>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.32871055603027</v>
+        <v>28.32871437072754</v>
       </c>
       <c r="C36" t="n">
         <v>5.507500171661377</v>
@@ -6684,7 +6684,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28.26490783691406</v>
+        <v>28.2649097442627</v>
       </c>
       <c r="C38" t="n">
         <v>5.521299839019775</v>
@@ -6705,7 +6705,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.3469409942627</v>
+        <v>28.34694290161133</v>
       </c>
       <c r="C39" t="n">
         <v>5.53980016708374</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.97891807556152</v>
+        <v>28.97891998291016</v>
       </c>
       <c r="C43" t="n">
         <v>5.569099903106689</v>
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28.87548828125</v>
+        <v>28.87549018859863</v>
       </c>
       <c r="C44" t="n">
         <v>5.517000198364258</v>
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>27.86940574645996</v>
+        <v>27.86940765380859</v>
       </c>
       <c r="C46" t="n">
         <v>5.40749979019165</v>
@@ -6915,7 +6915,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28.48998260498047</v>
+        <v>28.48998069763184</v>
       </c>
       <c r="C49" t="n">
         <v>5.386600017547607</v>
@@ -6936,7 +6936,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28.54639625549316</v>
+        <v>28.5463981628418</v>
       </c>
       <c r="C50" t="n">
         <v>5.370299816131592</v>
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>30.12603950500488</v>
+        <v>30.12604141235352</v>
       </c>
       <c r="C54" t="n">
         <v>5.367899894714355</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>30.24827003479004</v>
+        <v>30.24827194213867</v>
       </c>
       <c r="C55" t="n">
         <v>5.367700099945068</v>
@@ -7083,7 +7083,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31.43300437927246</v>
+        <v>31.43300819396973</v>
       </c>
       <c r="C57" t="n">
         <v>5.374300003051758</v>
@@ -7209,7 +7209,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>35.44792938232422</v>
+        <v>35.44793319702148</v>
       </c>
       <c r="C63" t="n">
         <v>5.197100162506104</v>
@@ -7251,7 +7251,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>35.01540756225586</v>
+        <v>35.01541137695312</v>
       </c>
       <c r="C65" t="n">
         <v>5.255000114440918</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>35.2786865234375</v>
+        <v>35.27868270874023</v>
       </c>
       <c r="C67" t="n">
         <v>5.237500190734863</v>
@@ -7356,7 +7356,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>35.09062957763672</v>
+        <v>35.09063339233398</v>
       </c>
       <c r="C70" t="n">
         <v>5.21589994430542</v>
@@ -7377,7 +7377,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>35.11883544921875</v>
+        <v>35.11883926391602</v>
       </c>
       <c r="C71" t="n">
         <v>5.19159984588623</v>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>35.80522918701172</v>
+        <v>35.80523300170898</v>
       </c>
       <c r="C72" t="n">
         <v>5.196199893951416</v>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>34.68631362915039</v>
+        <v>34.68631744384766</v>
       </c>
       <c r="C74" t="n">
         <v>5.213900089263916</v>
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>35.55135726928711</v>
+        <v>35.55136108398438</v>
       </c>
       <c r="C76" t="n">
         <v>5.234399795532227</v>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>37.20622253417969</v>
+        <v>37.20622634887695</v>
       </c>
       <c r="C79" t="n">
         <v>5.170899868011475</v>
@@ -7566,7 +7566,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>37.20622253417969</v>
+        <v>37.20622634887695</v>
       </c>
       <c r="C80" t="n">
         <v>5.151999950408936</v>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>38.5037841796875</v>
+        <v>38.50378799438477</v>
       </c>
       <c r="C84" t="n">
         <v>5.170300006866455</v>
@@ -7692,7 +7692,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>38.25931549072266</v>
+        <v>38.25931930541992</v>
       </c>
       <c r="C86" t="n">
         <v>5.230100154876709</v>
@@ -7734,7 +7734,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>40.58176803588867</v>
+        <v>40.58177185058594</v>
       </c>
       <c r="C88" t="n">
         <v>5.243500232696533</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>42.31185150146484</v>
+        <v>42.31185913085938</v>
       </c>
       <c r="C91" t="n">
         <v>5.151400089263916</v>
@@ -7839,7 +7839,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>43.12047958374023</v>
+        <v>43.1204833984375</v>
       </c>
       <c r="C93" t="n">
         <v>5.329100131988525</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>43.60942077636719</v>
+        <v>43.60941696166992</v>
       </c>
       <c r="C94" t="n">
         <v>5.233399868011475</v>
@@ -7902,7 +7902,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>43.98551940917969</v>
+        <v>43.98552322387695</v>
       </c>
       <c r="C96" t="n">
         <v>5.262100219726562</v>
@@ -7923,7 +7923,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>42.94182968139648</v>
+        <v>42.94182586669922</v>
       </c>
       <c r="C97" t="n">
         <v>5.219900131225586</v>
@@ -7965,7 +7965,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>44.44625091552734</v>
+        <v>44.44625473022461</v>
       </c>
       <c r="C99" t="n">
         <v>5.232900142669678</v>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>45.15145111083984</v>
+        <v>45.15144729614258</v>
       </c>
       <c r="C101" t="n">
         <v>5.236800193786621</v>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>45.61217498779297</v>
+        <v>45.61217880249023</v>
       </c>
       <c r="C108" t="n">
         <v>5.150599956512451</v>
@@ -8175,7 +8175,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>43.82567596435547</v>
+        <v>43.82567977905273</v>
       </c>
       <c r="C109" t="n">
         <v>5.100200176239014</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>45.01980972290039</v>
+        <v>45.01981353759766</v>
       </c>
       <c r="C113" t="n">
         <v>4.984799861907959</v>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>44.08895111083984</v>
+        <v>44.08895492553711</v>
       </c>
       <c r="C114" t="n">
         <v>4.992400169372559</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>45.67800140380859</v>
+        <v>45.67799758911133</v>
       </c>
       <c r="C115" t="n">
         <v>4.987090110778809</v>
@@ -8343,7 +8343,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>44.21118545532227</v>
+        <v>44.21118927001953</v>
       </c>
       <c r="C117" t="n">
         <v>4.952400207519531</v>
@@ -8364,7 +8364,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>44.82235717773438</v>
+        <v>44.82235336303711</v>
       </c>
       <c r="C118" t="n">
         <v>4.984899997711182</v>
@@ -11126,6 +11126,27 @@
       </c>
       <c r="E249">
         <f>LN(D249/D248)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>52.20000076293945</v>
+      </c>
+      <c r="C250" t="n">
+        <v>5.345900058746338</v>
+      </c>
+      <c r="D250">
+        <f>B250/C250</f>
+        <v/>
+      </c>
+      <c r="E250">
+        <f>LN(D250/D249)</f>
         <v/>
       </c>
     </row>
@@ -11192,11 +11213,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>363</v>
+        <v>370.1300048828125</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -11211,18 +11232,18 @@
         </is>
       </c>
       <c r="H2">
-        <f>(D252/D46-1)*100</f>
+        <f>(D252/D45-1)*100</f>
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>370.1300048828125</v>
+        <v>368.1199951171875</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -11248,11 +11269,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>368.1199951171875</v>
+        <v>368.7799987792969</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
@@ -11278,11 +11299,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>368.7799987792969</v>
+        <v>362.3200073242188</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -11308,11 +11329,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>362.3200073242188</v>
+        <v>366.510009765625</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
@@ -11329,11 +11350,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>366.510009765625</v>
+        <v>366.0700073242188</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -11352,17 +11373,17 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-6.219242743798329</v>
+        <v>-7.459576177563519</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>366.0700073242188</v>
+        <v>368.3099975585938</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -11381,17 +11402,17 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.895316804407711</v>
+        <v>-0.4214735363250756</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>368.3099975585938</v>
+        <v>378.3800048828125</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -11410,17 +11431,17 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>28.59957492231657</v>
+        <v>28.56469590636622</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>378.3800048828125</v>
+        <v>379.8699951171875</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -11437,11 +11458,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>379.8699951171875</v>
+        <v>385.989990234375</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
@@ -11456,18 +11477,18 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Snapshot as of 2026-10-29 18:25 UTC</t>
+          <t>Snapshot as of 2026-10-30 01:58 UTC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>385.989990234375</v>
+        <v>382.8699951171875</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -11484,11 +11505,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>382.8699951171875</v>
+        <v>375.9599914550781</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -11505,11 +11526,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>375.9599914550781</v>
+        <v>371.6499938964844</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -11526,11 +11547,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>371.6499938964844</v>
+        <v>374.3500061035156</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -11547,11 +11568,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>374.3500061035156</v>
+        <v>374.9599914550781</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
@@ -11568,11 +11589,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>374.9599914550781</v>
+        <v>374.8500061035156</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -11589,11 +11610,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>374.8500061035156</v>
+        <v>374.2699890136719</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -11610,11 +11631,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>374.2699890136719</v>
+        <v>380.2000122070312</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
@@ -11631,11 +11652,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>380.2000122070312</v>
+        <v>380.0799865722656</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
@@ -11652,11 +11673,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>380.0799865722656</v>
+        <v>383.1199951171875</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
@@ -11673,11 +11694,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>383.1199951171875</v>
+        <v>387.8800048828125</v>
       </c>
       <c r="C22" t="n">
         <v>1</v>
@@ -11694,11 +11715,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>387.8800048828125</v>
+        <v>389.75</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -11715,11 +11736,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>389.75</v>
+        <v>387.239990234375</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -11736,11 +11757,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>387.239990234375</v>
+        <v>386.8800048828125</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -11757,11 +11778,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>386.8800048828125</v>
+        <v>387.1300048828125</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -11778,11 +11799,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>387.1300048828125</v>
+        <v>386.4400024414062</v>
       </c>
       <c r="C27" t="n">
         <v>1</v>
@@ -11799,11 +11820,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>386.4400024414062</v>
+        <v>385.4200134277344</v>
       </c>
       <c r="C28" t="n">
         <v>1</v>
@@ -11820,11 +11841,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>385.4200134277344</v>
+        <v>387.3999938964844</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
@@ -11841,11 +11862,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>387.3999938964844</v>
+        <v>389.0499877929688</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -11862,11 +11883,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>389.0499877929688</v>
+        <v>393.239990234375</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
@@ -11883,11 +11904,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>393.239990234375</v>
+        <v>395.4400024414062</v>
       </c>
       <c r="C32" t="n">
         <v>1</v>
@@ -11904,11 +11925,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>395.4400024414062</v>
+        <v>395.7999877929688</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -11925,11 +11946,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>395.7999877929688</v>
+        <v>395.8900146484375</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
@@ -11946,11 +11967,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>395.8900146484375</v>
+        <v>399.2900085449219</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
@@ -11967,11 +11988,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>399.2900085449219</v>
+        <v>398.5700073242188</v>
       </c>
       <c r="C36" t="n">
         <v>1</v>
@@ -11988,11 +12009,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>398.5700073242188</v>
+        <v>399.0199890136719</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -12009,11 +12030,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>399.0199890136719</v>
+        <v>408.2300109863281</v>
       </c>
       <c r="C38" t="n">
         <v>1</v>
@@ -12030,11 +12051,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>408.2300109863281</v>
+        <v>413.6400146484375</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
@@ -12051,11 +12072,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>413.6400146484375</v>
+        <v>411.9299926757812</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -12072,11 +12093,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>411.9299926757812</v>
+        <v>416.739990234375</v>
       </c>
       <c r="C41" t="n">
         <v>1</v>
@@ -12093,11 +12114,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>416.739990234375</v>
+        <v>398.6000061035156</v>
       </c>
       <c r="C42" t="n">
         <v>1</v>
@@ -12114,11 +12135,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>398.6000061035156</v>
+        <v>398.8900146484375</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -12135,11 +12156,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>398.8900146484375</v>
+        <v>396.3099975585938</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -12156,11 +12177,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>396.3099975585938</v>
+        <v>398.2799987792969</v>
       </c>
       <c r="C45" t="n">
         <v>1</v>
@@ -12177,11 +12198,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>398.2799987792969</v>
+        <v>408.760009765625</v>
       </c>
       <c r="C46" t="n">
         <v>1</v>
@@ -12198,11 +12219,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>408.760009765625</v>
+        <v>413.1799926757812</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -12219,11 +12240,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>413.1799926757812</v>
+        <v>409.2300109863281</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -12240,11 +12261,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>409.2300109863281</v>
+        <v>411.489990234375</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -12261,11 +12282,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>411.489990234375</v>
+        <v>414.4700012207031</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
@@ -12282,11 +12303,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>414.4700012207031</v>
+        <v>422.2300109863281</v>
       </c>
       <c r="C51" t="n">
         <v>1</v>
@@ -12303,11 +12324,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>422.2300109863281</v>
+        <v>421.6300048828125</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
@@ -12324,11 +12345,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>421.6300048828125</v>
+        <v>425.9400024414062</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -12345,11 +12366,11 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>425.9400024414062</v>
+        <v>423.3299865722656</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -12366,11 +12387,11 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>423.3299865722656</v>
+        <v>421.2900085449219</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -12387,11 +12408,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>421.2900085449219</v>
+        <v>437.2300109863281</v>
       </c>
       <c r="C56" t="n">
         <v>1</v>
@@ -12408,11 +12429,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>437.2300109863281</v>
+        <v>443.6000061035156</v>
       </c>
       <c r="C57" t="n">
         <v>1</v>
@@ -12429,11 +12450,11 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>443.6000061035156</v>
+        <v>451.7900085449219</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -12450,11 +12471,11 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>451.7900085449219</v>
+        <v>458</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -12471,11 +12492,11 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>458</v>
+        <v>464.7000122070312</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -12492,11 +12513,11 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>464.7000122070312</v>
+        <v>476.1000061035156</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -12513,11 +12534,11 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>476.1000061035156</v>
+        <v>494.5599975585938</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -12534,11 +12555,11 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>494.5599975585938</v>
+        <v>495.8999938964844</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -12555,11 +12576,11 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>495.8999938964844</v>
+        <v>444.9500122070312</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -12576,11 +12597,11 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>444.9500122070312</v>
+        <v>427.1300048828125</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -12597,11 +12618,11 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>427.1300048828125</v>
+        <v>454.2900085449219</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -12618,11 +12639,11 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>454.2900085449219</v>
+        <v>453.9700012207031</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -12639,11 +12660,11 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>453.9700012207031</v>
+        <v>441.8800048828125</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -12660,11 +12681,11 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>441.8800048828125</v>
+        <v>455.4599914550781</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -12681,11 +12702,11 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>455.4599914550781</v>
+        <v>467.0299987792969</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -12702,11 +12723,11 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>467.0299987792969</v>
+        <v>462.3999938964844</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -12723,11 +12744,11 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>462.3999938964844</v>
+        <v>467.6300048828125</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
@@ -12744,11 +12765,11 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>467.6300048828125</v>
+        <v>451.3900146484375</v>
       </c>
       <c r="C73" t="n">
         <v>1</v>
@@ -12765,11 +12786,11 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>451.3900146484375</v>
+        <v>462.6199951171875</v>
       </c>
       <c r="C74" t="n">
         <v>1</v>
@@ -12786,11 +12807,11 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>462.6199951171875</v>
+        <v>448.2000122070312</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -12807,11 +12828,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>448.2000122070312</v>
+        <v>458.2799987792969</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
@@ -12828,11 +12849,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>458.2799987792969</v>
+        <v>459.5599975585938</v>
       </c>
       <c r="C77" t="n">
         <v>1</v>
@@ -12849,11 +12870,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>459.5599975585938</v>
+        <v>468.6199951171875</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
@@ -12870,11 +12891,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>468.6199951171875</v>
+        <v>481.2799987792969</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
@@ -12891,11 +12912,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>481.2799987792969</v>
+        <v>474.6099853515625</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -12912,11 +12933,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>474.6099853515625</v>
+        <v>473.4200134277344</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -12933,11 +12954,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>473.4200134277344</v>
+        <v>477.4800109863281</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -12954,11 +12975,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>477.4800109863281</v>
+        <v>483.75</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -12975,11 +12996,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>483.75</v>
+        <v>490</v>
       </c>
       <c r="C84" t="n">
         <v>1</v>
@@ -12996,11 +13017,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>490</v>
+        <v>468.1400146484375</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -13017,11 +13038,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>468.1400146484375</v>
+        <v>471.7999877929688</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -13038,11 +13059,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>471.7999877929688</v>
+        <v>466.1300048828125</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
@@ -13059,11 +13080,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>466.1300048828125</v>
+        <v>473.510009765625</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -13080,11 +13101,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>473.510009765625</v>
+        <v>472.5299987792969</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
@@ -13101,11 +13122,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>472.5299987792969</v>
+        <v>477.8599853515625</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -13122,11 +13143,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>477.8599853515625</v>
+        <v>476.239990234375</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -13143,11 +13164,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>476.239990234375</v>
+        <v>466.8800048828125</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -13164,11 +13185,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>466.8800048828125</v>
+        <v>460.8399963378906</v>
       </c>
       <c r="C93" t="n">
         <v>1</v>
@@ -13185,11 +13206,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>460.8399963378906</v>
+        <v>460.4299926757812</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -13206,11 +13227,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>460.4299926757812</v>
+        <v>459.2699890136719</v>
       </c>
       <c r="C95" t="n">
         <v>1</v>
@@ -13227,11 +13248,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>459.2699890136719</v>
+        <v>444.739990234375</v>
       </c>
       <c r="C96" t="n">
         <v>1</v>
@@ -13248,11 +13269,11 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>444.739990234375</v>
+        <v>426.4100036621094</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -13269,11 +13290,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>426.4100036621094</v>
+        <v>413.3800048828125</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
@@ -13290,11 +13311,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>413.3800048828125</v>
+        <v>404.0400085449219</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
@@ -13311,11 +13332,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>404.0400085449219</v>
+        <v>404.1300048828125</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -13332,11 +13353,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>404.1300048828125</v>
+        <v>416.2900085449219</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -13353,11 +13374,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>416.2900085449219</v>
+        <v>400.6400146484375</v>
       </c>
       <c r="C102" t="n">
         <v>1</v>
@@ -13374,11 +13395,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>400.6400146484375</v>
+        <v>414.7000122070312</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -13395,11 +13416,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>414.7000122070312</v>
+        <v>414.5799865722656</v>
       </c>
       <c r="C104" t="n">
         <v>1</v>
@@ -13416,11 +13437,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>414.5799865722656</v>
+        <v>430.2900085449219</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
@@ -13437,11 +13458,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>430.2900085449219</v>
+        <v>437.8200073242188</v>
       </c>
       <c r="C106" t="n">
         <v>1</v>
@@ -13458,11 +13479,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>437.8200073242188</v>
+        <v>429.4100036621094</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -13479,11 +13500,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>429.4100036621094</v>
+        <v>427.6499938964844</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
@@ -13500,11 +13521,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>427.6499938964844</v>
+        <v>431.8099975585938</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
@@ -13521,11 +13542,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>431.8099975585938</v>
+        <v>434.5299987792969</v>
       </c>
       <c r="C110" t="n">
         <v>1</v>
@@ -13542,11 +13563,11 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>434.5299987792969</v>
+        <v>437.9100036621094</v>
       </c>
       <c r="C111" t="n">
         <v>1</v>
@@ -13563,11 +13584,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>437.9100036621094</v>
+        <v>437.1300048828125</v>
       </c>
       <c r="C112" t="n">
         <v>1</v>
@@ -13584,11 +13605,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>437.1300048828125</v>
+        <v>435.3599853515625</v>
       </c>
       <c r="C113" t="n">
         <v>1</v>
@@ -13605,11 +13626,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>435.3599853515625</v>
+        <v>445.0899963378906</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -13626,11 +13647,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>445.0899963378906</v>
+        <v>440.4599914550781</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -13647,11 +13668,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>440.4599914550781</v>
+        <v>440.0799865722656</v>
       </c>
       <c r="C116" t="n">
         <v>1</v>
@@ -13668,11 +13689,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>440.0799865722656</v>
+        <v>445.9299926757812</v>
       </c>
       <c r="C117" t="n">
         <v>1</v>
@@ -13689,11 +13710,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>445.9299926757812</v>
+        <v>442.0899963378906</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
@@ -13710,11 +13731,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>442.0899963378906</v>
+        <v>429.5700073242188</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -13731,11 +13752,11 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>429.5700073242188</v>
+        <v>435.260009765625</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -13752,11 +13773,11 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>435.260009765625</v>
+        <v>431.0400085449219</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
@@ -13773,11 +13794,11 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>431.0400085449219</v>
+        <v>433.25</v>
       </c>
       <c r="C122" t="n">
         <v>1</v>
@@ -13794,11 +13815,11 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>433.25</v>
+        <v>429.8900146484375</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -13815,11 +13836,11 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>429.8900146484375</v>
+        <v>421.9100036621094</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -13836,11 +13857,11 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>421.9100036621094</v>
+        <v>417.4100036621094</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -13857,11 +13878,11 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>417.4100036621094</v>
+        <v>423.6600036621094</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -13878,11 +13899,11 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>423.6600036621094</v>
+        <v>423.1799926757812</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -13899,11 +13920,11 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>423.1799926757812</v>
+        <v>414.7099914550781</v>
       </c>
       <c r="C128" t="n">
         <v>1</v>
@@ -13920,11 +13941,11 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>414.7099914550781</v>
+        <v>418.2699890136719</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -13941,11 +13962,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>418.2699890136719</v>
+        <v>430.9599914550781</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -13962,11 +13983,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>430.9599914550781</v>
+        <v>431.6799926757812</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -13983,11 +14004,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>431.6799926757812</v>
+        <v>433.7699890136719</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
@@ -14004,11 +14025,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>433.7699890136719</v>
+        <v>434.6499938964844</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -14025,11 +14046,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>434.6499938964844</v>
+        <v>432.9299926757812</v>
       </c>
       <c r="C134" t="n">
         <v>1</v>
@@ -14046,11 +14067,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>432.9299926757812</v>
+        <v>430.5</v>
       </c>
       <c r="C135" t="n">
         <v>1</v>
@@ -14067,11 +14088,11 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>430.5</v>
+        <v>427.2099914550781</v>
       </c>
       <c r="C136" t="n">
         <v>1</v>
@@ -14088,11 +14109,11 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>427.2099914550781</v>
+        <v>417.2900085449219</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
@@ -14109,11 +14130,11 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>417.2900085449219</v>
+        <v>418.4299926757812</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
@@ -14130,11 +14151,11 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>418.4299926757812</v>
+        <v>411.5</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
@@ -14151,11 +14172,11 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>411.5</v>
+        <v>417.3999938964844</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -14172,11 +14193,11 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>417.3999938964844</v>
+        <v>416.989990234375</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
@@ -14193,11 +14214,11 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>416.989990234375</v>
+        <v>413.8200073242188</v>
       </c>
       <c r="C142" t="n">
         <v>1</v>
@@ -14214,11 +14235,11 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>413.8200073242188</v>
+        <v>414</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -14235,11 +14256,11 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>414</v>
+        <v>408.489990234375</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
@@ -14256,11 +14277,11 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>408.489990234375</v>
+        <v>412.7699890136719</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
@@ -14277,11 +14298,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>412.7699890136719</v>
+        <v>417.1199951171875</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
@@ -14298,11 +14319,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>417.1199951171875</v>
+        <v>411.260009765625</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
@@ -14319,11 +14340,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>411.260009765625</v>
+        <v>411.9500122070312</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
@@ -14340,11 +14361,11 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>411.9500122070312</v>
+        <v>407.8699951171875</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
@@ -14361,11 +14382,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>407.8699951171875</v>
+        <v>411.2699890136719</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
@@ -14382,11 +14403,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>411.2699890136719</v>
+        <v>396.239990234375</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -14403,11 +14424,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>396.239990234375</v>
+        <v>397.2699890136719</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -14424,11 +14445,11 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>397.2699890136719</v>
+        <v>390.7799987792969</v>
       </c>
       <c r="C153" t="n">
         <v>1</v>
@@ -14445,11 +14466,11 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>390.7799987792969</v>
+        <v>374.5799865722656</v>
       </c>
       <c r="C154" t="n">
         <v>1</v>
@@ -14466,11 +14487,11 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>374.5799865722656</v>
+        <v>386.3200073242188</v>
       </c>
       <c r="C155" t="n">
         <v>1</v>
@@ -14487,11 +14508,11 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>386.3200073242188</v>
+        <v>386.5400085449219</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
@@ -14508,11 +14529,11 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>386.5400085449219</v>
+        <v>396.5499877929688</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -14529,11 +14550,11 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>396.5499877929688</v>
+        <v>397.6300048828125</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -14550,11 +14571,11 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>397.6300048828125</v>
+        <v>388.6000061035156</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
@@ -14571,11 +14592,11 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>388.6000061035156</v>
+        <v>387.1199951171875</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
@@ -14592,11 +14613,11 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>387.1199951171875</v>
+        <v>384.5899963378906</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -14613,11 +14634,11 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>384.5899963378906</v>
+        <v>377.3200073242188</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -14634,11 +14655,11 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>377.3200073242188</v>
+        <v>365.9200134277344</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -14655,11 +14676,11 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>365.9200134277344</v>
+        <v>369.4599914550781</v>
       </c>
       <c r="C164" t="n">
         <v>1</v>
@@ -14676,11 +14697,11 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>369.4599914550781</v>
+        <v>373.6300048828125</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
@@ -14697,11 +14718,11 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>373.6300048828125</v>
+        <v>368.5799865722656</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
@@ -14718,11 +14739,11 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>368.5799865722656</v>
+        <v>368.3800048828125</v>
       </c>
       <c r="C167" t="n">
         <v>1</v>
@@ -14739,11 +14760,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>368.3800048828125</v>
+        <v>370.6000061035156</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
@@ -14760,11 +14781,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>370.6000061035156</v>
+        <v>378.1300048828125</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
@@ -14781,11 +14802,11 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>378.1300048828125</v>
+        <v>382.1300048828125</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
@@ -14802,11 +14823,11 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>382.1300048828125</v>
+        <v>377.489990234375</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -14823,11 +14844,11 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>377.489990234375</v>
+        <v>374.4500122070312</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
@@ -14844,11 +14865,11 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>374.4500122070312</v>
+        <v>378.1799926757812</v>
       </c>
       <c r="C173" t="n">
         <v>1</v>
@@ -14865,11 +14886,11 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>378.1799926757812</v>
+        <v>377.010009765625</v>
       </c>
       <c r="C174" t="n">
         <v>1</v>
@@ -14886,11 +14907,11 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>377.010009765625</v>
+        <v>367.1300048828125</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
@@ -14907,11 +14928,11 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>367.1300048828125</v>
+        <v>372.1499938964844</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
@@ -14928,11 +14949,11 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>372.1499938964844</v>
+        <v>372.3500061035156</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
@@ -14949,11 +14970,11 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>372.3500061035156</v>
+        <v>364.9599914550781</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
@@ -14970,11 +14991,11 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>364.9599914550781</v>
+        <v>368.4100036621094</v>
       </c>
       <c r="C179" t="n">
         <v>1</v>
@@ -14991,11 +15012,11 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>368.4100036621094</v>
+        <v>367.6000061035156</v>
       </c>
       <c r="C180" t="n">
         <v>1</v>
@@ -15012,11 +15033,11 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>367.6000061035156</v>
+        <v>374.8099975585938</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
@@ -15033,11 +15054,11 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>374.8099975585938</v>
+        <v>379.1199951171875</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -15054,11 +15075,11 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>379.1199951171875</v>
+        <v>371.5199890136719</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
@@ -15075,11 +15096,11 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>371.5199890136719</v>
+        <v>371.8999938964844</v>
       </c>
       <c r="C184" t="n">
         <v>1</v>
@@ -15096,11 +15117,11 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>371.8999938964844</v>
+        <v>374.6300048828125</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -15117,11 +15138,11 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>374.6300048828125</v>
+        <v>369.3699951171875</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
@@ -15138,11 +15159,11 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>369.3699951171875</v>
+        <v>371.0799865722656</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
@@ -15159,11 +15180,11 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>371.0799865722656</v>
+        <v>377.1600036621094</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -15180,11 +15201,11 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>377.1600036621094</v>
+        <v>371.5400085449219</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
@@ -15201,11 +15222,11 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>371.5400085449219</v>
+        <v>371.7099914550781</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -15222,11 +15243,11 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>371.7099914550781</v>
+        <v>374.1600036621094</v>
       </c>
       <c r="C191" t="n">
         <v>1</v>
@@ -15243,11 +15264,11 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>374.1600036621094</v>
+        <v>389.6400146484375</v>
       </c>
       <c r="C192" t="n">
         <v>1</v>
@@ -15264,11 +15285,11 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>389.6400146484375</v>
+        <v>389.6700134277344</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
@@ -15285,11 +15306,11 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>389.6700134277344</v>
+        <v>398.4700012207031</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -15306,11 +15327,11 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>398.4700012207031</v>
+        <v>402.5400085449219</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
@@ -15327,11 +15348,11 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>402.5400085449219</v>
+        <v>400.9599914550781</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
@@ -15348,11 +15369,11 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>400.9599914550781</v>
+        <v>404.9200134277344</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -15369,11 +15390,11 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>404.9200134277344</v>
+        <v>398.9599914550781</v>
       </c>
       <c r="C198" t="n">
         <v>1</v>
@@ -15390,11 +15411,11 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>398.9599914550781</v>
+        <v>401.4800109863281</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
@@ -15411,11 +15432,11 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>401.4800109863281</v>
+        <v>405.489990234375</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
@@ -15432,11 +15453,11 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>405.489990234375</v>
+        <v>398.5499877929688</v>
       </c>
       <c r="C201" t="n">
         <v>1</v>
@@ -15453,11 +15474,11 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>398.5499877929688</v>
+        <v>413.8399963378906</v>
       </c>
       <c r="C202" t="n">
         <v>1</v>
@@ -15474,11 +15495,11 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>413.8399963378906</v>
+        <v>415.260009765625</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
@@ -15495,11 +15516,11 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>415.260009765625</v>
+        <v>423.3599853515625</v>
       </c>
       <c r="C204" t="n">
         <v>1</v>
@@ -15516,11 +15537,11 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>423.3599853515625</v>
+        <v>426.6900024414062</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
@@ -15537,11 +15558,11 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>426.6900024414062</v>
+        <v>428.0700073242188</v>
       </c>
       <c r="C206" t="n">
         <v>1</v>
@@ -15558,11 +15579,11 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>428.0700073242188</v>
+        <v>421.3200073242188</v>
       </c>
       <c r="C207" t="n">
         <v>1</v>
@@ -15579,11 +15600,11 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>421.3200073242188</v>
+        <v>422.6000061035156</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
@@ -15600,11 +15621,11 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>422.6000061035156</v>
+        <v>408.8900146484375</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
@@ -15621,11 +15642,11 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>408.8900146484375</v>
+        <v>408.4200134277344</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
@@ -15642,11 +15663,11 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>408.4200134277344</v>
+        <v>396.75</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
@@ -15663,11 +15684,11 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>396.75</v>
+        <v>402.7799987792969</v>
       </c>
       <c r="C212" t="n">
         <v>1</v>
@@ -15684,11 +15705,11 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>402.7799987792969</v>
+        <v>410.2200012207031</v>
       </c>
       <c r="C213" t="n">
         <v>1</v>
@@ -15705,11 +15726,11 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>410.2200012207031</v>
+        <v>406.7699890136719</v>
       </c>
       <c r="C214" t="n">
         <v>1</v>
@@ -15726,11 +15747,11 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>406.7699890136719</v>
+        <v>399.7200012207031</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
@@ -15747,11 +15768,11 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>399.7200012207031</v>
+        <v>403.3500061035156</v>
       </c>
       <c r="C216" t="n">
         <v>1</v>
@@ -15768,11 +15789,11 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>403.3500061035156</v>
+        <v>396.3599853515625</v>
       </c>
       <c r="C217" t="n">
         <v>1</v>
@@ -15789,11 +15810,11 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>396.3599853515625</v>
+        <v>398.7699890136719</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
@@ -15810,11 +15831,11 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>398.7699890136719</v>
+        <v>392.8399963378906</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
@@ -15831,11 +15852,11 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>392.8399963378906</v>
+        <v>394.1499938964844</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
@@ -15852,11 +15873,11 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>394.1499938964844</v>
+        <v>391.739990234375</v>
       </c>
       <c r="C221" t="n">
         <v>1</v>
@@ -15873,11 +15894,11 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>391.739990234375</v>
+        <v>398.3599853515625</v>
       </c>
       <c r="C222" t="n">
         <v>1</v>
@@ -15894,11 +15915,11 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>398.3599853515625</v>
+        <v>401.1700134277344</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
@@ -15915,11 +15936,11 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>401.1700134277344</v>
+        <v>398.3800048828125</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
@@ -15936,11 +15957,11 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>398.3800048828125</v>
+        <v>400.0700073242188</v>
       </c>
       <c r="C225" t="n">
         <v>1</v>
@@ -15957,11 +15978,11 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>400.0700073242188</v>
+        <v>392.8800048828125</v>
       </c>
       <c r="C226" t="n">
         <v>1</v>
@@ -15978,11 +15999,11 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>392.8800048828125</v>
+        <v>391.6900024414062</v>
       </c>
       <c r="C227" t="n">
         <v>1</v>
@@ -15999,11 +16020,11 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>391.6900024414062</v>
+        <v>393.4100036621094</v>
       </c>
       <c r="C228" t="n">
         <v>1</v>
@@ -16020,11 +16041,11 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>393.4100036621094</v>
+        <v>377.9100036621094</v>
       </c>
       <c r="C229" t="n">
         <v>1</v>
@@ -16041,11 +16062,11 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>377.9100036621094</v>
+        <v>382.8900146484375</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
@@ -16062,11 +16083,11 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>382.8900146484375</v>
+        <v>380.8399963378906</v>
       </c>
       <c r="C231" t="n">
         <v>1</v>
@@ -16083,11 +16104,11 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>380.8399963378906</v>
+        <v>382.760009765625</v>
       </c>
       <c r="C232" t="n">
         <v>1</v>
@@ -16104,11 +16125,11 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>382.760009765625</v>
+        <v>380.1400146484375</v>
       </c>
       <c r="C233" t="n">
         <v>1</v>
@@ -16125,11 +16146,11 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>380.1400146484375</v>
+        <v>379.5499877929688</v>
       </c>
       <c r="C234" t="n">
         <v>1</v>
@@ -16146,11 +16167,11 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>379.5499877929688</v>
+        <v>382.2699890136719</v>
       </c>
       <c r="C235" t="n">
         <v>1</v>
@@ -16167,11 +16188,11 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>382.2699890136719</v>
+        <v>375.8800048828125</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
@@ -16188,11 +16209,11 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>375.8800048828125</v>
+        <v>378.6199951171875</v>
       </c>
       <c r="C237" t="n">
         <v>1</v>
@@ -16209,11 +16230,11 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>378.6199951171875</v>
+        <v>384.5799865722656</v>
       </c>
       <c r="C238" t="n">
         <v>1</v>
@@ -16230,11 +16251,11 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>384.5799865722656</v>
+        <v>382.1499938964844</v>
       </c>
       <c r="C239" t="n">
         <v>1</v>
@@ -16251,11 +16272,11 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>382.1499938964844</v>
+        <v>381.6700134277344</v>
       </c>
       <c r="C240" t="n">
         <v>1</v>
@@ -16272,11 +16293,11 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>381.6700134277344</v>
+        <v>375.989990234375</v>
       </c>
       <c r="C241" t="n">
         <v>1</v>
@@ -16293,11 +16314,11 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>375.989990234375</v>
+        <v>382.7099914550781</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
@@ -16314,11 +16335,11 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>382.7099914550781</v>
+        <v>382.010009765625</v>
       </c>
       <c r="C243" t="n">
         <v>1</v>
@@ -16335,11 +16356,11 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>382.010009765625</v>
+        <v>379.6900024414062</v>
       </c>
       <c r="C244" t="n">
         <v>1</v>
@@ -16356,11 +16377,11 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>379.6900024414062</v>
+        <v>377.6499938964844</v>
       </c>
       <c r="C245" t="n">
         <v>1</v>
@@ -16377,11 +16398,11 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>377.6499938964844</v>
+        <v>378.9500122070312</v>
       </c>
       <c r="C246" t="n">
         <v>1</v>
@@ -16398,11 +16419,11 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>378.9500122070312</v>
+        <v>369</v>
       </c>
       <c r="C247" t="n">
         <v>1</v>
@@ -16419,11 +16440,11 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>369</v>
+        <v>366.6099853515625</v>
       </c>
       <c r="C248" t="n">
         <v>1</v>
@@ -16440,11 +16461,11 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>366.6099853515625</v>
+        <v>367.8200073242188</v>
       </c>
       <c r="C249" t="n">
         <v>1</v>
@@ -16461,11 +16482,11 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>367.8200073242188</v>
+        <v>372.2799987792969</v>
       </c>
       <c r="C250" t="n">
         <v>1</v>
@@ -16482,11 +16503,11 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>372.2799987792969</v>
+        <v>373.510009765625</v>
       </c>
       <c r="C251" t="n">
         <v>1</v>
@@ -16503,11 +16524,11 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>373.510009765625</v>
+        <v>368.5700073242188</v>
       </c>
       <c r="C252" t="n">
         <v>1</v>
